--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Increase Announcement Calendar - 03/06/2026</t>
+          <t>Estimated Dividend Increase Announcement Calendar - 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>46096</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46300</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02091029465724359</v>
+        <v>0.02123442826954228</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         <v>46096</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46196</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.05013927363491755</v>
+        <v>0.05043193807276123</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>46122</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46132</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02760692241919218</v>
+        <v>0.02742783112167496</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +804,7 @@
         <v>46127</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46503</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.01863128817928794</v>
+        <v>0.01920125840726826</v>
       </c>
     </row>
     <row r="10">
@@ -850,7 +850,7 @@
         <v>46128</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46165</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02179425374964139</v>
+        <v>0.02153164487221803</v>
       </c>
     </row>
     <row r="11">
@@ -896,7 +896,7 @@
         <v>46134</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46161</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03100775159142471</v>
+        <v>0.03071620865694696</v>
       </c>
     </row>
     <row r="12">
@@ -942,7 +942,7 @@
         <v>46141</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46191</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05029091984291129</v>
+        <v>0.04996858131518413</v>
       </c>
     </row>
     <row r="13">
@@ -988,7 +988,7 @@
         <v>46143</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46152</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04367386099191616</v>
+        <v>0.04428952183157404</v>
       </c>
     </row>
     <row r="14">
@@ -1034,7 +1034,7 @@
         <v>46162</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46198</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03125000094443982</v>
+        <v>0.03135003990293934</v>
       </c>
     </row>
     <row r="15">
@@ -1080,7 +1080,7 @@
         <v>46176</v>
       </c>
       <c r="I15" s="20" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J15" s="19" t="n">
         <v>46197</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03963385818268213</v>
+        <v>0.03995053847357968</v>
       </c>
     </row>
     <row r="16">
@@ -1126,7 +1126,7 @@
         <v>46218</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46248</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01803942519245617</v>
+        <v>0.01847529122044088</v>
       </c>
     </row>
     <row r="17">
@@ -1172,7 +1172,7 @@
         <v>46220</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46264</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02161061800994751</v>
+        <v>0.02209016195988108</v>
       </c>
     </row>
     <row r="18">
@@ -1218,7 +1218,7 @@
         <v>46227</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46267</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04412839732925053</v>
+        <v>0.04586268860329277</v>
       </c>
     </row>
     <row r="19">
@@ -1264,7 +1264,7 @@
         <v>46232</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46246</v>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.0434896963373957</v>
+        <v>0.04514220705346985</v>
       </c>
     </row>
     <row r="20">
@@ -1310,7 +1310,7 @@
         <v>46232</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46264</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02961427247426216</v>
+        <v>0.02994460207493484</v>
       </c>
     </row>
     <row r="21">
@@ -1356,7 +1356,7 @@
         <v>46263</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46297</v>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02880983789161461</v>
+        <v>0.02911414781981898</v>
       </c>
     </row>
     <row r="22">
@@ -1402,7 +1402,7 @@
         <v>46267</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46303</v>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05433605865719647</v>
+        <v>0.05419734985467445</v>
       </c>
     </row>
     <row r="23">
@@ -1448,7 +1448,7 @@
         <v>46278</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46344</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008881514816818951</v>
+        <v>0.008929447230883993</v>
       </c>
     </row>
     <row r="24">
@@ -1494,7 +1494,7 @@
         <v>46285</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46325</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02941633490976144</v>
+        <v>0.02961572656987358</v>
       </c>
     </row>
     <row r="25">
@@ -1540,7 +1540,7 @@
         <v>46305</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46339</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.0384657892455476</v>
+        <v>0.03938879524734049</v>
       </c>
     </row>
     <row r="26">
@@ -1586,7 +1586,7 @@
         <v>46311</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46386</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01197083029429245</v>
+        <v>0.01218125357404984</v>
       </c>
     </row>
     <row r="27">
@@ -1632,7 +1632,7 @@
         <v>46317</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46351</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01280653322421403</v>
+        <v>0.01305087977945609</v>
       </c>
     </row>
     <row r="28">
@@ -1678,7 +1678,7 @@
         <v>46322</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46338</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02432535207111895</v>
+        <v>0.0247438625812264</v>
       </c>
     </row>
     <row r="29">
@@ -1724,7 +1724,7 @@
         <v>46329</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46338</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.00670822057103366</v>
+        <v>0.006716574317527649</v>
       </c>
     </row>
     <row r="30">
@@ -1770,7 +1770,7 @@
         <v>46332</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46346</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02614869390488948</v>
+        <v>0.02662955919332545</v>
       </c>
     </row>
     <row r="31">
@@ -1816,7 +1816,7 @@
         <v>46341</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46339</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02711775290341838</v>
+        <v>0.02687365511453597</v>
       </c>
     </row>
     <row r="32">
@@ -1862,7 +1862,7 @@
         <v>46344</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46385</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02969378118246405</v>
+        <v>0.02996960741873846</v>
       </c>
     </row>
     <row r="33">
@@ -1908,7 +1908,7 @@
         <v>46347</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46358</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02873412138550337</v>
+        <v>0.0293796246055187</v>
       </c>
     </row>
     <row r="34">
@@ -1954,7 +1954,7 @@
         <v>46352</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46400</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04825030695041271</v>
+        <v>0.04913016233452121</v>
       </c>
     </row>
     <row r="35">
@@ -2000,7 +2000,7 @@
         <v>46360</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46371</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04750459268387158</v>
+        <v>0.04944084822343214</v>
       </c>
     </row>
     <row r="36">
@@ -2046,7 +2046,7 @@
         <v>46366</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46432</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.0273942735353147</v>
+        <v>0.02715992761331142</v>
       </c>
     </row>
     <row r="37">
@@ -2092,7 +2092,7 @@
         <v>46370</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46413</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06450402928726036</v>
+        <v>0.0649056603773585</v>
       </c>
     </row>
     <row r="38">
@@ -2138,7 +2138,7 @@
         <v>46371</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46344</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02107191945064864</v>
+        <v>0.02131603343958685</v>
       </c>
     </row>
     <row r="39">
@@ -2184,7 +2184,7 @@
         <v>46411</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46435</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03827412485747456</v>
+        <v>0.03888005694645721</v>
       </c>
     </row>
     <row r="40">
@@ -2230,7 +2230,7 @@
         <v>46416</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46483</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01596288658098838</v>
+        <v>0.01616161616161616</v>
       </c>
     </row>
     <row r="41">
@@ -2276,7 +2276,7 @@
         <v>46417</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46433</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03753690570923929</v>
+        <v>0.03728334269512545</v>
       </c>
     </row>
     <row r="42">
@@ -2322,7 +2322,7 @@
         <v>46419</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46472</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03025906855367032</v>
+        <v>0.02953970594222538</v>
       </c>
     </row>
     <row r="43">
@@ -2368,7 +2368,7 @@
         <v>46423</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46435</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06470066120416362</v>
+        <v>0.06718558010043858</v>
       </c>
     </row>
     <row r="44">
@@ -2414,7 +2414,7 @@
         <v>46428</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46452</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01441483983229846</v>
+        <v>0.01437492589275465</v>
       </c>
     </row>
     <row r="45">
@@ -2460,7 +2460,7 @@
         <v>46430</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46460</v>
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05657330701696998</v>
+        <v>0.05776665748201185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2487,29 +2487,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.1132075471698112</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46442</v>
+        <v>46481</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2517,45 +2517,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.09570154154918477</v>
+        <v>0.02167305457492465</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.41</v>
+        <v>1.883</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.4</v>
+        <v>1.864</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46481</v>
+        <v>46425</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2563,45 +2563,45 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.02076212234906543</v>
+        <v>0.002867978565556691</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.864</v>
+        <v>1.15</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>4.043478260869565</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.002844991090000402</v>
+        <v>0.0157497678726076</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.15</v>
+        <v>0.22</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>4.043478260869565</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0.06</v>
@@ -2644,10 +2644,10 @@
         <v>46433</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46383</v>
+        <v>46276</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.01577112918840002</v>
+        <v>0.0209422706286886</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.24</v>
+        <v>1.423</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.22</v>
+        <v>1.355</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0.06</v>
@@ -2690,10 +2690,10 @@
         <v>46433</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46276</v>
+        <v>46177</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.02145011679340417</v>
+        <v>0.035575</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2717,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.423</v>
+        <v>0.79</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1.355</v>
+        <v>0.78</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.01282051282051283</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H51" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46177</v>
+        <v>46270</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03607783384584436</v>
+        <v>0.03556355726313094</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2763,29 +2763,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.79</v>
+        <v>0.555</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.78</v>
+        <v>0.588964</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.01282051282051283</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H52" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.0346111708036702</v>
+        <v>0.03373347640718918</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2809,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.555</v>
+        <v>0.27</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.25</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46243</v>
+        <v>46449</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.03333834092339166</v>
+        <v>0.0095566762196685</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2859,25 +2859,25 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.02222222222222214</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>46440</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46449</v>
+        <v>46455</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.009166525231687333</v>
+        <v>0.02635385774024195</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.02222222222222214</v>
+        <v>0.05633802816901413</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46440</v>
+        <v>46451</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46455</v>
+        <v>46487</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2931,53 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.02575155278654199</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>0.05633802816901413</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>46451</v>
-      </c>
-      <c r="I56" s="13" t="n">
-        <v>364</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="n">
-        <v>0.01658031088082901</v>
+        <v>0.01678087038133019</v>
       </c>
     </row>
   </sheetData>
@@ -2991,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3012,7 +2966,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 03/06/2026</t>
+          <t>Expected Increase Announcements by Month - 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4447,20 +4401,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46442</v>
+        <v>46481</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.1132075471698112</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4471,20 +4425,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46481</v>
+        <v>46425</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.41</v>
+        <v>1.883</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4495,20 +4449,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>4.043478260869565</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4519,20 +4473,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46383</v>
+        <v>46276</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>4.043478260869565</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4543,20 +4497,20 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B83" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C83" s="10" t="n">
-        <v>46276</v>
+        <v>46177</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>0.24</v>
+        <v>1.423</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
@@ -4567,20 +4521,20 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B84" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C84" s="10" t="n">
-        <v>46177</v>
+        <v>46270</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>1.423</v>
+        <v>0.79</v>
       </c>
       <c r="E84" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.01282051282051283</v>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
@@ -4591,20 +4545,20 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B85" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C85" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.79</v>
+        <v>0.555</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0.01282051282051283</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
@@ -4615,20 +4569,20 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B86" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C86" s="10" t="n">
-        <v>46243</v>
+        <v>46449</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>0.555</v>
+        <v>0.27</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
@@ -4639,20 +4593,20 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B87" s="10" t="n">
         <v>46440</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46449</v>
+        <v>46455</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.02222222222222214</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -4660,88 +4614,64 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>46455</v>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0.02222222222222214</v>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="89">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A90" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B90" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C90" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="B92" s="10" t="n">
+      <c r="B91" s="10" t="n">
         <v>46451</v>
       </c>
-      <c r="C92" s="10" t="n">
+      <c r="C91" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="D92" s="7" t="n">
+      <c r="D91" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E92" s="8" t="n">
+      <c r="E91" s="8" t="n">
         <v>0.05633802816901413</v>
       </c>
-      <c r="F92" s="12" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4758,7 +4688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4786,7 +4716,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 03/06/2026</t>
+          <t>Complete Holdings Dividend Summary - 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009166525231687333</v>
+        <v>0.0095566762196685</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4943,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.0273942735353147</v>
+        <v>0.02715992761331142</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4996,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002844991090000402</v>
+        <v>0.002867978565556691</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5049,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03827412485747456</v>
+        <v>0.03888005694645721</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5102,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02961427247426216</v>
+        <v>0.02994460207493484</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5155,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.0434896963373957</v>
+        <v>0.04514220705346985</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5208,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01577112918840002</v>
+        <v>0.0157497678726076</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5261,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02107191945064864</v>
+        <v>0.02131603343958685</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5314,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.00670822057103366</v>
+        <v>0.006716574317527649</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5367,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02076212234906543</v>
+        <v>0.02167305457492465</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5420,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03753690570923929</v>
+        <v>0.03728334269512545</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5473,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01596288658098838</v>
+        <v>0.01616161616161616</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5526,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02145011679340417</v>
+        <v>0.0209422706286886</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5579,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04750459268387158</v>
+        <v>0.04944084822343214</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5632,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02432535207111895</v>
+        <v>0.0247438625812264</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5685,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01658031088082901</v>
+        <v>0.01678087038133019</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5738,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02575155278654199</v>
+        <v>0.02635385774024195</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5791,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01280653322421403</v>
+        <v>0.01305087977945609</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5844,7 +5774,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04825030695041271</v>
+        <v>0.04913016233452121</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5897,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02880983789161461</v>
+        <v>0.02911414781981898</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5950,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01441483983229846</v>
+        <v>0.01437492589275465</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -6003,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02179425374964139</v>
+        <v>0.02153164487221803</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6056,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02091029465724359</v>
+        <v>0.02123442826954228</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6109,7 +6039,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01863128817928794</v>
+        <v>0.01920125840726826</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6162,7 +6092,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01197083029429245</v>
+        <v>0.01218125357404984</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6215,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03125000094443982</v>
+        <v>0.03135003990293934</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6268,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02969378118246405</v>
+        <v>0.02996960741873846</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6321,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008881514816818951</v>
+        <v>0.008929447230883993</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6374,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.0384657892455476</v>
+        <v>0.03938879524734049</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6427,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02873412138550337</v>
+        <v>0.0293796246055187</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6480,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.03025906855367032</v>
+        <v>0.02953970594222538</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6533,7 +6463,7 @@
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05013927363491755</v>
+        <v>0.05043193807276123</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6586,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04367386099191616</v>
+        <v>0.04428952183157404</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6639,10 +6569,10 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03607783384584436</v>
+        <v>0.035575</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>45996</v>
+        <v>46087</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>0.05018450184501849</v>
@@ -6692,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06450402928726036</v>
+        <v>0.0649056603773585</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6745,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.0346111708036702</v>
+        <v>0.03556355726313094</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6798,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02760692241919218</v>
+        <v>0.02742783112167496</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6851,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03963385818268213</v>
+        <v>0.03995053847357968</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6904,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03100775159142471</v>
+        <v>0.03071620865694696</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6957,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01803942519245617</v>
+        <v>0.01847529122044088</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6980,7 +6910,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -7000,29 +6930,29 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.59</v>
+        <v>2.44</v>
       </c>
       <c r="G45" s="24" t="n">
-        <v>2.36</v>
+        <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.09570154154918477</v>
+        <v>0.02662955919332545</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.1132075471698112</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>46431</v>
+        <v>46332</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>46442</v>
+        <v>46346</v>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
@@ -7033,7 +6963,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -7048,34 +6978,34 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>2.44</v>
+        <v>0.83</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>9.76</v>
+        <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02614869390488948</v>
+        <v>0.04586268860329277</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>46077</v>
+        <v>45992</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>46332</v>
+        <v>46227</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>46346</v>
+        <v>46267</v>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
@@ -7086,7 +7016,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -7101,34 +7031,34 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.83</v>
+        <v>1.27</v>
       </c>
       <c r="G47" s="24" t="n">
-        <v>3.32</v>
+        <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04412839732925053</v>
+        <v>0.05776665748201185</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.02419354838709679</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>46227</v>
+        <v>46430</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>46267</v>
+        <v>46460</v>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
@@ -7139,7 +7069,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -7159,29 +7089,29 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>1.27</v>
+        <v>0.994</v>
       </c>
       <c r="G48" s="24" t="n">
-        <v>5.08</v>
+        <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05657330701696998</v>
+        <v>0.04996858131518413</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>46006</v>
+        <v>45930</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.02419354838709679</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46430</v>
+        <v>46141</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46460</v>
+        <v>46191</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7192,7 +7122,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -7207,34 +7137,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Jan/May/Jul/Oct</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.994</v>
+        <v>1.42</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>3.976</v>
+        <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.05029091984291129</v>
+        <v>0.02961572656987358</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>46141</v>
+        <v>46285</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>46191</v>
+        <v>46325</v>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
@@ -7245,7 +7175,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -7260,34 +7190,34 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1.42</v>
+        <v>0.555</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>5.68</v>
+        <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.02941633490976144</v>
+        <v>0.03373347640718918</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>45961</v>
+        <v>46080</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46285</v>
+        <v>46433</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46325</v>
+        <v>46243</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7298,7 +7228,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -7313,7 +7243,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Feb/May/Aug/Dec</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -7322,25 +7252,25 @@
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.555</v>
+        <v>1.38</v>
       </c>
       <c r="G51" s="24" t="n">
-        <v>2.22</v>
+        <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03333834092339166</v>
+        <v>0.02209016195988108</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>46433</v>
+        <v>46220</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>46243</v>
+        <v>46264</v>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
@@ -7351,7 +7281,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -7366,34 +7296,34 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Dec</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>5.52</v>
+        <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02161061800994751</v>
+        <v>0.06718558010043858</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46080</v>
+        <v>46070</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>46220</v>
+        <v>46423</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>46264</v>
+        <v>46435</v>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
@@ -7404,7 +7334,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -7419,34 +7349,34 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G53" s="24" t="n">
-        <v>6.56</v>
+        <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06470066120416362</v>
+        <v>0.05419734985467445</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>46070</v>
+        <v>46034</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.01769911504424764</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46423</v>
+        <v>46267</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46435</v>
+        <v>46303</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7457,7 +7387,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -7472,89 +7402,36 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="G54" s="24" t="n">
-        <v>2.76</v>
+        <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.05433605865719647</v>
+        <v>0.02687365511453597</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>46034</v>
+        <v>46065</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>46267</v>
+        <v>46341</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="M54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Quality Dividend</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Feb/May/Aug/Nov</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G55" s="24" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>0.02711775290341838</v>
-      </c>
-      <c r="I55" s="10" t="n">
-        <v>46065</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="K55" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="L55" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="M55" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -7563,252 +7440,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D7E5A6-E20A-4DF3-BFF2-95F97C57AE72}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF21B2D4-F516-4342-87AE-293F72731B69}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59FB35DC-1CBC-48BE-AD11-52F29A542886}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02123442826954228</v>
+        <v>0.02121453103874677</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02742783112167496</v>
+        <v>0.02739228916625031</v>
       </c>
     </row>
     <row r="9">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.01920125840726826</v>
+        <v>0.01920881664280072</v>
       </c>
     </row>
     <row r="10">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02153164487221803</v>
+        <v>0.02149426448033362</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03071620865694696</v>
+        <v>0.03080281382732013</v>
       </c>
     </row>
     <row r="12">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.04996858131518413</v>
+        <v>0.05015136303254195</v>
       </c>
     </row>
     <row r="13">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04428952183157404</v>
+        <v>0.0442328363231826</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03135003990293934</v>
+        <v>0.03133274513596635</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03995053847357968</v>
+        <v>0.03983685846384099</v>
       </c>
     </row>
     <row r="16">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01847529122044088</v>
+        <v>0.01853235729177887</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02209016195988108</v>
+        <v>0.02219006320105184</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04586268860329277</v>
+        <v>0.04562006087790191</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04514220705346985</v>
+        <v>0.04474515172102556</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02994460207493484</v>
+        <v>0.02999737495505726</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02911414781981898</v>
+        <v>0.02907414731213221</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05419734985467445</v>
+        <v>0.05425594766958137</v>
       </c>
     </row>
     <row r="23">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008929447230883993</v>
+        <v>0.008920912704678053</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02961572656987358</v>
+        <v>0.0295018959954971</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03938879524734049</v>
+        <v>0.03919580848635087</v>
       </c>
     </row>
     <row r="26">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01218125357404984</v>
+        <v>0.01213238156980056</v>
       </c>
     </row>
     <row r="27">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01305087977945609</v>
+        <v>0.01302378267198593</v>
       </c>
     </row>
     <row r="28">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.0247438625812264</v>
+        <v>0.02470088783361854</v>
       </c>
     </row>
     <row r="29">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006716574317527649</v>
+        <v>0.006686354219858174</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02662955919332545</v>
+        <v>0.02660487893585036</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02687365511453597</v>
+        <v>0.02701816415230371</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02996960741873846</v>
+        <v>0.02983914777488941</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0293796246055187</v>
+        <v>0.02940649070358215</v>
       </c>
     </row>
     <row r="34">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04913016233452121</v>
+        <v>0.04899665536211755</v>
       </c>
     </row>
     <row r="35">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04944084822343214</v>
+        <v>0.04913358039101189</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02715992761331142</v>
+        <v>0.02705096172588151</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.0649056603773585</v>
+        <v>0.06457668425829059</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02131603343958685</v>
+        <v>0.02126110737520193</v>
       </c>
     </row>
     <row r="39">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03888005694645721</v>
+        <v>0.03877283613701961</v>
       </c>
     </row>
     <row r="40">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01616161616161616</v>
+        <v>0.01613309756254796</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03728334269512545</v>
+        <v>0.03738710307037856</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02953970594222538</v>
+        <v>0.02949487391735364</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06718558010043858</v>
+        <v>0.0673269375929841</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01437492589275465</v>
+        <v>0.0143575856591362</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05776665748201185</v>
+        <v>0.05770104437952199</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02167305457492465</v>
+        <v>0.02170747761421622</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002867978565556691</v>
+        <v>0.002859887618201491</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.0157497678726076</v>
+        <v>0.01572228216065075</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.0209422706286886</v>
+        <v>0.02106649125365334</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.035575</v>
+        <v>0.03544211437923245</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03556355726313094</v>
+        <v>0.03564981974006005</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03373347640718918</v>
+        <v>0.03367462870281667</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.0095566762196685</v>
+        <v>0.009558368177881913</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02635385774024195</v>
+        <v>0.02633197570613341</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01678087038133019</v>
+        <v>0.01674995154553761</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.0095566762196685</v>
+        <v>0.009558368177881913</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02715992761331142</v>
+        <v>0.02705096172588151</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002867978565556691</v>
+        <v>0.002859887618201491</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4979,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03888005694645721</v>
+        <v>0.03877283613701961</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02994460207493484</v>
+        <v>0.02999737495505726</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04514220705346985</v>
+        <v>0.04474515172102556</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.0157497678726076</v>
+        <v>0.01572228216065075</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02131603343958685</v>
+        <v>0.02126110737520193</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006716574317527649</v>
+        <v>0.006686354219858174</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02167305457492465</v>
+        <v>0.02170747761421622</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03728334269512545</v>
+        <v>0.03738710307037856</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01616161616161616</v>
+        <v>0.01613309756254796</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.0209422706286886</v>
+        <v>0.02106649125365334</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04944084822343214</v>
+        <v>0.04913358039101189</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5562,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.0247438625812264</v>
+        <v>0.02470088783361854</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01678087038133019</v>
+        <v>0.01674995154553761</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02635385774024195</v>
+        <v>0.02633197570613341</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01305087977945609</v>
+        <v>0.01302378267198593</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5774,7 +5774,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04913016233452121</v>
+        <v>0.04899665536211755</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02911414781981898</v>
+        <v>0.02907414731213221</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01437492589275465</v>
+        <v>0.0143575856591362</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02153164487221803</v>
+        <v>0.02149426448033362</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02123442826954228</v>
+        <v>0.02121453103874677</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6039,7 +6039,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01920125840726826</v>
+        <v>0.01920881664280072</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6092,7 +6092,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01218125357404984</v>
+        <v>0.01213238156980056</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03135003990293934</v>
+        <v>0.03133274513596635</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02996960741873846</v>
+        <v>0.02983914777488941</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008929447230883993</v>
+        <v>0.008920912704678053</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03938879524734049</v>
+        <v>0.03919580848635087</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.0293796246055187</v>
+        <v>0.02940649070358215</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02953970594222538</v>
+        <v>0.02949487391735364</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04428952183157404</v>
+        <v>0.0442328363231826</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.035575</v>
+        <v>0.03544211437923245</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.0649056603773585</v>
+        <v>0.06457668425829059</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03556355726313094</v>
+        <v>0.03564981974006005</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02742783112167496</v>
+        <v>0.02739228916625031</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6781,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03995053847357968</v>
+        <v>0.03983685846384099</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03071620865694696</v>
+        <v>0.03080281382732013</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01847529122044088</v>
+        <v>0.01853235729177887</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02662955919332545</v>
+        <v>0.02660487893585036</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04586268860329277</v>
+        <v>0.04562006087790191</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05776665748201185</v>
+        <v>0.05770104437952199</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7099,7 +7099,7 @@
         <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.04996858131518413</v>
+        <v>0.05015136303254195</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>45930</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02961572656987358</v>
+        <v>0.0295018959954971</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03373347640718918</v>
+        <v>0.03367462870281667</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02209016195988108</v>
+        <v>0.02219006320105184</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06718558010043858</v>
+        <v>0.0673269375929841</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7364,7 +7364,7 @@
         <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05419734985467445</v>
+        <v>0.05425594766958137</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46034</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.02687365511453597</v>
+        <v>0.02701816415230371</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Increase Announcement Calendar - 03/09/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02121453103874677</v>
+        <v>0.02119504806369122</v>
       </c>
     </row>
     <row r="7">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.05043193807276123</v>
+        <v>0.05034965154355045</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02739228916625031</v>
+        <v>0.02727741935483871</v>
       </c>
     </row>
     <row r="9">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02149426448033362</v>
+        <v>0.02148050215080976</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03080281382732013</v>
+        <v>0.03074409163455258</v>
       </c>
     </row>
     <row r="12">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.0442328363231826</v>
+        <v>0.04409513061317685</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03133274513596635</v>
+        <v>0.031328942531305</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03983685846384099</v>
+        <v>0.03981797370433927</v>
       </c>
     </row>
     <row r="16">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01853235729177887</v>
+        <v>0.01847437419906703</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02219006320105184</v>
+        <v>0.02215132662276064</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04562006087790191</v>
+        <v>0.04558874204086234</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04474515172102556</v>
+        <v>0.04471892854040119</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02999737495505726</v>
+        <v>0.02995132840580906</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02907414731213221</v>
+        <v>0.02913742568083891</v>
       </c>
     </row>
     <row r="22">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008920912704678053</v>
+        <v>0.008907815804125249</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.0295018959954971</v>
+        <v>0.02945279029468497</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03919580848635087</v>
+        <v>0.0391429058858542</v>
       </c>
     </row>
     <row r="26">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01302378267198593</v>
+        <v>0.01302424312160127</v>
       </c>
     </row>
     <row r="28">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02470088783361854</v>
+        <v>0.02470803961895</v>
       </c>
     </row>
     <row r="29">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006686354219858174</v>
+        <v>0.00667389699330431</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02660487893585036</v>
+        <v>0.02659835377735491</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02701816415230371</v>
+        <v>0.0270358948520336</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02983914777488941</v>
+        <v>0.02981135061549272</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02940649070358215</v>
+        <v>0.02932498922437534</v>
       </c>
     </row>
     <row r="34">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04899665536211755</v>
+        <v>0.04895572154782055</v>
       </c>
     </row>
     <row r="35">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04913358039101189</v>
+        <v>0.04915155017554527</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02705096172588151</v>
+        <v>0.02704515637116994</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06457668425829059</v>
+        <v>0.06462521190274421</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02126110737520193</v>
+        <v>0.02126675995597667</v>
       </c>
     </row>
     <row r="39">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03877283613701961</v>
+        <v>0.03876481892072992</v>
       </c>
     </row>
     <row r="40">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01613309756254796</v>
+        <v>0.01611197819931539</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03738710307037856</v>
+        <v>0.03736944337173671</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02949487391735364</v>
+        <v>0.02950985209615581</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.0673269375929841</v>
+        <v>0.06707223536149663</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.0143575856591362</v>
+        <v>0.01433523238208774</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05770104437952199</v>
+        <v>0.05765520332323296</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02170747761421622</v>
+        <v>0.02169168609460287</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002859887618201491</v>
+        <v>0.002862332969886891</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01572228216065075</v>
+        <v>0.01571832726835254</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02106649125365334</v>
+        <v>0.02104340250935508</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03544211437923245</v>
+        <v>0.03542775488038615</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03564981974006005</v>
+        <v>0.03551758971162827</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03367462870281667</v>
+        <v>0.0336542124345548</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009558368177881913</v>
+        <v>0.009564293460084524</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02633197570613341</v>
+        <v>0.02634819613999891</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01674995154553761</v>
+        <v>0.01672380685044243</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009558368177881913</v>
+        <v>0.009564293460084524</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02705096172588151</v>
+        <v>0.02704515637116994</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002859887618201491</v>
+        <v>0.002862332969886891</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4979,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03877283613701961</v>
+        <v>0.03876481892072992</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02999737495505726</v>
+        <v>0.02995132840580906</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04474515172102556</v>
+        <v>0.04471892854040119</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01572228216065075</v>
+        <v>0.01571832726835254</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02126110737520193</v>
+        <v>0.02126675995597667</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006686354219858174</v>
+        <v>0.00667389699330431</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02170747761421622</v>
+        <v>0.02169168609460287</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03738710307037856</v>
+        <v>0.03736944337173671</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01613309756254796</v>
+        <v>0.01611197819931539</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02106649125365334</v>
+        <v>0.02104340250935508</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04913358039101189</v>
+        <v>0.04915155017554527</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5562,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02470088783361854</v>
+        <v>0.02470803961895</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01674995154553761</v>
+        <v>0.01672380685044243</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02633197570613341</v>
+        <v>0.02634819613999891</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01302378267198593</v>
+        <v>0.01302424312160127</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5774,7 +5774,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04899665536211755</v>
+        <v>0.04895572154782055</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02907414731213221</v>
+        <v>0.02913742568083891</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.0143575856591362</v>
+        <v>0.01433523238208774</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02149426448033362</v>
+        <v>0.02148050215080976</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02121453103874677</v>
+        <v>0.02119504806369122</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03133274513596635</v>
+        <v>0.031328942531305</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02983914777488941</v>
+        <v>0.02981135061549272</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008920912704678053</v>
+        <v>0.008907815804125249</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03919580848635087</v>
+        <v>0.0391429058858542</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02940649070358215</v>
+        <v>0.02932498922437534</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02949487391735364</v>
+        <v>0.02950985209615581</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6463,7 +6463,7 @@
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05043193807276123</v>
+        <v>0.05034965154355045</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.0442328363231826</v>
+        <v>0.04409513061317685</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03544211437923245</v>
+        <v>0.03542775488038615</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06457668425829059</v>
+        <v>0.06462521190274421</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03564981974006005</v>
+        <v>0.03551758971162827</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02739228916625031</v>
+        <v>0.02727741935483871</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6781,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03983685846384099</v>
+        <v>0.03981797370433927</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03080281382732013</v>
+        <v>0.03074409163455258</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01853235729177887</v>
+        <v>0.01847437419906703</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02660487893585036</v>
+        <v>0.02659835377735491</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04562006087790191</v>
+        <v>0.04558874204086234</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05770104437952199</v>
+        <v>0.05765520332323296</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.0295018959954971</v>
+        <v>0.02945279029468497</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03367462870281667</v>
+        <v>0.0336542124345548</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02219006320105184</v>
+        <v>0.02215132662276064</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.0673269375929841</v>
+        <v>0.06707223536149663</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.02701816415230371</v>
+        <v>0.0270358948520336</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02119504806369122</v>
+        <v>0.02122179456541239</v>
       </c>
     </row>
     <row r="7">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.05034965154355045</v>
+        <v>0.05036922120038344</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02727741935483871</v>
+        <v>0.02730384135195723</v>
       </c>
     </row>
     <row r="9">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.01920881664280072</v>
+        <v>0.01917108628806277</v>
       </c>
     </row>
     <row r="10">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02148050215080976</v>
+        <v>0.02147784059679884</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03074409163455258</v>
+        <v>0.03075525900494868</v>
       </c>
     </row>
     <row r="12">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05015136303254195</v>
+        <v>0.05019884992214078</v>
       </c>
     </row>
     <row r="13">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04409513061317685</v>
+        <v>0.04404567617608033</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.031328942531305</v>
+        <v>0.03130511421721505</v>
       </c>
     </row>
     <row r="15">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01847437419906703</v>
+        <v>0.01849941002255952</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02215132662276064</v>
+        <v>0.02213578260450285</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04558874204086234</v>
+        <v>0.04569855375457042</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04471892854040119</v>
+        <v>0.0446887115547832</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02995132840580906</v>
+        <v>0.02996703721930623</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02913742568083891</v>
+        <v>0.02918668873610638</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05425594766958137</v>
+        <v>0.05425061425061425</v>
       </c>
     </row>
     <row r="23">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008907815804125249</v>
+        <v>0.008915884722130965</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02945279029468497</v>
+        <v>0.02948964218888402</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.0391429058858542</v>
+        <v>0.03922010445554732</v>
       </c>
     </row>
     <row r="26">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01213238156980056</v>
+        <v>0.01213447726249195</v>
       </c>
     </row>
     <row r="27">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01302424312160127</v>
+        <v>0.01305365730304481</v>
       </c>
     </row>
     <row r="28">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.00667389699330431</v>
+        <v>0.006678818383022291</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02659835377735491</v>
+        <v>0.02657908685782614</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0270358948520336</v>
+        <v>0.02705274079904521</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02981135061549272</v>
+        <v>0.02979978256876964</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02932498922437534</v>
+        <v>0.02934156895668128</v>
       </c>
     </row>
     <row r="34">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04915155017554527</v>
+        <v>0.04921634927810189</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02704515637116994</v>
+        <v>0.02706112986729535</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06462521190274421</v>
+        <v>0.06451612940151463</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02126675995597667</v>
+        <v>0.02125202080256858</v>
       </c>
     </row>
     <row r="39">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01611197819931539</v>
+        <v>0.01611684689405836</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03736944337173671</v>
+        <v>0.03739692222714045</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02950985209615581</v>
+        <v>0.02951469931046555</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06707223536149663</v>
+        <v>0.06708252314739867</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01433523238208774</v>
+        <v>0.01433186490455213</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05765520332323296</v>
+        <v>0.05764539007092199</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02169168609460287</v>
+        <v>0.02171322688342915</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002862332969886891</v>
+        <v>0.002868437213485854</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01571832726835254</v>
+        <v>0.01571412869357315</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02104340250935508</v>
+        <v>0.02103878977707973</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03542775488038615</v>
+        <v>0.03545312919218709</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03551758971162827</v>
+        <v>0.03557757274102019</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.0336542124345548</v>
+        <v>0.03365676214089882</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009564293460084524</v>
+        <v>0.009565564073129746</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02634819613999891</v>
+        <v>0.02636178760835363</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01672380685044243</v>
+        <v>0.01675041818963462</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009564293460084524</v>
+        <v>0.009565564073129746</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02704515637116994</v>
+        <v>0.02706112986729535</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002862332969886891</v>
+        <v>0.002868437213485854</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02995132840580906</v>
+        <v>0.02996703721930623</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04471892854040119</v>
+        <v>0.0446887115547832</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01571832726835254</v>
+        <v>0.01571412869357315</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02126675995597667</v>
+        <v>0.02125202080256858</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.00667389699330431</v>
+        <v>0.006678818383022291</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02169168609460287</v>
+        <v>0.02171322688342915</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03736944337173671</v>
+        <v>0.03739692222714045</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01611197819931539</v>
+        <v>0.01611684689405836</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02104340250935508</v>
+        <v>0.02103878977707973</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04915155017554527</v>
+        <v>0.04921634927810189</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01672380685044243</v>
+        <v>0.01675041818963462</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02634819613999891</v>
+        <v>0.02636178760835363</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01302424312160127</v>
+        <v>0.01305365730304481</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02913742568083891</v>
+        <v>0.02918668873610638</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01433523238208774</v>
+        <v>0.01433186490455213</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02148050215080976</v>
+        <v>0.02147784059679884</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02119504806369122</v>
+        <v>0.02122179456541239</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6039,7 +6039,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01920881664280072</v>
+        <v>0.01917108628806277</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6092,7 +6092,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01213238156980056</v>
+        <v>0.01213447726249195</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.031328942531305</v>
+        <v>0.03130511421721505</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02981135061549272</v>
+        <v>0.02979978256876964</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008907815804125249</v>
+        <v>0.008915884722130965</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.0391429058858542</v>
+        <v>0.03922010445554732</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02932498922437534</v>
+        <v>0.02934156895668128</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02950985209615581</v>
+        <v>0.02951469931046555</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6463,7 +6463,7 @@
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05034965154355045</v>
+        <v>0.05036922120038344</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04409513061317685</v>
+        <v>0.04404567617608033</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03542775488038615</v>
+        <v>0.03545312919218709</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06462521190274421</v>
+        <v>0.06451612940151463</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03551758971162827</v>
+        <v>0.03557757274102019</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02727741935483871</v>
+        <v>0.02730384135195723</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03074409163455258</v>
+        <v>0.03075525900494868</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01847437419906703</v>
+        <v>0.01849941002255952</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02659835377735491</v>
+        <v>0.02657908685782614</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04558874204086234</v>
+        <v>0.04569855375457042</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05765520332323296</v>
+        <v>0.05764539007092199</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7099,7 +7099,7 @@
         <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05015136303254195</v>
+        <v>0.05019884992214078</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>45930</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02945279029468497</v>
+        <v>0.02948964218888402</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.0336542124345548</v>
+        <v>0.03365676214089882</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02215132662276064</v>
+        <v>0.02213578260450285</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06707223536149663</v>
+        <v>0.06708252314739867</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7364,7 +7364,7 @@
         <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05425594766958137</v>
+        <v>0.05425061425061425</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46034</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.0270358948520336</v>
+        <v>0.02705274079904521</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02122179456541239</v>
+        <v>0.02118606763468473</v>
       </c>
     </row>
     <row r="7">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.05036922120038344</v>
+        <v>0.0503574787754833</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02730384135195723</v>
+        <v>0.02730781041266806</v>
       </c>
     </row>
     <row r="9">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02147784059679884</v>
+        <v>0.02145745679037531</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03075525900494868</v>
+        <v>0.03072270827023568</v>
       </c>
     </row>
     <row r="12">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05019884992214078</v>
+        <v>0.05014503662619306</v>
       </c>
     </row>
     <row r="13">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04404567617608033</v>
+        <v>0.04409513061317685</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03130511421721505</v>
+        <v>0.03128442430258861</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03981797370433927</v>
+        <v>0.03978026072324462</v>
       </c>
     </row>
     <row r="16">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01849941002255952</v>
+        <v>0.01853281796928462</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02213578260450285</v>
+        <v>0.02211538407459298</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04569855375457042</v>
+        <v>0.04567340608739388</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.0446887115547832</v>
+        <v>0.04467261149718091</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02996703721930623</v>
+        <v>0.02996479013707762</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02918668873610638</v>
+        <v>0.02924393627768818</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05425061425061425</v>
+        <v>0.054234624348638</v>
       </c>
     </row>
     <row r="23">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008915884722130965</v>
+        <v>0.008916105327617881</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02948964218888402</v>
+        <v>0.02946516508850564</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03922010445554732</v>
+        <v>0.03926878686690426</v>
       </c>
     </row>
     <row r="26">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01305365730304481</v>
+        <v>0.01302562654183874</v>
       </c>
     </row>
     <row r="28">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02470803961895</v>
+        <v>0.02469254810363466</v>
       </c>
     </row>
     <row r="29">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006678818383022291</v>
+        <v>0.006666666666666666</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02657908685782614</v>
+        <v>0.02658386340520765</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02705274079904521</v>
+        <v>0.0270358948520336</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02979978256876964</v>
+        <v>0.02980440941591902</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02934156895668128</v>
+        <v>0.0293066480849006</v>
       </c>
     </row>
     <row r="34">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04921634927810189</v>
+        <v>0.04916593766536496</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02706112986729535</v>
+        <v>0.02704225352112676</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06451612940151463</v>
+        <v>0.06450402928726036</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02125202080256858</v>
+        <v>0.02122995314264688</v>
       </c>
     </row>
     <row r="39">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03876481892072992</v>
+        <v>0.03871145406976317</v>
       </c>
     </row>
     <row r="40">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01611684689405836</v>
+        <v>0.01611319509721077</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03739692222714045</v>
+        <v>0.03743526236660243</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02951469931046555</v>
+        <v>0.02951731132190974</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06708252314739867</v>
+        <v>0.06706537684676347</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01433186490455213</v>
+        <v>0.01434365993325098</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05764539007092199</v>
+        <v>0.05765520332323296</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02171322688342915</v>
+        <v>0.02170891574227562</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002868437213485854</v>
+        <v>0.002859225259362572</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01571412869357315</v>
+        <v>0.01569378272750932</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02103878977707973</v>
+        <v>0.02108963071937463</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03545312919218709</v>
+        <v>0.0354112218830431</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03557757274102019</v>
+        <v>0.03550162817841074</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03365676214089882</v>
+        <v>0.03363891063880556</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009565564073129746</v>
+        <v>0.009550338318464836</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02636178760835363</v>
+        <v>0.02634970689052226</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01675041818963462</v>
+        <v>0.01674247309135909</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009565564073129746</v>
+        <v>0.009550338318464836</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02706112986729535</v>
+        <v>0.02704225352112676</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002868437213485854</v>
+        <v>0.002859225259362572</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4979,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03876481892072992</v>
+        <v>0.03871145406976317</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02996703721930623</v>
+        <v>0.02996479013707762</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.0446887115547832</v>
+        <v>0.04467261149718091</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01571412869357315</v>
+        <v>0.01569378272750932</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02125202080256858</v>
+        <v>0.02122995314264688</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006678818383022291</v>
+        <v>0.006666666666666666</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02171322688342915</v>
+        <v>0.02170891574227562</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03739692222714045</v>
+        <v>0.03743526236660243</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01611684689405836</v>
+        <v>0.01611319509721077</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02103878977707973</v>
+        <v>0.02108963071937463</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04921634927810189</v>
+        <v>0.04916593766536496</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5562,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02470803961895</v>
+        <v>0.02469254810363466</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01675041818963462</v>
+        <v>0.01674247309135909</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02636178760835363</v>
+        <v>0.02634970689052226</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01305365730304481</v>
+        <v>0.01302562654183874</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02918668873610638</v>
+        <v>0.02924393627768818</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01433186490455213</v>
+        <v>0.01434365993325098</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02147784059679884</v>
+        <v>0.02145745679037531</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02122179456541239</v>
+        <v>0.02118606763468473</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03130511421721505</v>
+        <v>0.03128442430258861</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02979978256876964</v>
+        <v>0.02980440941591902</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008915884722130965</v>
+        <v>0.008916105327617881</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03922010445554732</v>
+        <v>0.03926878686690426</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02934156895668128</v>
+        <v>0.0293066480849006</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02951469931046555</v>
+        <v>0.02951731132190974</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6463,7 +6463,7 @@
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05036922120038344</v>
+        <v>0.0503574787754833</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04404567617608033</v>
+        <v>0.04409513061317685</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03545312919218709</v>
+        <v>0.0354112218830431</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06451612940151463</v>
+        <v>0.06450402928726036</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03557757274102019</v>
+        <v>0.03550162817841074</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02730384135195723</v>
+        <v>0.02730781041266806</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6781,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03981797370433927</v>
+        <v>0.03978026072324462</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03075525900494868</v>
+        <v>0.03072270827023568</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01849941002255952</v>
+        <v>0.01853281796928462</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02657908685782614</v>
+        <v>0.02658386340520765</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04569855375457042</v>
+        <v>0.04567340608739388</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05764539007092199</v>
+        <v>0.05765520332323296</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7099,7 +7099,7 @@
         <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05019884992214078</v>
+        <v>0.05014503662619306</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>45930</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02948964218888402</v>
+        <v>0.02946516508850564</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03365676214089882</v>
+        <v>0.03363891063880556</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02213578260450285</v>
+        <v>0.02211538407459298</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06708252314739867</v>
+        <v>0.06706537684676347</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7364,7 +7364,7 @@
         <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05425061425061425</v>
+        <v>0.054234624348638</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46034</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.02705274079904521</v>
+        <v>0.0270358948520336</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02118606763468473</v>
+        <v>0.02107777672595685</v>
       </c>
     </row>
     <row r="7">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0503574787754833</v>
+        <v>0.0502832330683914</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02730781041266806</v>
+        <v>0.02734887911391143</v>
       </c>
     </row>
     <row r="9">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.01917108628806277</v>
+        <v>0.0191185115491923</v>
       </c>
     </row>
     <row r="10">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02145745679037531</v>
+        <v>0.0214406371832991</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03072270827023568</v>
+        <v>0.03101305197389307</v>
       </c>
     </row>
     <row r="12">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05014503662619306</v>
+        <v>0.04979960148261006</v>
       </c>
     </row>
     <row r="13">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04409513061317685</v>
+        <v>0.04435318205669831</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03128442430258861</v>
+        <v>0.03147686392939742</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03978026072324462</v>
+        <v>0.03980665259182842</v>
       </c>
     </row>
     <row r="16">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01853281796928462</v>
+        <v>0.01840627435560767</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02211538407459298</v>
+        <v>0.02207426047670711</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04567340608739388</v>
+        <v>0.04593248555713791</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04467261149718091</v>
+        <v>0.04429936011903342</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02996479013707762</v>
+        <v>0.03002664947611661</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02924393627768818</v>
+        <v>0.02938541407714164</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.054234624348638</v>
+        <v>0.05432536135067838</v>
       </c>
     </row>
     <row r="23">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008916105327617881</v>
+        <v>0.008997540670366096</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02946516508850564</v>
+        <v>0.02960337804006746</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03926878686690426</v>
+        <v>0.03932203389830508</v>
       </c>
     </row>
     <row r="26">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01213447726249195</v>
+        <v>0.0121351769357421</v>
       </c>
     </row>
     <row r="27">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01302562654183874</v>
+        <v>0.012998940490614</v>
       </c>
     </row>
     <row r="28">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02469254810363466</v>
+        <v>0.02465212547457339</v>
       </c>
     </row>
     <row r="29">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006666666666666666</v>
+        <v>0.006711034150127849</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02658386340520765</v>
+        <v>0.02656505215607025</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0270358948520336</v>
+        <v>0.02720698476496106</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02980440941591902</v>
+        <v>0.02987745716675765</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0293066480849006</v>
+        <v>0.02943293244023248</v>
       </c>
     </row>
     <row r="34">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04895572154782055</v>
+        <v>0.04943062190025668</v>
       </c>
     </row>
     <row r="35">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04916593766536496</v>
+        <v>0.04941539619496375</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02704225352112676</v>
+        <v>0.02703717558600346</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06450402928726036</v>
+        <v>0.06466165320802771</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02122995314264688</v>
+        <v>0.02121282044403359</v>
       </c>
     </row>
     <row r="39">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03871145406976317</v>
+        <v>0.03895276222330631</v>
       </c>
     </row>
     <row r="40">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01611319509721077</v>
+        <v>0.01608040201005025</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03743526236660243</v>
+        <v>0.03746973918488582</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02951731132190974</v>
+        <v>0.0298225449431034</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06706537684676347</v>
+        <v>0.06705509431890479</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01434365993325098</v>
+        <v>0.01433523238208774</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05765520332323296</v>
+        <v>0.05732340151835449</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02170891574227562</v>
+        <v>0.02154775964851256</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002859225259362572</v>
+        <v>0.002850244752221173</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01569378272750932</v>
+        <v>0.01572277553050933</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02108963071937463</v>
+        <v>0.02128603176230392</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.0354112218830431</v>
+        <v>0.03546417445482866</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03550162817841074</v>
+        <v>0.03563976729680052</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03363891063880556</v>
+        <v>0.03369451180275464</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009550338318464836</v>
+        <v>0.009530112764911504</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02634970689052226</v>
+        <v>0.02648511006763391</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01674247309135909</v>
+        <v>0.0167168164926196</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009550338318464836</v>
+        <v>0.009530112764911504</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02704225352112676</v>
+        <v>0.02703717558600346</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002859225259362572</v>
+        <v>0.002850244752221173</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4979,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03871145406976317</v>
+        <v>0.03895276222330631</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02996479013707762</v>
+        <v>0.03002664947611661</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04467261149718091</v>
+        <v>0.04429936011903342</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01569378272750932</v>
+        <v>0.01572277553050933</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02122995314264688</v>
+        <v>0.02121282044403359</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006666666666666666</v>
+        <v>0.006711034150127849</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02170891574227562</v>
+        <v>0.02154775964851256</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03743526236660243</v>
+        <v>0.03746973918488582</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01611319509721077</v>
+        <v>0.01608040201005025</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02108963071937463</v>
+        <v>0.02128603176230392</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04916593766536496</v>
+        <v>0.04941539619496375</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5562,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02469254810363466</v>
+        <v>0.02465212547457339</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01674247309135909</v>
+        <v>0.0167168164926196</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02634970689052226</v>
+        <v>0.02648511006763391</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01302562654183874</v>
+        <v>0.012998940490614</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5774,7 +5774,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04895572154782055</v>
+        <v>0.04943062190025668</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02924393627768818</v>
+        <v>0.02938541407714164</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01434365993325098</v>
+        <v>0.01433523238208774</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02145745679037531</v>
+        <v>0.0214406371832991</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02118606763468473</v>
+        <v>0.02107777672595685</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6039,7 +6039,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01917108628806277</v>
+        <v>0.0191185115491923</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6092,7 +6092,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01213447726249195</v>
+        <v>0.0121351769357421</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03128442430258861</v>
+        <v>0.03147686392939742</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02980440941591902</v>
+        <v>0.02987745716675765</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008916105327617881</v>
+        <v>0.008997540670366096</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03926878686690426</v>
+        <v>0.03932203389830508</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.0293066480849006</v>
+        <v>0.02943293244023248</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02951731132190974</v>
+        <v>0.0298225449431034</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6463,7 +6463,7 @@
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.0503574787754833</v>
+        <v>0.0502832330683914</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04409513061317685</v>
+        <v>0.04435318205669831</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.0354112218830431</v>
+        <v>0.03546417445482866</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06450402928726036</v>
+        <v>0.06466165320802771</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03550162817841074</v>
+        <v>0.03563976729680052</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02730781041266806</v>
+        <v>0.02734887911391143</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6781,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03978026072324462</v>
+        <v>0.03980665259182842</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03072270827023568</v>
+        <v>0.03101305197389307</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01853281796928462</v>
+        <v>0.01840627435560767</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02658386340520765</v>
+        <v>0.02656505215607025</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04567340608739388</v>
+        <v>0.04593248555713791</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05765520332323296</v>
+        <v>0.05732340151835449</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7099,7 +7099,7 @@
         <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05014503662619306</v>
+        <v>0.04979960148261006</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>45930</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02946516508850564</v>
+        <v>0.02960337804006746</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03363891063880556</v>
+        <v>0.03369451180275464</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02211538407459298</v>
+        <v>0.02207426047670711</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06706537684676347</v>
+        <v>0.06705509431890479</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7364,7 +7364,7 @@
         <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.054234624348638</v>
+        <v>0.05432536135067838</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46034</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.0270358948520336</v>
+        <v>0.02720698476496106</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02107777672595685</v>
+        <v>0.02108370329294528</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02734887911391143</v>
+        <v>0.02736215300994221</v>
       </c>
     </row>
     <row r="9">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.0214406371832991</v>
+        <v>0.02146277045649526</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03101305197389307</v>
+        <v>0.03098033121458188</v>
       </c>
     </row>
     <row r="12">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.04979960148261006</v>
+        <v>0.0497404156056366</v>
       </c>
     </row>
     <row r="13">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04435318205669831</v>
+        <v>0.04442616304920324</v>
       </c>
     </row>
     <row r="14">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03147686392939742</v>
+        <v>0.03151353654511192</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0.03980665259182842</v>
+        <v>0.03985197859686609</v>
       </c>
     </row>
     <row r="16">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01840627435560767</v>
+        <v>0.0183789927246624</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02207426047670711</v>
+        <v>0.02207381868407455</v>
       </c>
     </row>
     <row r="18">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04593248555713791</v>
+        <v>0.04588804519723013</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04429936011903342</v>
+        <v>0.04432727243222405</v>
       </c>
     </row>
     <row r="20">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.03002664947611661</v>
+        <v>0.02999737495505726</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02938541407714164</v>
+        <v>0.02941704035874439</v>
       </c>
     </row>
     <row r="22">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05432536135067838</v>
+        <v>0.05436752628908985</v>
       </c>
     </row>
     <row r="23">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008997540670366096</v>
+        <v>0.008989540825074586</v>
       </c>
     </row>
     <row r="24">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02960337804006746</v>
+        <v>0.02956870279760218</v>
       </c>
     </row>
     <row r="25">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03932203389830508</v>
+        <v>0.03935316055626335</v>
       </c>
     </row>
     <row r="26">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.0121351769357421</v>
+        <v>0.0121181900273712</v>
       </c>
     </row>
     <row r="27">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.012998940490614</v>
+        <v>0.01299985884667673</v>
       </c>
     </row>
     <row r="28">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02465212547457339</v>
+        <v>0.02466281237702379</v>
       </c>
     </row>
     <row r="29">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006711034150127849</v>
+        <v>0.006702974673435055</v>
       </c>
     </row>
     <row r="30">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02656505215607025</v>
+        <v>0.02656215963191535</v>
       </c>
     </row>
     <row r="31">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02720698476496106</v>
+        <v>0.0271517058840861</v>
       </c>
     </row>
     <row r="32">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02987745716675765</v>
+        <v>0.02988094439452906</v>
       </c>
     </row>
     <row r="33">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02943293244023248</v>
+        <v>0.02942764995815325</v>
       </c>
     </row>
     <row r="34">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04943062190025668</v>
+        <v>0.04944104635191109</v>
       </c>
     </row>
     <row r="35">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04941539619496375</v>
+        <v>0.0494190337633541</v>
       </c>
     </row>
     <row r="36">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02703717558600346</v>
+        <v>0.02704660692255828</v>
       </c>
     </row>
     <row r="37">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06466165320802771</v>
+        <v>0.06470446765057743</v>
       </c>
     </row>
     <row r="38">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02121282044403359</v>
+        <v>0.02123730393539037</v>
       </c>
     </row>
     <row r="39">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03895276222330631</v>
+        <v>0.03899056978520801</v>
       </c>
     </row>
     <row r="40">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01608040201005025</v>
+        <v>0.01607919006011586</v>
       </c>
     </row>
     <row r="41">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03746973918488582</v>
+        <v>0.03744215325453691</v>
       </c>
     </row>
     <row r="42">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.0298225449431034</v>
+        <v>0.02984083274840852</v>
       </c>
     </row>
     <row r="43">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06705509431890479</v>
+        <v>0.06715806694824922</v>
       </c>
     </row>
     <row r="44">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01433523238208774</v>
+        <v>0.01432008925840888</v>
       </c>
     </row>
     <row r="45">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05732340151835449</v>
+        <v>0.05723943661971831</v>
       </c>
     </row>
     <row r="46">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02154775964851256</v>
+        <v>0.02154917453072534</v>
       </c>
     </row>
     <row r="47">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002850244752221173</v>
+        <v>0.002847900971446654</v>
       </c>
     </row>
     <row r="48">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01572277553050933</v>
+        <v>0.01572425884410382</v>
       </c>
     </row>
     <row r="49">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02128603176230392</v>
+        <v>0.02122485097758049</v>
       </c>
     </row>
     <row r="50">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03546417445482866</v>
+        <v>0.03548849692412532</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03563976729680052</v>
+        <v>0.0356478100250136</v>
       </c>
     </row>
     <row r="52">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03369451180275464</v>
+        <v>0.03372066576854548</v>
       </c>
     </row>
     <row r="53">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009530112764911504</v>
+        <v>0.009520451135020374</v>
       </c>
     </row>
     <row r="54">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02648511006763391</v>
+        <v>0.02648167842900664</v>
       </c>
     </row>
     <row r="55">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.0167168164926196</v>
+        <v>0.01673506256411583</v>
       </c>
     </row>
   </sheetData>
@@ -4820,7 +4820,7 @@
         <v>1.08</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009530112764911504</v>
+        <v>0.009520451135020374</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>45982</v>
@@ -4873,7 +4873,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02703717558600346</v>
+        <v>0.02704660692255828</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4926,7 +4926,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002850244752221173</v>
+        <v>0.002847900971446654</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4979,7 +4979,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03895276222330631</v>
+        <v>0.03899056978520801</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5032,7 +5032,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03002664947611661</v>
+        <v>0.02999737495505726</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5085,7 +5085,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04429936011903342</v>
+        <v>0.04432727243222405</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5138,7 +5138,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01572277553050933</v>
+        <v>0.01572425884410382</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46003</v>
@@ -5191,7 +5191,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02121282044403359</v>
+        <v>0.02123730393539037</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5244,7 +5244,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006711034150127849</v>
+        <v>0.006702974673435055</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5297,7 +5297,7 @@
         <v>1.64</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02154775964851256</v>
+        <v>0.02154917453072534</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46024</v>
@@ -5350,7 +5350,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03746973918488582</v>
+        <v>0.03744215325453691</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5403,7 +5403,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01608040201005025</v>
+        <v>0.01607919006011586</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5456,7 +5456,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02128603176230392</v>
+        <v>0.02122485097758049</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46006</v>
@@ -5509,7 +5509,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04941539619496375</v>
+        <v>0.0494190337633541</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46006</v>
@@ -5562,7 +5562,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02465212547457339</v>
+        <v>0.02466281237702379</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0167168164926196</v>
+        <v>0.01673506256411583</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5668,7 +5668,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02648511006763391</v>
+        <v>0.02648167842900664</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>45995</v>
@@ -5721,7 +5721,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.012998940490614</v>
+        <v>0.01299985884667673</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5774,7 +5774,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04943062190025668</v>
+        <v>0.04944104635191109</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5827,7 +5827,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02938541407714164</v>
+        <v>0.02941704035874439</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5880,7 +5880,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01433523238208774</v>
+        <v>0.01432008925840888</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5933,7 +5933,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.0214406371832991</v>
+        <v>0.02146277045649526</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5986,7 +5986,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02107777672595685</v>
+        <v>0.02108370329294528</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6092,7 +6092,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.0121351769357421</v>
+        <v>0.0121181900273712</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6145,7 +6145,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03147686392939742</v>
+        <v>0.03151353654511192</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6198,7 +6198,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02987745716675765</v>
+        <v>0.02988094439452906</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6251,7 +6251,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008997540670366096</v>
+        <v>0.008989540825074586</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6304,7 +6304,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03932203389830508</v>
+        <v>0.03935316055626335</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6357,7 +6357,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02943293244023248</v>
+        <v>0.02942764995815325</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6410,7 +6410,7 @@
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.0298225449431034</v>
+        <v>0.02984083274840852</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6516,7 +6516,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04435318205669831</v>
+        <v>0.04442616304920324</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6569,7 +6569,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03546417445482866</v>
+        <v>0.03548849692412532</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6622,7 +6622,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06466165320802771</v>
+        <v>0.06470446765057743</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6675,7 +6675,7 @@
         <v>3.16</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03563976729680052</v>
+        <v>0.0356478100250136</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>45994</v>
@@ -6728,7 +6728,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02734887911391143</v>
+        <v>0.02736215300994221</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6781,7 +6781,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03980665259182842</v>
+        <v>0.03985197859686609</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46013</v>
@@ -6834,7 +6834,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03101305197389307</v>
+        <v>0.03098033121458188</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6887,7 +6887,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01840627435560767</v>
+        <v>0.0183789927246624</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6940,7 +6940,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02656505215607025</v>
+        <v>0.02656215963191535</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -6993,7 +6993,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04593248555713791</v>
+        <v>0.04588804519723013</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>45992</v>
@@ -7046,7 +7046,7 @@
         <v>5.08</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05732340151835449</v>
+        <v>0.05723943661971831</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46006</v>
@@ -7099,7 +7099,7 @@
         <v>3.976</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.04979960148261006</v>
+        <v>0.0497404156056366</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>45930</v>
@@ -7152,7 +7152,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02960337804006746</v>
+        <v>0.02956870279760218</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45961</v>
@@ -7205,7 +7205,7 @@
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03369451180275464</v>
+        <v>0.03372066576854548</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7258,7 +7258,7 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02207426047670711</v>
+        <v>0.02207381868407455</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7311,7 +7311,7 @@
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06705509431890479</v>
+        <v>0.06715806694824922</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7364,7 +7364,7 @@
         <v>2.76</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05432536135067838</v>
+        <v>0.05436752628908985</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46034</v>
@@ -7417,7 +7417,7 @@
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.02720698476496106</v>
+        <v>0.0271517058840861</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7440,4 +7440,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD13515E-AAC2-4A62-A915-4EB462477D7D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7D812E-3AA2-400E-AD80-634357178F15}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186EFF90-78C9-48B9-9F0B-E40CEC7F0AAA}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,12 +72,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00856404"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
@@ -94,7 +88,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -104,11 +98,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a3a5c"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,19 +131,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -534,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -561,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/09/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/23/2026</t>
         </is>
       </c>
     </row>
@@ -637,7 +623,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -647,29 +633,29 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.5</v>
+        <v>1.057</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1.4</v>
+        <v>1.007</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.04965243296921554</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46096</v>
+        <v>46122</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>46300</v>
+        <v>46132</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
@@ -677,45 +663,45 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02108370329294528</v>
+        <v>0.0291535954348521</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.27</v>
+        <v>0.976</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.269</v>
+        <v>0.884</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.003717472118959111</v>
+        <v>0.1040723981900452</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46096</v>
+        <v>46127</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46196</v>
+        <v>46503</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -723,13 +709,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0502832330683914</v>
+        <v>0.02049343832020997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -739,29 +725,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.057</v>
+        <v>1.3</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.007</v>
+        <v>1.24</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46122</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>32</v>
+        <v>46128</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>24</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46132</v>
+        <v>46165</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -769,45 +755,45 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02736215300994221</v>
+        <v>0.02203016500553975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.976</v>
+        <v>1.27</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.884</v>
+        <v>1.2</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46127</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>37</v>
+        <v>46134</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46503</v>
+        <v>46161</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -815,13 +801,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.0191185115491923</v>
+        <v>0.02895742012250174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -831,29 +817,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.3</v>
+        <v>0.994</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.24</v>
+        <v>0.831</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46128</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>38</v>
+        <v>46140</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>36</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46165</v>
+        <v>46190</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -861,13 +847,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02146277045649526</v>
+        <v>0.04551803170526622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -881,25 +867,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46134</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>44</v>
+        <v>46143</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>39</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46161</v>
+        <v>46152</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -907,13 +893,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03098033121458188</v>
+        <v>0.04596967353172818</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -927,25 +913,25 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.994</v>
+        <v>0.71</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.831</v>
+        <v>0.7</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46141</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>51</v>
+        <v>46162</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>58</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -953,59 +939,59 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.0497404156056366</v>
+        <v>0.03268124223397447</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.1020408163265307</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>46143</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>46152</v>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>0.04442616304920324</v>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>46176</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>0.04154713772034981</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1015,29 +1001,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>72</v>
+        <v>46218</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>114</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46198</v>
+        <v>46248</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1045,59 +1031,59 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.03151353654511192</v>
+        <v>0.01846291281599689</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>86</v>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="n">
-        <v>0.03985197859686609</v>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>114</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0.01846291281599689</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1111,25 +1097,25 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.89</v>
+        <v>1.34</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>128</v>
+        <v>46220</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>116</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1137,13 +1123,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.0183789927246624</v>
+        <v>0.02307065393635178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1153,29 +1139,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>130</v>
+        <v>46227</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>123</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1183,13 +1169,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02207381868407455</v>
+        <v>0.04739810245968331</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1199,29 +1185,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>137</v>
+        <v>46232</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>128</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1229,7 +1215,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04588804519723013</v>
+        <v>0.03003454137242492</v>
       </c>
     </row>
     <row r="19">
@@ -1263,8 +1249,8 @@
       <c r="H19" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I19" s="13" t="n">
-        <v>142</v>
+      <c r="I19" s="11" t="n">
+        <v>128</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46246</v>
@@ -1275,13 +1261,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04432727243222405</v>
+        <v>0.04611808330319646</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1291,29 +1277,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>142</v>
+        <v>46263</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>159</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1321,13 +1307,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02999737495505726</v>
+        <v>0.02994613381315931</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1341,25 +1327,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.678</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01769911504424764</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>173</v>
+        <v>46267</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>163</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1367,13 +1353,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02941704035874439</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1383,29 +1369,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.678</v>
+        <v>0.83</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>177</v>
+        <v>46278</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>174</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46303</v>
+        <v>46344</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1413,13 +1399,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.05436752628908985</v>
+        <v>0.009441793172158741</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1429,29 +1415,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.83</v>
+        <v>1.36</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>188</v>
+        <v>46285</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>181</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46344</v>
+        <v>46325</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1459,13 +1445,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.008989540825074586</v>
+        <v>0.0297506811988012</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1475,29 +1461,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>195</v>
+        <v>46305</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>201</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1505,13 +1491,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02956870279760218</v>
+        <v>0.04068272109836166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1521,29 +1507,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>215</v>
+        <v>46311</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>207</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1551,13 +1537,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03935316055626335</v>
+        <v>0.01230577473752138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1567,29 +1553,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I26" s="13" t="n">
-        <v>221</v>
+        <v>46317</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>213</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1597,13 +1583,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.0121181900273712</v>
+        <v>0.01366336633663366</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1617,25 +1603,25 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="I27" s="13" t="n">
-        <v>227</v>
+        <v>46322</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>218</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1643,13 +1629,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01299985884667673</v>
+        <v>0.02537542692959548</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1663,22 +1649,22 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>232</v>
+        <v>46329</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>225</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46338</v>
@@ -1689,13 +1675,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02466281237702379</v>
+        <v>0.007356208990148843</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1709,25 +1695,25 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>239</v>
+        <v>46332</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>228</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1735,13 +1721,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.006702974673435055</v>
+        <v>0.0268223978014428</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1755,25 +1741,25 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>242</v>
+        <v>46341</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>237</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1781,13 +1767,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02656215963191535</v>
+        <v>0.02607182508545984</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1797,29 +1783,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I31" s="13" t="n">
-        <v>251</v>
+        <v>46344</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>240</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1827,13 +1813,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0271517058840861</v>
+        <v>0.0359617910086034</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1847,25 +1833,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>254</v>
+        <v>46347</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>243</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1873,13 +1859,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.02988094439452906</v>
+        <v>0.03073463233210399</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1889,29 +1875,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>257</v>
+        <v>46352</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>248</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1919,13 +1905,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02942764995815325</v>
+        <v>0.05265049361856506</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1935,29 +1921,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>262</v>
+        <v>46360</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>256</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1965,13 +1951,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04944104635191109</v>
+        <v>0.04986272751327035</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1981,29 +1967,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I35" s="13" t="n">
-        <v>270</v>
+        <v>46366</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>262</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2011,13 +1997,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0494190337633541</v>
+        <v>0.02869097539422992</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2027,29 +2013,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.52</v>
+        <v>0.43</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2.38</v>
+        <v>0.42</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>276</v>
+        <v>46370</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>266</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46432</v>
+        <v>46413</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2057,13 +2043,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02704660692255828</v>
+        <v>0.06394052135283915</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2073,29 +2059,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="I37" s="13" t="n">
-        <v>280</v>
+        <v>46371</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>267</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46413</v>
+        <v>46344</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2103,13 +2089,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06470446765057743</v>
+        <v>0.02188391959954028</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2119,29 +2105,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.23</v>
+        <v>0.703</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.22</v>
+        <v>0.676</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>281</v>
+        <v>46411</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>307</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46344</v>
+        <v>46435</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2149,13 +2135,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.02123730393539037</v>
+        <v>0.04124678949944683</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2165,29 +2151,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.703</v>
+        <v>0.8</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.676</v>
+        <v>0.75</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.06666666666666672</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I39" s="13" t="n">
-        <v>321</v>
+        <v>46416</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>312</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46435</v>
+        <v>46483</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2195,13 +2181,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03899056978520801</v>
+        <v>0.01629162014983631</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2211,29 +2197,29 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.8</v>
+        <v>1.78</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46416</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>326</v>
+        <v>46417</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>313</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2241,45 +2227,45 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01607919006011586</v>
+        <v>0.03538327635252886</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.78</v>
+        <v>0.584</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.71</v>
+        <v>0.513</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.142300194931774</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>327</v>
+        <v>46419</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>315</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2287,45 +2273,45 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03744215325453691</v>
+        <v>0.03161028351510873</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.584</v>
+        <v>1.64</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.513</v>
+        <v>1.63</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>1.142300194931774</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46419</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>329</v>
+        <v>46423</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>319</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46472</v>
+        <v>46435</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2333,13 +2319,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02984083274840852</v>
+        <v>0.06706880854454768</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2349,29 +2335,29 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1.64</v>
+        <v>0.61</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1.63</v>
+        <v>0.58</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>333</v>
+        <v>46428</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>324</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46435</v>
+        <v>46452</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2379,13 +2365,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.06715806694824922</v>
+        <v>0.01475211662660081</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2399,13 +2385,13 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.08</v>
@@ -2413,11 +2399,11 @@
       <c r="H44" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I44" s="13" t="n">
-        <v>338</v>
+      <c r="I44" s="11" t="n">
+        <v>324</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2425,45 +2411,45 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01432008925840888</v>
+        <v>0.05940820373037564</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.27</v>
+        <v>1.883</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.24</v>
+        <v>1.864</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.02419354838709679</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46430</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>340</v>
+        <v>46433</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46460</v>
+        <v>46425</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2471,13 +2457,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.05723943661971831</v>
+        <v>0.002723282372501188</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2487,29 +2473,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.41</v>
+        <v>7.45</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.4</v>
+        <v>1.25</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>4.96</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>342</v>
+        <v>46433</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46481</v>
+        <v>46383</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2517,45 +2503,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.02154917453072534</v>
+        <v>0.09735221224892325</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.883</v>
+        <v>0.24</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.864</v>
+        <v>0.22</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H47" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I47" s="13" t="n">
-        <v>343</v>
+      <c r="I47" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46425</v>
+        <v>46276</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2563,13 +2549,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.002847900971446654</v>
+        <v>0.02006479204737895</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2579,17 +2565,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.25</v>
+        <v>1.423</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.15</v>
+        <v>1.355</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>4.043478260869565</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0.06</v>
@@ -2597,11 +2583,11 @@
       <c r="H48" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I48" s="13" t="n">
-        <v>343</v>
+      <c r="I48" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46383</v>
+        <v>46177</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2609,13 +2595,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01572425884410382</v>
+        <v>0.03783686339934728</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2629,25 +2615,25 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.22</v>
+        <v>0.79</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I49" s="13" t="n">
-        <v>343</v>
+      <c r="I49" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2655,13 +2641,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02122485097758049</v>
+        <v>0.03720497524150213</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2671,17 +2657,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1.423</v>
+        <v>0.555</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1.355</v>
+        <v>0.588964</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0.06</v>
@@ -2689,11 +2675,11 @@
       <c r="H50" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I50" s="13" t="n">
-        <v>343</v>
+      <c r="I50" s="11" t="n">
+        <v>329</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46177</v>
+        <v>46243</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2701,13 +2687,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03548849692412532</v>
+        <v>0.03599513623773182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2703,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.78</v>
+        <v>0.27</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.01282051282051283</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>343</v>
+        <v>46440</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>336</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46270</v>
+        <v>46450</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2733,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.0356478100250136</v>
+        <v>0.01011774953826027</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2763,29 +2749,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.555</v>
+        <v>2.33</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.588964</v>
+        <v>2.3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>343</v>
+        <v>46441</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>337</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46243</v>
+        <v>46456</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2779,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.03372066576854548</v>
+        <v>0.02796825186337326</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2795,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.27</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.25</v>
+        <v>1.42</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.05633802816901413</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>350</v>
+        <v>46451</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>347</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46449</v>
+        <v>46487</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,59 +2825,59 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.009520451135020374</v>
+        <v>0.0174218562737619</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>0.02222222222222214</v>
-      </c>
-      <c r="G54" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>46455</v>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="n">
-        <v>0.02648167842900664</v>
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>46460</v>
+      </c>
+      <c r="I54" s="19" t="n">
+        <v>356</v>
+      </c>
+      <c r="J54" s="18" t="n">
+        <v>46481</v>
+      </c>
+      <c r="K54" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0.02079898581784063</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2901,29 +2887,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.05633802816901413</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46451</v>
-      </c>
-      <c r="I55" s="13" t="n">
-        <v>361</v>
+        <v>46461</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>357</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2931,7 +2917,53 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01673506256411583</v>
+        <v>0.02058107236004315</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>0.003717472118959111</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>357</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>46196</v>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>0.05314088789783094</v>
       </c>
     </row>
   </sheetData>
@@ -2945,7 +2977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2966,44 +2998,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 03/09/2026</t>
+          <t>Expected Increase Announcements by Month - 03/23/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>March 2026</t>
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>April 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3012,20 +3044,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46096</v>
+        <v>46122</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46300</v>
+        <v>46132</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.5</v>
+        <v>1.057</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.04965243296921554</v>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
@@ -3036,20 +3068,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46096</v>
+        <v>46127</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>46196</v>
+        <v>46503</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.27</v>
+        <v>0.976</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.003717472118959111</v>
+        <v>0.1040723981900452</v>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
@@ -3057,134 +3089,134 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>46165</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.04838709677419359</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>April 2026</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.2021660649819495</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>46122</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>46132</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.04965243296921554</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>46127</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>46503</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.1040723981900452</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>46128</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>46165</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.04838709677419359</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46134</v>
+        <v>46143</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46161</v>
+        <v>46152</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3195,20 +3227,20 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.994</v>
+        <v>0.71</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
@@ -3217,211 +3249,244 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>May 2026</t>
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>June 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>46152</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.1020408163265307</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.0142857142857143</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>July 2026</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.05263157894736847</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
@@ -3429,95 +3494,62 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
@@ -3526,39 +3558,39 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3567,20 +3599,20 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01769911504424764</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3588,110 +3620,110 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B41" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F39" s="23" t="inlineStr">
+      <c r="F41" s="22" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>46303</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.01769911504424764</v>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>46285</v>
+        <v>46305</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -3699,134 +3731,134 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>LECO</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>46386</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.05333333333333338</v>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B48" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D48" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E48" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F45" s="23" t="inlineStr">
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C48" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.02222222222222208</v>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="C49" s="10" t="n">
         <v>46338</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -3834,62 +3866,95 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.1401869158878504</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D52" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46329</v>
+        <v>46347</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46338</v>
+        <v>46358</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -3900,20 +3965,20 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>46332</v>
+        <v>46352</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>46346</v>
+        <v>46400</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2.44</v>
+        <v>0.293</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
@@ -3921,95 +3986,62 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>46358</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4017,134 +4049,134 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.05882352941176476</v>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>46370</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>46413</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.02380952380952383</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="23" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B61" s="23" t="inlineStr">
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="C64" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="D64" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E61" s="23" t="inlineStr">
+      <c r="E64" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F61" s="23" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>46413</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.02380952380952383</v>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46371</v>
+        <v>46411</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46344</v>
+        <v>46435</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.23</v>
+        <v>0.703</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4152,110 +4184,110 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>46416</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.06666666666666672</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="22" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="23" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B68" s="23" t="inlineStr">
+      <c r="B70" s="22" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
+      <c r="C70" s="22" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D68" s="23" t="inlineStr">
+      <c r="D70" s="22" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E68" s="23" t="inlineStr">
+      <c r="E70" s="22" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F68" s="23" t="inlineStr">
+      <c r="F70" s="22" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>BKH</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>46435</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.03994082840236673</v>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>46416</v>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>0.06666666666666672</v>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46417</v>
+        <v>46419</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1.78</v>
+        <v>0.584</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.142300194931774</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4263,62 +4295,95 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>46423</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.00613496932515338</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="73">
-      <c r="A73" s="22" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B74" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D74" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E74" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F74" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.02362204724409451</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46419</v>
+        <v>46433</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46472</v>
+        <v>46425</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0.584</v>
+        <v>1.883</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1.142300194931774</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4329,20 +4394,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46423</v>
+        <v>46433</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46435</v>
+        <v>46383</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1.64</v>
+        <v>7.45</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>4.96</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4353,20 +4418,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46452</v>
+        <v>46276</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4377,20 +4442,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46430</v>
+        <v>46433</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46460</v>
+        <v>46177</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1.27</v>
+        <v>1.423</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.02419354838709679</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4401,20 +4466,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46481</v>
+        <v>46270</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4425,20 +4490,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46425</v>
+        <v>46243</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1.883</v>
+        <v>0.555</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4449,20 +4514,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>4.043478260869565</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4473,20 +4538,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46276</v>
+        <v>46456</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>0.24</v>
+        <v>2.33</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4494,184 +4559,136 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46177</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.05018450184501849</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.01282051282051283</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A84" s="21" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>46243</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.005735494868956323</v>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B86" s="10" t="n">
-        <v>46440</v>
+        <v>46451</v>
       </c>
       <c r="C86" s="10" t="n">
-        <v>46449</v>
+        <v>46487</v>
       </c>
       <c r="D86" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.05633802816901413</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="n">
+        <v>46460</v>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>46481</v>
+      </c>
+      <c r="D87" s="15" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.07142857142857149</v>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>46196</v>
+      </c>
+      <c r="D89" s="7" t="n">
         <v>0.27</v>
       </c>
-      <c r="E86" s="8" t="n">
-        <v>0.08000000000000007</v>
-      </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>46455</v>
-      </c>
-      <c r="D87" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0.02222222222222214</v>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B90" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C90" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D90" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E90" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F90" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="n">
-        <v>46451</v>
-      </c>
-      <c r="C91" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.05633802816901413</v>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
+      <c r="E89" s="8" t="n">
+        <v>0.003717472118959111</v>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4688,7 +4705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4716,7 +4733,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 03/09/2026</t>
+          <t>Complete Holdings Dividend Summary - 03/23/2026</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4812,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -4814,25 +4831,25 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>1.08</v>
+        <v>0.29</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009520451135020374</v>
+        <v>0.01011774953826027</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>45982</v>
+        <v>46090</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>46440</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>46449</v>
+        <v>46450</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -4848,7 +4865,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4869,11 +4886,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="23" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02704660692255828</v>
+        <v>0.02869097539422992</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4901,7 +4918,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4922,11 +4939,11 @@
       <c r="F7" s="7" t="n">
         <v>1.883</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="23" t="n">
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002847900971446654</v>
+        <v>0.002723282372501188</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4954,7 +4971,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4975,11 +4992,11 @@
       <c r="F8" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="23" t="n">
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03899056978520801</v>
+        <v>0.04124678949944683</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5007,7 +5024,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5028,11 +5045,11 @@
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="23" t="n">
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02999737495505726</v>
+        <v>0.03003454137242492</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5060,7 +5077,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5081,11 +5098,11 @@
       <c r="F10" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="23" t="n">
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04432727243222405</v>
+        <v>0.04611808330319646</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5113,7 +5130,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5132,19 +5149,19 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>5</v>
+        <v>7.45</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.01572425884410382</v>
+        <v>0.09735221224892325</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>46003</v>
+        <v>46091</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>4.043478260869565</v>
+        <v>4.96</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>46433</v>
@@ -5166,7 +5183,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5187,11 +5204,11 @@
       <c r="F12" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="23" t="n">
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02123730393539037</v>
+        <v>0.02188391959954028</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5219,7 +5236,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5240,11 +5257,11 @@
       <c r="F13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="23" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.006702974673435055</v>
+        <v>0.007356208990148843</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5265,55 +5282,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Quality Dividend</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>QDVD/DAC</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="15" t="n">
         <v>0.41</v>
       </c>
       <c r="G14" s="24" t="n">
         <v>1.64</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>0.02154917453072534</v>
-      </c>
-      <c r="I14" s="10" t="n">
+      <c r="H14" s="17" t="n">
+        <v>0.02079898581784063</v>
+      </c>
+      <c r="I14" s="18" t="n">
         <v>46024</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="16" t="n">
         <v>0.02499999999999988</v>
       </c>
-      <c r="K14" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="L14" s="10" t="n">
+      <c r="K14" s="18" t="n">
+        <v>46460</v>
+      </c>
+      <c r="L14" s="18" t="n">
         <v>46481</v>
       </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5342,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5346,11 +5363,11 @@
       <c r="F15" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="23" t="n">
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03744215325453691</v>
+        <v>0.03538327635252886</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5378,7 +5395,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5399,11 +5416,11 @@
       <c r="F16" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="23" t="n">
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01607919006011586</v>
+        <v>0.01629162014983631</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5431,7 +5448,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5452,14 +5469,14 @@
       <c r="F17" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="23" t="n">
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02122485097758049</v>
+        <v>0.02006479204737895</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>46006</v>
+        <v>46094</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.09090909090909087</v>
@@ -5484,7 +5501,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5505,14 +5522,14 @@
       <c r="F18" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="23" t="n">
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.0494190337633541</v>
+        <v>0.04986272751327035</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>46006</v>
+        <v>46094</v>
       </c>
       <c r="J18" s="8" t="n">
         <v>0.01204819277108435</v>
@@ -5537,7 +5554,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5558,11 +5575,11 @@
       <c r="F19" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="23" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02466281237702379</v>
+        <v>0.02537542692959548</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5590,7 +5607,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5611,11 +5628,11 @@
       <c r="F20" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="23" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01673506256411583</v>
+        <v>0.0174218562737619</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5643,7 +5660,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -5662,25 +5679,25 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G21" s="24" t="n">
-        <v>9.199999999999999</v>
+        <v>2.33</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02648167842900664</v>
+        <v>0.02796825186337326</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>45995</v>
+        <v>46093</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.02222222222222214</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>46455</v>
+        <v>46456</v>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
@@ -5696,7 +5713,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -5717,11 +5734,11 @@
       <c r="F22" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="23" t="n">
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01299985884667673</v>
+        <v>0.01366336633663366</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5749,7 +5766,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5770,11 +5787,11 @@
       <c r="F23" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="23" t="n">
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.04944104635191109</v>
+        <v>0.05265049361856506</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5802,7 +5819,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -5823,11 +5840,11 @@
       <c r="F24" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="23" t="n">
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02941704035874439</v>
+        <v>0.02994613381315931</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5855,7 +5872,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -5876,11 +5893,11 @@
       <c r="F25" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="23" t="n">
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01432008925840888</v>
+        <v>0.01475211662660081</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5908,7 +5925,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -5929,11 +5946,11 @@
       <c r="F26" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="G26" s="23" t="n">
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02146277045649526</v>
+        <v>0.02203016500553975</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5961,7 +5978,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5982,11 +5999,11 @@
       <c r="F27" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="23" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02108370329294528</v>
+        <v>0.02058107236004315</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -5995,7 +6012,7 @@
         <v>0.07142857142857149</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>46096</v>
+        <v>46461</v>
       </c>
       <c r="L27" s="10" t="n">
         <v>46300</v>
@@ -6014,7 +6031,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -6035,11 +6052,11 @@
       <c r="F28" s="7" t="n">
         <v>0.976</v>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="23" t="n">
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.0191185115491923</v>
+        <v>0.02049343832020997</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6067,7 +6084,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -6088,11 +6105,11 @@
       <c r="F29" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G29" s="23" t="n">
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.0121181900273712</v>
+        <v>0.01230577473752138</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6120,7 +6137,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -6141,11 +6158,11 @@
       <c r="F30" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="23" t="n">
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03151353654511192</v>
+        <v>0.03268124223397447</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46017</v>
@@ -6173,7 +6190,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -6194,11 +6211,11 @@
       <c r="F31" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="23" t="n">
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.02988094439452906</v>
+        <v>0.0359617910086034</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6226,7 +6243,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -6247,11 +6264,11 @@
       <c r="F32" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="23" t="n">
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008989540825074586</v>
+        <v>0.009441793172158741</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6279,7 +6296,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -6300,11 +6317,11 @@
       <c r="F33" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="23" t="n">
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03935316055626335</v>
+        <v>0.04068272109836166</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6332,7 +6349,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -6353,11 +6370,11 @@
       <c r="F34" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="23" t="n">
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02942764995815325</v>
+        <v>0.03073463233210399</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6385,7 +6402,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -6406,11 +6423,11 @@
       <c r="F35" s="7" t="n">
         <v>0.584</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="23" t="n">
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02984083274840852</v>
+        <v>0.03161028351510873</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6438,7 +6455,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -6459,11 +6476,11 @@
       <c r="F36" s="7" t="n">
         <v>0.27</v>
       </c>
-      <c r="G36" s="24" t="n">
+      <c r="G36" s="23" t="n">
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.0502832330683914</v>
+        <v>0.05314088789783094</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6472,7 +6489,7 @@
         <v>0.003717472118959111</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>46096</v>
+        <v>46461</v>
       </c>
       <c r="L36" s="10" t="n">
         <v>46196</v>
@@ -6491,7 +6508,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -6512,11 +6529,11 @@
       <c r="F37" s="7" t="n">
         <v>1.08</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="23" t="n">
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04442616304920324</v>
+        <v>0.04596967353172818</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6544,7 +6561,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -6565,11 +6582,11 @@
       <c r="F38" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="23" t="n">
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03548849692412532</v>
+        <v>0.03783686339934728</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6597,7 +6614,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -6618,11 +6635,11 @@
       <c r="F39" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G39" s="24" t="n">
+      <c r="G39" s="23" t="n">
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06470446765057743</v>
+        <v>0.06394052135283915</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6650,7 +6667,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -6669,19 +6686,19 @@
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G40" s="24" t="n">
-        <v>3.16</v>
+        <v>0.8</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.0356478100250136</v>
+        <v>0.03720497524150213</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>45994</v>
+        <v>46092</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.01282051282051283</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="K40" s="10" t="n">
         <v>46433</v>
@@ -6703,7 +6720,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -6724,11 +6741,11 @@
       <c r="F41" s="7" t="n">
         <v>1.057</v>
       </c>
-      <c r="G41" s="24" t="n">
+      <c r="G41" s="23" t="n">
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02736215300994221</v>
+        <v>0.0291535954348521</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6749,53 +6766,53 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Quality Dividend</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>QDVD/DAC/SMID</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="15" t="n">
         <v>0.525</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="H42" s="18" t="n">
-        <v>0.03985197859686609</v>
-      </c>
-      <c r="I42" s="19" t="n">
+      <c r="H42" s="17" t="n">
+        <v>0.04154713772034981</v>
+      </c>
+      <c r="I42" s="18" t="n">
         <v>46013</v>
       </c>
-      <c r="J42" s="17" t="n">
+      <c r="J42" s="16" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="K42" s="19" t="n">
+      <c r="K42" s="18" t="n">
         <v>46176</v>
       </c>
-      <c r="L42" s="19" t="n">
+      <c r="L42" s="18" t="n">
         <v>46197</v>
       </c>
-      <c r="M42" s="21" t="inlineStr">
+      <c r="M42" s="20" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6809,7 +6826,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -6830,11 +6847,11 @@
       <c r="F43" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G43" s="24" t="n">
+      <c r="G43" s="23" t="n">
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03098033121458188</v>
+        <v>0.02895742012250174</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6862,7 +6879,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -6883,11 +6900,11 @@
       <c r="F44" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G44" s="24" t="n">
+      <c r="G44" s="23" t="n">
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0183789927246624</v>
+        <v>0.01846291281599689</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6910,12 +6927,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6930,29 +6947,29 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="G45" s="24" t="n">
-        <v>9.76</v>
+        <v>0.93</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>3.72</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02656215963191535</v>
+        <v>0.01846291281599689</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46077</v>
+        <v>46070</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>46332</v>
+        <v>46218</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>46346</v>
+        <v>46248</v>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
@@ -6963,12 +6980,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -6978,34 +6995,34 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G46" s="24" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>9.76</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04588804519723013</v>
+        <v>0.0268223978014428</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>45992</v>
+        <v>46077</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>46227</v>
+        <v>46332</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>46267</v>
+        <v>46346</v>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
@@ -7016,12 +7033,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>DAC/SMID</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -7031,34 +7048,34 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G47" s="24" t="n">
-        <v>5.08</v>
+        <v>0.83</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>3.32</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05723943661971831</v>
+        <v>0.04739810245968331</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>46006</v>
+        <v>46091</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.02419354838709679</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>46430</v>
+        <v>46227</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>46460</v>
+        <v>46267</v>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
@@ -7069,12 +7086,12 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC/SMID</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -7089,29 +7106,29 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="G48" s="24" t="n">
-        <v>3.976</v>
+        <v>1.3</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>5.2</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.0497404156056366</v>
+        <v>0.05940820373037564</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>45930</v>
+        <v>46097</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46141</v>
+        <v>46428</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46191</v>
+        <v>46460</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7122,12 +7139,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -7137,34 +7154,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Oct</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G49" s="24" t="n">
-        <v>5.68</v>
+        <v>0.994</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>3.976</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02956870279760218</v>
+        <v>0.04551803170526622</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>46285</v>
+        <v>46140</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>46325</v>
+        <v>46190</v>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
@@ -7175,12 +7192,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -7190,34 +7207,34 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Jan/May/Jul/Oct</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="G50" s="24" t="n">
-        <v>2.22</v>
+        <v>1.42</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <v>5.68</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03372066576854548</v>
+        <v>0.0297506811988012</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>46080</v>
+        <v>46052</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46433</v>
+        <v>46285</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46243</v>
+        <v>46325</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7228,12 +7245,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -7243,7 +7260,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Dec</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -7252,25 +7269,25 @@
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G51" s="24" t="n">
-        <v>5.52</v>
+        <v>0.555</v>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>2.22</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02207381868407455</v>
+        <v>0.03599513623773182</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>46220</v>
+        <v>46433</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
@@ -7281,12 +7298,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -7296,34 +7313,34 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Feb/May/Aug/Dec</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G52" s="24" t="n">
-        <v>6.56</v>
+        <v>1.38</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>5.52</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06715806694824922</v>
+        <v>0.02307065393635178</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46070</v>
+        <v>46080</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>46423</v>
+        <v>46220</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>46435</v>
+        <v>46264</v>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
@@ -7334,12 +7351,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Quality Dividend</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7349,34 +7366,34 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="G53" s="24" t="n">
-        <v>2.76</v>
+        <v>1.64</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>6.56</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05436752628908985</v>
+        <v>0.06706880854454768</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>46034</v>
+        <v>46070</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46267</v>
+        <v>46423</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46303</v>
+        <v>46435</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7387,51 +7404,104 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/DAC</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Jan/Apr/Jul/Oct</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>46034</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>0.01769911504424764</v>
+      </c>
+      <c r="K54" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Quality Dividend</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/DAC</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="F54" s="7" t="n">
+      <c r="F55" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G54" s="24" t="n">
+      <c r="G55" s="23" t="n">
         <v>4.12</v>
       </c>
-      <c r="H54" s="9" t="n">
-        <v>0.0271517058840861</v>
-      </c>
-      <c r="I54" s="10" t="n">
+      <c r="H55" s="9" t="n">
+        <v>0.02607182508545984</v>
+      </c>
+      <c r="I55" s="10" t="n">
         <v>46065</v>
       </c>
-      <c r="J54" s="8" t="n">
+      <c r="J55" s="8" t="n">
         <v>0.04040404040404044</v>
       </c>
-      <c r="K54" s="10" t="n">
+      <c r="K55" s="10" t="n">
         <v>46341</v>
       </c>
-      <c r="L54" s="10" t="n">
+      <c r="L55" s="10" t="n">
         <v>46339</v>
       </c>
-      <c r="M54" s="12" t="inlineStr">
+      <c r="M55" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -7440,252 +7510,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD13515E-AAC2-4A62-A915-4EB462477D7D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7D812E-3AA2-400E-AD80-634357178F15}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186EFF90-78C9-48B9-9F0B-E40CEC7F0AAA}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7510,4 +7510,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{161435CF-554B-4E9C-8EF7-D306330B17B9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94120F72-60DA-490F-BAAC-86AA11994D08}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8340C35D-F94E-472C-A02F-046046F1B44A}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
@@ -88,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a3a5c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,16 +142,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,10 +164,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -547,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/23/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/30/2026</t>
         </is>
       </c>
     </row>
@@ -652,7 +666,7 @@
         <v>46122</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46132</v>
@@ -663,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.0291535954348521</v>
+        <v>0.02939990314843966</v>
       </c>
     </row>
     <row r="7">
@@ -697,8 +711,8 @@
       <c r="H7" s="10" t="n">
         <v>46127</v>
       </c>
-      <c r="I7" s="11" t="n">
-        <v>23</v>
+      <c r="I7" s="13" t="n">
+        <v>16</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46503</v>
@@ -709,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02049343832020997</v>
+        <v>0.02049244854572341</v>
       </c>
     </row>
     <row r="8">
@@ -743,8 +757,8 @@
       <c r="H8" s="10" t="n">
         <v>46128</v>
       </c>
-      <c r="I8" s="11" t="n">
-        <v>24</v>
+      <c r="I8" s="13" t="n">
+        <v>17</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46165</v>
@@ -755,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02203016500553975</v>
+        <v>0.02150270835143434</v>
       </c>
     </row>
     <row r="9">
@@ -789,8 +803,8 @@
       <c r="H9" s="10" t="n">
         <v>46134</v>
       </c>
-      <c r="I9" s="11" t="n">
-        <v>30</v>
+      <c r="I9" s="13" t="n">
+        <v>23</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46161</v>
@@ -801,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02895742012250174</v>
+        <v>0.02688399565783459</v>
       </c>
     </row>
     <row r="10">
@@ -835,8 +849,8 @@
       <c r="H10" s="10" t="n">
         <v>46140</v>
       </c>
-      <c r="I10" s="11" t="n">
-        <v>36</v>
+      <c r="I10" s="13" t="n">
+        <v>29</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46190</v>
@@ -847,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.04551803170526622</v>
+        <v>0.0429535990399483</v>
       </c>
     </row>
     <row r="11">
@@ -881,8 +895,8 @@
       <c r="H11" s="10" t="n">
         <v>46143</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>39</v>
+      <c r="I11" s="13" t="n">
+        <v>32</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46152</v>
@@ -893,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.04596967353172818</v>
+        <v>0.04682926829268293</v>
       </c>
     </row>
     <row r="12">
@@ -927,8 +941,8 @@
       <c r="H12" s="10" t="n">
         <v>46162</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>58</v>
+      <c r="I12" s="13" t="n">
+        <v>51</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46198</v>
@@ -939,53 +953,53 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.03268124223397447</v>
+        <v>0.03263617685080991</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.525</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>0.04</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>46176</v>
       </c>
-      <c r="I13" s="19" t="n">
-        <v>72</v>
-      </c>
-      <c r="J13" s="18" t="n">
+      <c r="I13" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J13" s="19" t="n">
         <v>46197</v>
       </c>
-      <c r="K13" s="20" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="L13" s="17" t="n">
-        <v>0.04154713772034981</v>
+      <c r="L13" s="18" t="n">
+        <v>0.0402723172224527</v>
       </c>
     </row>
     <row r="14">
@@ -1019,8 +1033,8 @@
       <c r="H14" s="10" t="n">
         <v>46218</v>
       </c>
-      <c r="I14" s="11" t="n">
-        <v>114</v>
+      <c r="I14" s="13" t="n">
+        <v>107</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46248</v>
@@ -1031,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.01846291281599689</v>
+        <v>0.01864755074222239</v>
       </c>
     </row>
     <row r="15">
@@ -1065,8 +1079,8 @@
       <c r="H15" s="10" t="n">
         <v>46218</v>
       </c>
-      <c r="I15" s="11" t="n">
-        <v>114</v>
+      <c r="I15" s="13" t="n">
+        <v>107</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46248</v>
@@ -1077,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01846291281599689</v>
+        <v>0.01864755074222239</v>
       </c>
     </row>
     <row r="16">
@@ -1111,8 +1125,8 @@
       <c r="H16" s="10" t="n">
         <v>46220</v>
       </c>
-      <c r="I16" s="11" t="n">
-        <v>116</v>
+      <c r="I16" s="13" t="n">
+        <v>109</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46264</v>
@@ -1123,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02307065393635178</v>
+        <v>0.02292834890965732</v>
       </c>
     </row>
     <row r="17">
@@ -1157,8 +1171,8 @@
       <c r="H17" s="10" t="n">
         <v>46227</v>
       </c>
-      <c r="I17" s="11" t="n">
-        <v>123</v>
+      <c r="I17" s="13" t="n">
+        <v>116</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46267</v>
@@ -1169,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.04739810245968331</v>
+        <v>0.04879482591603472</v>
       </c>
     </row>
     <row r="18">
@@ -1203,8 +1217,8 @@
       <c r="H18" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I18" s="11" t="n">
-        <v>128</v>
+      <c r="I18" s="13" t="n">
+        <v>121</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46264</v>
@@ -1215,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.03003454137242492</v>
+        <v>0.02967138990015516</v>
       </c>
     </row>
     <row r="19">
@@ -1249,8 +1263,8 @@
       <c r="H19" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I19" s="11" t="n">
-        <v>128</v>
+      <c r="I19" s="13" t="n">
+        <v>121</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46246</v>
@@ -1261,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04611808330319646</v>
+        <v>0.04900701556039189</v>
       </c>
     </row>
     <row r="20">
@@ -1295,8 +1309,8 @@
       <c r="H20" s="10" t="n">
         <v>46263</v>
       </c>
-      <c r="I20" s="11" t="n">
-        <v>159</v>
+      <c r="I20" s="13" t="n">
+        <v>152</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46297</v>
@@ -1307,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02994613381315931</v>
+        <v>0.02918668873610638</v>
       </c>
     </row>
     <row r="21">
@@ -1341,8 +1355,8 @@
       <c r="H21" s="10" t="n">
         <v>46267</v>
       </c>
-      <c r="I21" s="11" t="n">
-        <v>163</v>
+      <c r="I21" s="13" t="n">
+        <v>156</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46303</v>
@@ -1353,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.0552</v>
+        <v>0.05448429504518887</v>
       </c>
     </row>
     <row r="22">
@@ -1387,8 +1401,8 @@
       <c r="H22" s="10" t="n">
         <v>46278</v>
       </c>
-      <c r="I22" s="11" t="n">
-        <v>174</v>
+      <c r="I22" s="13" t="n">
+        <v>167</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46344</v>
@@ -1399,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.009441793172158741</v>
+        <v>0.01011349878049246</v>
       </c>
     </row>
     <row r="23">
@@ -1433,8 +1447,8 @@
       <c r="H23" s="10" t="n">
         <v>46285</v>
       </c>
-      <c r="I23" s="11" t="n">
-        <v>181</v>
+      <c r="I23" s="13" t="n">
+        <v>174</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46325</v>
@@ -1445,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.0297506811988012</v>
+        <v>0.02987833617940912</v>
       </c>
     </row>
     <row r="24">
@@ -1479,8 +1493,8 @@
       <c r="H24" s="10" t="n">
         <v>46305</v>
       </c>
-      <c r="I24" s="11" t="n">
-        <v>201</v>
+      <c r="I24" s="13" t="n">
+        <v>194</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46339</v>
@@ -1491,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.04068272109836166</v>
+        <v>0.03850409499617897</v>
       </c>
     </row>
     <row r="25">
@@ -1525,8 +1539,8 @@
       <c r="H25" s="10" t="n">
         <v>46311</v>
       </c>
-      <c r="I25" s="11" t="n">
-        <v>207</v>
+      <c r="I25" s="13" t="n">
+        <v>200</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46386</v>
@@ -1537,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01230577473752138</v>
+        <v>0.01275659546945501</v>
       </c>
     </row>
     <row r="26">
@@ -1571,8 +1585,8 @@
       <c r="H26" s="10" t="n">
         <v>46317</v>
       </c>
-      <c r="I26" s="11" t="n">
-        <v>213</v>
+      <c r="I26" s="13" t="n">
+        <v>206</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46351</v>
@@ -1583,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01366336633663366</v>
+        <v>0.0146463000754747</v>
       </c>
     </row>
     <row r="27">
@@ -1617,8 +1631,8 @@
       <c r="H27" s="10" t="n">
         <v>46322</v>
       </c>
-      <c r="I27" s="11" t="n">
-        <v>218</v>
+      <c r="I27" s="13" t="n">
+        <v>211</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46338</v>
@@ -1629,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02537542692959548</v>
+        <v>0.02327378459090542</v>
       </c>
     </row>
     <row r="28">
@@ -1663,8 +1677,8 @@
       <c r="H28" s="10" t="n">
         <v>46329</v>
       </c>
-      <c r="I28" s="11" t="n">
-        <v>225</v>
+      <c r="I28" s="13" t="n">
+        <v>218</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46338</v>
@@ -1675,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.007356208990148843</v>
+        <v>0.007635530491459991</v>
       </c>
     </row>
     <row r="29">
@@ -1709,8 +1723,8 @@
       <c r="H29" s="10" t="n">
         <v>46332</v>
       </c>
-      <c r="I29" s="11" t="n">
-        <v>228</v>
+      <c r="I29" s="13" t="n">
+        <v>221</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46346</v>
@@ -1721,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.0268223978014428</v>
+        <v>0.02719988759972165</v>
       </c>
     </row>
     <row r="30">
@@ -1755,8 +1769,8 @@
       <c r="H30" s="10" t="n">
         <v>46341</v>
       </c>
-      <c r="I30" s="11" t="n">
-        <v>237</v>
+      <c r="I30" s="13" t="n">
+        <v>230</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46339</v>
@@ -1767,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02607182508545984</v>
+        <v>0.02356574933849925</v>
       </c>
     </row>
     <row r="31">
@@ -1801,8 +1815,8 @@
       <c r="H31" s="10" t="n">
         <v>46344</v>
       </c>
-      <c r="I31" s="11" t="n">
-        <v>240</v>
+      <c r="I31" s="13" t="n">
+        <v>233</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46385</v>
@@ -1813,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0359617910086034</v>
+        <v>0.0361990943977892</v>
       </c>
     </row>
     <row r="32">
@@ -1847,8 +1861,8 @@
       <c r="H32" s="10" t="n">
         <v>46347</v>
       </c>
-      <c r="I32" s="11" t="n">
-        <v>243</v>
+      <c r="I32" s="13" t="n">
+        <v>236</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46358</v>
@@ -1859,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03073463233210399</v>
+        <v>0.03174603183979984</v>
       </c>
     </row>
     <row r="33">
@@ -1893,8 +1907,8 @@
       <c r="H33" s="10" t="n">
         <v>46352</v>
       </c>
-      <c r="I33" s="11" t="n">
-        <v>248</v>
+      <c r="I33" s="13" t="n">
+        <v>241</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46400</v>
@@ -1905,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05265049361856506</v>
+        <v>0.05067012721677747</v>
       </c>
     </row>
     <row r="34">
@@ -1939,8 +1953,8 @@
       <c r="H34" s="10" t="n">
         <v>46360</v>
       </c>
-      <c r="I34" s="11" t="n">
-        <v>256</v>
+      <c r="I34" s="13" t="n">
+        <v>249</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46371</v>
@@ -1951,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04986272751327035</v>
+        <v>0.04632565912794535</v>
       </c>
     </row>
     <row r="35">
@@ -1985,8 +1999,8 @@
       <c r="H35" s="10" t="n">
         <v>46366</v>
       </c>
-      <c r="I35" s="11" t="n">
-        <v>262</v>
+      <c r="I35" s="13" t="n">
+        <v>255</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46432</v>
@@ -1997,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.02869097539422992</v>
+        <v>0.02867628152814483</v>
       </c>
     </row>
     <row r="36">
@@ -2031,8 +2045,8 @@
       <c r="H36" s="10" t="n">
         <v>46370</v>
       </c>
-      <c r="I36" s="11" t="n">
-        <v>266</v>
+      <c r="I36" s="13" t="n">
+        <v>259</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46413</v>
@@ -2043,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.06394052135283915</v>
+        <v>0.06281177656172118</v>
       </c>
     </row>
     <row r="37">
@@ -2077,8 +2091,8 @@
       <c r="H37" s="10" t="n">
         <v>46371</v>
       </c>
-      <c r="I37" s="11" t="n">
-        <v>267</v>
+      <c r="I37" s="13" t="n">
+        <v>260</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46344</v>
@@ -2089,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.02188391959954028</v>
+        <v>0.0214252452124615</v>
       </c>
     </row>
     <row r="38">
@@ -2123,8 +2137,8 @@
       <c r="H38" s="10" t="n">
         <v>46411</v>
       </c>
-      <c r="I38" s="11" t="n">
-        <v>307</v>
+      <c r="I38" s="13" t="n">
+        <v>300</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46435</v>
@@ -2135,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.04124678949944683</v>
+        <v>0.040594776039757</v>
       </c>
     </row>
     <row r="39">
@@ -2169,8 +2183,8 @@
       <c r="H39" s="10" t="n">
         <v>46416</v>
       </c>
-      <c r="I39" s="11" t="n">
-        <v>312</v>
+      <c r="I39" s="13" t="n">
+        <v>305</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46483</v>
@@ -2181,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.01629162014983631</v>
+        <v>0.01634988749254875</v>
       </c>
     </row>
     <row r="40">
@@ -2215,8 +2229,8 @@
       <c r="H40" s="10" t="n">
         <v>46417</v>
       </c>
-      <c r="I40" s="11" t="n">
-        <v>313</v>
+      <c r="I40" s="13" t="n">
+        <v>306</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46433</v>
@@ -2227,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03538327635252886</v>
+        <v>0.03326092504050905</v>
       </c>
     </row>
     <row r="41">
@@ -2261,8 +2275,8 @@
       <c r="H41" s="10" t="n">
         <v>46419</v>
       </c>
-      <c r="I41" s="11" t="n">
-        <v>315</v>
+      <c r="I41" s="13" t="n">
+        <v>308</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46472</v>
@@ -2273,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03161028351510873</v>
+        <v>0.03309719381407237</v>
       </c>
     </row>
     <row r="42">
@@ -2307,8 +2321,8 @@
       <c r="H42" s="10" t="n">
         <v>46423</v>
       </c>
-      <c r="I42" s="11" t="n">
-        <v>319</v>
+      <c r="I42" s="13" t="n">
+        <v>312</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46435</v>
@@ -2319,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.06706880854454768</v>
+        <v>0.06847598946793178</v>
       </c>
     </row>
     <row r="43">
@@ -2353,8 +2367,8 @@
       <c r="H43" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I43" s="11" t="n">
-        <v>324</v>
+      <c r="I43" s="13" t="n">
+        <v>317</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46452</v>
@@ -2365,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01475211662660081</v>
+        <v>0.01577348219982237</v>
       </c>
     </row>
     <row r="44">
@@ -2399,8 +2413,8 @@
       <c r="H44" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I44" s="11" t="n">
-        <v>324</v>
+      <c r="I44" s="13" t="n">
+        <v>317</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46460</v>
@@ -2411,45 +2425,45 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.05940820373037564</v>
+        <v>0.0581557898200166</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.883</v>
+        <v>0.41</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.864</v>
+        <v>0.4</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>329</v>
+        <v>46432</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>321</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46425</v>
+        <v>46481</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2457,45 +2471,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.002723282372501188</v>
+        <v>0.02077527171622906</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>7.45</v>
+        <v>1.883</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.25</v>
+        <v>1.864</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>4.96</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I46" s="11" t="n">
-        <v>329</v>
+      <c r="I46" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46383</v>
+        <v>46425</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2503,13 +2517,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.09735221224892325</v>
+        <v>0.00296196100543417</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2519,17 +2533,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.24</v>
+        <v>7.45</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>4.96</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0.06</v>
@@ -2537,11 +2551,11 @@
       <c r="H47" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I47" s="11" t="n">
-        <v>329</v>
+      <c r="I47" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46276</v>
+        <v>46383</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2549,13 +2563,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.02006479204737895</v>
+        <v>0.1007675883168235</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2565,17 +2579,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.423</v>
+        <v>0.24</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.355</v>
+        <v>0.22</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0.06</v>
@@ -2583,11 +2597,11 @@
       <c r="H48" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I48" s="11" t="n">
-        <v>329</v>
+      <c r="I48" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46177</v>
+        <v>46276</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2595,13 +2609,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03783686339934728</v>
+        <v>0.01829616881390908</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2611,29 +2625,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.8</v>
+        <v>1.423</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.79</v>
+        <v>1.355</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I49" s="11" t="n">
-        <v>329</v>
+      <c r="I49" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46270</v>
+        <v>46177</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2641,13 +2655,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03720497524150213</v>
+        <v>0.03653519090405939</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2657,29 +2671,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.555</v>
+        <v>0.8</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.79</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I50" s="11" t="n">
-        <v>329</v>
+      <c r="I50" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46243</v>
+        <v>46270</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2687,13 +2701,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03599513623773182</v>
+        <v>0.03650051405080914</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2703,29 +2717,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.29</v>
+        <v>0.555</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.27</v>
+        <v>0.588964</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I51" s="11" t="n">
-        <v>336</v>
+        <v>46433</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>322</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46450</v>
+        <v>46243</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2733,13 +2747,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.01011774953826027</v>
+        <v>0.03716103009083437</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2753,25 +2767,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2.33</v>
+        <v>0.29</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2.3</v>
+        <v>0.27</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I52" s="11" t="n">
-        <v>337</v>
+        <v>46440</v>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>329</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46456</v>
+        <v>46450</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2779,13 +2793,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02796825186337326</v>
+        <v>0.01014074662286406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2795,83 +2809,83 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.05633802816901413</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H53" s="10" t="n">
+        <v>46441</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>330</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>46456</v>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>0.02851809941441286</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>0.05633802816901413</v>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H54" s="10" t="n">
         <v>46451</v>
       </c>
-      <c r="I53" s="11" t="n">
-        <v>347</v>
-      </c>
-      <c r="J53" s="10" t="n">
+      <c r="I54" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="J54" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L53" s="9" t="n">
-        <v>0.0174218562737619</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="G54" s="17" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H54" s="18" t="n">
-        <v>46460</v>
-      </c>
-      <c r="I54" s="19" t="n">
-        <v>356</v>
-      </c>
-      <c r="J54" s="18" t="n">
-        <v>46481</v>
-      </c>
-      <c r="K54" s="20" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L54" s="17" t="n">
-        <v>0.02079898581784063</v>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>0.01724782270450997</v>
       </c>
     </row>
     <row r="55">
@@ -2905,8 +2919,8 @@
       <c r="H55" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I55" s="11" t="n">
-        <v>357</v>
+      <c r="I55" s="13" t="n">
+        <v>350</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46300</v>
@@ -2917,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.02058107236004315</v>
+        <v>0.02104414080461985</v>
       </c>
     </row>
     <row r="56">
@@ -2951,8 +2965,8 @@
       <c r="H56" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I56" s="11" t="n">
-        <v>357</v>
+      <c r="I56" s="13" t="n">
+        <v>350</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46196</v>
@@ -2963,7 +2977,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.05314088789783094</v>
+        <v>0.05277732582200233</v>
       </c>
     </row>
   </sheetData>
@@ -2998,44 +3012,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 03/23/2026</t>
+          <t>Expected Increase Announcements by Month - 03/30/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3162,39 +3176,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3249,102 +3263,102 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>June 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>46176</v>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="19" t="n">
         <v>46197</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>0.525</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3495,39 +3509,39 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3558,39 +3572,39 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3669,39 +3683,39 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E41" s="22" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3804,39 +3818,39 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F48" s="22" t="inlineStr">
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3987,39 +4001,39 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B57" s="22" t="inlineStr">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C57" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D57" s="22" t="inlineStr">
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="E57" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4122,39 +4136,39 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="A63" s="22" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B64" s="22" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C64" s="22" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D64" s="22" t="inlineStr">
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E64" s="22" t="inlineStr">
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="F64" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4233,39 +4247,39 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="A69" s="22" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="inlineStr">
+      <c r="A70" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B70" s="22" t="inlineStr">
+      <c r="B70" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C70" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D70" s="22" t="inlineStr">
+      <c r="D70" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E70" s="22" t="inlineStr">
+      <c r="E70" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F70" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4370,20 +4384,20 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46433</v>
+        <v>46432</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46425</v>
+        <v>46481</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1.883</v>
+        <v>0.41</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4394,20 +4408,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46383</v>
+        <v>46425</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>7.45</v>
+        <v>1.883</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4.96</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4418,20 +4432,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46276</v>
+        <v>46383</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.24</v>
+        <v>7.45</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>4.96</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4442,20 +4456,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46177</v>
+        <v>46276</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1.423</v>
+        <v>0.24</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4466,20 +4480,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46270</v>
+        <v>46177</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.8</v>
+        <v>1.423</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4490,20 +4504,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46243</v>
+        <v>46270</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.555</v>
+        <v>0.8</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4514,20 +4528,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46440</v>
+        <v>46433</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46450</v>
+        <v>46243</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.29</v>
+        <v>0.555</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4538,111 +4552,111 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>46440</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.07407407407407393</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="B82" s="10" t="n">
+      <c r="B83" s="10" t="n">
         <v>46441</v>
       </c>
-      <c r="C82" s="10" t="n">
+      <c r="C83" s="10" t="n">
         <v>46456</v>
       </c>
-      <c r="D82" s="7" t="n">
+      <c r="D83" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="E82" s="8" t="n">
+      <c r="E83" s="8" t="n">
         <v>0.01304347826086967</v>
       </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
         <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B85" s="22" t="inlineStr">
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C85" s="22" t="inlineStr">
+      <c r="C86" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D85" s="22" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E85" s="22" t="inlineStr">
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F85" s="22" t="inlineStr">
+      <c r="F86" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n">
+      <c r="B87" s="10" t="n">
         <v>46451</v>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C87" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="D86" s="7" t="n">
+      <c r="D87" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E87" s="8" t="n">
         <v>0.05633802816901413</v>
       </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="B87" s="18" t="n">
-        <v>46460</v>
-      </c>
-      <c r="C87" s="18" t="n">
-        <v>46481</v>
-      </c>
-      <c r="D87" s="15" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F87" s="20" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 03/23/2026</t>
+          <t>Complete Holdings Dividend Summary - 03/30/2026</t>
         </is>
       </c>
     </row>
@@ -4833,11 +4847,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="24" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01011774953826027</v>
+        <v>0.01014074662286406</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4886,11 +4900,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="24" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02869097539422992</v>
+        <v>0.02867628152814483</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4939,11 +4953,11 @@
       <c r="F7" s="7" t="n">
         <v>1.883</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="24" t="n">
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002723282372501188</v>
+        <v>0.00296196100543417</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -4992,11 +5006,11 @@
       <c r="F8" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="24" t="n">
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.04124678949944683</v>
+        <v>0.040594776039757</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5045,11 +5059,11 @@
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03003454137242492</v>
+        <v>0.02967138990015516</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5098,11 +5112,11 @@
       <c r="F10" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="24" t="n">
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04611808330319646</v>
+        <v>0.04900701556039189</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5151,11 +5165,11 @@
       <c r="F11" s="7" t="n">
         <v>7.45</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.09735221224892325</v>
+        <v>0.1007675883168235</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5204,11 +5218,11 @@
       <c r="F12" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02188391959954028</v>
+        <v>0.0214252452124615</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5257,11 +5271,11 @@
       <c r="F13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="24" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007356208990148843</v>
+        <v>0.007635530491459991</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5282,55 +5296,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>QDVD/DAC</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="7" t="n">
         <v>0.41</v>
       </c>
       <c r="G14" s="24" t="n">
         <v>1.64</v>
       </c>
-      <c r="H14" s="17" t="n">
-        <v>0.02079898581784063</v>
-      </c>
-      <c r="I14" s="18" t="n">
+      <c r="H14" s="9" t="n">
+        <v>0.02077527171622906</v>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="8" t="n">
         <v>0.02499999999999988</v>
       </c>
-      <c r="K14" s="18" t="n">
-        <v>46460</v>
-      </c>
-      <c r="L14" s="18" t="n">
+      <c r="K14" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="L14" s="10" t="n">
         <v>46481</v>
       </c>
-      <c r="M14" s="20" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -5363,11 +5377,11 @@
       <c r="F15" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="24" t="n">
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03538327635252886</v>
+        <v>0.03326092504050905</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5416,11 +5430,11 @@
       <c r="F16" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01629162014983631</v>
+        <v>0.01634988749254875</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5469,11 +5483,11 @@
       <c r="F17" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="24" t="n">
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02006479204737895</v>
+        <v>0.01829616881390908</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5522,11 +5536,11 @@
       <c r="F18" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="24" t="n">
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04986272751327035</v>
+        <v>0.04632565912794535</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5575,11 +5589,11 @@
       <c r="F19" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="24" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02537542692959548</v>
+        <v>0.02327378459090542</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5628,11 +5642,11 @@
       <c r="F20" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="24" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0174218562737619</v>
+        <v>0.01724782270450997</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5681,11 +5695,11 @@
       <c r="F21" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="24" t="n">
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02796825186337326</v>
+        <v>0.02851809941441286</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5734,11 +5748,11 @@
       <c r="F22" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="24" t="n">
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01366336633663366</v>
+        <v>0.0146463000754747</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5787,11 +5801,11 @@
       <c r="F23" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="24" t="n">
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05265049361856506</v>
+        <v>0.05067012721677747</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5840,11 +5854,11 @@
       <c r="F24" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="24" t="n">
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02994613381315931</v>
+        <v>0.02918668873610638</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46024</v>
@@ -5893,11 +5907,11 @@
       <c r="F25" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01475211662660081</v>
+        <v>0.01577348219982237</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5946,11 +5960,11 @@
       <c r="F26" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02203016500553975</v>
+        <v>0.02150270835143434</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5999,11 +6013,11 @@
       <c r="F27" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02058107236004315</v>
+        <v>0.02104414080461985</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6052,11 +6066,11 @@
       <c r="F28" s="7" t="n">
         <v>0.976</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="24" t="n">
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02049343832020997</v>
+        <v>0.02049244854572341</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6105,11 +6119,11 @@
       <c r="F29" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="24" t="n">
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01230577473752138</v>
+        <v>0.01275659546945501</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46022</v>
@@ -6158,14 +6172,14 @@
       <c r="F30" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03268124223397447</v>
+        <v>0.03263617685080991</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>46017</v>
+        <v>46108</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>0.0142857142857143</v>
@@ -6211,11 +6225,11 @@
       <c r="F31" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="24" t="n">
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.0359617910086034</v>
+        <v>0.0361990943977892</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6264,11 +6278,11 @@
       <c r="F32" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G32" s="23" t="n">
+      <c r="G32" s="24" t="n">
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.009441793172158741</v>
+        <v>0.01011349878049246</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6317,11 +6331,11 @@
       <c r="F33" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="24" t="n">
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.04068272109836166</v>
+        <v>0.03850409499617897</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6370,11 +6384,11 @@
       <c r="F34" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G34" s="23" t="n">
+      <c r="G34" s="24" t="n">
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03073463233210399</v>
+        <v>0.03174603183979984</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6423,11 +6437,11 @@
       <c r="F35" s="7" t="n">
         <v>0.584</v>
       </c>
-      <c r="G35" s="23" t="n">
+      <c r="G35" s="24" t="n">
         <v>1.168</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.03161028351510873</v>
+        <v>0.03309719381407237</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>45887</v>
@@ -6476,11 +6490,11 @@
       <c r="F36" s="7" t="n">
         <v>0.27</v>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G36" s="24" t="n">
         <v>3.24</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05314088789783094</v>
+        <v>0.05277732582200233</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46080</v>
@@ -6529,11 +6543,11 @@
       <c r="F37" s="7" t="n">
         <v>1.08</v>
       </c>
-      <c r="G37" s="23" t="n">
+      <c r="G37" s="24" t="n">
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04596967353172818</v>
+        <v>0.04682926829268293</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6582,11 +6596,11 @@
       <c r="F38" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="G38" s="23" t="n">
+      <c r="G38" s="24" t="n">
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03783686339934728</v>
+        <v>0.03653519090405939</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6635,11 +6649,11 @@
       <c r="F39" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G39" s="23" t="n">
+      <c r="G39" s="24" t="n">
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06394052135283915</v>
+        <v>0.06281177656172118</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6688,11 +6702,11 @@
       <c r="F40" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G40" s="23" t="n">
+      <c r="G40" s="24" t="n">
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03720497524150213</v>
+        <v>0.03650051405080914</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6741,11 +6755,11 @@
       <c r="F41" s="7" t="n">
         <v>1.057</v>
       </c>
-      <c r="G41" s="23" t="n">
+      <c r="G41" s="24" t="n">
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.0291535954348521</v>
+        <v>0.02939990314843966</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6766,53 +6780,53 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>QDVD/DAC/SMID</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F42" s="15" t="n">
+      <c r="F42" s="16" t="n">
         <v>0.525</v>
       </c>
-      <c r="G42" s="24" t="n">
+      <c r="G42" s="25" t="n">
         <v>2.1</v>
       </c>
-      <c r="H42" s="17" t="n">
-        <v>0.04154713772034981</v>
-      </c>
-      <c r="I42" s="18" t="n">
-        <v>46013</v>
-      </c>
-      <c r="J42" s="16" t="n">
+      <c r="H42" s="18" t="n">
+        <v>0.0402723172224527</v>
+      </c>
+      <c r="I42" s="19" t="n">
+        <v>46104</v>
+      </c>
+      <c r="J42" s="17" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="K42" s="18" t="n">
+      <c r="K42" s="19" t="n">
         <v>46176</v>
       </c>
-      <c r="L42" s="18" t="n">
+      <c r="L42" s="19" t="n">
         <v>46197</v>
       </c>
-      <c r="M42" s="20" t="inlineStr">
+      <c r="M42" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6847,11 +6861,11 @@
       <c r="F43" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G43" s="23" t="n">
+      <c r="G43" s="24" t="n">
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02895742012250174</v>
+        <v>0.02688399565783459</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6900,11 +6914,11 @@
       <c r="F44" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G44" s="23" t="n">
+      <c r="G44" s="24" t="n">
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01846291281599689</v>
+        <v>0.01864755074222239</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6953,11 +6967,11 @@
       <c r="F45" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G45" s="23" t="n">
+      <c r="G45" s="24" t="n">
         <v>3.72</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.01846291281599689</v>
+        <v>0.01864755074222239</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46070</v>
@@ -7006,11 +7020,11 @@
       <c r="F46" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G46" s="23" t="n">
+      <c r="G46" s="24" t="n">
         <v>9.76</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.0268223978014428</v>
+        <v>0.02719988759972165</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46077</v>
@@ -7059,11 +7073,11 @@
       <c r="F47" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G47" s="23" t="n">
+      <c r="G47" s="24" t="n">
         <v>3.32</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04739810245968331</v>
+        <v>0.04879482591603472</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46091</v>
@@ -7112,11 +7126,11 @@
       <c r="F48" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G48" s="23" t="n">
+      <c r="G48" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05940820373037564</v>
+        <v>0.0581557898200166</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46097</v>
@@ -7165,11 +7179,11 @@
       <c r="F49" s="7" t="n">
         <v>0.994</v>
       </c>
-      <c r="G49" s="23" t="n">
+      <c r="G49" s="24" t="n">
         <v>3.976</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04551803170526622</v>
+        <v>0.0429535990399483</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>45930</v>
@@ -7218,11 +7232,11 @@
       <c r="F50" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G50" s="23" t="n">
+      <c r="G50" s="24" t="n">
         <v>5.68</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.0297506811988012</v>
+        <v>0.02987833617940912</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46052</v>
@@ -7271,11 +7285,11 @@
       <c r="F51" s="7" t="n">
         <v>0.555</v>
       </c>
-      <c r="G51" s="23" t="n">
+      <c r="G51" s="24" t="n">
         <v>2.22</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03599513623773182</v>
+        <v>0.03716103009083437</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7324,11 +7338,11 @@
       <c r="F52" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G52" s="23" t="n">
+      <c r="G52" s="24" t="n">
         <v>5.52</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02307065393635178</v>
+        <v>0.02292834890965732</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46080</v>
@@ -7377,11 +7391,11 @@
       <c r="F53" s="7" t="n">
         <v>1.64</v>
       </c>
-      <c r="G53" s="23" t="n">
+      <c r="G53" s="24" t="n">
         <v>6.56</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06706880854454768</v>
+        <v>0.06847598946793178</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46070</v>
@@ -7430,11 +7444,11 @@
       <c r="F54" s="7" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="G54" s="23" t="n">
+      <c r="G54" s="24" t="n">
         <v>2.76</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.0552</v>
+        <v>0.05448429504518887</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46034</v>
@@ -7483,11 +7497,11 @@
       <c r="F55" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G55" s="23" t="n">
+      <c r="G55" s="24" t="n">
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02607182508545984</v>
+        <v>0.02356574933849925</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46065</v>
@@ -7510,252 +7524,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{161435CF-554B-4E9C-8EF7-D306330B17B9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94120F72-60DA-490F-BAAC-86AA11994D08}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8340C35D-F94E-472C-A02F-046046F1B44A}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 03/30/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/06/2026</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>46122</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46132</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02939990314843966</v>
+        <v>0.02946546684884909</v>
       </c>
     </row>
     <row r="7">
@@ -711,8 +711,8 @@
       <c r="H7" s="10" t="n">
         <v>46127</v>
       </c>
-      <c r="I7" s="13" t="n">
-        <v>16</v>
+      <c r="I7" s="11" t="n">
+        <v>9</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46503</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02049244854572341</v>
+        <v>0.0195944584037564</v>
       </c>
     </row>
     <row r="8">
@@ -757,8 +757,8 @@
       <c r="H8" s="10" t="n">
         <v>46128</v>
       </c>
-      <c r="I8" s="13" t="n">
-        <v>17</v>
+      <c r="I8" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46165</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02150270835143434</v>
+        <v>0.02139433526031882</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +804,7 @@
         <v>46134</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46161</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02688399565783459</v>
+        <v>0.02905015235229855</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.994</v>
+        <v>0.974</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0.831</v>
@@ -850,7 +850,7 @@
         <v>46140</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46190</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.0429535990399483</v>
+        <v>0.04255365613034411</v>
       </c>
     </row>
     <row r="11">
@@ -896,7 +896,7 @@
         <v>46143</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46152</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.04682926829268293</v>
+        <v>0.04695652173913044</v>
       </c>
     </row>
     <row r="12">
@@ -942,7 +942,7 @@
         <v>46162</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46198</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.03263617685080991</v>
+        <v>0.03260661162396298</v>
       </c>
     </row>
     <row r="13">
@@ -988,7 +988,7 @@
         <v>46176</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J13" s="19" t="n">
         <v>46197</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="18" t="n">
-        <v>0.0402723172224527</v>
+        <v>0.03943291630609523</v>
       </c>
     </row>
     <row r="14">
@@ -1034,7 +1034,7 @@
         <v>46218</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46248</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.01864755074222239</v>
+        <v>0.0182053974002074</v>
       </c>
     </row>
     <row r="15">
@@ -1080,7 +1080,7 @@
         <v>46218</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46248</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01864755074222239</v>
+        <v>0.0182053974002074</v>
       </c>
     </row>
     <row r="16">
@@ -1126,7 +1126,7 @@
         <v>46220</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46264</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02292834890965732</v>
+        <v>0.02260395961839812</v>
       </c>
     </row>
     <row r="17">
@@ -1172,7 +1172,7 @@
         <v>46227</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46267</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.04879482591603472</v>
+        <v>0.04888823179157632</v>
       </c>
     </row>
     <row r="18">
@@ -1218,7 +1218,7 @@
         <v>46232</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46264</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.02967138990015516</v>
+        <v>0.02880910342347681</v>
       </c>
     </row>
     <row r="19">
@@ -1264,7 +1264,7 @@
         <v>46232</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46246</v>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04900701556039189</v>
+        <v>0.04837608562423524</v>
       </c>
     </row>
     <row r="20">
@@ -1310,7 +1310,7 @@
         <v>46263</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46297</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02918668873610638</v>
+        <v>0.02911802652356768</v>
       </c>
     </row>
     <row r="21">
@@ -1356,7 +1356,7 @@
         <v>46267</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46303</v>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.05448429504518887</v>
+        <v>0.05561152409027773</v>
       </c>
     </row>
     <row r="22">
@@ -1402,7 +1402,7 @@
         <v>46278</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46344</v>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.01011349878049246</v>
+        <v>0.009770500924087532</v>
       </c>
     </row>
     <row r="23">
@@ -1448,7 +1448,7 @@
         <v>46285</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46325</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02987833617940912</v>
+        <v>0.02878279634676914</v>
       </c>
     </row>
     <row r="24">
@@ -1494,7 +1494,7 @@
         <v>46305</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46339</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03850409499617897</v>
+        <v>0.038431804337001</v>
       </c>
     </row>
     <row r="25">
@@ -1540,7 +1540,7 @@
         <v>46311</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46386</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01275659546945501</v>
+        <v>0.01301965272377644</v>
       </c>
     </row>
     <row r="26">
@@ -1586,7 +1586,7 @@
         <v>46317</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46351</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.0146463000754747</v>
+        <v>0.01372656238853958</v>
       </c>
     </row>
     <row r="27">
@@ -1632,7 +1632,7 @@
         <v>46322</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46338</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02327378459090542</v>
+        <v>0.02220680106790347</v>
       </c>
     </row>
     <row r="28">
@@ -1678,7 +1678,7 @@
         <v>46329</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46338</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.007635530491459991</v>
+        <v>0.007531774818673483</v>
       </c>
     </row>
     <row r="29">
@@ -1724,7 +1724,7 @@
         <v>46332</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46346</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02719988759972165</v>
+        <v>0.02673633489571878</v>
       </c>
     </row>
     <row r="30">
@@ -1770,7 +1770,7 @@
         <v>46341</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46339</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02356574933849925</v>
+        <v>0.02562587564240667</v>
       </c>
     </row>
     <row r="31">
@@ -1816,7 +1816,7 @@
         <v>46344</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46385</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0361990943977892</v>
+        <v>0.03831570498132009</v>
       </c>
     </row>
     <row r="32">
@@ -1862,7 +1862,7 @@
         <v>46347</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46358</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03174603183979984</v>
+        <v>0.03746858539749241</v>
       </c>
     </row>
     <row r="33">
@@ -1908,7 +1908,7 @@
         <v>46352</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46400</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05067012721677747</v>
+        <v>0.05307971032833607</v>
       </c>
     </row>
     <row r="34">
@@ -1954,7 +1954,7 @@
         <v>46360</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46371</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04632565912794535</v>
+        <v>0.04515521885010952</v>
       </c>
     </row>
     <row r="35">
@@ -2000,7 +2000,7 @@
         <v>46366</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46432</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.02867628152814483</v>
+        <v>0.02915401301518438</v>
       </c>
     </row>
     <row r="36">
@@ -2046,7 +2046,7 @@
         <v>46370</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46413</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.06281177656172118</v>
+        <v>0.06112295797109072</v>
       </c>
     </row>
     <row r="37">
@@ -2092,7 +2092,7 @@
         <v>46371</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46344</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.0214252452124615</v>
+        <v>0.02106227091511688</v>
       </c>
     </row>
     <row r="38">
@@ -2138,7 +2138,7 @@
         <v>46411</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46435</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.040594776039757</v>
+        <v>0.03977650487500992</v>
       </c>
     </row>
     <row r="39">
@@ -2184,7 +2184,7 @@
         <v>46416</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46483</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.01634988749254875</v>
+        <v>0.01618941586923297</v>
       </c>
     </row>
     <row r="40">
@@ -2230,7 +2230,7 @@
         <v>46417</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46433</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03326092504050905</v>
+        <v>0.03602783048703352</v>
       </c>
     </row>
     <row r="41">
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E41" s="7" t="n">
         <v>0.584</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>0.513</v>
-      </c>
       <c r="F41" s="8" t="n">
-        <v>1.142300194931774</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0.12</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46419</v>
+        <v>46422</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46472</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03309719381407237</v>
+        <v>0.06854838569090677</v>
       </c>
     </row>
     <row r="42">
@@ -2322,7 +2322,7 @@
         <v>46423</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46435</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.06847598946793178</v>
+        <v>0.06725790489254314</v>
       </c>
     </row>
     <row r="43">
@@ -2368,7 +2368,7 @@
         <v>46428</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46452</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01577348219982237</v>
+        <v>0.01528008289635777</v>
       </c>
     </row>
     <row r="44">
@@ -2414,7 +2414,7 @@
         <v>46428</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46460</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.0581557898200166</v>
+        <v>0.05781632042302506</v>
       </c>
     </row>
     <row r="45">
@@ -2445,25 +2445,25 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E45" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>0.4</v>
-      </c>
       <c r="F45" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46481</v>
+        <v>46480</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.02077527171622906</v>
+        <v>0.02118403623397195</v>
       </c>
     </row>
     <row r="46">
@@ -2506,7 +2506,7 @@
         <v>46433</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46425</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.00296196100543417</v>
+        <v>0.002892672996696654</v>
       </c>
     </row>
     <row r="47">
@@ -2552,7 +2552,7 @@
         <v>46433</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46383</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.1007675883168235</v>
+        <v>0.09680353545512323</v>
       </c>
     </row>
     <row r="48">
@@ -2598,7 +2598,7 @@
         <v>46433</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46276</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01829616881390908</v>
+        <v>0.01938806446195164</v>
       </c>
     </row>
     <row r="49">
@@ -2644,7 +2644,7 @@
         <v>46433</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46177</v>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03653519090405939</v>
+        <v>0.03651761197349492</v>
       </c>
     </row>
     <row r="50">
@@ -2690,7 +2690,7 @@
         <v>46433</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46270</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03650051405080914</v>
+        <v>0.03542370102874154</v>
       </c>
     </row>
     <row r="51">
@@ -2736,7 +2736,7 @@
         <v>46433</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46243</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03716103009083437</v>
+        <v>0.03963578051289666</v>
       </c>
     </row>
     <row r="52">
@@ -2782,7 +2782,7 @@
         <v>46440</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46450</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.01014074662286406</v>
+        <v>0.009962640308522799</v>
       </c>
     </row>
     <row r="53">
@@ -2828,7 +2828,7 @@
         <v>46441</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46456</v>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02851809941441286</v>
+        <v>0.02894409937888199</v>
       </c>
     </row>
     <row r="54">
@@ -2874,7 +2874,7 @@
         <v>46451</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46487</v>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.01724782270450997</v>
+        <v>0.0172314755590317</v>
       </c>
     </row>
     <row r="55">
@@ -2920,7 +2920,7 @@
         <v>46461</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46300</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.02104414080461985</v>
+        <v>0.02029289318332066</v>
       </c>
     </row>
     <row r="56">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E56" s="7" t="n">
         <v>0.27</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>0.269</v>
-      </c>
       <c r="F56" s="8" t="n">
-        <v>0.003717472118959111</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>0.02</v>
@@ -2966,7 +2966,7 @@
         <v>46461</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46196</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.05277732582200233</v>
+        <v>0.05231660244502703</v>
       </c>
     </row>
   </sheetData>
@@ -3012,7 +3012,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 03/30/2026</t>
+          <t>Expected Increase Announcements by Month - 04/06/2026</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
         <v>46190</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.994</v>
+        <v>0.974</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0.2021660649819495</v>
@@ -4292,16 +4292,16 @@
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46419</v>
+        <v>46422</v>
       </c>
       <c r="C71" s="10" t="n">
         <v>46472</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>0.584</v>
+        <v>1.275</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1.142300194931774</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46481</v>
+        <v>46480</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4697,10 +4697,10 @@
         <v>46196</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.003717472118959111</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 03/30/2026</t>
+          <t>Complete Holdings Dividend Summary - 04/06/2026</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01014074662286406</v>
+        <v>0.009962640308522799</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4904,7 +4904,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02867628152814483</v>
+        <v>0.02915401301518438</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4957,7 +4957,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.00296196100543417</v>
+        <v>0.002892672996696654</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5010,7 +5010,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.040594776039757</v>
+        <v>0.03977650487500992</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5063,7 +5063,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02967138990015516</v>
+        <v>0.02880910342347681</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5116,7 +5116,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04900701556039189</v>
+        <v>0.04837608562423524</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5169,7 +5169,7 @@
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.1007675883168235</v>
+        <v>0.09680353545512323</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5222,7 +5222,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.0214252452124615</v>
+        <v>0.02106227091511688</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5275,7 +5275,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007635530491459991</v>
+        <v>0.007531774818673483</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5322,25 +5322,25 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02077527171622906</v>
+        <v>0.02118403623397195</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>46024</v>
+        <v>46114</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>46481</v>
+        <v>46480</v>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03326092504050905</v>
+        <v>0.03602783048703352</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5434,7 +5434,7 @@
         <v>3.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01634988749254875</v>
+        <v>0.01618941586923297</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46035</v>
@@ -5487,7 +5487,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01829616881390908</v>
+        <v>0.01938806446195164</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5540,7 +5540,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04632565912794535</v>
+        <v>0.04515521885010952</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5593,7 +5593,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02327378459090542</v>
+        <v>0.02220680106790347</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5646,7 +5646,7 @@
         <v>6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01724782270450997</v>
+        <v>0.0172314755590317</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46038</v>
@@ -5699,7 +5699,7 @@
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02851809941441286</v>
+        <v>0.02894409937888199</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5752,7 +5752,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.0146463000754747</v>
+        <v>0.01372656238853958</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5805,7 +5805,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05067012721677747</v>
+        <v>0.05307971032833607</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5858,10 +5858,10 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02918668873610638</v>
+        <v>0.02911802652356768</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>46024</v>
+        <v>46113</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>0.02499999999999988</v>
@@ -5911,7 +5911,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01577348219982237</v>
+        <v>0.01528008289635777</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5964,7 +5964,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02150270835143434</v>
+        <v>0.02139433526031882</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6017,7 +6017,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02104414080461985</v>
+        <v>0.02029289318332066</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46028</v>
@@ -6070,7 +6070,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02049244854572341</v>
+        <v>0.0195944584037564</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6123,10 +6123,10 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01275659546945501</v>
+        <v>0.01301965272377644</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>0.05333333333333338</v>
@@ -6176,7 +6176,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03263617685080991</v>
+        <v>0.03260661162396298</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6229,7 +6229,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.0361990943977892</v>
+        <v>0.03831570498132009</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6282,7 +6282,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.01011349878049246</v>
+        <v>0.009770500924087532</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6335,7 +6335,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03850409499617897</v>
+        <v>0.038431804337001</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46036</v>
@@ -6388,7 +6388,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03174603183979984</v>
+        <v>0.03746858539749241</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6435,22 +6435,22 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.584</v>
+        <v>1.275</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>1.168</v>
+        <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.03309719381407237</v>
+        <v>0.06854838569090677</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>45887</v>
+        <v>46111</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>1.142300194931774</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>46419</v>
+        <v>46422</v>
       </c>
       <c r="L35" s="10" t="n">
         <v>46472</v>
@@ -6488,19 +6488,19 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="G36" s="24" t="n">
-        <v>3.24</v>
+        <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05277732582200233</v>
+        <v>0.05231660244502703</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>46080</v>
+        <v>46112</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.003717472118959111</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="K36" s="10" t="n">
         <v>46461</v>
@@ -6547,7 +6547,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04682926829268293</v>
+        <v>0.04695652173913044</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6600,7 +6600,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03653519090405939</v>
+        <v>0.03651761197349492</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6653,7 +6653,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06281177656172118</v>
+        <v>0.06112295797109072</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6706,7 +6706,7 @@
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03650051405080914</v>
+        <v>0.03542370102874154</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6759,7 +6759,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02939990314843966</v>
+        <v>0.02946546684884909</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6812,7 +6812,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.0402723172224527</v>
+        <v>0.03943291630609523</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46104</v>
@@ -6865,7 +6865,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02688399565783459</v>
+        <v>0.02905015235229855</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6918,7 +6918,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01864755074222239</v>
+        <v>0.0182053974002074</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6971,7 +6971,7 @@
         <v>3.72</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.01864755074222239</v>
+        <v>0.0182053974002074</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46070</v>
@@ -7024,7 +7024,7 @@
         <v>9.76</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02719988759972165</v>
+        <v>0.02673633489571878</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46077</v>
@@ -7077,7 +7077,7 @@
         <v>3.32</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04879482591603472</v>
+        <v>0.04888823179157632</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46091</v>
@@ -7130,7 +7130,7 @@
         <v>5.2</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.0581557898200166</v>
+        <v>0.05781632042302506</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46097</v>
@@ -7177,16 +7177,16 @@
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.994</v>
+        <v>0.974</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>3.976</v>
+        <v>3.896</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.0429535990399483</v>
+        <v>0.04255365613034411</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>45930</v>
+        <v>46112</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>0.2021660649819495</v>
@@ -7236,7 +7236,7 @@
         <v>5.68</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.02987833617940912</v>
+        <v>0.02878279634676914</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46052</v>
@@ -7289,7 +7289,7 @@
         <v>2.22</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03716103009083437</v>
+        <v>0.03963578051289666</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7342,7 +7342,7 @@
         <v>5.52</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02292834890965732</v>
+        <v>0.02260395961839812</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46080</v>
@@ -7395,7 +7395,7 @@
         <v>6.56</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06847598946793178</v>
+        <v>0.06725790489254314</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46070</v>
@@ -7448,7 +7448,7 @@
         <v>2.76</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.05448429504518887</v>
+        <v>0.05561152409027773</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46034</v>
@@ -7501,7 +7501,7 @@
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02356574933849925</v>
+        <v>0.02562587564240667</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7524,4 +7524,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD01F46B-E70E-4E75-9A21-05C9862856AE}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{844DA483-6868-46EE-8DEC-2DB25D264EF2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6A27D70-83F6-4C97-9F74-EA5E31419677}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/06/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/13/2026</t>
         </is>
       </c>
     </row>
@@ -637,12 +637,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -651,25 +651,25 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.057</v>
+        <v>0.976</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1.007</v>
+        <v>0.884</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.1040723981900452</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>46132</v>
+        <v>46503</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.02946546684884909</v>
+        <v>0.01865443435957342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.976</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.884</v>
+        <v>1.24</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46503</v>
+        <v>46165</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0195944584037564</v>
+        <v>0.02185149377369338</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -743,25 +743,25 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46165</v>
+        <v>46161</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02139433526031882</v>
+        <v>0.03194646949561728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -785,29 +785,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.27</v>
+        <v>0.974</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.2</v>
+        <v>0.831</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46161</v>
+        <v>46190</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02905015235229855</v>
+        <v>0.04196240991734994</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -831,29 +831,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.974</v>
+        <v>1.08</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.831</v>
+        <v>0.98</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46190</v>
+        <v>46152</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.04255365613034411</v>
+        <v>0.04968943959843446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -877,129 +877,129 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G11" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>46162</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>46198</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>0.03271512590566655</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>46176</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="J12" s="19" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="n">
+        <v>0.03939592886178251</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H11" s="10" t="n">
-        <v>46143</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>46152</v>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>0.04695652173913044</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0.0142857142857143</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>0.03260661162396298</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="n">
-        <v>0.03943291630609523</v>
+      <c r="H13" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>0.01848906588679996</v>
       </c>
     </row>
     <row r="14">
@@ -1034,7 +1034,7 @@
         <v>46218</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46248</v>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.0182053974002074</v>
+        <v>0.01848906588679996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.89</v>
+        <v>1.34</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.0182053974002074</v>
+        <v>0.02218025518665177</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1107,29 +1107,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>102</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02260395961839812</v>
+        <v>0.04672765457281513</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1153,29 +1153,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.04888823179157632</v>
+        <v>0.02825058339894573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1203,25 +1203,25 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>46232</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46264</v>
+        <v>46246</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.02880910342347681</v>
+        <v>0.0478315725534199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1245,29 +1245,29 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46246</v>
+        <v>46297</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.04837608562423524</v>
+        <v>0.02897526579881178</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1291,29 +1291,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46263</v>
+        <v>46278</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46297</v>
+        <v>46344</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02911802652356768</v>
+        <v>0.009670434802419548</v>
       </c>
     </row>
     <row r="21">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>0.678</v>
-      </c>
       <c r="F21" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0.02</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46303</v>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.05561152409027773</v>
+        <v>0.06217343682622542</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1383,29 +1383,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.83</v>
+        <v>1.36</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>160</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46344</v>
+        <v>46325</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.009770500924087532</v>
+        <v>0.02667981815454341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1429,29 +1429,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46285</v>
+        <v>46305</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02878279634676914</v>
+        <v>0.03675538644680129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1475,29 +1475,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.038431804337001</v>
+        <v>0.01232749822106043</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1521,29 +1521,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1551,13 +1551,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01301965272377644</v>
+        <v>0.01385055422704897</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1571,25 +1571,25 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01372656238853958</v>
+        <v>0.02218755469700068</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1617,19 +1617,19 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>204</v>
@@ -1643,13 +1643,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02220680106790347</v>
+        <v>0.007491221225126805</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1663,25 +1663,25 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.007531774818673483</v>
+        <v>0.02590989921883621</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1709,25 +1709,25 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02673633489571878</v>
+        <v>0.02700931022247884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1751,29 +1751,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02562587564240667</v>
+        <v>0.0358075352153408</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1801,25 +1801,25 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.03831570498132009</v>
+        <v>0.03857253431942761</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1843,29 +1843,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03746858539749241</v>
+        <v>0.05740876548815603</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1889,29 +1889,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05307971032833607</v>
+        <v>0.0459675756739481</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1935,29 +1935,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.04515521885010952</v>
+        <v>0.02871058732843804</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1981,29 +1981,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2.52</v>
+        <v>0.43</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>2.38</v>
+        <v>0.42</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46366</v>
+        <v>46370</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46432</v>
+        <v>46413</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.02915401301518438</v>
+        <v>0.0636094653019155</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2027,29 +2027,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46413</v>
+        <v>46344</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.06112295797109072</v>
+        <v>0.02132591592527367</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2073,29 +2073,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46371</v>
+        <v>46402</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46344</v>
+        <v>46483</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.02106227091511688</v>
+        <v>0.01787337991559126</v>
       </c>
     </row>
     <row r="38">
@@ -2138,7 +2138,7 @@
         <v>46411</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46435</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.03977650487500992</v>
+        <v>0.0385179111813246</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2165,29 +2165,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.8</v>
+        <v>1.78</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2195,45 +2195,45 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.01618941586923297</v>
+        <v>0.03739692222714045</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.78</v>
+        <v>1.275</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46417</v>
+        <v>46422</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2241,45 +2241,45 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03602783048703352</v>
+        <v>0.06807261244854079</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.275</v>
+        <v>1.64</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.584</v>
+        <v>1.63</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46422</v>
+        <v>46423</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46472</v>
+        <v>46435</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.06854838569090677</v>
+        <v>0.06562625110126678</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2303,29 +2303,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.64</v>
+        <v>0.61</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1.63</v>
+        <v>0.58</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46423</v>
+        <v>46428</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46435</v>
+        <v>46452</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.06725790489254314</v>
+        <v>0.01639895228241406</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0.08</v>
@@ -2368,10 +2368,10 @@
         <v>46428</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01528008289635777</v>
+        <v>0.05675616507437827</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2395,29 +2395,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2425,45 +2425,45 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.05781632042302506</v>
+        <v>0.02058823567910728</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.42</v>
+        <v>1.883</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0.41</v>
+        <v>1.864</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46480</v>
+        <v>46425</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2471,45 +2471,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.02118403623397195</v>
+        <v>0.00257071872298131</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.883</v>
+        <v>7.45</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.864</v>
+        <v>1.25</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>4.96</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.002892672996696654</v>
+        <v>0.1000738804559087</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>7.45</v>
+        <v>0.24</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.25</v>
+        <v>0.22</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>4.96</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0.06</v>
@@ -2552,10 +2552,10 @@
         <v>46433</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46383</v>
+        <v>46276</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.09680353545512323</v>
+        <v>0.02007108432466542</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2579,17 +2579,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.24</v>
+        <v>1.423</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.22</v>
+        <v>1.355</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0.06</v>
@@ -2598,10 +2598,10 @@
         <v>46433</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46276</v>
+        <v>46177</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.01938806446195164</v>
+        <v>0.03648951727390919</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2625,29 +2625,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.423</v>
+        <v>0.8</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.355</v>
+        <v>0.79</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46177</v>
+        <v>46270</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03651761197349492</v>
+        <v>0.03491162854189175</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2671,29 +2671,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.8</v>
+        <v>0.555</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.79</v>
+        <v>0.588964</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2701,13 +2701,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03542370102874154</v>
+        <v>0.03825607524899725</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2717,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.555</v>
+        <v>0.29</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="I51" s="13" t="n">
         <v>315</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03963578051289666</v>
+        <v>0.009040252331598577</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2767,25 +2767,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.009962640308522799</v>
+        <v>0.02796489436856701</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2809,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46441</v>
+        <v>46452</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02894409937888199</v>
+        <v>0.01881768090793178</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2855,29 +2855,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.05633802816901413</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46451</v>
+        <v>46461</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2885,45 +2885,45 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.0172314755590317</v>
+        <v>0.01950236473909606</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H55" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46300</v>
+        <v>46196</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2931,45 +2931,45 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.02029289318332066</v>
+        <v>0.05132170620781536</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.271</v>
+        <v>1.057</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.27</v>
+        <v>1.007</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.04965243296921554</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46461</v>
+        <v>46487</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46196</v>
+        <v>46497</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.05231660244502703</v>
+        <v>0.02922311455651426</v>
       </c>
     </row>
   </sheetData>
@@ -2991,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3012,7 +3012,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 04/06/2026</t>
+          <t>Expected Increase Announcements by Month - 04/13/2026</t>
         </is>
       </c>
     </row>
@@ -3058,20 +3058,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46132</v>
+        <v>46503</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1.057</v>
+        <v>0.976</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.1040723981900452</v>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
@@ -3082,20 +3082,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>46503</v>
+        <v>46165</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.976</v>
+        <v>1.3</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
@@ -3106,20 +3106,20 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>46128</v>
+        <v>46134</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>46165</v>
+        <v>46161</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
@@ -3130,20 +3130,20 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>46134</v>
+        <v>46140</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>46161</v>
+        <v>46190</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.27</v>
+        <v>0.974</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
@@ -3151,86 +3151,86 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>46190</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.2021660649819495</v>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>May 2026</t>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.1020408163265307</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46152</v>
+        <v>46198</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3238,129 +3238,129 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.0142857142857143</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>June 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>June 2026</t>
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
-        <is>
-          <t>July 2026</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -3391,20 +3391,20 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
@@ -3415,20 +3415,20 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
@@ -3439,20 +3439,20 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -3463,20 +3463,20 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
         <v>46232</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46264</v>
+        <v>46246</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -3484,129 +3484,129 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>46297</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -3617,16 +3617,16 @@
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="C36" s="10" t="n">
         <v>46303</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3637,20 +3637,20 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46344</v>
+        <v>46325</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3658,86 +3658,86 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.0235294117647059</v>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -3748,20 +3748,20 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3772,20 +3772,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3793,86 +3793,86 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C45" s="10" t="n">
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C48" s="10" t="n">
         <v>46338</v>
       </c>
-      <c r="D45" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="D48" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -3883,20 +3883,20 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="C50" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
@@ -3907,20 +3907,20 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -3931,20 +3931,20 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
@@ -3955,20 +3955,20 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -3976,86 +3976,86 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>HRL</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>46400</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.01034482758620691</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E57" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F57" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4066,20 +4066,20 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>46366</v>
+        <v>46370</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46432</v>
+        <v>46413</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>2.52</v>
+        <v>0.43</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4090,20 +4090,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46413</v>
+        <v>46344</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4111,66 +4111,66 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>January 2027</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E63" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D64" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E64" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -4201,20 +4201,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
-        <v>46416</v>
+        <v>46417</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.8</v>
+        <v>1.78</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4222,86 +4222,86 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C67" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D67" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E67" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E69" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B70" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C70" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D70" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>46422</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>46472</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>1.183219178082192</v>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46422</v>
+        <v>46423</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46472</v>
+        <v>46435</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1.275</v>
+        <v>1.64</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4312,20 +4312,20 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B72" s="10" t="n">
-        <v>46423</v>
+        <v>46428</v>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46435</v>
+        <v>46452</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>1.64</v>
+        <v>0.61</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
@@ -4336,20 +4336,20 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
         <v>46428</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4360,20 +4360,20 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B74" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
@@ -4384,20 +4384,20 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46480</v>
+        <v>46425</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0.42</v>
+        <v>1.883</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4408,20 +4408,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1.883</v>
+        <v>7.45</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>4.96</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4432,20 +4432,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46383</v>
+        <v>46276</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>7.45</v>
+        <v>0.24</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>4.96</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4456,20 +4456,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46276</v>
+        <v>46177</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0.24</v>
+        <v>1.423</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4480,20 +4480,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46177</v>
+        <v>46270</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.423</v>
+        <v>0.8</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4504,20 +4504,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.8</v>
+        <v>0.555</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4528,20 +4528,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.555</v>
+        <v>0.29</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4552,20 +4552,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4573,86 +4573,86 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E85" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B86" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C86" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D86" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E86" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F86" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B87" s="10" t="n">
-        <v>46451</v>
+        <v>46461</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.05633802816901413</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -4663,20 +4663,20 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46300</v>
+        <v>46196</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4684,25 +4684,64 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>46196</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E91" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>46497</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.04965243296921554</v>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4747,7 +4786,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 04/06/2026</t>
+          <t>Complete Holdings Dividend Summary - 04/13/2026</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4890,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009962640308522799</v>
+        <v>0.009040252331598577</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4904,7 +4943,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02915401301518438</v>
+        <v>0.02871058732843804</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4957,7 +4996,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002892672996696654</v>
+        <v>0.00257071872298131</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5010,7 +5049,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03977650487500992</v>
+        <v>0.0385179111813246</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5063,7 +5102,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02880910342347681</v>
+        <v>0.02825058339894573</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5116,7 +5155,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04837608562423524</v>
+        <v>0.0478315725534199</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5169,7 +5208,7 @@
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.09680353545512323</v>
+        <v>0.1000738804559087</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5222,7 +5261,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02106227091511688</v>
+        <v>0.02132591592527367</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5275,7 +5314,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007531774818673483</v>
+        <v>0.007491221225126805</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5328,7 +5367,7 @@
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02118403623397195</v>
+        <v>0.02058823567910728</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5381,7 +5420,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03602783048703352</v>
+        <v>0.03739692222714045</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5428,22 +5467,22 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01618941586923297</v>
+        <v>0.01787337991559126</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.06666666666666672</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>46416</v>
+        <v>46402</v>
       </c>
       <c r="L16" s="10" t="n">
         <v>46483</v>
@@ -5487,7 +5526,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01938806446195164</v>
+        <v>0.02007108432466542</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5540,7 +5579,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04515521885010952</v>
+        <v>0.0459675756739481</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5593,7 +5632,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02220680106790347</v>
+        <v>0.02218755469700068</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5640,22 +5679,22 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>6</v>
+        <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0172314755590317</v>
+        <v>0.01881768090793178</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>46038</v>
+        <v>46122</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.05633802816901413</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>46451</v>
+        <v>46452</v>
       </c>
       <c r="L20" s="10" t="n">
         <v>46487</v>
@@ -5699,7 +5738,7 @@
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02894409937888199</v>
+        <v>0.02796489436856701</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5752,7 +5791,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01372656238853958</v>
+        <v>0.01385055422704897</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5805,7 +5844,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05307971032833607</v>
+        <v>0.05740876548815603</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46034</v>
@@ -5858,7 +5897,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02911802652356768</v>
+        <v>0.02897526579881178</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5911,7 +5950,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01528008289635777</v>
+        <v>0.01639895228241406</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5964,7 +6003,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02139433526031882</v>
+        <v>0.02185149377369338</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6017,10 +6056,10 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02029289318332066</v>
+        <v>0.01950236473909606</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>46028</v>
+        <v>46118</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>0.07142857142857149</v>
@@ -6070,7 +6109,7 @@
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.0195944584037564</v>
+        <v>0.01865443435957342</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6123,7 +6162,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01301965272377644</v>
+        <v>0.01232749822106043</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6176,7 +6215,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03260661162396298</v>
+        <v>0.03271512590566655</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6229,7 +6268,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.03831570498132009</v>
+        <v>0.0358075352153408</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6282,7 +6321,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.009770500924087532</v>
+        <v>0.009670434802419548</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6335,10 +6374,10 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.038431804337001</v>
+        <v>0.03675538644680129</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>46036</v>
+        <v>46120</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0.0235294117647059</v>
@@ -6388,7 +6427,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03746858539749241</v>
+        <v>0.03857253431942761</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6441,7 +6480,7 @@
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.06854838569090677</v>
+        <v>0.06807261244854079</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6494,7 +6533,7 @@
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05231660244502703</v>
+        <v>0.05132170620781536</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46112</v>
@@ -6547,7 +6586,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04695652173913044</v>
+        <v>0.04968943959843446</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6600,7 +6639,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03651761197349492</v>
+        <v>0.03648951727390919</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6653,7 +6692,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06112295797109072</v>
+        <v>0.0636094653019155</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6706,7 +6745,7 @@
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03542370102874154</v>
+        <v>0.03491162854189175</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6759,7 +6798,7 @@
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02946546684884909</v>
+        <v>0.02922311455651426</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6768,10 +6807,10 @@
         <v>0.04965243296921554</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>46122</v>
+        <v>46487</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>46132</v>
+        <v>46497</v>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
@@ -6812,7 +6851,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0.03943291630609523</v>
+        <v>0.03939592886178251</v>
       </c>
       <c r="I42" s="19" t="n">
         <v>46104</v>
@@ -6865,7 +6904,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02905015235229855</v>
+        <v>0.03194646949561728</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6918,7 +6957,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0182053974002074</v>
+        <v>0.01848906588679996</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6971,7 +7010,7 @@
         <v>3.72</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.0182053974002074</v>
+        <v>0.01848906588679996</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46070</v>
@@ -7024,7 +7063,7 @@
         <v>9.76</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02673633489571878</v>
+        <v>0.02590989921883621</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46077</v>
@@ -7077,7 +7116,7 @@
         <v>3.32</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04888823179157632</v>
+        <v>0.04672765457281513</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46091</v>
@@ -7130,7 +7169,7 @@
         <v>5.2</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05781632042302506</v>
+        <v>0.05675616507437827</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46097</v>
@@ -7183,7 +7222,7 @@
         <v>3.896</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04255365613034411</v>
+        <v>0.04196240991734994</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46112</v>
@@ -7236,7 +7275,7 @@
         <v>5.68</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.02878279634676914</v>
+        <v>0.02667981815454341</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46052</v>
@@ -7289,7 +7328,7 @@
         <v>2.22</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03963578051289666</v>
+        <v>0.03825607524899725</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7342,7 +7381,7 @@
         <v>5.52</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02260395961839812</v>
+        <v>0.02218025518665177</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46080</v>
@@ -7395,7 +7434,7 @@
         <v>6.56</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06725790489254314</v>
+        <v>0.06562625110126678</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46070</v>
@@ -7442,22 +7481,22 @@
         </is>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="G54" s="24" t="n">
-        <v>2.76</v>
+        <v>2.832</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.05561152409027773</v>
+        <v>0.06217343682622542</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>46034</v>
+        <v>46122</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.01769911504424764</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="L54" s="10" t="n">
         <v>46303</v>
@@ -7501,7 +7540,7 @@
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02562587564240667</v>
+        <v>0.02700931022247884</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46065</v>
@@ -7524,252 +7563,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD01F46B-E70E-4E75-9A21-05C9862856AE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{844DA483-6868-46EE-8DEC-2DB25D264EF2}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6A27D70-83F6-4C97-9F74-EA5E31419677}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,13 +73,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00856404"/>
+      <color rgb="00dc3545"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="00666666"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -94,7 +100,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -108,12 +114,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +163,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -165,8 +179,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -561,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/13/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/20/2026</t>
         </is>
       </c>
     </row>
@@ -663,10 +677,10 @@
         <v>0.06</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46127</v>
+        <v>46054</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>2</v>
+        <v>-78</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46503</v>
@@ -677,13 +691,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.01865443435957342</v>
+        <v>0.01896066107686591</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -693,29 +707,29 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46128</v>
+        <v>46058</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>3</v>
+        <v>-74</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46165</v>
+        <v>46435</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -723,13 +737,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.02185149377369338</v>
+        <v>0.06164254945377635</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -739,29 +753,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.27</v>
+        <v>1.057</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.2</v>
+        <v>1.007</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04965243296921554</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46134</v>
+        <v>46122</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46161</v>
+        <v>46497</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -769,13 +783,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.03194646949561728</v>
+        <v>0.02906241493104229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -785,29 +799,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.974</v>
+        <v>1.3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.831</v>
+        <v>1.24</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46140</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>15</v>
+        <v>46128</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>-4</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46190</v>
+        <v>46530</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -815,13 +829,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.04196240991734994</v>
+        <v>0.02234636900814657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -835,25 +849,25 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.98</v>
+        <v>1.2</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46152</v>
+        <v>46161</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -861,13 +875,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.04968943959843446</v>
+        <v>0.03266671069026816</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -881,25 +895,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.71</v>
+        <v>0.974</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.7</v>
+        <v>0.831</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46162</v>
+        <v>46140</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46198</v>
+        <v>46190</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -907,59 +921,59 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.03271512590566655</v>
+        <v>0.04455117365305194</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L12" s="18" t="n">
-        <v>0.03939592886178251</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.1020408163265307</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>46152</v>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>0.04656426762542244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -969,29 +983,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.93</v>
+        <v>0.71</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>93</v>
+        <v>46162</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46248</v>
+        <v>46198</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -999,59 +1013,59 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.01848906588679996</v>
+        <v>0.03266996422443251</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>93</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>46248</v>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>0.01848906588679996</v>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>46176</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>0.04010312102908895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1065,25 +1079,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.38</v>
+        <v>0.93</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.34</v>
+        <v>0.89</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>95</v>
+        <v>46218</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>86</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46264</v>
+        <v>46248</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1091,13 +1105,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.02218025518665177</v>
+        <v>0.01761655633402893</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1107,29 +1121,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>102</v>
+        <v>46218</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>86</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1137,13 +1151,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.04672765457281513</v>
+        <v>0.01761655633402893</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1157,22 +1171,22 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.95</v>
+        <v>1.34</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>107</v>
+        <v>46220</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>88</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46264</v>
@@ -1183,13 +1197,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02825058339894573</v>
+        <v>0.02200781372621784</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1199,29 +1213,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.24</v>
+        <v>0.83</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1.22</v>
+        <v>0.82</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>107</v>
+        <v>46227</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>95</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46246</v>
+        <v>46267</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1229,13 +1243,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.0478315725534199</v>
+        <v>0.04531804399659041</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1245,29 +1259,29 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>138</v>
+        <v>46232</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46297</v>
+        <v>46264</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1275,13 +1289,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02897526579881178</v>
+        <v>0.02772579109685063</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1291,29 +1305,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.91</v>
+        <v>1.24</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>153</v>
+        <v>46232</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46344</v>
+        <v>46246</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1321,13 +1335,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.009670434802419548</v>
+        <v>0.04882370488037944</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1341,25 +1355,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.708</v>
+        <v>0.82</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>155</v>
+        <v>46263</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>131</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1367,13 +1381,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.06217343682622542</v>
+        <v>0.028482110938654</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1383,29 +1397,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.42</v>
+        <v>0.91</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1.36</v>
+        <v>0.83</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>160</v>
+        <v>46278</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>146</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46325</v>
+        <v>46344</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1413,13 +1427,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02667981815454341</v>
+        <v>0.008636644221988921</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1429,29 +1443,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.87</v>
+        <v>0.708</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>180</v>
+        <v>46280</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>148</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46339</v>
+        <v>46303</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1459,13 +1473,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03675538644680129</v>
+        <v>0.06077905195421872</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1475,29 +1489,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.79</v>
+        <v>1.42</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.75</v>
+        <v>1.36</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>186</v>
+        <v>46285</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>153</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46386</v>
+        <v>46325</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1505,13 +1519,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.01232749822106043</v>
+        <v>0.02450176783946032</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1525,25 +1539,25 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1.38</v>
+        <v>0.87</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>192</v>
+        <v>46305</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>173</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46351</v>
+        <v>46339</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1551,13 +1565,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.01385055422704897</v>
+        <v>0.03609583930933605</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1567,29 +1581,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I26" s="13" t="n">
-        <v>197</v>
+        <v>46311</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>179</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46338</v>
+        <v>46386</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1597,13 +1611,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.02218755469700068</v>
+        <v>0.01214777203969057</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1617,25 +1631,25 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.6</v>
+        <v>1.38</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.55</v>
+        <v>1.35</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I27" s="13" t="n">
-        <v>204</v>
+        <v>46317</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>185</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46338</v>
+        <v>46351</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1643,13 +1657,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.007491221225126805</v>
+        <v>0.01400091275623278</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1663,25 +1677,25 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2.44</v>
+        <v>0.64</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2.14</v>
+        <v>0.6</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>207</v>
+        <v>46322</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>190</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46346</v>
+        <v>46338</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1689,13 +1703,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02590989921883621</v>
+        <v>0.02227539640653369</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1709,25 +1723,25 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>216</v>
+        <v>46329</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>197</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1735,13 +1749,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02700931022247884</v>
+        <v>0.007368743966992668</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1751,29 +1765,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.48</v>
+        <v>2.44</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.45</v>
+        <v>2.14</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>219</v>
+        <v>46332</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>200</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46385</v>
+        <v>46346</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1781,13 +1795,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.0358075352153408</v>
+        <v>0.02567340042608691</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1797,29 +1811,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.41</v>
+        <v>1.03</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I31" s="13" t="n">
-        <v>222</v>
+        <v>46341</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>209</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46358</v>
+        <v>46339</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1827,13 +1841,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.03857253431942761</v>
+        <v>0.02780308444092603</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1843,29 +1857,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.293</v>
+        <v>0.48</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>227</v>
+        <v>46344</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>212</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46400</v>
+        <v>46385</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1873,13 +1887,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.05740876548815603</v>
+        <v>0.03616159630581837</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1893,25 +1907,25 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>235</v>
+        <v>46347</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>215</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46371</v>
+        <v>46358</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1919,13 +1933,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0459675756739481</v>
+        <v>0.0357805177868014</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1935,29 +1949,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2.52</v>
+        <v>0.293</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>2.38</v>
+        <v>0.29</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>241</v>
+        <v>46352</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>220</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46432</v>
+        <v>46400</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1965,13 +1979,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.02871058732843804</v>
+        <v>0.05489461260231227</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1981,29 +1995,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="I35" s="13" t="n">
-        <v>245</v>
+        <v>46360</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>228</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46413</v>
+        <v>46371</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2011,13 +2025,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0636094653019155</v>
+        <v>0.04560879711568076</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2027,29 +2041,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.23</v>
+        <v>2.52</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.22</v>
+        <v>2.38</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>246</v>
+        <v>46366</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>234</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46344</v>
+        <v>46432</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2057,13 +2071,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02132591592527367</v>
+        <v>0.02857547838412473</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2073,29 +2087,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I37" s="13" t="n">
-        <v>277</v>
+        <v>46370</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>238</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46483</v>
+        <v>46413</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2103,13 +2117,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01787337991559126</v>
+        <v>0.06222865549860192</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2119,29 +2133,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.703</v>
+        <v>0.23</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.676</v>
+        <v>0.22</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>286</v>
+        <v>46371</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>239</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46435</v>
+        <v>46344</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2149,13 +2163,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.0385179111813246</v>
+        <v>0.0213754642293257</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2165,29 +2179,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.78</v>
+        <v>0.86</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.71</v>
+        <v>0.8</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I39" s="13" t="n">
-        <v>292</v>
+        <v>46402</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>270</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46433</v>
+        <v>46483</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2195,45 +2209,45 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.03739692222714045</v>
+        <v>0.01763469457548388</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.275</v>
+        <v>0.703</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.584</v>
+        <v>0.676</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>297</v>
+        <v>46411</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>279</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46472</v>
+        <v>46435</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2241,13 +2255,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.06807261244854079</v>
+        <v>0.03685693777425871</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2261,25 +2275,25 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46423</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>298</v>
+        <v>46417</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>285</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2287,18 +2301,18 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.06562625110126678</v>
+        <v>0.03836415568100161</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2307,25 +2321,25 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.61</v>
+        <v>1.275</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.58</v>
+        <v>0.584</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>303</v>
+        <v>46422</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>290</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46452</v>
+        <v>46472</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2333,13 +2347,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.01639895228241406</v>
+        <v>0.06297851060243667</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2353,13 +2367,13 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>1.27</v>
+        <v>0.58</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0.08</v>
@@ -2367,11 +2381,11 @@
       <c r="H43" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I43" s="13" t="n">
-        <v>303</v>
+      <c r="I43" s="14" t="n">
+        <v>296</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46460</v>
+        <v>46452</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2379,13 +2393,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.05675616507437827</v>
+        <v>0.01572975810214969</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2395,29 +2409,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0.41</v>
+        <v>1.27</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>306</v>
+        <v>46428</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>296</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46480</v>
+        <v>46460</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2425,45 +2439,45 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02058823567910728</v>
+        <v>0.05335795908161366</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.883</v>
+        <v>0.42</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.864</v>
+        <v>0.41</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>308</v>
+        <v>46431</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>299</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46425</v>
+        <v>46480</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2471,45 +2485,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.00257071872298131</v>
+        <v>0.01933479125101876</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>7.45</v>
+        <v>1.883</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.25</v>
+        <v>1.864</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>4.96</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I46" s="13" t="n">
-        <v>308</v>
+      <c r="I46" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46383</v>
+        <v>46425</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2517,13 +2531,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.1000738804559087</v>
+        <v>0.002588209316692858</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2533,17 +2547,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.24</v>
+        <v>7.45</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.22</v>
+        <v>1.25</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>4.96</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0.06</v>
@@ -2551,11 +2565,11 @@
       <c r="H47" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I47" s="13" t="n">
-        <v>308</v>
+      <c r="I47" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46276</v>
+        <v>46383</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2563,13 +2577,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.02007108432466542</v>
+        <v>0.1030535623205178</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2579,17 +2593,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.423</v>
+        <v>0.24</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.355</v>
+        <v>0.22</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0.06</v>
@@ -2597,11 +2611,11 @@
       <c r="H48" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I48" s="13" t="n">
-        <v>308</v>
+      <c r="I48" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46177</v>
+        <v>46276</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2609,13 +2623,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03648951727390919</v>
+        <v>0.02127659624835675</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2625,29 +2639,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.8</v>
+        <v>1.423</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.79</v>
+        <v>1.355</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I49" s="13" t="n">
-        <v>308</v>
+      <c r="I49" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46270</v>
+        <v>46177</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2655,13 +2669,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03491162854189175</v>
+        <v>0.03625708516997186</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2671,29 +2685,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.555</v>
+        <v>0.8</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.79</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I50" s="13" t="n">
-        <v>308</v>
+      <c r="I50" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46243</v>
+        <v>46270</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2701,13 +2715,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03825607524899725</v>
+        <v>0.03317781338777243</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2731,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.29</v>
+        <v>0.555</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.27</v>
+        <v>0.588964</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>315</v>
+        <v>46433</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>301</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46450</v>
+        <v>46243</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2761,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.009040252331598577</v>
+        <v>0.03814426439293622</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2767,25 +2781,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2.33</v>
+        <v>0.29</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>2.3</v>
+        <v>0.27</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>316</v>
+        <v>46440</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>308</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46456</v>
+        <v>46450</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2807,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02796489436856701</v>
+        <v>0.009033213103202842</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2823,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>327</v>
+        <v>46441</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>309</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46487</v>
+        <v>46456</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,13 +2853,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.01881768090793178</v>
+        <v>0.02702937868968329</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2855,29 +2869,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E54" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="F54" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>336</v>
+        <v>46452</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>320</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46300</v>
+        <v>46487</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2885,45 +2899,45 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.01950236473909606</v>
+        <v>0.0189161857620277</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.271</v>
+        <v>1.5</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0.27</v>
+        <v>1.4</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H55" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I55" s="13" t="n">
-        <v>336</v>
+      <c r="I55" s="14" t="n">
+        <v>329</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46196</v>
+        <v>46300</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2931,45 +2945,45 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.05132170620781536</v>
+        <v>0.01909064824484362</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.057</v>
+        <v>0.271</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1.007</v>
+        <v>0.27</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="I56" s="13" t="n">
-        <v>362</v>
+        <v>46461</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>329</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46497</v>
+        <v>46196</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2977,7 +2991,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.02922311455651426</v>
+        <v>0.04995775311493071</v>
       </c>
     </row>
   </sheetData>
@@ -3012,44 +3026,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 04/13/2026</t>
+          <t>Expected Increase Announcements by Month - 04/20/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>April 2026</t>
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>February 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3062,7 +3076,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46127</v>
+        <v>46054</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>46503</v>
@@ -3082,131 +3096,131 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.00613496932515338</v>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>46122</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>46497</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.04965243296921554</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>JNJ</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B12" s="10" t="n">
         <v>46128</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>46165</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="C12" s="10" t="n">
+        <v>46530</v>
+      </c>
+      <c r="D12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E12" s="8" t="n">
         <v>0.04838709677419359</v>
       </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>46134</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TTE</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>46140</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>46190</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.2021660649819495</v>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46143</v>
+        <v>46134</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46152</v>
+        <v>46161</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -3217,266 +3231,233 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.2021660649819495</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>46143</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>46152</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.1020408163265307</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>MDT</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B19" s="10" t="n">
         <v>46162</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C19" s="10" t="n">
         <v>46198</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D19" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E19" s="8" t="n">
         <v>0.0142857142857143</v>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>June 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>46176</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>July 2026</t>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.05263157894736847</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -3484,62 +3465,95 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46263</v>
+        <v>46232</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46297</v>
+        <v>46264</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
@@ -3547,86 +3561,86 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>CLX</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.01639344262295083</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46280</v>
+        <v>46263</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.708</v>
+        <v>0.82</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3634,86 +3648,86 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>46305</v>
+        <v>46280</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>46339</v>
+        <v>46303</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.87</v>
+        <v>0.708</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
@@ -3724,131 +3738,131 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.0235294117647059</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>LECO</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B47" s="10" t="n">
         <v>46311</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C47" s="10" t="n">
         <v>46386</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D47" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E47" s="8" t="n">
         <v>0.05333333333333338</v>
       </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0.02222222222222208</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>46338</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>46329</v>
+        <v>46317</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46338</v>
+        <v>46351</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.6</v>
+        <v>1.38</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -3859,20 +3873,20 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46332</v>
+        <v>46322</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46346</v>
+        <v>46338</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2.44</v>
+        <v>0.64</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -3880,95 +3894,62 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>November 2026</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>46358</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46352</v>
+        <v>46329</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46400</v>
+        <v>46338</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.293</v>
+        <v>0.6</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -3976,62 +3957,95 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.1401869158878504</v>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C56" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D56" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E56" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>46360</v>
+        <v>46347</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46371</v>
+        <v>46358</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -4042,131 +4056,131 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>HRL</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>46400</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.01034482758620691</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>December 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B63" s="10" t="n">
         <v>46366</v>
       </c>
-      <c r="C58" s="10" t="n">
+      <c r="C63" s="10" t="n">
         <v>46432</v>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D63" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="E58" s="8" t="n">
+      <c r="E63" s="8" t="n">
         <v>0.05882352941176476</v>
       </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>46413</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E59" s="8" t="n">
-        <v>0.02380952380952383</v>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46402</v>
+        <v>46370</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46483</v>
+        <v>46413</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4177,20 +4191,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46411</v>
+        <v>46371</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46435</v>
+        <v>46344</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.703</v>
+        <v>0.23</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4198,86 +4212,86 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>January 2027</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B69" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C69" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D69" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E69" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B70" s="10" t="n">
-        <v>46422</v>
+        <v>46411</v>
       </c>
       <c r="C70" s="10" t="n">
-        <v>46472</v>
+        <v>46435</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>1.275</v>
+        <v>0.703</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
@@ -4288,20 +4302,20 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46423</v>
+        <v>46417</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4309,95 +4323,62 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.05172413793103453</v>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C73" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>46480</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.02439024390243905</v>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46433</v>
+        <v>46422</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46425</v>
+        <v>46472</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1.883</v>
+        <v>1.275</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4408,20 +4389,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46433</v>
+        <v>46428</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46383</v>
+        <v>46452</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>7.45</v>
+        <v>0.61</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>4.96</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4432,20 +4413,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46433</v>
+        <v>46428</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46276</v>
+        <v>46460</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.24</v>
+        <v>1.3</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4456,20 +4437,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46433</v>
+        <v>46431</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46177</v>
+        <v>46480</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1.423</v>
+        <v>0.42</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4480,20 +4461,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46270</v>
+        <v>46425</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.8</v>
+        <v>1.883</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4504,20 +4485,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46243</v>
+        <v>46383</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.555</v>
+        <v>7.45</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>4.96</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4528,20 +4509,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46440</v>
+        <v>46433</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46450</v>
+        <v>46276</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4552,20 +4533,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46441</v>
+        <v>46433</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46456</v>
+        <v>46177</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>2.33</v>
+        <v>1.423</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4573,173 +4554,206 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.01265822784810128</v>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="84">
-      <c r="A84" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>UL</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.005735494868956323</v>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B85" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C85" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D85" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E85" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F85" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n">
+        <v>46440</v>
+      </c>
+      <c r="C85" s="10" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.07407407407407393</v>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>46441</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>46456</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.01304347826086967</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n">
+      <c r="B90" s="10" t="n">
         <v>46452</v>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C90" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="D86" s="7" t="n">
+      <c r="D90" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E90" s="8" t="n">
         <v>0.06000000000000005</v>
       </c>
-      <c r="F86" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="B87" s="10" t="n">
+      <c r="B91" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="C87" s="10" t="n">
+      <c r="C91" s="10" t="n">
         <v>46300</v>
       </c>
-      <c r="D87" s="7" t="n">
+      <c r="D91" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E91" s="8" t="n">
         <v>0.07142857142857149</v>
       </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>46196</v>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="F88" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="22" t="inlineStr">
-        <is>
-          <t>April 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E91" s="23" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F91" s="23" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B92" s="10" t="n">
-        <v>46487</v>
+        <v>46461</v>
       </c>
       <c r="C92" s="10" t="n">
-        <v>46497</v>
+        <v>46196</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>1.057</v>
+        <v>0.271</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
@@ -4786,7 +4800,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 04/13/2026</t>
+          <t>Complete Holdings Dividend Summary - 04/20/2026</t>
         </is>
       </c>
     </row>
@@ -4886,11 +4900,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="25" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009040252331598577</v>
+        <v>0.009033213103202842</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4939,11 +4953,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="25" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02871058732843804</v>
+        <v>0.02857547838412473</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4992,11 +5006,11 @@
       <c r="F7" s="7" t="n">
         <v>1.883</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="25" t="n">
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.00257071872298131</v>
+        <v>0.002588209316692858</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5045,11 +5059,11 @@
       <c r="F8" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="25" t="n">
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.0385179111813246</v>
+        <v>0.03685693777425871</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5098,11 +5112,11 @@
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="25" t="n">
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02825058339894573</v>
+        <v>0.02772579109685063</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5151,11 +5165,11 @@
       <c r="F10" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="25" t="n">
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.0478315725534199</v>
+        <v>0.04882370488037944</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46050</v>
@@ -5204,11 +5218,11 @@
       <c r="F11" s="7" t="n">
         <v>7.45</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="25" t="n">
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.1000738804559087</v>
+        <v>0.1030535623205178</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5257,11 +5271,11 @@
       <c r="F12" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="25" t="n">
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02132591592527367</v>
+        <v>0.0213754642293257</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5310,11 +5324,11 @@
       <c r="F13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="25" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007491221225126805</v>
+        <v>0.007368743966992668</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5363,11 +5377,11 @@
       <c r="F14" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="25" t="n">
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.02058823567910728</v>
+        <v>0.01933479125101876</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5416,11 +5430,11 @@
       <c r="F15" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="25" t="n">
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03739692222714045</v>
+        <v>0.03836415568100161</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5469,11 +5483,11 @@
       <c r="F16" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="25" t="n">
         <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01787337991559126</v>
+        <v>0.01763469457548388</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46118</v>
@@ -5522,11 +5536,11 @@
       <c r="F17" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="25" t="n">
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02007108432466542</v>
+        <v>0.02127659624835675</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5575,11 +5589,11 @@
       <c r="F18" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="25" t="n">
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.0459675756739481</v>
+        <v>0.04560879711568076</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5628,11 +5642,11 @@
       <c r="F19" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="25" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02218755469700068</v>
+        <v>0.02227539640653369</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5681,11 +5695,11 @@
       <c r="F20" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01881768090793178</v>
+        <v>0.0189161857620277</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46122</v>
@@ -5734,11 +5748,11 @@
       <c r="F21" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="25" t="n">
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02796489436856701</v>
+        <v>0.02702937868968329</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5787,11 +5801,11 @@
       <c r="F22" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="25" t="n">
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01385055422704897</v>
+        <v>0.01400091275623278</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5840,14 +5854,14 @@
       <c r="F23" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="25" t="n">
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05740876548815603</v>
+        <v>0.05489461260231227</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>46034</v>
+        <v>46125</v>
       </c>
       <c r="J23" s="8" t="n">
         <v>0.01034482758620691</v>
@@ -5893,11 +5907,11 @@
       <c r="F24" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="25" t="n">
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02897526579881178</v>
+        <v>0.028482110938654</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5946,11 +5960,11 @@
       <c r="F25" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="25" t="n">
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01639895228241406</v>
+        <v>0.01572975810214969</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5999,11 +6013,11 @@
       <c r="F26" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="G26" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02185149377369338</v>
+        <v>0.02234636900814657</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6015,7 +6029,7 @@
         <v>46128</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>46165</v>
+        <v>46530</v>
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
@@ -6052,11 +6066,11 @@
       <c r="F27" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="25" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01950236473909606</v>
+        <v>0.01909064824484362</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46118</v>
@@ -6105,11 +6119,11 @@
       <c r="F28" s="7" t="n">
         <v>0.976</v>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="25" t="n">
         <v>1.952</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01865443435957342</v>
+        <v>0.01896066107686591</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>45853</v>
@@ -6118,7 +6132,7 @@
         <v>0.1040723981900452</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>46127</v>
+        <v>46054</v>
       </c>
       <c r="L28" s="10" t="n">
         <v>46503</v>
@@ -6158,11 +6172,11 @@
       <c r="F29" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G29" s="25" t="n">
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01232749822106043</v>
+        <v>0.01214777203969057</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6211,11 +6225,11 @@
       <c r="F30" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="25" t="n">
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03271512590566655</v>
+        <v>0.03266996422443251</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6264,11 +6278,11 @@
       <c r="F31" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="25" t="n">
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.0358075352153408</v>
+        <v>0.03616159630581837</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46020</v>
@@ -6317,11 +6331,11 @@
       <c r="F32" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="25" t="n">
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.009670434802419548</v>
+        <v>0.008636644221988921</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6370,11 +6384,11 @@
       <c r="F33" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="25" t="n">
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03675538644680129</v>
+        <v>0.03609583930933605</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46120</v>
@@ -6423,11 +6437,11 @@
       <c r="F34" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="25" t="n">
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03857253431942761</v>
+        <v>0.0357805177868014</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6476,11 +6490,11 @@
       <c r="F35" s="7" t="n">
         <v>1.275</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="25" t="n">
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.06807261244854079</v>
+        <v>0.06297851060243667</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6529,11 +6543,11 @@
       <c r="F36" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G36" s="24" t="n">
+      <c r="G36" s="25" t="n">
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05132170620781536</v>
+        <v>0.04995775311493071</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46112</v>
@@ -6582,11 +6596,11 @@
       <c r="F37" s="7" t="n">
         <v>1.08</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="25" t="n">
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04968943959843446</v>
+        <v>0.04656426762542244</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6635,11 +6649,11 @@
       <c r="F38" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="25" t="n">
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03648951727390919</v>
+        <v>0.03625708516997186</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6688,11 +6702,11 @@
       <c r="F39" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G39" s="24" t="n">
+      <c r="G39" s="25" t="n">
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.0636094653019155</v>
+        <v>0.06222865549860192</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6741,11 +6755,11 @@
       <c r="F40" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G40" s="24" t="n">
+      <c r="G40" s="25" t="n">
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03491162854189175</v>
+        <v>0.03317781338777243</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6794,11 +6808,11 @@
       <c r="F41" s="7" t="n">
         <v>1.057</v>
       </c>
-      <c r="G41" s="24" t="n">
+      <c r="G41" s="25" t="n">
         <v>4.228</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02922311455651426</v>
+        <v>0.02906241493104229</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46045</v>
@@ -6807,7 +6821,7 @@
         <v>0.04965243296921554</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>46487</v>
+        <v>46122</v>
       </c>
       <c r="L41" s="10" t="n">
         <v>46497</v>
@@ -6819,53 +6833,53 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>QDVD/DAC/SMID</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>0.525</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="26" t="n">
         <v>2.1</v>
       </c>
-      <c r="H42" s="18" t="n">
-        <v>0.03939592886178251</v>
-      </c>
-      <c r="I42" s="19" t="n">
+      <c r="H42" s="19" t="n">
+        <v>0.04010312102908895</v>
+      </c>
+      <c r="I42" s="20" t="n">
         <v>46104</v>
       </c>
-      <c r="J42" s="17" t="n">
+      <c r="J42" s="18" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="K42" s="19" t="n">
+      <c r="K42" s="20" t="n">
         <v>46176</v>
       </c>
-      <c r="L42" s="19" t="n">
+      <c r="L42" s="20" t="n">
         <v>46197</v>
       </c>
-      <c r="M42" s="21" t="inlineStr">
+      <c r="M42" s="22" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6900,11 +6914,11 @@
       <c r="F43" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G43" s="24" t="n">
+      <c r="G43" s="25" t="n">
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03194646949561728</v>
+        <v>0.03266671069026816</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6953,11 +6967,11 @@
       <c r="F44" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G44" s="24" t="n">
+      <c r="G44" s="25" t="n">
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01848906588679996</v>
+        <v>0.01761655633402893</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -7006,11 +7020,11 @@
       <c r="F45" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G45" s="24" t="n">
+      <c r="G45" s="25" t="n">
         <v>3.72</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.01848906588679996</v>
+        <v>0.01761655633402893</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46070</v>
@@ -7059,11 +7073,11 @@
       <c r="F46" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G46" s="24" t="n">
+      <c r="G46" s="25" t="n">
         <v>9.76</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02590989921883621</v>
+        <v>0.02567340042608691</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46077</v>
@@ -7112,11 +7126,11 @@
       <c r="F47" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G47" s="24" t="n">
+      <c r="G47" s="25" t="n">
         <v>3.32</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04672765457281513</v>
+        <v>0.04531804399659041</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46091</v>
@@ -7165,11 +7179,11 @@
       <c r="F48" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G48" s="24" t="n">
+      <c r="G48" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05675616507437827</v>
+        <v>0.05335795908161366</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46097</v>
@@ -7218,11 +7232,11 @@
       <c r="F49" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G49" s="24" t="n">
+      <c r="G49" s="25" t="n">
         <v>3.896</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04196240991734994</v>
+        <v>0.04455117365305194</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46112</v>
@@ -7271,11 +7285,11 @@
       <c r="F50" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G50" s="24" t="n">
+      <c r="G50" s="25" t="n">
         <v>5.68</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.02667981815454341</v>
+        <v>0.02450176783946032</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46052</v>
@@ -7324,11 +7338,11 @@
       <c r="F51" s="7" t="n">
         <v>0.555</v>
       </c>
-      <c r="G51" s="24" t="n">
+      <c r="G51" s="25" t="n">
         <v>2.22</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03825607524899725</v>
+        <v>0.03814426439293622</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7377,11 +7391,11 @@
       <c r="F52" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G52" s="24" t="n">
+      <c r="G52" s="25" t="n">
         <v>5.52</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02218025518665177</v>
+        <v>0.02200781372621784</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46080</v>
@@ -7430,11 +7444,11 @@
       <c r="F53" s="7" t="n">
         <v>1.64</v>
       </c>
-      <c r="G53" s="24" t="n">
+      <c r="G53" s="25" t="n">
         <v>6.56</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06562625110126678</v>
+        <v>0.06164254945377635</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46070</v>
@@ -7443,7 +7457,7 @@
         <v>0.00613496932515338</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46423</v>
+        <v>46058</v>
       </c>
       <c r="L53" s="10" t="n">
         <v>46435</v>
@@ -7483,11 +7497,11 @@
       <c r="F54" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G54" s="24" t="n">
+      <c r="G54" s="25" t="n">
         <v>2.832</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.06217343682622542</v>
+        <v>0.06077905195421872</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46122</v>
@@ -7536,11 +7550,11 @@
       <c r="F55" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G55" s="24" t="n">
+      <c r="G55" s="25" t="n">
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02700931022247884</v>
+        <v>0.02780308444092603</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46065</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7577,4 +7577,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9EE666-59A1-445B-A6BB-685A9ABB2D2B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5669A616-8E12-4102-B2C2-12C542DC3108}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DFD854-7B62-4A32-ACE5-0295C9E9EA2A}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/20/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/27/2026</t>
         </is>
       </c>
     </row>
@@ -651,39 +651,39 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.976</v>
+        <v>1.64</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.884</v>
+        <v>1.63</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46054</v>
+        <v>46058</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-78</v>
+        <v>-81</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>46503</v>
+        <v>46435</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.01896066107686591</v>
+        <v>0.06094388737641394</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -707,29 +707,29 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1.64</v>
+        <v>0.974</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1.63</v>
+        <v>0.831</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46058</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>-74</v>
+        <v>46140</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46435</v>
+        <v>46190</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.06164254945377635</v>
+        <v>0.04327446465428495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -753,29 +753,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.057</v>
+        <v>1.08</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.007</v>
+        <v>0.98</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46122</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>-10</v>
+        <v>46143</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46497</v>
+        <v>46152</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -783,13 +783,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02906241493104229</v>
+        <v>0.04790684617465937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -799,29 +799,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.3</v>
+        <v>0.71</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46128</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>-4</v>
+        <v>46162</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46530</v>
+        <v>46198</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -829,59 +829,59 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02234636900814657</v>
+        <v>0.03404459436990546</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="G10" s="9" t="n">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="G10" s="19" t="n">
         <v>0.04</v>
       </c>
-      <c r="H10" s="10" t="n">
-        <v>46134</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>46161</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>0.03266671069026816</v>
+      <c r="H10" s="20" t="n">
+        <v>46176</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>46197</v>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>0.04078857871427848</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -891,29 +891,29 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.974</v>
+        <v>0.93</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.831</v>
+        <v>0.89</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46140</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>8</v>
+        <v>46218</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>79</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46190</v>
+        <v>46248</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.04455117365305194</v>
+        <v>0.01770164219863074</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -937,29 +937,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.98</v>
+        <v>1.34</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46143</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>11</v>
+        <v>46220</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>81</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46152</v>
+        <v>46264</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.04656426762542244</v>
+        <v>0.0205977842499729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -983,29 +983,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46162</v>
+        <v>46227</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46198</v>
+        <v>46267</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1013,59 +1013,59 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03266996422443251</v>
+        <v>0.04208391463665842</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>46176</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>44</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>0.04010312102908895</v>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.05263157894736847</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0.02804852382638342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1079,25 +1079,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01761655633402893</v>
+        <v>0.05085875336986107</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1121,29 +1121,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46218</v>
+        <v>46263</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46248</v>
+        <v>46297</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01761655633402893</v>
+        <v>0.02885545924901842</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1167,29 +1167,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46220</v>
+        <v>46278</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46264</v>
+        <v>46344</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02200781372621784</v>
+        <v>0.008662541395183453</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1213,29 +1213,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.83</v>
+        <v>0.708</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46227</v>
+        <v>46280</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46267</v>
+        <v>46303</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.04531804399659041</v>
+        <v>0.05880398689727525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1259,29 +1259,29 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.95</v>
+        <v>1.36</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46232</v>
+        <v>46285</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46264</v>
+        <v>46325</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02772579109685063</v>
+        <v>0.02084135954529386</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1305,29 +1305,29 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1.24</v>
+        <v>0.87</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1.22</v>
+        <v>0.85</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46232</v>
+        <v>46305</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46246</v>
+        <v>46339</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.04882370488037944</v>
+        <v>0.03434493071613531</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1351,29 +1351,29 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46263</v>
+        <v>46311</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46297</v>
+        <v>46386</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.028482110938654</v>
+        <v>0.01222247967649055</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1401,25 +1401,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.91</v>
+        <v>1.38</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.83</v>
+        <v>1.35</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46278</v>
+        <v>46317</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46344</v>
+        <v>46351</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.008636644221988921</v>
+        <v>0.01513987906635631</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1443,29 +1443,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.708</v>
+        <v>0.64</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46303</v>
+        <v>46338</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.06077905195421872</v>
+        <v>0.02240308108169822</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1489,29 +1489,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.42</v>
+        <v>0.6</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1.36</v>
+        <v>0.55</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46285</v>
+        <v>46329</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46325</v>
+        <v>46338</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.02450176783946032</v>
+        <v>0.007717290187350596</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1539,25 +1539,25 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.87</v>
+        <v>2.44</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.85</v>
+        <v>2.14</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46305</v>
+        <v>46332</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03609583930933605</v>
+        <v>0.02590474067531757</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1581,29 +1581,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.79</v>
+        <v>1.03</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46311</v>
+        <v>46341</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46386</v>
+        <v>46339</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.01214777203969057</v>
+        <v>0.02741001973866671</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1627,29 +1627,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.38</v>
+        <v>0.48</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1.35</v>
+        <v>0.45</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46317</v>
+        <v>46344</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46351</v>
+        <v>46385</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.01400091275623278</v>
+        <v>0.03731415667429284</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1673,29 +1673,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46322</v>
+        <v>46347</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46338</v>
+        <v>46358</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02227539640653369</v>
+        <v>0.03633543948128567</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1719,29 +1719,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.6</v>
+        <v>0.293</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46338</v>
+        <v>46400</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.007368743966992668</v>
+        <v>0.05397190843953674</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1765,29 +1765,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.44</v>
+        <v>0.84</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2.14</v>
+        <v>0.83</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46332</v>
+        <v>46360</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46346</v>
+        <v>46371</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02567340042608691</v>
+        <v>0.04653095198172495</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1811,29 +1811,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.99</v>
+        <v>2.38</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46341</v>
+        <v>46366</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46339</v>
+        <v>46432</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02780308444092603</v>
+        <v>0.02907077430897583</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1857,29 +1857,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46344</v>
+        <v>46370</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46385</v>
+        <v>46413</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03616159630581837</v>
+        <v>0.06320044057895932</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1903,29 +1903,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46347</v>
+        <v>46371</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46358</v>
+        <v>46344</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.0357805177868014</v>
+        <v>0.02140032482159259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1949,29 +1949,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.293</v>
+        <v>0.86</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.29</v>
+        <v>0.8</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46352</v>
+        <v>46402</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46400</v>
+        <v>46483</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.05489461260231227</v>
+        <v>0.01747390294878716</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1995,29 +1995,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.84</v>
+        <v>0.703</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.83</v>
+        <v>0.676</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46360</v>
+        <v>46411</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46371</v>
+        <v>46435</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04560879711568076</v>
+        <v>0.03730432611381523</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2045,25 +2045,25 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.52</v>
+        <v>1.78</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46366</v>
+        <v>46417</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2071,45 +2071,45 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.02857547838412473</v>
+        <v>0.03812416391836682</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.43</v>
+        <v>1.275</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.42</v>
+        <v>0.584</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46370</v>
+        <v>46422</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46413</v>
+        <v>46472</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06222865549860192</v>
+        <v>0.06160908522839336</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2133,29 +2133,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.22</v>
+        <v>0.58</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46371</v>
+        <v>46428</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46344</v>
+        <v>46452</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.0213754642293257</v>
+        <v>0.01610029660749452</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2179,29 +2179,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46402</v>
+        <v>46428</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46483</v>
+        <v>46460</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2209,13 +2209,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.01763469457548388</v>
+        <v>0.05239030924280169</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2225,29 +2225,29 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.703</v>
+        <v>0.42</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.676</v>
+        <v>0.41</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46411</v>
+        <v>46431</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46435</v>
+        <v>46480</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2255,18 +2255,18 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03685693777425871</v>
+        <v>0.01895095150229958</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2275,25 +2275,25 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.78</v>
+        <v>1.883</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.71</v>
+        <v>1.864</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.01019313304721025</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>46417</v>
+        <v>46433</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46433</v>
+        <v>46425</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2301,45 +2301,45 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03836415568100161</v>
+        <v>0.002626055610008967</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.275</v>
+        <v>7.45</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.584</v>
+        <v>1.25</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>4.96</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46422</v>
+        <v>46433</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46472</v>
+        <v>46383</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.06297851060243667</v>
+        <v>0.1047691045609153</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2363,29 +2363,29 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46452</v>
+        <v>46276</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01572975810214969</v>
+        <v>0.01982037726397964</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2409,29 +2409,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.3</v>
+        <v>1.423</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1.27</v>
+        <v>1.355</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46460</v>
+        <v>46177</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.05335795908161366</v>
+        <v>0.03655865462755013</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2455,29 +2455,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46480</v>
+        <v>46270</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2485,45 +2485,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.01933479125101876</v>
+        <v>0.03201921074472783</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.883</v>
+        <v>0.555</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.864</v>
+        <v>0.588964</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46425</v>
+        <v>46243</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.002588209316692858</v>
+        <v>0.03820998379180393</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2547,29 +2547,29 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>7.45</v>
+        <v>0.29</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.25</v>
+        <v>0.27</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>4.96</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="I47" s="14" t="n">
         <v>301</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2577,13 +2577,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.1030535623205178</v>
+        <v>0.008561517108053597</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2593,29 +2593,29 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.24</v>
+        <v>2.33</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.22</v>
+        <v>2.3</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46276</v>
+        <v>46456</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02127659624835675</v>
+        <v>0.02780014914243102</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -2639,29 +2639,29 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.423</v>
+        <v>1.59</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.355</v>
+        <v>1.5</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46433</v>
+        <v>46452</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46177</v>
+        <v>46487</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.03625708516997186</v>
+        <v>0.01997425255346736</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2685,29 +2685,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.79</v>
+        <v>1.4</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46433</v>
+        <v>46461</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2715,45 +2715,45 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.03317781338777243</v>
+        <v>0.019392372716101</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.555</v>
+        <v>0.271</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46433</v>
+        <v>46461</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46243</v>
+        <v>46196</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.03814426439293622</v>
+        <v>0.0510678389512458</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2777,29 +2777,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.29</v>
+        <v>1.089</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0.27</v>
+        <v>1.057</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46440</v>
+        <v>46488</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46450</v>
+        <v>46498</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.009033213103202842</v>
+        <v>0.02928206615253558</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>2.33</v>
+        <v>1.087</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>2.3</v>
+        <v>0.976</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46441</v>
+        <v>46492</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46456</v>
+        <v>46501</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02702937868968329</v>
+        <v>0.02119218228202975</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2869,29 +2869,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46452</v>
+        <v>46493</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46487</v>
+        <v>46530</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.0189161857620277</v>
+        <v>0.02285916208230909</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2915,29 +2915,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46461</v>
+        <v>46499</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46300</v>
+        <v>46526</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2945,53 +2945,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.01909064824484362</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="F56" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>329</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>46196</v>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="n">
-        <v>0.04995775311493071</v>
+        <v>0.03061716523663033</v>
       </c>
     </row>
   </sheetData>
@@ -3005,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3026,7 +2980,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 04/20/2026</t>
+          <t>Expected Increase Announcements by Month - 04/27/2026</t>
         </is>
       </c>
     </row>
@@ -3072,20 +3026,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46054</v>
+        <v>46058</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46503</v>
+        <v>46435</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.976</v>
+        <v>1.64</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
@@ -3093,158 +3047,125 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>46058</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>46435</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.00613496932515338</v>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>April 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>April 2026</t>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>46190</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.2021660649819495</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>46122</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>46497</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1.057</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.04965243296921554</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>46128</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>46530</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.04838709677419359</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>46134</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46190</v>
+        <v>46152</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.974</v>
+        <v>1.08</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3252,97 +3173,97 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>May 2026</t>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>46198</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.0142857142857143</v>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>46152</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.1020408163265307</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.0142857142857143</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>46176</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
@@ -3379,85 +3300,118 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>46176</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>July 2026</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.05263157894736847</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
@@ -3465,95 +3419,62 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
@@ -3561,86 +3482,86 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46263</v>
+        <v>46280</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.82</v>
+        <v>0.708</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3648,86 +3569,86 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B39" s="24" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F39" s="24" t="inlineStr">
+      <c r="F40" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>46280</v>
+        <v>46305</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.708</v>
+        <v>0.87</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
@@ -3738,20 +3659,20 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>46285</v>
+        <v>46311</v>
       </c>
       <c r="C42" s="10" t="n">
-        <v>46325</v>
+        <v>46386</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.42</v>
+        <v>0.79</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
@@ -3759,110 +3680,110 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>October 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C45" s="24" t="inlineStr">
+      <c r="C47" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="D47" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F45" s="24" t="inlineStr">
+      <c r="F47" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>46317</v>
+        <v>46329</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.38</v>
+        <v>0.6</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -3873,20 +3794,20 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.64</v>
+        <v>2.44</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
@@ -3894,62 +3815,95 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>46347</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>46358</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46338</v>
+        <v>46400</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.6</v>
+        <v>0.293</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -3957,95 +3911,62 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.1401869158878504</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>46347</v>
+        <v>46360</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46358</v>
+        <v>46371</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -4056,20 +3977,20 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46352</v>
+        <v>46366</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46400</v>
+        <v>46432</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.293</v>
+        <v>2.52</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4077,110 +3998,110 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>46370</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>46413</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.02380952380952383</v>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>December 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B63" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D63" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="E63" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F61" s="24" t="inlineStr">
+      <c r="F63" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46370</v>
+        <v>46402</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46413</v>
+        <v>46483</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4191,20 +4112,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46371</v>
+        <v>46411</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46344</v>
+        <v>46435</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.23</v>
+        <v>0.703</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4212,86 +4133,86 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="23" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B68" s="24" t="inlineStr">
+      <c r="B69" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C68" s="24" t="inlineStr">
+      <c r="C69" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D68" s="24" t="inlineStr">
+      <c r="D69" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E68" s="24" t="inlineStr">
+      <c r="E69" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F68" s="24" t="inlineStr">
+      <c r="F69" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B70" s="10" t="n">
-        <v>46411</v>
+        <v>46422</v>
       </c>
       <c r="C70" s="10" t="n">
-        <v>46435</v>
+        <v>46472</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>0.703</v>
+        <v>1.275</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
@@ -4302,83 +4223,116 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46417</v>
+        <v>46428</v>
       </c>
       <c r="C71" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.02362204724409451</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="D71" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E71" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D74" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F74" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="C74" s="10" t="n">
+        <v>46425</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>1.883</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.01019313304721025</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46422</v>
+        <v>46433</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46472</v>
+        <v>46383</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1.275</v>
+        <v>7.45</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>4.96</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4389,20 +4343,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46452</v>
+        <v>46276</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4413,20 +4367,20 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46460</v>
+        <v>46177</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>1.3</v>
+        <v>1.423</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4437,20 +4391,20 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46480</v>
+        <v>46270</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4461,20 +4415,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46425</v>
+        <v>46243</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.883</v>
+        <v>0.555</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4485,20 +4439,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>7.45</v>
+        <v>0.29</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>4.96</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4509,20 +4463,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46276</v>
+        <v>46456</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.24</v>
+        <v>2.33</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4530,95 +4484,62 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>46177</v>
-      </c>
-      <c r="D82" s="7" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.05018450184501849</v>
-      </c>
-      <c r="F82" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.01265822784810128</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46243</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.005735494868956323</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B85" s="10" t="n">
-        <v>46440</v>
+        <v>46452</v>
       </c>
       <c r="C85" s="10" t="n">
-        <v>46450</v>
+        <v>46487</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.29</v>
+        <v>1.59</v>
       </c>
       <c r="E85" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
@@ -4629,20 +4550,20 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B86" s="10" t="n">
-        <v>46441</v>
+        <v>46461</v>
       </c>
       <c r="C86" s="10" t="n">
-        <v>46456</v>
+        <v>46300</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
@@ -4650,86 +4571,86 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="23" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>46196</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.003703703703703707</v>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B89" s="24" t="inlineStr">
+      <c r="B90" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C89" s="24" t="inlineStr">
+      <c r="C90" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D89" s="24" t="inlineStr">
+      <c r="D90" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E89" s="24" t="inlineStr">
+      <c r="E90" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F89" s="24" t="inlineStr">
+      <c r="F90" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B91" s="10" t="n">
-        <v>46461</v>
+        <v>46488</v>
       </c>
       <c r="C91" s="10" t="n">
-        <v>46300</v>
+        <v>46498</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>1.5</v>
+        <v>1.089</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
@@ -4740,22 +4661,70 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B92" s="10" t="n">
-        <v>46461</v>
+        <v>46492</v>
       </c>
       <c r="C92" s="10" t="n">
-        <v>46196</v>
+        <v>46501</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>0.271</v>
+        <v>1.087</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>46493</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>46530</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.04838709677419359</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>46499</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>46526</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4772,7 +4741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4800,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 04/20/2026</t>
+          <t>Complete Holdings Dividend Summary - 04/27/2026</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4848,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -4904,7 +4873,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009033213103202842</v>
+        <v>0.008561517108053597</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4957,7 +4926,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02857547838412473</v>
+        <v>0.02907077430897583</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -5010,7 +4979,7 @@
         <v>3.766</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002588209316692858</v>
+        <v>0.002626055610008967</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46063</v>
@@ -5038,7 +5007,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -5063,7 +5032,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03685693777425871</v>
+        <v>0.03730432611381523</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5091,7 +5060,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5116,7 +5085,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02772579109685063</v>
+        <v>0.02804852382638342</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5144,7 +5113,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5169,10 +5138,10 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.04882370488037944</v>
+        <v>0.05085875336986107</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>46050</v>
+        <v>46134</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>0.01639344262295083</v>
@@ -5222,7 +5191,7 @@
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.1030535623205178</v>
+        <v>0.1047691045609153</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5250,7 +5219,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5275,7 +5244,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.0213754642293257</v>
+        <v>0.02140032482159259</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5303,7 +5272,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5328,7 +5297,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007368743966992668</v>
+        <v>0.007717290187350596</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5381,7 +5350,7 @@
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.01933479125101876</v>
+        <v>0.01895095150229958</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5434,7 +5403,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03836415568100161</v>
+        <v>0.03812416391836682</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5462,7 +5431,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5487,7 +5456,7 @@
         <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01763469457548388</v>
+        <v>0.01747390294878716</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46118</v>
@@ -5515,7 +5484,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5540,7 +5509,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02127659624835675</v>
+        <v>0.01982037726397964</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5568,7 +5537,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5593,7 +5562,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04560879711568076</v>
+        <v>0.04653095198172495</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5646,7 +5615,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02227539640653369</v>
+        <v>0.02240308108169822</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46062</v>
@@ -5699,7 +5668,7 @@
         <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0189161857620277</v>
+        <v>0.01997425255346736</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46122</v>
@@ -5752,7 +5721,7 @@
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02702937868968329</v>
+        <v>0.02780014914243102</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5780,7 +5749,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -5805,7 +5774,7 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01400091275623278</v>
+        <v>0.01513987906635631</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5833,7 +5802,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5858,7 +5827,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05489461260231227</v>
+        <v>0.05397190843953674</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46125</v>
@@ -5886,7 +5855,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -5911,7 +5880,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.028482110938654</v>
+        <v>0.02885545924901842</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5939,7 +5908,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -5964,7 +5933,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01572975810214969</v>
+        <v>0.01610029660749452</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -6017,7 +5986,7 @@
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02234636900814657</v>
+        <v>0.02285916208230909</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6026,7 +5995,7 @@
         <v>0.04838709677419359</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>46128</v>
+        <v>46493</v>
       </c>
       <c r="L26" s="10" t="n">
         <v>46530</v>
@@ -6070,7 +6039,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01909064824484362</v>
+        <v>0.019392372716101</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46118</v>
@@ -6117,25 +6086,25 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.976</v>
+        <v>1.087</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>1.952</v>
+        <v>2.174</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01896066107686591</v>
+        <v>0.02119218228202975</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>45853</v>
+        <v>46132</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.1040723981900452</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>46054</v>
+        <v>46492</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>46503</v>
+        <v>46501</v>
       </c>
       <c r="M28" s="12" t="inlineStr">
         <is>
@@ -6151,7 +6120,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -6176,7 +6145,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01214777203969057</v>
+        <v>0.01222247967649055</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6229,7 +6198,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03266996422443251</v>
+        <v>0.03404459436990546</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6257,7 +6226,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -6282,10 +6251,10 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.03616159630581837</v>
+        <v>0.03731415667429284</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>46020</v>
+        <v>46132</v>
       </c>
       <c r="J31" s="8" t="n">
         <v>0.0666666666666666</v>
@@ -6335,7 +6304,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008636644221988921</v>
+        <v>0.008662541395183453</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6363,7 +6332,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -6388,7 +6357,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03609583930933605</v>
+        <v>0.03434493071613531</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46120</v>
@@ -6441,7 +6410,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.0357805177868014</v>
+        <v>0.03633543948128567</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6494,7 +6463,7 @@
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.06297851060243667</v>
+        <v>0.06160908522839336</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6547,7 +6516,7 @@
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.04995775311493071</v>
+        <v>0.0510678389512458</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46112</v>
@@ -6575,7 +6544,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -6600,7 +6569,7 @@
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04656426762542244</v>
+        <v>0.04790684617465937</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6653,7 +6622,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03625708516997186</v>
+        <v>0.03655865462755013</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6706,7 +6675,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06222865549860192</v>
+        <v>0.06320044057895932</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6734,7 +6703,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -6759,7 +6728,7 @@
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03317781338777243</v>
+        <v>0.03201921074472783</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6806,25 +6775,25 @@
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>1.057</v>
+        <v>1.089</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>4.228</v>
+        <v>4.356</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02906241493104229</v>
+        <v>0.02928206615253558</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>46045</v>
+        <v>46136</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0.04965243296921554</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>46122</v>
+        <v>46488</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>46497</v>
+        <v>46498</v>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
@@ -6840,7 +6809,7 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -6865,7 +6834,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>0.04010312102908895</v>
+        <v>0.04078857871427848</v>
       </c>
       <c r="I42" s="20" t="n">
         <v>46104</v>
@@ -6918,7 +6887,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03266671069026816</v>
+        <v>0.03061716523663033</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6927,10 +6896,10 @@
         <v>0.05833333333333339</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>46134</v>
+        <v>46499</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>46161</v>
+        <v>46526</v>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
@@ -6946,7 +6915,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -6971,7 +6940,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01761655633402893</v>
+        <v>0.01770164219863074</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6994,12 +6963,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -7014,29 +6983,29 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.93</v>
+        <v>2.44</v>
       </c>
       <c r="G45" s="25" t="n">
-        <v>3.72</v>
+        <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.01761655633402893</v>
+        <v>0.02590474067531757</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>46218</v>
+        <v>46332</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>46248</v>
+        <v>46346</v>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
@@ -7047,12 +7016,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -7062,34 +7031,34 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>2.44</v>
+        <v>0.83</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>9.76</v>
+        <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02567340042608691</v>
+        <v>0.04208391463665842</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>46332</v>
+        <v>46227</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>46346</v>
+        <v>46267</v>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
@@ -7100,12 +7069,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>DAC/SMID</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -7115,34 +7084,34 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.83</v>
+        <v>1.3</v>
       </c>
       <c r="G47" s="25" t="n">
-        <v>3.32</v>
+        <v>5.2</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.04531804399659041</v>
+        <v>0.05239030924280169</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>46091</v>
+        <v>46097</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>46227</v>
+        <v>46428</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>46267</v>
+        <v>46460</v>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
@@ -7153,12 +7122,12 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC/SMID</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -7173,29 +7142,29 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>1.3</v>
+        <v>0.974</v>
       </c>
       <c r="G48" s="25" t="n">
-        <v>5.2</v>
+        <v>3.896</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.05335795908161366</v>
+        <v>0.04327446465428495</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>46097</v>
+        <v>46112</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.2021660649819495</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46428</v>
+        <v>46140</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46460</v>
+        <v>46190</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7206,12 +7175,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -7221,34 +7190,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Jan/May/Jul/Oct</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.974</v>
+        <v>1.42</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>3.896</v>
+        <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04455117365305194</v>
+        <v>0.02084135954529386</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>46112</v>
+        <v>46052</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>46140</v>
+        <v>46285</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>46190</v>
+        <v>46325</v>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
@@ -7259,12 +7228,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -7274,34 +7243,34 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1.42</v>
+        <v>0.555</v>
       </c>
       <c r="G50" s="25" t="n">
-        <v>5.68</v>
+        <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.02450176783946032</v>
+        <v>0.03820998379180393</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>46052</v>
+        <v>46080</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46285</v>
+        <v>46433</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46325</v>
+        <v>46243</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7312,12 +7281,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -7327,7 +7296,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Feb/May/Aug/Dec</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -7336,25 +7305,25 @@
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.555</v>
+        <v>1.38</v>
       </c>
       <c r="G51" s="25" t="n">
-        <v>2.22</v>
+        <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.03814426439293622</v>
+        <v>0.0205977842499729</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>46433</v>
+        <v>46220</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>46243</v>
+        <v>46264</v>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
@@ -7365,7 +7334,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -7380,34 +7349,34 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Dec</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="G52" s="25" t="n">
-        <v>5.52</v>
+        <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.02200781372621784</v>
+        <v>0.06094388737641394</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46080</v>
+        <v>46070</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.00613496932515338</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>46220</v>
+        <v>46058</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>46264</v>
+        <v>46435</v>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7387,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -7433,34 +7402,34 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1.64</v>
+        <v>0.708</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>6.56</v>
+        <v>2.832</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06164254945377635</v>
+        <v>0.05880398689727525</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>46070</v>
+        <v>46122</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.00613496932515338</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46058</v>
+        <v>46280</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46435</v>
+        <v>46303</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7471,7 +7440,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -7486,89 +7455,36 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.708</v>
+        <v>1.03</v>
       </c>
       <c r="G54" s="25" t="n">
-        <v>2.832</v>
+        <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.06077905195421872</v>
+        <v>0.02741001973866671</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>46122</v>
+        <v>46065</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>46280</v>
+        <v>46341</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="M54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Feb/May/Aug/Nov</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G55" s="25" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>0.02780308444092603</v>
-      </c>
-      <c r="I55" s="10" t="n">
-        <v>46065</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="K55" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="L55" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="M55" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -7577,252 +7493,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A9EE666-59A1-445B-A6BB-685A9ABB2D2B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5669A616-8E12-4102-B2C2-12C542DC3108}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72DFD854-7B62-4A32-ACE5-0295C9E9EA2A}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7493,4 +7493,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4624C93C-24C1-4E35-9BED-B6DE663E2ECF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D951A183-83FE-49AA-BF5F-B471344742F8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26D25A5B-8C48-43FA-9943-0C7D65EA1BB7}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,12 +84,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00856404"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001a3a5c"/>
       <sz val="12"/>
     </font>
@@ -100,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -122,11 +116,6 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,26 +152,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 04/27/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 05/04/2026</t>
         </is>
       </c>
     </row>
@@ -680,7 +655,7 @@
         <v>46058</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-81</v>
+        <v>-88</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46435</v>
@@ -691,7 +666,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06094388737641394</v>
+        <v>0.06627266716725133</v>
       </c>
     </row>
     <row r="7">
@@ -725,11 +700,11 @@
       <c r="H7" s="10" t="n">
         <v>46140</v>
       </c>
-      <c r="I7" s="13" t="n">
-        <v>1</v>
+      <c r="I7" s="11" t="n">
+        <v>-6</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46190</v>
+        <v>46555</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -737,13 +712,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.04327446465428495</v>
+        <v>0.04255133359420153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -753,29 +728,29 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.98</v>
+        <v>0.7</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46152</v>
+        <v>46198</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -783,13 +758,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.04790684617465937</v>
+        <v>0.03583370258558077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -799,89 +774,89 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G9" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0.01773201829949195</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="G10" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>0.03404459436990546</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>46176</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>37</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>46197</v>
-      </c>
-      <c r="K10" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="n">
-        <v>0.04078857871427848</v>
+      <c r="H10" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0.02081722633876427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -891,29 +866,29 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>79</v>
+        <v>46227</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>81</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -921,13 +896,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.01770164219863074</v>
+        <v>0.04247696832708157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -941,22 +916,22 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>81</v>
+        <v>46232</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>86</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46264</v>
@@ -967,13 +942,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.0205977842499729</v>
+        <v>0.02846367348427877</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -983,29 +958,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>88</v>
+        <v>46232</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>86</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46267</v>
+        <v>46246</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1013,13 +988,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.04208391463665842</v>
+        <v>0.05755395663072553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1029,29 +1004,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>93</v>
+        <v>46263</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>117</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1059,13 +1034,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.02804852382638342</v>
+        <v>0.02992427681539705</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1075,29 +1050,29 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.22</v>
+        <v>0.83</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>93</v>
+        <v>46278</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>132</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46246</v>
+        <v>46344</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1105,13 +1080,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.05085875336986107</v>
+        <v>0.008761373116221174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1125,25 +1100,25 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.82</v>
+        <v>0.708</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>124</v>
+        <v>46280</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>134</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1151,13 +1126,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02885545924901842</v>
+        <v>0.05969646041274478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1167,29 +1142,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.83</v>
+        <v>1.36</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I17" s="14" t="n">
+        <v>46285</v>
+      </c>
+      <c r="I17" s="13" t="n">
         <v>139</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46344</v>
+        <v>46325</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1197,13 +1172,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.008662541395183453</v>
+        <v>0.02028028118339007</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1213,29 +1188,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.708</v>
+        <v>0.87</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>141</v>
+        <v>46305</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>159</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1243,13 +1218,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.05880398689727525</v>
+        <v>0.0342823359941388</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1259,29 +1234,29 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.42</v>
+        <v>0.79</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1.36</v>
+        <v>0.75</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>146</v>
+        <v>46311</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>165</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46325</v>
+        <v>46386</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1289,13 +1264,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02084135954529386</v>
+        <v>0.0118734494103574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1309,25 +1284,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.87</v>
+        <v>1.38</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>166</v>
+        <v>46317</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>171</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46339</v>
+        <v>46351</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1335,13 +1310,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.03434493071613531</v>
+        <v>0.01521331731813701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1351,29 +1326,29 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>172</v>
+        <v>46322</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>176</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46386</v>
+        <v>46338</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1381,13 +1356,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.01222247967649055</v>
+        <v>0.02192813345130483</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1401,25 +1376,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.38</v>
+        <v>0.6</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1.35</v>
+        <v>0.55</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>178</v>
+        <v>46329</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>183</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1427,13 +1402,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.01513987906635631</v>
+        <v>0.007863953539765047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1447,25 +1422,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.64</v>
+        <v>2.44</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.6</v>
+        <v>2.14</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>183</v>
+        <v>46332</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>186</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1473,13 +1448,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02240308108169822</v>
+        <v>0.02582659671485322</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1493,25 +1468,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>190</v>
+        <v>46341</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>195</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1519,13 +1494,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.007717290187350596</v>
+        <v>0.02716065616513814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1535,29 +1510,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2.44</v>
+        <v>0.48</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>2.14</v>
+        <v>0.45</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>193</v>
+        <v>46344</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>198</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46346</v>
+        <v>46385</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1565,13 +1540,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.02590474067531757</v>
+        <v>0.03869407580269512</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1581,29 +1556,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>202</v>
+        <v>46347</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>201</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46339</v>
+        <v>46358</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1611,13 +1586,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.02741001973866671</v>
+        <v>0.03723042062212387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1627,29 +1602,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.48</v>
+        <v>0.293</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>205</v>
+        <v>46352</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>206</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46385</v>
+        <v>46400</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1657,13 +1632,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.03731415667429284</v>
+        <v>0.05557136043245535</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1677,25 +1652,25 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>208</v>
+        <v>46360</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>214</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46358</v>
+        <v>46371</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1703,13 +1678,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.03633543948128567</v>
+        <v>0.04368742478236734</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1719,29 +1694,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.293</v>
+        <v>2.52</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>213</v>
+        <v>46366</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>220</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46400</v>
+        <v>46432</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1749,13 +1724,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.05397190843953674</v>
+        <v>0.030992498778321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1765,29 +1740,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.84</v>
+        <v>0.43</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>221</v>
+        <v>46370</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>224</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46371</v>
+        <v>46413</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1795,13 +1770,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.04653095198172495</v>
+        <v>0.06502835351180732</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1811,29 +1786,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>2.38</v>
+        <v>0.22</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>227</v>
+        <v>46371</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>225</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46432</v>
+        <v>46344</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1841,13 +1816,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.02907077430897583</v>
+        <v>0.02120792939943494</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1857,29 +1832,29 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>231</v>
+        <v>46402</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>256</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46413</v>
+        <v>46483</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1887,13 +1862,13 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.06320044057895932</v>
+        <v>0.01798128714599146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1903,29 +1878,29 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.23</v>
+        <v>0.703</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.22</v>
+        <v>0.676</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>232</v>
+        <v>46411</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>265</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46344</v>
+        <v>46435</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1933,13 +1908,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.02140032482159259</v>
+        <v>0.03724503311258278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1949,29 +1924,29 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.86</v>
+        <v>1.78</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.8</v>
+        <v>1.71</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>263</v>
+        <v>46417</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>271</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46483</v>
+        <v>46433</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1979,45 +1954,45 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01747390294878716</v>
+        <v>0.03749045758210754</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.703</v>
+        <v>1.275</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.676</v>
+        <v>0.584</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>272</v>
+        <v>46422</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>276</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46435</v>
+        <v>46472</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2025,13 +2000,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.03730432611381523</v>
+        <v>0.0575101486518865</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2041,29 +2016,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1.78</v>
+        <v>0.61</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1.71</v>
+        <v>0.58</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>278</v>
+        <v>46428</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>282</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46433</v>
+        <v>46452</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2071,18 +2046,18 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.03812416391836682</v>
+        <v>0.01587456472419767</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2091,25 +2066,25 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.275</v>
+        <v>1.3</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.584</v>
+        <v>1.27</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>283</v>
+        <v>46428</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>282</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46472</v>
+        <v>46460</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2117,13 +2092,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.06160908522839336</v>
+        <v>0.05057381847338947</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2133,29 +2108,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.58</v>
+        <v>0.41</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>289</v>
+        <v>46431</v>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>285</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46452</v>
+        <v>46480</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2163,13 +2138,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.01610029660749452</v>
+        <v>0.01807228933461354</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2179,29 +2154,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.3</v>
+        <v>3.177</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.27</v>
+        <v>1.883</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H39" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>289</v>
+        <v>46433</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46460</v>
+        <v>46425</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2209,13 +2184,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.05239030924280169</v>
+        <v>0.008985741953404</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2225,29 +2200,29 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.42</v>
+        <v>7.45</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.41</v>
+        <v>1.25</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>4.96</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>292</v>
+        <v>46433</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46480</v>
+        <v>46383</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2255,45 +2230,45 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01895095150229958</v>
+        <v>0.1034201569911252</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>1.883</v>
+        <v>0.24</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>1.864</v>
+        <v>0.22</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I41" s="14" t="n">
-        <v>294</v>
+      <c r="I41" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46425</v>
+        <v>46276</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2301,13 +2276,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.002626055610008967</v>
+        <v>0.01886785057271592</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2317,17 +2292,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>7.45</v>
+        <v>1.423</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1.25</v>
+        <v>1.355</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>4.96</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0.06</v>
@@ -2335,11 +2310,11 @@
       <c r="H42" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I42" s="14" t="n">
-        <v>294</v>
+      <c r="I42" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46383</v>
+        <v>46177</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2347,13 +2322,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.1047691045609153</v>
+        <v>0.03639735396576806</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2367,25 +2342,25 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.22</v>
+        <v>0.79</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H43" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I43" s="14" t="n">
-        <v>294</v>
+      <c r="I43" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2393,13 +2368,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01982037726397964</v>
+        <v>0.03186933456120915</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2409,17 +2384,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>1.423</v>
+        <v>0.555</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1.355</v>
+        <v>0.588964</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.05018450184501849</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.06</v>
@@ -2427,11 +2402,11 @@
       <c r="H44" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I44" s="14" t="n">
-        <v>294</v>
+      <c r="I44" s="13" t="n">
+        <v>287</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46177</v>
+        <v>46243</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2439,13 +2414,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.03655865462755013</v>
+        <v>0.03789689195303377</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2455,29 +2430,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.8</v>
+        <v>0.29</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I45" s="14" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I45" s="13" t="n">
         <v>294</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46270</v>
+        <v>46450</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2485,13 +2460,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.03201921074472783</v>
+        <v>0.008837758232805483</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2501,29 +2476,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.555</v>
+        <v>2.33</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0.588964</v>
+        <v>2.3</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>294</v>
+        <v>46441</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>295</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46243</v>
+        <v>46456</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2531,13 +2506,13 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.03820998379180393</v>
+        <v>0.02911772179138039</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -2547,29 +2522,29 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.29</v>
+        <v>1.59</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.27</v>
+        <v>1.5</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>301</v>
+        <v>46452</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>306</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46450</v>
+        <v>46487</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2577,13 +2552,13 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.008561517108053597</v>
+        <v>0.01828479500193592</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -2593,29 +2568,29 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>302</v>
+        <v>46461</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>315</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46456</v>
+        <v>46300</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2623,45 +2598,45 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02780014914243102</v>
+        <v>0.01941873191358482</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.59</v>
+        <v>0.271</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.5</v>
+        <v>0.27</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>313</v>
+        <v>46461</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>315</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46487</v>
+        <v>46196</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2669,13 +2644,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.01997425255346736</v>
+        <v>0.05111600211565201</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2685,29 +2660,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1.5</v>
+        <v>1.089</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1.4</v>
+        <v>1.057</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>322</v>
+        <v>46488</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>342</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46300</v>
+        <v>46498</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2715,45 +2690,45 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.019392372716101</v>
+        <v>0.0301005432072106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.271</v>
+        <v>1.087</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.27</v>
+        <v>0.976</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>322</v>
+        <v>46492</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>346</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46196</v>
+        <v>46501</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2761,13 +2736,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.0510678389512458</v>
+        <v>0.02120148215905465</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2777,75 +2752,75 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.089</v>
+        <v>0.525</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.057</v>
+        <v>0.5</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>349</v>
+        <v>46492</v>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>346</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46498</v>
+        <v>46197</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Notion + yfinance</t>
+          <t>yfinance</t>
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02928206615253558</v>
+        <v>0.04235578706019035</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.087</v>
+        <v>1.3</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.976</v>
+        <v>1.24</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>353</v>
+        <v>46493</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>347</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46501</v>
+        <v>46530</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2853,13 +2828,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02119218228202975</v>
+        <v>0.02290547045254723</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2873,25 +2848,25 @@
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>354</v>
+        <v>46499</v>
+      </c>
+      <c r="I54" s="13" t="n">
+        <v>353</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46530</v>
+        <v>46526</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2899,13 +2874,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.02285916208230909</v>
+        <v>0.02894256994270739</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2919,25 +2894,25 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>360</v>
+        <v>46508</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>362</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46526</v>
+        <v>46517</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2945,7 +2920,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.03061716523663033</v>
+        <v>0.04635441830727234</v>
       </c>
     </row>
   </sheetData>
@@ -2980,44 +2955,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 04/27/2026</t>
+          <t>Expected Increase Announcements by Month - 05/04/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>February 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3048,39 +3023,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>April 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3096,7 +3071,7 @@
         <v>46140</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46190</v>
+        <v>46555</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>0.974</v>
@@ -3111,39 +3086,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3152,20 +3127,20 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46152</v>
+        <v>46198</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.1020408163265307</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3173,221 +3148,221 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>46198</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.0142857142857143</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>June 2026</t>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.05263157894736847</v>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>CLX</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>46246</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.01639344262295083</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n">
-        <v>46176</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>July 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>RGA</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
@@ -3395,86 +3370,86 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46263</v>
+        <v>46280</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.82</v>
+        <v>0.708</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
@@ -3482,86 +3457,86 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F34" s="24" t="inlineStr">
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46280</v>
+        <v>46305</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46303</v>
+        <v>46339</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.708</v>
+        <v>0.87</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3572,20 +3547,20 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46285</v>
+        <v>46311</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46325</v>
+        <v>46386</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.42</v>
+        <v>0.79</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3593,110 +3568,110 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>October 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F40" s="24" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>46317</v>
+        <v>46329</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>1.38</v>
+        <v>0.6</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
@@ -3707,20 +3682,20 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46322</v>
+        <v>46332</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.64</v>
+        <v>2.44</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3728,62 +3703,95 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>46347</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>46358</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>46329</v>
+        <v>46352</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>46338</v>
+        <v>46400</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.6</v>
+        <v>0.293</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
@@ -3791,95 +3799,62 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="C49" s="10" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.1401869158878504</v>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>46347</v>
+        <v>46360</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46358</v>
+        <v>46371</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
@@ -3890,20 +3865,20 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46352</v>
+        <v>46366</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46400</v>
+        <v>46432</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.293</v>
+        <v>2.52</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -3911,110 +3886,110 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="n">
+        <v>46370</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>46413</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.02380952380952383</v>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
-      <c r="A55" s="23" t="inlineStr">
-        <is>
-          <t>December 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D58" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F56" s="24" t="inlineStr">
+      <c r="F58" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C58" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>46370</v>
+        <v>46402</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46413</v>
+        <v>46483</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4025,20 +4000,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46371</v>
+        <v>46411</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46344</v>
+        <v>46435</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.23</v>
+        <v>0.703</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4046,86 +4021,86 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="23" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D63" s="24" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E63" s="24" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F63" s="24" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="C64" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="F64" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
-        <v>46411</v>
+        <v>46422</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46435</v>
+        <v>46472</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.703</v>
+        <v>1.275</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4136,83 +4111,116 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
-        <v>46417</v>
+        <v>46428</v>
       </c>
       <c r="C66" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.02362204724409451</v>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="D66" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F66" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="23" t="inlineStr">
-        <is>
-          <t>February 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="24" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C69" s="24" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E69" s="24" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F69" s="24" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="C69" s="10" t="n">
+        <v>46425</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0.6872012745618694</v>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B70" s="10" t="n">
-        <v>46422</v>
+        <v>46433</v>
       </c>
       <c r="C70" s="10" t="n">
-        <v>46472</v>
+        <v>46383</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>1.275</v>
+        <v>7.45</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>4.96</v>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
@@ -4223,20 +4231,20 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46452</v>
+        <v>46276</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>0.61</v>
+        <v>0.24</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4247,20 +4255,20 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B72" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46460</v>
+        <v>46177</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>1.3</v>
+        <v>1.423</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05018450184501849</v>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
@@ -4271,20 +4279,20 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46480</v>
+        <v>46270</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4295,20 +4303,20 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B74" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>46425</v>
+        <v>46243</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1.883</v>
+        <v>0.555</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
@@ -4319,20 +4327,20 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B75" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>7.45</v>
+        <v>0.29</v>
       </c>
       <c r="E75" s="8" t="n">
-        <v>4.96</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
@@ -4343,20 +4351,20 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B76" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>46276</v>
+        <v>46456</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>0.24</v>
+        <v>2.33</v>
       </c>
       <c r="E76" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
@@ -4364,95 +4372,62 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C77" s="10" t="n">
-        <v>46177</v>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0.05018450184501849</v>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C78" s="10" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0.01265822784810128</v>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C79" s="10" t="n">
-        <v>46243</v>
-      </c>
-      <c r="D79" s="7" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0.005735494868956323</v>
-      </c>
-      <c r="F79" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46440</v>
+        <v>46452</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46450</v>
+        <v>46487</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.29</v>
+        <v>1.59</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4463,20 +4438,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46441</v>
+        <v>46461</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46456</v>
+        <v>46300</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4484,86 +4459,86 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="23" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>46196</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.003703703703703707</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B84" s="24" t="inlineStr">
+      <c r="B85" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C84" s="24" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D84" s="24" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E84" s="24" t="inlineStr">
+      <c r="E85" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F84" s="24" t="inlineStr">
+      <c r="F85" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B86" s="10" t="n">
-        <v>46461</v>
+        <v>46488</v>
       </c>
       <c r="C86" s="10" t="n">
-        <v>46300</v>
+        <v>46498</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>1.5</v>
+        <v>1.089</v>
       </c>
       <c r="E86" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
@@ -4574,20 +4549,20 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B87" s="10" t="n">
-        <v>46461</v>
+        <v>46492</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46196</v>
+        <v>46501</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.271</v>
+        <v>1.087</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -4595,134 +4570,134 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="89">
-      <c r="A89" s="23" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>46493</v>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>46530</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.04838709677419359</v>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="n">
+        <v>46499</v>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>46526</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B90" s="24" t="inlineStr">
+      <c r="B93" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C90" s="24" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D90" s="24" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E90" s="24" t="inlineStr">
+      <c r="E93" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F90" s="24" t="inlineStr">
+      <c r="F93" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="C91" s="10" t="n">
-        <v>46498</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.03027436140018924</v>
-      </c>
-      <c r="F91" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C92" s="10" t="n">
-        <v>46501</v>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>1.087</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0.1137295081967213</v>
-      </c>
-      <c r="F92" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="C93" s="10" t="n">
-        <v>46530</v>
-      </c>
-      <c r="D93" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E93" s="8" t="n">
-        <v>0.04838709677419359</v>
-      </c>
-      <c r="F93" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B94" s="10" t="n">
-        <v>46499</v>
+        <v>46508</v>
       </c>
       <c r="C94" s="10" t="n">
-        <v>46526</v>
+        <v>46517</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.1020408163265307</v>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
@@ -4769,7 +4744,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 04/27/2026</t>
+          <t>Complete Holdings Dividend Summary - 05/04/2026</t>
         </is>
       </c>
     </row>
@@ -4869,11 +4844,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="16" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.008561517108053597</v>
+        <v>0.008837758232805483</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46090</v>
@@ -4922,11 +4897,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="16" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02907077430897583</v>
+        <v>0.030992498778321</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46066</v>
@@ -4959,12 +4934,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Feb/May</t>
+          <t>Feb/Apr/May/Nov</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -4973,19 +4948,19 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1.883</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>3.766</v>
+        <v>3.177</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.002626055610008967</v>
+        <v>0.008985741953404</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>46063</v>
+        <v>46139</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.01019313304721025</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>46433</v>
@@ -5028,11 +5003,11 @@
       <c r="F8" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="16" t="n">
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03730432611381523</v>
+        <v>0.03724503311258278</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46070</v>
@@ -5081,11 +5056,11 @@
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="16" t="n">
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02804852382638342</v>
+        <v>0.02846367348427877</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5134,11 +5109,11 @@
       <c r="F10" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="16" t="n">
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05085875336986107</v>
+        <v>0.05755395663072553</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46134</v>
@@ -5187,11 +5162,11 @@
       <c r="F11" s="7" t="n">
         <v>7.45</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="16" t="n">
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.1047691045609153</v>
+        <v>0.1034201569911252</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5240,11 +5215,11 @@
       <c r="F12" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02140032482159259</v>
+        <v>0.02120792939943494</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46072</v>
@@ -5293,11 +5268,11 @@
       <c r="F13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="16" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.007717290187350596</v>
+        <v>0.007863953539765047</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46066</v>
@@ -5346,11 +5321,11 @@
       <c r="F14" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="16" t="n">
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.01895095150229958</v>
+        <v>0.01807228933461354</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5399,11 +5374,11 @@
       <c r="F15" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="16" t="n">
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03812416391836682</v>
+        <v>0.03749045758210754</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46070</v>
@@ -5452,11 +5427,11 @@
       <c r="F16" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="16" t="n">
         <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01747390294878716</v>
+        <v>0.01798128714599146</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46118</v>
@@ -5505,11 +5480,11 @@
       <c r="F17" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01982037726397964</v>
+        <v>0.01886785057271592</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5558,11 +5533,11 @@
       <c r="F18" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="16" t="n">
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04653095198172495</v>
+        <v>0.04368742478236734</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5611,14 +5586,14 @@
       <c r="F19" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="16" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02240308108169822</v>
+        <v>0.02192813345130483</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>46062</v>
+        <v>46143</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.06666666666666674</v>
@@ -5664,11 +5639,11 @@
       <c r="F20" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="16" t="n">
         <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01997425255346736</v>
+        <v>0.01828479500193592</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46122</v>
@@ -5717,11 +5692,11 @@
       <c r="F21" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="16" t="n">
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02780014914243102</v>
+        <v>0.02911772179138039</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5770,11 +5745,11 @@
       <c r="F22" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="16" t="n">
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01513987906635631</v>
+        <v>0.01521331731813701</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5823,11 +5798,11 @@
       <c r="F23" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="16" t="n">
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05397190843953674</v>
+        <v>0.05557136043245535</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46125</v>
@@ -5876,11 +5851,11 @@
       <c r="F24" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="16" t="n">
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.02885545924901842</v>
+        <v>0.02992427681539705</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5929,11 +5904,11 @@
       <c r="F25" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="16" t="n">
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01610029660749452</v>
+        <v>0.01587456472419767</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5982,11 +5957,11 @@
       <c r="F26" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="16" t="n">
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02285916208230909</v>
+        <v>0.02290547045254723</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -6035,11 +6010,11 @@
       <c r="F27" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="16" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.019392372716101</v>
+        <v>0.01941873191358482</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46118</v>
@@ -6088,11 +6063,11 @@
       <c r="F28" s="7" t="n">
         <v>1.087</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="16" t="n">
         <v>2.174</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02119218228202975</v>
+        <v>0.02120148215905465</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46132</v>
@@ -6141,11 +6116,11 @@
       <c r="F29" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="16" t="n">
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01222247967649055</v>
+        <v>0.0118734494103574</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6194,11 +6169,11 @@
       <c r="F30" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="16" t="n">
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03404459436990546</v>
+        <v>0.03583370258558077</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6247,11 +6222,11 @@
       <c r="F31" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="16" t="n">
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.03731415667429284</v>
+        <v>0.03869407580269512</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46132</v>
@@ -6300,11 +6275,11 @@
       <c r="F32" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="16" t="n">
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008662541395183453</v>
+        <v>0.008761373116221174</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46072</v>
@@ -6353,11 +6328,11 @@
       <c r="F33" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="16" t="n">
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03434493071613531</v>
+        <v>0.0342823359941388</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46120</v>
@@ -6406,11 +6381,11 @@
       <c r="F34" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="16" t="n">
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03633543948128567</v>
+        <v>0.03723042062212387</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6459,11 +6434,11 @@
       <c r="F35" s="7" t="n">
         <v>1.275</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="16" t="n">
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.06160908522839336</v>
+        <v>0.0575101486518865</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6512,14 +6487,14 @@
       <c r="F36" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="16" t="n">
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.0510678389512458</v>
+        <v>0.05111600211565201</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0.003703703703703707</v>
@@ -6565,11 +6540,11 @@
       <c r="F37" s="7" t="n">
         <v>1.08</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="16" t="n">
         <v>4.32</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04790684617465937</v>
+        <v>0.04635441830727234</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46050</v>
@@ -6578,10 +6553,10 @@
         <v>0.1020408163265307</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>46143</v>
+        <v>46508</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>46152</v>
+        <v>46517</v>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
@@ -6618,11 +6593,11 @@
       <c r="F38" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="16" t="n">
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03655865462755013</v>
+        <v>0.03639735396576806</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6671,11 +6646,11 @@
       <c r="F39" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="16" t="n">
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06320044057895932</v>
+        <v>0.06502835351180732</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46045</v>
@@ -6724,11 +6699,11 @@
       <c r="F40" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="16" t="n">
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03201921074472783</v>
+        <v>0.03186933456120915</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6777,11 +6752,11 @@
       <c r="F41" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="16" t="n">
         <v>4.356</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.02928206615253558</v>
+        <v>0.0301005432072106</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46136</v>
@@ -6802,53 +6777,53 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>QDVD/SMID/DAC</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="F42" s="17" t="n">
+      <c r="F42" s="7" t="n">
         <v>0.525</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G42" s="16" t="n">
         <v>2.1</v>
       </c>
-      <c r="H42" s="19" t="n">
-        <v>0.04078857871427848</v>
-      </c>
-      <c r="I42" s="20" t="n">
+      <c r="H42" s="9" t="n">
+        <v>0.04235578706019035</v>
+      </c>
+      <c r="I42" s="10" t="n">
         <v>46104</v>
       </c>
-      <c r="J42" s="18" t="n">
+      <c r="J42" s="8" t="n">
         <v>0.05000000000000004</v>
       </c>
-      <c r="K42" s="20" t="n">
-        <v>46176</v>
-      </c>
-      <c r="L42" s="20" t="n">
+      <c r="K42" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="L42" s="10" t="n">
         <v>46197</v>
       </c>
-      <c r="M42" s="22" t="inlineStr">
+      <c r="M42" s="12" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -6883,11 +6858,11 @@
       <c r="F43" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G43" s="25" t="n">
+      <c r="G43" s="16" t="n">
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.03061716523663033</v>
+        <v>0.02894256994270739</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46076</v>
@@ -6936,11 +6911,11 @@
       <c r="F44" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="16" t="n">
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01770164219863074</v>
+        <v>0.01773201829949195</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46070</v>
@@ -6989,11 +6964,11 @@
       <c r="F45" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="16" t="n">
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02590474067531757</v>
+        <v>0.02582659671485322</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46077</v>
@@ -7042,11 +7017,11 @@
       <c r="F46" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="16" t="n">
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04208391463665842</v>
+        <v>0.04247696832708157</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46091</v>
@@ -7095,11 +7070,11 @@
       <c r="F47" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="16" t="n">
         <v>5.2</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05239030924280169</v>
+        <v>0.05057381847338947</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46097</v>
@@ -7148,11 +7123,11 @@
       <c r="F48" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="16" t="n">
         <v>3.896</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.04327446465428495</v>
+        <v>0.04255133359420153</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46112</v>
@@ -7164,7 +7139,7 @@
         <v>46140</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46190</v>
+        <v>46555</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7201,11 +7176,11 @@
       <c r="F49" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="16" t="n">
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.02084135954529386</v>
+        <v>0.02028028118339007</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46052</v>
@@ -7254,11 +7229,11 @@
       <c r="F50" s="7" t="n">
         <v>0.555</v>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="16" t="n">
         <v>2.22</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03820998379180393</v>
+        <v>0.03789689195303377</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46080</v>
@@ -7307,11 +7282,11 @@
       <c r="F51" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G51" s="16" t="n">
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.0205977842499729</v>
+        <v>0.02081722633876427</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7360,11 +7335,11 @@
       <c r="F52" s="7" t="n">
         <v>1.64</v>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="16" t="n">
         <v>6.56</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06094388737641394</v>
+        <v>0.06627266716725133</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46070</v>
@@ -7413,11 +7388,11 @@
       <c r="F53" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G53" s="25" t="n">
+      <c r="G53" s="16" t="n">
         <v>2.832</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.05880398689727525</v>
+        <v>0.05969646041274478</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46122</v>
@@ -7466,11 +7441,11 @@
       <c r="F54" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="16" t="n">
         <v>4.12</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.02741001973866671</v>
+        <v>0.02716065616513814</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46065</v>
@@ -7493,252 +7468,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4624C93C-24C1-4E35-9BED-B6DE663E2ECF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D951A183-83FE-49AA-BF5F-B471344742F8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26D25A5B-8C48-43FA-9943-0C7D65EA1BB7}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -7468,4 +7468,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123FB276-79FB-4CA8-AD69-1A76076D0F8D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1964285-05F4-49CE-8EBF-50A81CC132D6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33583B90-AA89-4198-8DE1-673A4D768C4C}"/>
 </file>
--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,12 +84,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00856404"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001a3a5c"/>
       <sz val="12"/>
     </font>
@@ -100,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -122,11 +116,6 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -145,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,14 +152,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -564,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 05/18/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 05/25/2026</t>
         </is>
       </c>
     </row>
@@ -640,7 +626,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -654,25 +640,25 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.974</v>
+        <v>0.71</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.831</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>46555</v>
+        <v>46563</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
@@ -680,13 +666,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.04214634983756138</v>
+        <v>0.03613231622307302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -696,29 +682,29 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>46162</v>
+        <v>46218</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>46198</v>
+        <v>46248</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
@@ -726,13 +712,13 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.03683050158890475</v>
+        <v>0.01737992953039871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -746,25 +732,25 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.89</v>
+        <v>1.34</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>58</v>
+        <v>46220</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>53</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
@@ -772,13 +758,13 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.01731682279661019</v>
+        <v>0.02076124529346597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -788,29 +774,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1.34</v>
+        <v>0.82</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I9" s="14" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I9" s="13" t="n">
         <v>60</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -818,13 +804,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.02021459644759173</v>
+        <v>0.04342139732871405</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -834,29 +820,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.05263157894736847</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>67</v>
+        <v>46232</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>65</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -864,13 +850,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.04394149939236475</v>
+        <v>0.02869852102073829</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -884,25 +870,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.95</v>
+        <v>1.22</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I11" s="14" t="n">
-        <v>72</v>
+      <c r="I11" s="13" t="n">
+        <v>65</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46264</v>
+        <v>46246</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -910,13 +896,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02926115646889512</v>
+        <v>0.05215014160624624</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -926,29 +912,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>72</v>
+        <v>46263</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>96</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46246</v>
+        <v>46297</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -956,13 +942,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05358107395864369</v>
+        <v>0.03202812110838314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -972,29 +958,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>103</v>
+        <v>46278</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>111</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46297</v>
+        <v>46344</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1002,13 +988,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03172146955122707</v>
+        <v>0.008696275261740157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1018,29 +1004,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>118</v>
+        <v>46280</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>113</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46344</v>
+        <v>46303</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1048,13 +1034,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.008624979291824134</v>
+        <v>0.05857290774302305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1068,25 +1054,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>120</v>
+        <v>46285</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>118</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1094,13 +1080,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.06147167394746399</v>
+        <v>0.01836939347681198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1110,29 +1096,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>125</v>
+        <v>46305</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>138</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1140,13 +1126,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.0188588410646018</v>
+        <v>0.03267605633802817</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1156,29 +1142,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>145</v>
+        <v>46311</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>144</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1186,13 +1172,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.03312392995306462</v>
+        <v>0.011995596886681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1202,29 +1188,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>151</v>
+        <v>46317</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>150</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1232,13 +1218,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01208043490409386</v>
+        <v>0.01721610552954179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1252,25 +1238,25 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>157</v>
+        <v>46322</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>155</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1278,13 +1264,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.01686526185724039</v>
+        <v>0.02277580040255237</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1298,21 +1284,21 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I20" s="14" t="n">
+        <v>46329</v>
+      </c>
+      <c r="I20" s="13" t="n">
         <v>162</v>
       </c>
       <c r="J20" s="10" t="n">
@@ -1324,13 +1310,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02337365865633077</v>
+        <v>0.008730129744386562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1344,25 +1330,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>169</v>
+        <v>46332</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>165</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1370,13 +1356,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.00922988195879138</v>
+        <v>0.02661939223366119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1390,25 +1376,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>172</v>
+        <v>46341</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>174</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1416,13 +1402,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02692933862328275</v>
+        <v>0.02659437160273528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1432,29 +1418,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>181</v>
+        <v>46344</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>177</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1462,13 +1448,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02639418282315602</v>
+        <v>0.04016736465785078</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1482,25 +1468,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>184</v>
+        <v>46347</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>180</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1508,13 +1494,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.04072110154537709</v>
+        <v>0.03671367958864462</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1524,29 +1510,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>187</v>
+        <v>46352</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>185</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1554,13 +1540,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03883587099965592</v>
+        <v>0.05517890831588747</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1570,29 +1556,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>192</v>
+        <v>46360</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>193</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1600,13 +1586,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.05813492107493477</v>
+        <v>0.04533189254576684</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1616,29 +1602,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>200</v>
+        <v>46366</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>199</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1646,13 +1632,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.04713804794530811</v>
+        <v>0.02970822388048694</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1662,29 +1648,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2.52</v>
+        <v>0.43</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2.38</v>
+        <v>0.42</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>206</v>
+        <v>46370</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>203</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46432</v>
+        <v>46413</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1692,13 +1678,13 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.03101729232332405</v>
+        <v>0.06640926738737934</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1708,29 +1694,29 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.43</v>
+        <v>0.23</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>210</v>
+        <v>46371</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>204</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>46413</v>
+        <v>46344</v>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
@@ -1738,13 +1724,13 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.06783671982067387</v>
+        <v>0.02148026991987978</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1754,29 +1740,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>211</v>
+        <v>46402</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>235</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46344</v>
+        <v>46483</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1784,13 +1770,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.02206764284733259</v>
+        <v>0.01762204744474112</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1800,29 +1786,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.8</v>
+        <v>0.676</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>242</v>
+        <v>46411</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>244</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1830,13 +1816,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01807957072978263</v>
+        <v>0.03785166193761971</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1850,25 +1836,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.676</v>
+        <v>1.71</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>251</v>
+        <v>46417</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>250</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1876,45 +1862,45 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03765399020499349</v>
+        <v>0.0371937537084845</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1.78</v>
+        <v>1.275</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>257</v>
+        <v>46422</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>255</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1922,18 +1908,18 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03735180034824172</v>
+        <v>0.05671708300547242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1942,25 +1928,25 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1.275</v>
+        <v>0.61</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>262</v>
+        <v>46428</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>261</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46472</v>
+        <v>46452</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1968,13 +1954,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.05665407898449212</v>
+        <v>0.01740495012131711</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1988,13 +1974,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0.08</v>
@@ -2002,11 +1988,11 @@
       <c r="H35" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I35" s="14" t="n">
-        <v>268</v>
+      <c r="I35" s="13" t="n">
+        <v>261</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2014,13 +2000,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01760334744430971</v>
+        <v>0.05029499981330527</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2030,29 +2016,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>268</v>
+        <v>46431</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>264</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2060,13 +2046,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.05068720329098433</v>
+        <v>0.01395232911639436</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2076,29 +2062,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.42</v>
+        <v>3.177</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.41</v>
+        <v>1.883</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>271</v>
+        <v>46433</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46480</v>
+        <v>46425</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2106,13 +2092,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.0144069976091816</v>
+        <v>0.007782472784615239</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2122,29 +2108,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.177</v>
+        <v>7.45</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I38" s="14" t="n">
-        <v>273</v>
+      <c r="I38" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2152,13 +2138,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.008584514566529328</v>
+        <v>0.102324619290005</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2168,17 +2154,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>7.45</v>
+        <v>0.24</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.25</v>
+        <v>0.22</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.96</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0.06</v>
@@ -2186,11 +2172,11 @@
       <c r="H39" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I39" s="14" t="n">
-        <v>273</v>
+      <c r="I39" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46383</v>
+        <v>46276</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2198,13 +2184,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.09787821334941105</v>
+        <v>0.02033036796236036</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2218,25 +2204,25 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.22</v>
+        <v>0.79</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I40" s="14" t="n">
-        <v>273</v>
+      <c r="I40" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2244,13 +2230,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.01966810024564586</v>
+        <v>0.03081367402039418</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2260,29 +2246,29 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.8</v>
+        <v>0.545</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.79</v>
+        <v>0.588964</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I41" s="14" t="n">
-        <v>273</v>
+      <c r="I41" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2290,13 +2276,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03145272328671384</v>
+        <v>0.03801220676551045</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2306,29 +2292,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I42" s="14" t="n">
+        <v>46440</v>
+      </c>
+      <c r="I42" s="13" t="n">
         <v>273</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2336,13 +2322,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03791304347826088</v>
+        <v>0.01055793183764243</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2356,25 +2342,25 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>280</v>
+        <v>46441</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>274</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2382,13 +2368,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.009968633363084246</v>
+        <v>0.02976969937062066</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2398,29 +2384,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>281</v>
+        <v>46452</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>285</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2428,13 +2414,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.03076339202025604</v>
+        <v>0.01854822166962447</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2444,29 +2430,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>292</v>
+        <v>46461</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>294</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2474,45 +2460,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.01879404861908646</v>
+        <v>0.01958352341659811</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I46" s="14" t="n">
-        <v>301</v>
+      <c r="I46" s="13" t="n">
+        <v>294</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46300</v>
+        <v>46196</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2520,45 +2506,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01995145073922394</v>
+        <v>0.05243469809734441</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.271</v>
+        <v>1.089</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.27</v>
+        <v>1.057</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>301</v>
+        <v>46488</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>321</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46196</v>
+        <v>46498</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2566,18 +2552,18 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.05273655966461101</v>
+        <v>0.03015785050105535</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2586,25 +2572,25 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.089</v>
+        <v>1.087</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.057</v>
+        <v>0.976</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>328</v>
+        <v>46492</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>325</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2612,59 +2598,59 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.03023110632736219</v>
+        <v>0.0202817422379329</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.087</v>
+        <v>0.525</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.976</v>
+        <v>0.5</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I49" s="14" t="n">
-        <v>332</v>
+      <c r="I49" s="13" t="n">
+        <v>325</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46501</v>
+        <v>46197</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Notion + yfinance</t>
+          <t>yfinance</t>
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02067915967656243</v>
+        <v>0.04215174654483525</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2674,37 +2660,37 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.525</v>
+        <v>0.974</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.5</v>
+        <v>0.994</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I50" s="14" t="n">
-        <v>332</v>
+      <c r="I50" s="13" t="n">
+        <v>325</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46197</v>
+        <v>46376</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>Notion + yfinance</t>
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.04357298502536404</v>
+        <v>0.04253275180021647</v>
       </c>
     </row>
     <row r="51">
@@ -2738,8 +2724,8 @@
       <c r="H51" s="10" t="n">
         <v>46493</v>
       </c>
-      <c r="I51" s="14" t="n">
-        <v>333</v>
+      <c r="I51" s="13" t="n">
+        <v>326</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46530</v>
@@ -2750,7 +2736,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.02284609633168951</v>
+        <v>0.02218998071717222</v>
       </c>
     </row>
     <row r="52">
@@ -2784,8 +2770,8 @@
       <c r="H52" s="10" t="n">
         <v>46499</v>
       </c>
-      <c r="I52" s="14" t="n">
-        <v>339</v>
+      <c r="I52" s="13" t="n">
+        <v>332</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46526</v>
@@ -2796,7 +2782,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02921891166551359</v>
+        <v>0.02858911548315806</v>
       </c>
     </row>
     <row r="53">
@@ -2830,8 +2816,8 @@
       <c r="H53" s="10" t="n">
         <v>46508</v>
       </c>
-      <c r="I53" s="14" t="n">
-        <v>348</v>
+      <c r="I53" s="13" t="n">
+        <v>341</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46518</v>
@@ -2842,7 +2828,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.05108118393206977</v>
+        <v>0.04907216494845361</v>
       </c>
     </row>
     <row r="54">
@@ -2876,8 +2862,8 @@
       <c r="H54" s="10" t="n">
         <v>46517</v>
       </c>
-      <c r="I54" s="14" t="n">
-        <v>357</v>
+      <c r="I54" s="13" t="n">
+        <v>350</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46542</v>
@@ -2888,7 +2874,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.03806082513724484</v>
+        <v>0.03780301337001037</v>
       </c>
     </row>
   </sheetData>
@@ -2902,7 +2888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2923,44 +2909,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 05/18/2026</t>
+          <t>Expected Increase Announcements by Month - 05/25/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>April 2026</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2969,20 +2955,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46555</v>
+        <v>46563</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.974</v>
+        <v>0.71</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.0142857142857143</v>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
@@ -2991,39 +2977,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>May 2026</t>
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3032,20 +3018,20 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46162</v>
+        <v>46218</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46198</v>
+        <v>46248</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
@@ -3053,62 +3039,95 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>July 2026</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.05263157894736847</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
@@ -3116,95 +3135,62 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.05263157894736847</v>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>46246</v>
+        <v>46297</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
@@ -3213,39 +3199,39 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3254,20 +3240,20 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46263</v>
+        <v>46278</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46297</v>
+        <v>46344</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
@@ -3275,110 +3261,110 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0.02608695652173916</v>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.09638554216867479</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C27" s="10" t="n">
-        <v>46303</v>
-      </c>
-      <c r="D27" s="7" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.02608695652173916</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46285</v>
+        <v>46305</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
@@ -3386,134 +3372,134 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>LECO</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>46386</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0.05333333333333338</v>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>46351</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.02222222222222208</v>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>46338</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0.06666666666666674</v>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>MSM</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C32" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.0235294117647059</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>LECO</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.05333333333333338</v>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>46351</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.02222222222222208</v>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="C35" s="10" t="n">
         <v>46338</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
@@ -3521,62 +3507,95 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>SNA</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>46332</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>46346</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.1401869158878504</v>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>November 2026</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46329</v>
+        <v>46347</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46338</v>
+        <v>46358</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -3587,20 +3606,20 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>46332</v>
+        <v>46352</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>46346</v>
+        <v>46400</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2.44</v>
+        <v>0.293</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -3608,95 +3627,62 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>46358</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3704,134 +3690,134 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0.05882352941176476</v>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>46370</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>46413</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.02380952380952383</v>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>CNP</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>EMN</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="C48" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.01204819277108435</v>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="C49" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.05882352941176476</v>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>46413</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.02380952380952383</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>46371</v>
+        <v>46402</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46344</v>
+        <v>46483</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.23</v>
+        <v>0.86</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.0454545454545455</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -3839,110 +3825,110 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>BKH</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>46411</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.03994082840236673</v>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>January 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>46417</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0.04093567251461992</v>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C56" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="D56" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="F56" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>BKH</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46435</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.03994082840236673</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>46417</v>
+        <v>46422</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1.78</v>
+        <v>1.275</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -3950,62 +3936,95 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.05172413793103453</v>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>46460</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0.02362204724409451</v>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n">
+        <v>46431</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>46480</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.02439024390243905</v>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46422</v>
+        <v>46433</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46472</v>
+        <v>46425</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1.275</v>
+        <v>3.177</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4016,20 +4035,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46452</v>
+        <v>46383</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>0.61</v>
+        <v>7.45</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>4.96</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4040,20 +4059,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
-        <v>46428</v>
+        <v>46433</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46460</v>
+        <v>46276</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.3</v>
+        <v>0.24</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.09090909090909087</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4064,20 +4083,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46431</v>
+        <v>46433</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46480</v>
+        <v>46270</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4088,20 +4107,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46425</v>
+        <v>46243</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>3.177</v>
+        <v>0.545</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4112,20 +4131,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46383</v>
+        <v>46450</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>7.45</v>
+        <v>0.29</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>4.96</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4136,20 +4155,20 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>46433</v>
+        <v>46441</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46276</v>
+        <v>46456</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.24</v>
+        <v>2.33</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
@@ -4157,95 +4176,62 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>46270</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0.01265822784810128</v>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>UL</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>46243</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.005735494868956323</v>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>ALSN</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>46450</v>
-      </c>
-      <c r="D70" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>0.07407407407407393</v>
-      </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B71" s="10" t="n">
-        <v>46441</v>
+        <v>46452</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E71" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
@@ -4253,110 +4239,110 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.07142857142857149</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="73">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>March 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>46196</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.003703703703703707</v>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B74" s="16" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C76" s="15" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E76" s="15" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="F76" s="15" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C76" s="10" t="n">
-        <v>46300</v>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.07142857142857149</v>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B77" s="10" t="n">
-        <v>46461</v>
+        <v>46488</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46196</v>
+        <v>46498</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.271</v>
+        <v>1.089</v>
       </c>
       <c r="E77" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
@@ -4364,62 +4350,95 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>KOF</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>46501</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.1137295081967213</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="79">
-      <c r="A79" s="15" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C79" s="10" t="n">
+        <v>46197</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E80" s="16" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>46376</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.001006036217303824</v>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46488</v>
+        <v>46493</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46498</v>
+        <v>46530</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.089</v>
+        <v>1.3</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.04838709677419359</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4430,20 +4449,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46492</v>
+        <v>46499</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46501</v>
+        <v>46526</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.087</v>
+        <v>1.27</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4451,160 +4470,88 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46197</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46530</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.04838709677419359</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>May 2027</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>PSX</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>46526</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.05833333333333339</v>
-      </c>
-      <c r="F85" s="12" t="inlineStr">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="15" t="inlineStr">
-        <is>
-          <t>May 2027</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="16" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F88" s="16" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>46518</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.1018518518518517</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n">
+      <c r="B87" s="10" t="n">
         <v>46517</v>
       </c>
-      <c r="C90" s="10" t="n">
+      <c r="C87" s="10" t="n">
         <v>46542</v>
       </c>
-      <c r="D90" s="7" t="n">
+      <c r="D87" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="E90" s="8" t="n">
+      <c r="E87" s="8" t="n">
         <v>0.05018450184501849</v>
       </c>
-      <c r="F90" s="12" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4649,7 +4596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 05/18/2026</t>
+          <t>Complete Holdings Dividend Summary - 05/25/2026</t>
         </is>
       </c>
     </row>
@@ -4749,14 +4696,14 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009968633363084246</v>
+        <v>0.01055793183764243</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>46090</v>
+        <v>46160</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>0.07407407407407393</v>
@@ -4802,11 +4749,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.03101729232332405</v>
+        <v>0.02970822388048694</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -4855,11 +4802,11 @@
       <c r="F7" s="7" t="n">
         <v>3.177</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="16" t="n">
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.008584514566529328</v>
+        <v>0.007782472784615239</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -4908,11 +4855,11 @@
       <c r="F8" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03765399020499349</v>
+        <v>0.03785166193761971</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46157</v>
@@ -4961,11 +4908,11 @@
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02926115646889512</v>
+        <v>0.02869852102073829</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46080</v>
@@ -5014,11 +4961,11 @@
       <c r="F10" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="16" t="n">
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05358107395864369</v>
+        <v>0.05215014160624624</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46134</v>
@@ -5067,11 +5014,11 @@
       <c r="F11" s="7" t="n">
         <v>7.45</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.09787821334941105</v>
+        <v>0.102324619290005</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5120,14 +5067,14 @@
       <c r="F12" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02206764284733259</v>
+        <v>0.02148026991987978</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>46072</v>
+        <v>46163</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>0.0454545454545455</v>
@@ -5173,11 +5120,11 @@
       <c r="F13" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.00922988195879138</v>
+        <v>0.008730129744386562</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46157</v>
@@ -5226,11 +5173,11 @@
       <c r="F14" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="16" t="n">
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.0144069976091816</v>
+        <v>0.01395232911639436</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5279,14 +5226,14 @@
       <c r="F15" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="16" t="n">
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.03735180034824172</v>
+        <v>0.0371937537084845</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>46070</v>
+        <v>46161</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0.04093567251461992</v>
@@ -5332,11 +5279,11 @@
       <c r="F16" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="16" t="n">
         <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01807957072978263</v>
+        <v>0.01762204744474112</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46118</v>
@@ -5385,11 +5332,11 @@
       <c r="F17" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="16" t="n">
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01966810024564586</v>
+        <v>0.02033036796236036</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5438,11 +5385,11 @@
       <c r="F18" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="16" t="n">
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04713804794530811</v>
+        <v>0.04533189254576684</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5491,11 +5438,11 @@
       <c r="F19" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="16" t="n">
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02337365865633077</v>
+        <v>0.02277580040255237</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46143</v>
@@ -5544,11 +5491,11 @@
       <c r="F20" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="16" t="n">
         <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01879404861908646</v>
+        <v>0.01854822166962447</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46122</v>
@@ -5597,11 +5544,11 @@
       <c r="F21" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="16" t="n">
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.03076339202025604</v>
+        <v>0.02976969937062066</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5650,11 +5597,11 @@
       <c r="F22" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="16" t="n">
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01686526185724039</v>
+        <v>0.01721610552954179</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46080</v>
@@ -5703,11 +5650,11 @@
       <c r="F23" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="16" t="n">
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05813492107493477</v>
+        <v>0.05517890831588747</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46125</v>
@@ -5756,11 +5703,11 @@
       <c r="F24" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="16" t="n">
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.03172146955122707</v>
+        <v>0.03202812110838314</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5809,11 +5756,11 @@
       <c r="F25" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="16" t="n">
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01760334744430971</v>
+        <v>0.01740495012131711</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5862,11 +5809,11 @@
       <c r="F26" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="16" t="n">
         <v>5.2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02284609633168951</v>
+        <v>0.02218998071717222</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46077</v>
@@ -5915,11 +5862,11 @@
       <c r="F27" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="16" t="n">
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01995145073922394</v>
+        <v>0.01958352341659811</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46118</v>
@@ -5968,11 +5915,11 @@
       <c r="F28" s="7" t="n">
         <v>1.087</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="16" t="n">
         <v>2.174</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02067915967656243</v>
+        <v>0.0202817422379329</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46132</v>
@@ -6021,11 +5968,11 @@
       <c r="F29" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="16" t="n">
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01208043490409386</v>
+        <v>0.011995596886681</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6074,11 +6021,11 @@
       <c r="F30" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="16" t="n">
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03683050158890475</v>
+        <v>0.03613231622307302</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6090,7 +6037,7 @@
         <v>46162</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>46198</v>
+        <v>46563</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
@@ -6127,11 +6074,11 @@
       <c r="F31" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="16" t="n">
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.04072110154537709</v>
+        <v>0.04016736465785078</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46132</v>
@@ -6180,14 +6127,14 @@
       <c r="F32" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G32" s="17" t="n">
+      <c r="G32" s="16" t="n">
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008624979291824134</v>
+        <v>0.008696275261740157</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>46072</v>
+        <v>46163</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>0.09638554216867479</v>
@@ -6233,11 +6180,11 @@
       <c r="F33" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G33" s="17" t="n">
+      <c r="G33" s="16" t="n">
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03312392995306462</v>
+        <v>0.03267605633802817</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46120</v>
@@ -6286,11 +6233,11 @@
       <c r="F34" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="16" t="n">
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03883587099965592</v>
+        <v>0.03671367958864462</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6339,11 +6286,11 @@
       <c r="F35" s="7" t="n">
         <v>1.275</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="16" t="n">
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.05665407898449212</v>
+        <v>0.05671708300547242</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6392,11 +6339,11 @@
       <c r="F36" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G36" s="17" t="n">
+      <c r="G36" s="16" t="n">
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05273655966461101</v>
+        <v>0.05243469809734441</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46142</v>
@@ -6445,11 +6392,11 @@
       <c r="F37" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G37" s="17" t="n">
+      <c r="G37" s="16" t="n">
         <v>4.76</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.05108118393206977</v>
+        <v>0.04907216494845361</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46155</v>
@@ -6498,11 +6445,11 @@
       <c r="F38" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="G38" s="17" t="n">
+      <c r="G38" s="16" t="n">
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03806082513724484</v>
+        <v>0.03780301337001037</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6551,11 +6498,11 @@
       <c r="F39" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G39" s="17" t="n">
+      <c r="G39" s="16" t="n">
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06783671982067387</v>
+        <v>0.06640926738737934</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46150</v>
@@ -6604,11 +6551,11 @@
       <c r="F40" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="G40" s="17" t="n">
+      <c r="G40" s="16" t="n">
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03145272328671384</v>
+        <v>0.03081367402039418</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6657,11 +6604,11 @@
       <c r="F41" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G41" s="17" t="n">
+      <c r="G41" s="16" t="n">
         <v>4.356</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03023110632736219</v>
+        <v>0.03015785050105535</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46136</v>
@@ -6710,11 +6657,11 @@
       <c r="F42" s="7" t="n">
         <v>0.525</v>
       </c>
-      <c r="G42" s="17" t="n">
+      <c r="G42" s="16" t="n">
         <v>2.1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04357298502536404</v>
+        <v>0.04215174654483525</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46104</v>
@@ -6763,14 +6710,14 @@
       <c r="F43" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G43" s="17" t="n">
+      <c r="G43" s="16" t="n">
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02921891166551359</v>
+        <v>0.02858911548315806</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>46076</v>
+        <v>46160</v>
       </c>
       <c r="J43" s="8" t="n">
         <v>0.05833333333333339</v>
@@ -6816,14 +6763,14 @@
       <c r="F44" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G44" s="17" t="n">
+      <c r="G44" s="16" t="n">
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01731682279661019</v>
+        <v>0.01737992953039871</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>46070</v>
+        <v>46161</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>0.04494382022471914</v>
@@ -6869,14 +6816,14 @@
       <c r="F45" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G45" s="17" t="n">
+      <c r="G45" s="16" t="n">
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02692933862328275</v>
+        <v>0.02661939223366119</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46077</v>
+        <v>46162</v>
       </c>
       <c r="J45" s="8" t="n">
         <v>0.1401869158878504</v>
@@ -6922,11 +6869,11 @@
       <c r="F46" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G46" s="17" t="n">
+      <c r="G46" s="16" t="n">
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04394149939236475</v>
+        <v>0.04342139732871405</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46091</v>
@@ -6975,11 +6922,11 @@
       <c r="F47" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G47" s="17" t="n">
+      <c r="G47" s="16" t="n">
         <v>5.2</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05068720329098433</v>
+        <v>0.05029499981330527</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46097</v>
@@ -7022,29 +6969,29 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="G48" s="16" t="n">
         <v>3.896</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.04214634983756138</v>
+        <v>0.04253275180021647</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46112</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.2021660649819495</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46140</v>
+        <v>46492</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46555</v>
+        <v>46376</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7081,11 +7028,11 @@
       <c r="F49" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="16" t="n">
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.0188588410646018</v>
+        <v>0.01836939347681198</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46147</v>
@@ -7134,11 +7081,11 @@
       <c r="F50" s="7" t="n">
         <v>0.545</v>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="16" t="n">
         <v>2.18</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03791304347826088</v>
+        <v>0.03801220676551045</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46157</v>
@@ -7187,11 +7134,11 @@
       <c r="F51" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G51" s="17" t="n">
+      <c r="G51" s="16" t="n">
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02021459644759173</v>
+        <v>0.02076124529346597</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46080</v>
@@ -7240,11 +7187,11 @@
       <c r="F52" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G52" s="16" t="n">
         <v>2.832</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.06147167394746399</v>
+        <v>0.05857290774302305</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46122</v>
@@ -7293,11 +7240,11 @@
       <c r="F53" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="16" t="n">
         <v>4.12</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02639418282315602</v>
+        <v>0.02659437160273528</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 05/25/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/01/2026</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         <v>46162</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46563</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.03613231622307302</v>
+        <v>0.03798822791396991</v>
       </c>
     </row>
     <row r="7">
@@ -701,7 +701,7 @@
         <v>46218</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46248</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.01737992953039871</v>
+        <v>0.01859581611162467</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         <v>46220</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46264</v>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02076124529346597</v>
+        <v>0.02116402056970356</v>
       </c>
     </row>
     <row r="9">
@@ -793,7 +793,7 @@
         <v>46227</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>46267</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.04342139732871405</v>
+        <v>0.04297178239972002</v>
       </c>
     </row>
     <row r="10">
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>0.95</v>
-      </c>
       <c r="F10" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
@@ -839,7 +839,7 @@
         <v>46232</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46264</v>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02869852102073829</v>
+        <v>0.03043622674109861</v>
       </c>
     </row>
     <row r="11">
@@ -885,7 +885,7 @@
         <v>46232</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46246</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.05215014160624624</v>
+        <v>0.05544997394320728</v>
       </c>
     </row>
     <row r="12">
@@ -931,7 +931,7 @@
         <v>46263</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46297</v>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.03202812110838314</v>
+        <v>0.03260437425199132</v>
       </c>
     </row>
     <row r="13">
@@ -977,7 +977,7 @@
         <v>46278</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46344</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.008696275261740157</v>
+        <v>0.007827956989247311</v>
       </c>
     </row>
     <row r="14">
@@ -1023,7 +1023,7 @@
         <v>46280</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46303</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.05857290774302305</v>
+        <v>0.05932132175180416</v>
       </c>
     </row>
     <row r="15">
@@ -1069,7 +1069,7 @@
         <v>46285</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46325</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01836939347681198</v>
+        <v>0.01952493873877673</v>
       </c>
     </row>
     <row r="16">
@@ -1115,7 +1115,7 @@
         <v>46305</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46339</v>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.03267605633802817</v>
+        <v>0.03207668972737766</v>
       </c>
     </row>
     <row r="17">
@@ -1161,7 +1161,7 @@
         <v>46311</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46386</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.011995596886681</v>
+        <v>0.01247717304408395</v>
       </c>
     </row>
     <row r="18">
@@ -1207,7 +1207,7 @@
         <v>46317</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46351</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01721610552954179</v>
+        <v>0.01850982488567165</v>
       </c>
     </row>
     <row r="19">
@@ -1253,7 +1253,7 @@
         <v>46322</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46338</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02277580040255237</v>
+        <v>0.023931943262468</v>
       </c>
     </row>
     <row r="20">
@@ -1299,7 +1299,7 @@
         <v>46329</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46338</v>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.008730129744386562</v>
+        <v>0.008972130483968787</v>
       </c>
     </row>
     <row r="21">
@@ -1345,7 +1345,7 @@
         <v>46332</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46346</v>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02661939223366119</v>
+        <v>0.02652642468034239</v>
       </c>
     </row>
     <row r="22">
@@ -1391,7 +1391,7 @@
         <v>46341</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46339</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02659437160273528</v>
+        <v>0.0276510067114094</v>
       </c>
     </row>
     <row r="23">
@@ -1437,7 +1437,7 @@
         <v>46344</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46385</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.04016736465785078</v>
+        <v>0.0406177275525001</v>
       </c>
     </row>
     <row r="24">
@@ -1483,7 +1483,7 @@
         <v>46347</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46358</v>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03671367958864462</v>
+        <v>0.03578441925543904</v>
       </c>
     </row>
     <row r="25">
@@ -1529,7 +1529,7 @@
         <v>46352</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46400</v>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.05517890831588747</v>
+        <v>0.0502572905376204</v>
       </c>
     </row>
     <row r="26">
@@ -1575,7 +1575,7 @@
         <v>46360</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46371</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04533189254576684</v>
+        <v>0.04449447165672079</v>
       </c>
     </row>
     <row r="27">
@@ -1621,7 +1621,7 @@
         <v>46366</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46432</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02970822388048694</v>
+        <v>0.0304605330321046</v>
       </c>
     </row>
     <row r="28">
@@ -1667,7 +1667,7 @@
         <v>46370</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46413</v>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.06640926738737934</v>
+        <v>0.06686882792307368</v>
       </c>
     </row>
     <row r="29">
@@ -1713,7 +1713,7 @@
         <v>46371</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46344</v>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02148026991987978</v>
+        <v>0.02198064771382014</v>
       </c>
     </row>
     <row r="30">
@@ -1759,7 +1759,7 @@
         <v>46402</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46483</v>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.01762204744474112</v>
+        <v>0.01754699192598384</v>
       </c>
     </row>
     <row r="31">
@@ -1805,7 +1805,7 @@
         <v>46411</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46435</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.03785166193761971</v>
+        <v>0.03916980030838525</v>
       </c>
     </row>
     <row r="32">
@@ -1851,7 +1851,7 @@
         <v>46417</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46433</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.0371937537084845</v>
+        <v>0.0382940836807255</v>
       </c>
     </row>
     <row r="33">
@@ -1897,7 +1897,7 @@
         <v>46422</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46472</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05671708300547242</v>
+        <v>0.05704697889209416</v>
       </c>
     </row>
     <row r="34">
@@ -1943,7 +1943,7 @@
         <v>46428</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46452</v>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01740495012131711</v>
+        <v>0.01771324863883848</v>
       </c>
     </row>
     <row r="35">
@@ -1989,7 +1989,7 @@
         <v>46428</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46460</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.05029499981330527</v>
+        <v>0.04959215180541567</v>
       </c>
     </row>
     <row r="36">
@@ -2035,7 +2035,7 @@
         <v>46431</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46480</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01395232911639436</v>
+        <v>0.01410579363160145</v>
       </c>
     </row>
     <row r="37">
@@ -2081,7 +2081,7 @@
         <v>46433</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46425</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.007782472784615239</v>
+        <v>0.007991648467354199</v>
       </c>
     </row>
     <row r="38">
@@ -2127,7 +2127,7 @@
         <v>46433</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46383</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.102324619290005</v>
+        <v>0.1111069719600328</v>
       </c>
     </row>
     <row r="39">
@@ -2173,7 +2173,7 @@
         <v>46433</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46276</v>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.02033036796236036</v>
+        <v>0.02049420985253447</v>
       </c>
     </row>
     <row r="40">
@@ -2219,7 +2219,7 @@
         <v>46433</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46270</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.03081367402039418</v>
+        <v>0.03104686144828515</v>
       </c>
     </row>
     <row r="41">
@@ -2265,7 +2265,7 @@
         <v>46433</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46243</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03801220676551045</v>
+        <v>0.03906109920010292</v>
       </c>
     </row>
     <row r="42">
@@ -2311,7 +2311,7 @@
         <v>46440</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46450</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.01055793183764243</v>
+        <v>0.01035205922842178</v>
       </c>
     </row>
     <row r="43">
@@ -2357,7 +2357,7 @@
         <v>46441</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46456</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.02976969937062066</v>
+        <v>0.0298545717812205</v>
       </c>
     </row>
     <row r="44">
@@ -2403,7 +2403,7 @@
         <v>46452</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46487</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01854822166962447</v>
+        <v>0.01863408644778464</v>
       </c>
     </row>
     <row r="45">
@@ -2449,7 +2449,7 @@
         <v>46461</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46300</v>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.01958352341659811</v>
+        <v>0.02003974557693619</v>
       </c>
     </row>
     <row r="46">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
@@ -2495,10 +2495,10 @@
         <v>46461</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46196</v>
+        <v>46386</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.05243469809734441</v>
+        <v>0.05379652537562463</v>
       </c>
     </row>
     <row r="47">
@@ -2541,7 +2541,7 @@
         <v>46488</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46498</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.03015785050105535</v>
+        <v>0.03095728656212699</v>
       </c>
     </row>
     <row r="48">
@@ -2587,7 +2587,7 @@
         <v>46492</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46501</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.0202817422379329</v>
+        <v>0.0204872076875597</v>
       </c>
     </row>
     <row r="49">
@@ -2633,7 +2633,7 @@
         <v>46492</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46197</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.04215174654483525</v>
+        <v>0.04247572933518482</v>
       </c>
     </row>
     <row r="50">
@@ -2679,7 +2679,7 @@
         <v>46492</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46376</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.04253275180021647</v>
+        <v>0.04387881472944864</v>
       </c>
     </row>
     <row r="51">
@@ -2710,13 +2710,13 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E51" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E51" s="7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="F51" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
@@ -2725,10 +2725,10 @@
         <v>46493</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46530</v>
+        <v>46531</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.02218998071717222</v>
+        <v>0.02409367805377783</v>
       </c>
     </row>
     <row r="52">
@@ -2771,7 +2771,7 @@
         <v>46499</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46526</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02858911548315806</v>
+        <v>0.02828271494384326</v>
       </c>
     </row>
     <row r="53">
@@ -2817,7 +2817,7 @@
         <v>46508</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46518</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.04907216494845361</v>
+        <v>0.0472577605327386</v>
       </c>
     </row>
     <row r="54">
@@ -2863,7 +2863,7 @@
         <v>46517</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46542</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.03780301337001037</v>
+        <v>0.03954705853105136</v>
       </c>
     </row>
   </sheetData>
@@ -2909,7 +2909,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 05/25/2026</t>
+          <t>Expected Increase Announcements by Month - 06/01/2026</t>
         </is>
       </c>
     </row>
@@ -3100,10 +3100,10 @@
         <v>46264</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46461</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46196</v>
+        <v>46386</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0.271</v>
@@ -4432,13 +4432,13 @@
         <v>46493</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46530</v>
+        <v>46531</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 05/25/2026</t>
+          <t>Complete Holdings Dividend Summary - 06/01/2026</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01055793183764243</v>
+        <v>0.01035205922842178</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4753,7 +4753,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02970822388048694</v>
+        <v>0.0304605330321046</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -4806,7 +4806,7 @@
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.007782472784615239</v>
+        <v>0.007991648467354199</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -4859,7 +4859,7 @@
         <v>2.812</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03785166193761971</v>
+        <v>0.03916980030838525</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>46157</v>
@@ -4906,19 +4906,19 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.02869852102073829</v>
+        <v>0.03043622674109861</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>46080</v>
+        <v>46171</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.05263157894736847</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>46232</v>
@@ -4965,7 +4965,7 @@
         <v>4.96</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05215014160624624</v>
+        <v>0.05544997394320728</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46134</v>
@@ -5018,7 +5018,7 @@
         <v>29.8</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.102324619290005</v>
+        <v>0.1111069719600328</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46091</v>
@@ -5071,7 +5071,7 @@
         <v>0.92</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02148026991987978</v>
+        <v>0.02198064771382014</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46163</v>
@@ -5124,7 +5124,7 @@
         <v>2.4</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.008730129744386562</v>
+        <v>0.008972130483968787</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46157</v>
@@ -5177,7 +5177,7 @@
         <v>1.68</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.01395232911639436</v>
+        <v>0.01410579363160145</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46114</v>
@@ -5230,7 +5230,7 @@
         <v>7.12</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.0371937537084845</v>
+        <v>0.0382940836807255</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46161</v>
@@ -5283,7 +5283,7 @@
         <v>3.44</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.01762204744474112</v>
+        <v>0.01754699192598384</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46118</v>
@@ -5336,7 +5336,7 @@
         <v>0.96</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.02033036796236036</v>
+        <v>0.02049420985253447</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46094</v>
@@ -5389,7 +5389,7 @@
         <v>3.36</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.04533189254576684</v>
+        <v>0.04449447165672079</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46094</v>
@@ -5442,7 +5442,7 @@
         <v>2.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.02277580040255237</v>
+        <v>0.023931943262468</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46143</v>
@@ -5495,7 +5495,7 @@
         <v>6.36</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01854822166962447</v>
+        <v>0.01863408644778464</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46122</v>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Aug/Nov</t>
+          <t>Mar/Aug/Sep/Nov</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -5548,7 +5548,7 @@
         <v>9.32</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.02976969937062066</v>
+        <v>0.0298545717812205</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46093</v>
@@ -5601,10 +5601,10 @@
         <v>5.52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.01721610552954179</v>
+        <v>0.01850982488567165</v>
       </c>
       <c r="I22" s="10" t="n">
-        <v>46080</v>
+        <v>46171</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>0.02222222222222208</v>
@@ -5654,7 +5654,7 @@
         <v>1.172</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.05517890831588747</v>
+        <v>0.0502572905376204</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46125</v>
@@ -5707,7 +5707,7 @@
         <v>3.28</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.03202812110838314</v>
+        <v>0.03260437425199132</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46113</v>
@@ -5760,7 +5760,7 @@
         <v>2.44</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.01740495012131711</v>
+        <v>0.01771324863883848</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46086</v>
@@ -5807,25 +5807,25 @@
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.02218998071717222</v>
+        <v>0.02409367805377783</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>46077</v>
+        <v>46168</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.04838709677419359</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="K26" s="10" t="n">
         <v>46493</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>46530</v>
+        <v>46531</v>
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01958352341659811</v>
+        <v>0.02003974557693619</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46118</v>
@@ -5919,7 +5919,7 @@
         <v>2.174</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.0202817422379329</v>
+        <v>0.0204872076875597</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46132</v>
@@ -5972,7 +5972,7 @@
         <v>3.16</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.011995596886681</v>
+        <v>0.01247717304408395</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46112</v>
@@ -6025,7 +6025,7 @@
         <v>2.84</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.03613231622307302</v>
+        <v>0.03798822791396991</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46108</v>
@@ -6078,7 +6078,7 @@
         <v>1.92</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.04016736465785078</v>
+        <v>0.0406177275525001</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46132</v>
@@ -6131,7 +6131,7 @@
         <v>3.64</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.008696275261740157</v>
+        <v>0.007827956989247311</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46163</v>
@@ -6184,7 +6184,7 @@
         <v>3.48</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03267605633802817</v>
+        <v>0.03207668972737766</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46120</v>
@@ -6237,7 +6237,7 @@
         <v>1.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.03671367958864462</v>
+        <v>0.03578441925543904</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46083</v>
@@ -6290,7 +6290,7 @@
         <v>2.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.05671708300547242</v>
+        <v>0.05704697889209416</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46111</v>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F36" s="7" t="n">
@@ -6343,10 +6343,10 @@
         <v>3.252</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05243469809734441</v>
+        <v>0.05379652537562463</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>46142</v>
+        <v>46171</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0.003703703703703707</v>
@@ -6355,7 +6355,7 @@
         <v>46461</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>46196</v>
+        <v>46386</v>
       </c>
       <c r="M36" s="12" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>4.76</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.04907216494845361</v>
+        <v>0.0472577605327386</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46155</v>
@@ -6449,7 +6449,7 @@
         <v>5.692</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.03780301337001037</v>
+        <v>0.03954705853105136</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46087</v>
@@ -6502,7 +6502,7 @@
         <v>1.72</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.06640926738737934</v>
+        <v>0.06686882792307368</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46150</v>
@@ -6555,7 +6555,7 @@
         <v>3.2</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03081367402039418</v>
+        <v>0.03104686144828515</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46092</v>
@@ -6608,7 +6608,7 @@
         <v>4.356</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03015785050105535</v>
+        <v>0.03095728656212699</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46136</v>
@@ -6661,7 +6661,7 @@
         <v>2.1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.04215174654483525</v>
+        <v>0.04247572933518482</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46104</v>
@@ -6714,7 +6714,7 @@
         <v>5.08</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02858911548315806</v>
+        <v>0.02828271494384326</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46160</v>
@@ -6767,7 +6767,7 @@
         <v>3.72</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.01737992953039871</v>
+        <v>0.01859581611162467</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46161</v>
@@ -6820,7 +6820,7 @@
         <v>9.76</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02661939223366119</v>
+        <v>0.02652642468034239</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46162</v>
@@ -6873,7 +6873,7 @@
         <v>3.32</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.04342139732871405</v>
+        <v>0.04297178239972002</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46091</v>
@@ -6926,7 +6926,7 @@
         <v>5.2</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.05029499981330527</v>
+        <v>0.04959215180541567</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46097</v>
@@ -6979,7 +6979,7 @@
         <v>3.896</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.04253275180021647</v>
+        <v>0.04387881472944864</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46112</v>
@@ -7032,7 +7032,7 @@
         <v>5.68</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.01836939347681198</v>
+        <v>0.01952493873877673</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46147</v>
@@ -7085,7 +7085,7 @@
         <v>2.18</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.03801220676551045</v>
+        <v>0.03906109920010292</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46157</v>
@@ -7138,10 +7138,10 @@
         <v>5.52</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02076124529346597</v>
+        <v>0.02116402056970356</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>46080</v>
+        <v>46171</v>
       </c>
       <c r="J51" s="8" t="n">
         <v>0.02985074626865658</v>
@@ -7191,7 +7191,7 @@
         <v>2.832</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.05857290774302305</v>
+        <v>0.05932132175180416</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46122</v>
@@ -7244,7 +7244,7 @@
         <v>4.12</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02659437160273528</v>
+        <v>0.0276510067114094</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00dc3545"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
@@ -88,7 +94,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a3a5c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,16 +142,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,10 +164,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -547,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/15/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/22/2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +637,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -633,29 +647,29 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.89</v>
+        <v>0.42</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>46218</v>
+        <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>30</v>
+        <v>-147</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>46248</v>
+        <v>46413</v>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
@@ -663,151 +677,151 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.01740473010680046</v>
+        <v>0.06873126977897696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0.01763534633993057</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>UNP</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D8" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>0.02985074626865658</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H8" s="10" t="n">
         <v>46220</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I8" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.02124752098652373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.08154506437768236</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="J7" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>0.02047591733577578</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.08154506437768236</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I8" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="J8" s="18" t="n">
+      <c r="J9" s="19" t="n">
         <v>46248</v>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
-      <c r="L8" s="17" t="n">
-        <v>0.02622268564025439</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>0.03826868889525783</v>
+      <c r="L9" s="18" t="n">
+        <v>0.02617162186093445</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -817,29 +831,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <v>44</v>
+        <v>46227</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>32</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -847,13 +861,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.02779089376053963</v>
+        <v>0.03782398111404369</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -867,25 +881,25 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I11" s="11" t="n">
-        <v>44</v>
+      <c r="I11" s="13" t="n">
+        <v>37</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -893,13 +907,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.05107609894784907</v>
+        <v>0.02793220338983051</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -909,29 +923,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>75</v>
+        <v>46232</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>37</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46297</v>
+        <v>46246</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -939,13 +953,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.032106498457542</v>
+        <v>0.05257857686051969</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -955,29 +969,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46278</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>90</v>
+        <v>46263</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>68</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46344</v>
+        <v>46297</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -985,13 +999,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.009130129594840641</v>
+        <v>0.03371537109041089</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1001,29 +1015,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.708</v>
+        <v>0.91</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46280</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>92</v>
+        <v>46278</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>83</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46303</v>
+        <v>46344</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1031,13 +1045,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.05953957913939176</v>
+        <v>0.009569377867591678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1051,25 +1065,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.42</v>
+        <v>0.708</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>97</v>
+        <v>46280</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>85</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46325</v>
+        <v>46303</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1077,13 +1091,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01808629269472995</v>
+        <v>0.06219391697573379</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1093,29 +1107,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.85</v>
+        <v>1.36</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46305</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>117</v>
+        <v>46285</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>90</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46339</v>
+        <v>46325</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1123,13 +1137,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.0297067745078635</v>
+        <v>0.01719830968486408</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1139,29 +1153,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>123</v>
+        <v>46305</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>110</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46386</v>
+        <v>46339</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1169,13 +1183,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.01185674287119766</v>
+        <v>0.02962206248349254</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1185,29 +1199,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.38</v>
+        <v>0.79</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1.35</v>
+        <v>0.75</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46317</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>129</v>
+        <v>46311</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>116</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46351</v>
+        <v>46386</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1215,13 +1229,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.0183883538928897</v>
+        <v>0.01150366739745763</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1235,25 +1249,25 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.64</v>
+        <v>1.38</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>134</v>
+        <v>46317</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>122</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46338</v>
+        <v>46351</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1261,13 +1275,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.02322627446604622</v>
+        <v>0.01983043645094449</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1281,22 +1295,22 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>0.55</v>
-      </c>
       <c r="F20" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>141</v>
+        <v>46322</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>127</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46338</v>
@@ -1307,13 +1321,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.00858184927616509</v>
+        <v>0.02287552422685487</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1327,25 +1341,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2.44</v>
+        <v>0.6</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2.14</v>
+        <v>0.55</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>144</v>
+        <v>46329</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>134</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46346</v>
+        <v>46338</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1353,13 +1367,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.02487384647164909</v>
+        <v>0.008822718698096135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1373,25 +1387,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.99</v>
+        <v>2.14</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>153</v>
+        <v>46332</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>137</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1399,13 +1413,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02960833762641</v>
+        <v>0.02508836232408511</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1415,29 +1429,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.48</v>
+        <v>1.03</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="I23" s="11" t="n">
-        <v>156</v>
+        <v>46341</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>146</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46385</v>
+        <v>46339</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1445,13 +1459,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03946151573673406</v>
+        <v>0.02998108030051665</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1465,25 +1479,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46347</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>159</v>
+        <v>46344</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>149</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46358</v>
+        <v>46385</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1491,13 +1505,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03599253921712346</v>
+        <v>0.04147764013882235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1507,29 +1521,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.293</v>
+        <v>0.41</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>164</v>
+        <v>46347</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>152</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46400</v>
+        <v>46358</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1537,13 +1551,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.04753002031413188</v>
+        <v>0.03697024295390339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1553,29 +1567,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.84</v>
+        <v>0.293</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.83</v>
+        <v>0.29</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46360</v>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>172</v>
+        <v>46352</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>157</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46371</v>
+        <v>46400</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1583,13 +1597,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04369310706540454</v>
+        <v>0.04857024619816713</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1599,29 +1613,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.52</v>
+        <v>0.84</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2.38</v>
+        <v>0.83</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46366</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>178</v>
+        <v>46360</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>165</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46432</v>
+        <v>46371</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1629,13 +1643,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02847859768995866</v>
+        <v>0.0464088388009079</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1645,29 +1659,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.43</v>
+        <v>2.52</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0.42</v>
+        <v>2.38</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="I28" s="11" t="n">
-        <v>182</v>
+        <v>46366</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>171</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46413</v>
+        <v>46432</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1675,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.06536195953231798</v>
+        <v>0.02948144216909636</v>
       </c>
     </row>
     <row r="29">
@@ -1709,8 +1723,8 @@
       <c r="H29" s="10" t="n">
         <v>46371</v>
       </c>
-      <c r="I29" s="11" t="n">
-        <v>183</v>
+      <c r="I29" s="13" t="n">
+        <v>176</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46344</v>
@@ -1721,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02149532748597274</v>
+        <v>0.02141776186201622</v>
       </c>
     </row>
     <row r="30">
@@ -1755,8 +1769,8 @@
       <c r="H30" s="10" t="n">
         <v>46402</v>
       </c>
-      <c r="I30" s="11" t="n">
-        <v>214</v>
+      <c r="I30" s="13" t="n">
+        <v>207</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46483</v>
@@ -1767,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.01697549866748671</v>
+        <v>0.01775667204802915</v>
       </c>
     </row>
     <row r="31">
@@ -1801,8 +1815,8 @@
       <c r="H31" s="10" t="n">
         <v>46411</v>
       </c>
-      <c r="I31" s="11" t="n">
-        <v>223</v>
+      <c r="I31" s="13" t="n">
+        <v>216</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46435</v>
@@ -1813,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.03857074339322991</v>
+        <v>0.03865823594422466</v>
       </c>
     </row>
     <row r="32">
@@ -1847,8 +1861,8 @@
       <c r="H32" s="10" t="n">
         <v>46417</v>
       </c>
-      <c r="I32" s="11" t="n">
-        <v>229</v>
+      <c r="I32" s="13" t="n">
+        <v>222</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46433</v>
@@ -1859,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03971219960188763</v>
+        <v>0.04095955775758391</v>
       </c>
     </row>
     <row r="33">
@@ -1893,8 +1907,8 @@
       <c r="H33" s="10" t="n">
         <v>46422</v>
       </c>
-      <c r="I33" s="11" t="n">
-        <v>234</v>
+      <c r="I33" s="13" t="n">
+        <v>227</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46472</v>
@@ -1905,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05762711864406779</v>
+        <v>0.05626667250263881</v>
       </c>
     </row>
     <row r="34">
@@ -1939,8 +1953,8 @@
       <c r="H34" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I34" s="11" t="n">
-        <v>240</v>
+      <c r="I34" s="13" t="n">
+        <v>233</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46452</v>
@@ -1951,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01835552647588875</v>
+        <v>0.01969330080670224</v>
       </c>
     </row>
     <row r="35">
@@ -1985,8 +1999,8 @@
       <c r="H35" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I35" s="11" t="n">
-        <v>240</v>
+      <c r="I35" s="13" t="n">
+        <v>233</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46460</v>
@@ -1997,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04697804576120251</v>
+        <v>0.0476364952871926</v>
       </c>
     </row>
     <row r="36">
@@ -2031,8 +2045,8 @@
       <c r="H36" s="10" t="n">
         <v>46431</v>
       </c>
-      <c r="I36" s="11" t="n">
-        <v>243</v>
+      <c r="I36" s="13" t="n">
+        <v>236</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46480</v>
@@ -2043,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01387856222755877</v>
+        <v>0.01383741001009712</v>
       </c>
     </row>
     <row r="37">
@@ -2077,8 +2091,8 @@
       <c r="H37" s="10" t="n">
         <v>46432</v>
       </c>
-      <c r="I37" s="11" t="n">
-        <v>244</v>
+      <c r="I37" s="13" t="n">
+        <v>237</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46455</v>
@@ -2089,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.03341646012442573</v>
+        <v>0.03346026542424558</v>
       </c>
     </row>
     <row r="38">
@@ -2123,8 +2137,8 @@
       <c r="H38" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I38" s="11" t="n">
-        <v>245</v>
+      <c r="I38" s="13" t="n">
+        <v>238</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46425</v>
@@ -2135,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.006747121110328045</v>
+        <v>0.006605229735607282</v>
       </c>
     </row>
     <row r="39">
@@ -2169,8 +2183,8 @@
       <c r="H39" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I39" s="11" t="n">
-        <v>245</v>
+      <c r="I39" s="13" t="n">
+        <v>238</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46383</v>
@@ -2181,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.019313983259679</v>
+        <v>0.02108763565929368</v>
       </c>
     </row>
     <row r="40">
@@ -2201,13 +2215,13 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E40" s="7" t="n">
         <v>0.24</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>0.22</v>
-      </c>
       <c r="F40" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0.06</v>
@@ -2215,8 +2229,8 @@
       <c r="H40" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I40" s="11" t="n">
-        <v>245</v>
+      <c r="I40" s="13" t="n">
+        <v>238</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46368</v>
@@ -2227,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02189281718143188</v>
+        <v>0.0301460204333374</v>
       </c>
     </row>
     <row r="41">
@@ -2261,8 +2275,8 @@
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I41" s="11" t="n">
-        <v>245</v>
+      <c r="I41" s="13" t="n">
+        <v>238</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46270</v>
@@ -2273,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02934860359077146</v>
+        <v>0.02958686615498475</v>
       </c>
     </row>
     <row r="42">
@@ -2307,8 +2321,8 @@
       <c r="H42" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I42" s="11" t="n">
-        <v>245</v>
+      <c r="I42" s="13" t="n">
+        <v>238</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46243</v>
@@ -2319,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03710322458292027</v>
+        <v>0.03775872481084097</v>
       </c>
     </row>
     <row r="43">
@@ -2353,8 +2367,8 @@
       <c r="H43" s="10" t="n">
         <v>46440</v>
       </c>
-      <c r="I43" s="11" t="n">
-        <v>252</v>
+      <c r="I43" s="13" t="n">
+        <v>245</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46450</v>
@@ -2365,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.00963535182225228</v>
+        <v>0.009718498609821541</v>
       </c>
     </row>
     <row r="44">
@@ -2399,8 +2413,8 @@
       <c r="H44" s="10" t="n">
         <v>46441</v>
       </c>
-      <c r="I44" s="11" t="n">
-        <v>253</v>
+      <c r="I44" s="13" t="n">
+        <v>246</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46456</v>
@@ -2411,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02800523758638565</v>
+        <v>0.02825055708305586</v>
       </c>
     </row>
     <row r="45">
@@ -2445,8 +2459,8 @@
       <c r="H45" s="10" t="n">
         <v>46452</v>
       </c>
-      <c r="I45" s="11" t="n">
-        <v>264</v>
+      <c r="I45" s="13" t="n">
+        <v>257</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46487</v>
@@ -2457,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.01765489721411033</v>
+        <v>0.0184674343897353</v>
       </c>
     </row>
     <row r="46">
@@ -2491,8 +2505,8 @@
       <c r="H46" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I46" s="11" t="n">
-        <v>273</v>
+      <c r="I46" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46300</v>
@@ -2503,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01860782416757036</v>
+        <v>0.0183281663555542</v>
       </c>
     </row>
     <row r="47">
@@ -2537,8 +2551,8 @@
       <c r="H47" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I47" s="11" t="n">
-        <v>273</v>
+      <c r="I47" s="13" t="n">
+        <v>266</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46386</v>
@@ -2549,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.05178344011954825</v>
+        <v>0.0538588927206442</v>
       </c>
     </row>
     <row r="48">
@@ -2583,8 +2597,8 @@
       <c r="H48" s="10" t="n">
         <v>46488</v>
       </c>
-      <c r="I48" s="11" t="n">
-        <v>300</v>
+      <c r="I48" s="13" t="n">
+        <v>293</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46498</v>
@@ -2595,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02903903108701614</v>
+        <v>0.02920745620106488</v>
       </c>
     </row>
     <row r="49">
@@ -2629,8 +2643,8 @@
       <c r="H49" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I49" s="11" t="n">
-        <v>304</v>
+      <c r="I49" s="13" t="n">
+        <v>297</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46501</v>
@@ -2641,7 +2655,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.01997060433410721</v>
+        <v>0.0203615254130588</v>
       </c>
     </row>
     <row r="50">
@@ -2675,8 +2689,8 @@
       <c r="H50" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I50" s="11" t="n">
-        <v>304</v>
+      <c r="I50" s="13" t="n">
+        <v>297</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46562</v>
@@ -2687,7 +2701,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.04173290963306585</v>
+        <v>0.04170390267283352</v>
       </c>
     </row>
     <row r="51">
@@ -2721,8 +2735,8 @@
       <c r="H51" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I51" s="11" t="n">
-        <v>304</v>
+      <c r="I51" s="13" t="n">
+        <v>297</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46376</v>
@@ -2733,7 +2747,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.04676509559683827</v>
+        <v>0.0483915028769668</v>
       </c>
     </row>
     <row r="52">
@@ -2767,8 +2781,8 @@
       <c r="H52" s="10" t="n">
         <v>46493</v>
       </c>
-      <c r="I52" s="11" t="n">
-        <v>305</v>
+      <c r="I52" s="13" t="n">
+        <v>298</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46531</v>
@@ -2779,7 +2793,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.0226022049945517</v>
+        <v>0.02339538683117294</v>
       </c>
     </row>
     <row r="53">
@@ -2813,8 +2827,8 @@
       <c r="H53" s="10" t="n">
         <v>46499</v>
       </c>
-      <c r="I53" s="11" t="n">
-        <v>311</v>
+      <c r="I53" s="13" t="n">
+        <v>304</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46526</v>
@@ -2825,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.0296728977252015</v>
+        <v>0.03053068104233697</v>
       </c>
     </row>
     <row r="54">
@@ -2859,8 +2873,8 @@
       <c r="H54" s="10" t="n">
         <v>46508</v>
       </c>
-      <c r="I54" s="11" t="n">
-        <v>320</v>
+      <c r="I54" s="13" t="n">
+        <v>313</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46518</v>
@@ -2871,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04691273022026855</v>
+        <v>0.04844290552121706</v>
       </c>
     </row>
     <row r="55">
@@ -2905,8 +2919,8 @@
       <c r="H55" s="10" t="n">
         <v>46515</v>
       </c>
-      <c r="I55" s="11" t="n">
-        <v>327</v>
+      <c r="I55" s="13" t="n">
+        <v>320</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46542</v>
@@ -2917,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.04087409621691405</v>
+        <v>0.0417518885698331</v>
       </c>
     </row>
     <row r="56">
@@ -2951,8 +2965,8 @@
       <c r="H56" s="10" t="n">
         <v>46527</v>
       </c>
-      <c r="I56" s="11" t="n">
-        <v>339</v>
+      <c r="I56" s="13" t="n">
+        <v>332</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46563</v>
@@ -2963,7 +2977,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.0353629695721003</v>
+        <v>0.03593581136590545</v>
       </c>
     </row>
   </sheetData>
@@ -2977,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2998,44 +3012,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 06/15/2026</t>
+          <t>Expected Increase Announcements by Month - 06/22/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>July 2026</t>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3044,20 +3058,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>46218</v>
+        <v>46048</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>46248</v>
+        <v>46413</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
@@ -3065,95 +3079,62 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.08154506437768236</v>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SWK</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.01219512195121952</v>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>46264</v>
+        <v>46248</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
@@ -3164,83 +3145,116 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.08154506437768236</v>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CFR</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>August 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="C14" s="10" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46263</v>
+        <v>46232</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>46297</v>
+        <v>46246</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
@@ -3249,39 +3263,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>September 2026</t>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3290,266 +3304,266 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B23" s="10" t="n">
         <v>46278</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C23" s="10" t="n">
         <v>46344</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D23" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E23" s="8" t="n">
         <v>0.09638554216867479</v>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>VZ</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B24" s="10" t="n">
         <v>46280</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C24" s="10" t="n">
         <v>46303</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D24" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E24" s="8" t="n">
         <v>0.02608695652173916</v>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>October 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>TXN</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.0441176470588234</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>MSM</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B29" s="10" t="n">
         <v>46305</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C29" s="10" t="n">
         <v>46339</v>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="D29" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E29" s="8" t="n">
         <v>0.0235294117647059</v>
       </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>LECO</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B30" s="10" t="n">
         <v>46311</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C30" s="10" t="n">
         <v>46386</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D30" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E30" s="8" t="n">
         <v>0.05333333333333338</v>
       </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>HII</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
+      <c r="B31" s="10" t="n">
         <v>46317</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C31" s="10" t="n">
         <v>46351</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D31" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E31" s="8" t="n">
         <v>0.02222222222222208</v>
       </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>46338</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>46329</v>
+        <v>46322</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>46338</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
@@ -3557,95 +3571,62 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>SNA</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
-        <v>46332</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.1401869158878504</v>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
-        <v>46341</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.04040404040404044</v>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>November 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>MKC</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>46385</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.0666666666666666</v>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46347</v>
+        <v>46329</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46358</v>
+        <v>46338</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3656,20 +3637,20 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46352</v>
+        <v>46332</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46400</v>
+        <v>46346</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.293</v>
+        <v>2.44</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3677,380 +3658,380 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>46341</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.04040404040404044</v>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>MKC</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>46385</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E40" s="22" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F40" s="22" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>46347</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>46358</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>HRL</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>46352</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>46400</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.01034482758620691</v>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>December 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
           <t>EMN</t>
         </is>
       </c>
-      <c r="B41" s="10" t="n">
+      <c r="B45" s="10" t="n">
         <v>46360</v>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C45" s="10" t="n">
         <v>46371</v>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D45" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E45" s="8" t="n">
         <v>0.01204819277108435</v>
       </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>AMGN</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B46" s="10" t="n">
         <v>46366</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C46" s="10" t="n">
         <v>46432</v>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D46" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E46" s="8" t="n">
         <v>0.05882352941176476</v>
       </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>46370</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>46413</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0.02380952380952383</v>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>CNP</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n">
+      <c r="B47" s="10" t="n">
         <v>46371</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C47" s="10" t="n">
         <v>46344</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D47" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E47" s="8" t="n">
         <v>0.0454545454545455</v>
       </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="D50" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E47" s="22" t="inlineStr">
+      <c r="E50" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F50" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>DGX</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n">
+      <c r="B51" s="10" t="n">
         <v>46402</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C51" s="10" t="n">
         <v>46483</v>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D51" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E51" s="8" t="n">
         <v>0.07499999999999993</v>
       </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>BKH</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B52" s="10" t="n">
         <v>46411</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C52" s="10" t="n">
         <v>46435</v>
       </c>
-      <c r="D49" s="7" t="n">
+      <c r="D52" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="E52" s="8" t="n">
         <v>0.03994082840236673</v>
       </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n">
+      <c r="B53" s="10" t="n">
         <v>46417</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C53" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D53" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E53" s="8" t="n">
         <v>0.04093567251461992</v>
       </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E56" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F56" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>46472</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>1.275</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>1.183219178082192</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.05172413793103453</v>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>46460</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.02362204724409451</v>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>46431</v>
+        <v>46422</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46480</v>
+        <v>46472</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.42</v>
+        <v>1.275</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -4061,20 +4042,20 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46432</v>
+        <v>46428</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46455</v>
+        <v>46452</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4085,20 +4066,20 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>46433</v>
+        <v>46428</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46425</v>
+        <v>46460</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3.177</v>
+        <v>1.3</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4109,20 +4090,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46433</v>
+        <v>46431</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46383</v>
+        <v>46480</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>4.96</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4133,20 +4114,20 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46433</v>
+        <v>46432</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46368</v>
+        <v>46455</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.24</v>
+        <v>0.67</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4157,20 +4138,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46270</v>
+        <v>46425</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>0.82</v>
+        <v>3.177</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4181,20 +4162,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46243</v>
+        <v>46383</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0.545</v>
+        <v>1.3</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>4.96</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4205,20 +4186,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
-        <v>46440</v>
+        <v>46433</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46450</v>
+        <v>46368</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4229,266 +4210,266 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>UL</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="n">
+        <v>46433</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>46243</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.005735494868956323</v>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n">
+        <v>46440</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0.07407407407407393</v>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="B65" s="10" t="n">
+      <c r="B68" s="10" t="n">
         <v>46441</v>
       </c>
-      <c r="C65" s="10" t="n">
+      <c r="C68" s="10" t="n">
         <v>46456</v>
       </c>
-      <c r="D65" s="7" t="n">
+      <c r="D68" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E68" s="8" t="n">
         <v>0.01304347826086967</v>
       </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="21" t="inlineStr">
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="22" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B71" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C71" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D68" s="22" t="inlineStr">
+      <c r="D71" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="E71" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F71" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>GD</t>
         </is>
       </c>
-      <c r="B69" s="10" t="n">
+      <c r="B72" s="10" t="n">
         <v>46452</v>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C72" s="10" t="n">
         <v>46487</v>
       </c>
-      <c r="D69" s="7" t="n">
+      <c r="D72" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="E69" s="8" t="n">
+      <c r="E72" s="8" t="n">
         <v>0.06000000000000005</v>
       </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="B70" s="10" t="n">
+      <c r="B73" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C73" s="10" t="n">
         <v>46300</v>
       </c>
-      <c r="D70" s="7" t="n">
+      <c r="D73" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E70" s="8" t="n">
+      <c r="E73" s="8" t="n">
         <v>0.07142857142857149</v>
       </c>
-      <c r="F70" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n">
+      <c r="B74" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="C71" s="10" t="n">
+      <c r="C74" s="10" t="n">
         <v>46386</v>
       </c>
-      <c r="D71" s="7" t="n">
+      <c r="D74" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="E71" s="8" t="n">
+      <c r="E74" s="8" t="n">
         <v>0.003703703703703707</v>
       </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="21" t="inlineStr">
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="22" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B77" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C74" s="22" t="inlineStr">
+      <c r="C77" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D74" s="22" t="inlineStr">
+      <c r="D77" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E74" s="22" t="inlineStr">
+      <c r="E77" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F74" s="22" t="inlineStr">
+      <c r="F77" s="23" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>46498</v>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.03027436140018924</v>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>KOF</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C76" s="10" t="n">
-        <v>46501</v>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>1.087</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.1137295081967213</v>
-      </c>
-      <c r="F76" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="C77" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46492</v>
+        <v>46488</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46376</v>
+        <v>46498</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0.974</v>
+        <v>1.089</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4499,20 +4480,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46493</v>
+        <v>46492</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46531</v>
+        <v>46501</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.34</v>
+        <v>1.087</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4523,133 +4504,205 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
+          <t>POR</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>46562</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="n">
+        <v>46492</v>
+      </c>
+      <c r="C81" s="10" t="n">
+        <v>46376</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0.001006036217303824</v>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>46493</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>46531</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.0307692307692308</v>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
           <t>PSX</t>
         </is>
       </c>
-      <c r="B80" s="10" t="n">
+      <c r="B83" s="10" t="n">
         <v>46499</v>
       </c>
-      <c r="C80" s="10" t="n">
+      <c r="C83" s="10" t="n">
         <v>46526</v>
       </c>
-      <c r="D80" s="7" t="n">
+      <c r="D83" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="E80" s="8" t="n">
+      <c r="E83" s="8" t="n">
         <v>0.05833333333333339</v>
       </c>
-      <c r="F80" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="21" t="inlineStr">
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="22" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B83" s="22" t="inlineStr">
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C86" s="23" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D83" s="22" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="E86" s="23" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
+      <c r="F86" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>PAYX</t>
         </is>
       </c>
-      <c r="B84" s="10" t="n">
+      <c r="B87" s="10" t="n">
         <v>46508</v>
       </c>
-      <c r="C84" s="10" t="n">
+      <c r="C87" s="10" t="n">
         <v>46518</v>
       </c>
-      <c r="D84" s="7" t="n">
+      <c r="D87" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="E84" s="8" t="n">
+      <c r="E87" s="8" t="n">
         <v>0.1018518518518517</v>
       </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>PEP</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n">
+      <c r="B88" s="10" t="n">
         <v>46515</v>
       </c>
-      <c r="C85" s="10" t="n">
+      <c r="C88" s="10" t="n">
         <v>46542</v>
       </c>
-      <c r="D85" s="7" t="n">
+      <c r="D88" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E88" s="8" t="n">
         <v>0.04005621925509482</v>
       </c>
-      <c r="F85" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>MDT</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n">
+      <c r="B89" s="10" t="n">
         <v>46527</v>
       </c>
-      <c r="C86" s="10" t="n">
+      <c r="C89" s="10" t="n">
         <v>46563</v>
       </c>
-      <c r="D86" s="7" t="n">
+      <c r="D89" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="E86" s="8" t="n">
+      <c r="E89" s="8" t="n">
         <v>0.0142857142857143</v>
       </c>
-      <c r="F86" s="12" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4694,7 +4747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 06/15/2026</t>
+          <t>Complete Holdings Dividend Summary - 06/22/2026</t>
         </is>
       </c>
     </row>
@@ -4794,11 +4847,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="24" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.00963535182225228</v>
+        <v>0.009718498609821541</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4847,11 +4900,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="24" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02847859768995866</v>
+        <v>0.02948144216909636</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -4900,11 +4953,11 @@
       <c r="F7" s="7" t="n">
         <v>3.177</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="24" t="n">
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.006747121110328045</v>
+        <v>0.006605229735607282</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -4925,53 +4978,53 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>AWR</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="16" t="n">
         <v>0.504</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="25" t="n">
         <v>2.016</v>
       </c>
-      <c r="H8" s="17" t="n">
-        <v>0.02622268564025439</v>
-      </c>
-      <c r="I8" s="18" t="n">
+      <c r="H8" s="18" t="n">
+        <v>0.02617162186093445</v>
+      </c>
+      <c r="I8" s="19" t="n">
         <v>46160</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.08154506437768236</v>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="K8" s="19" t="n">
         <v>46227</v>
       </c>
-      <c r="L8" s="18" t="n">
+      <c r="L8" s="19" t="n">
         <v>46248</v>
       </c>
-      <c r="M8" s="20" t="inlineStr">
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5006,11 +5059,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03857074339322991</v>
+        <v>0.03865823594422466</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46157</v>
@@ -5059,11 +5112,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="24" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02779089376053963</v>
+        <v>0.02793220338983051</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46171</v>
@@ -5112,11 +5165,11 @@
       <c r="F11" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <v>4.96</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05107609894784907</v>
+        <v>0.05257857686051969</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46134</v>
@@ -5165,11 +5218,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.019313983259679</v>
+        <v>0.02108763565929368</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46182</v>
@@ -5218,11 +5271,11 @@
       <c r="F13" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="24" t="n">
         <v>0.92</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02149532748597274</v>
+        <v>0.02141776186201622</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46163</v>
@@ -5271,11 +5324,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="24" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.00858184927616509</v>
+        <v>0.008822718698096135</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46157</v>
@@ -5324,11 +5377,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="24" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01387856222755877</v>
+        <v>0.01383741001009712</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46114</v>
@@ -5377,11 +5430,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03971219960188763</v>
+        <v>0.04095955775758391</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46161</v>
@@ -5430,11 +5483,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="24" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01697549866748671</v>
+        <v>0.01775667204802915</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46118</v>
@@ -5481,19 +5534,19 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>0.96</v>
+        <v>0.32</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02189281718143188</v>
+        <v>0.0301460204333374</v>
       </c>
       <c r="I18" s="10" t="n">
-        <v>46094</v>
+        <v>46188</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>0.09090909090909087</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>46433</v>
@@ -5536,14 +5589,14 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="24" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.04369310706540454</v>
+        <v>0.0464088388009079</v>
       </c>
       <c r="I19" s="10" t="n">
-        <v>46094</v>
+        <v>46188</v>
       </c>
       <c r="J19" s="8" t="n">
         <v>0.01204819277108435</v>
@@ -5589,11 +5642,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="24" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02322627446604622</v>
+        <v>0.02287552422685487</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46143</v>
@@ -5642,11 +5695,11 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="24" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01765489721411033</v>
+        <v>0.0184674343897353</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46122</v>
@@ -5695,11 +5748,11 @@
       <c r="F22" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="24" t="n">
         <v>9.32</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.02800523758638565</v>
+        <v>0.02825055708305586</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46177</v>
@@ -5748,11 +5801,11 @@
       <c r="F23" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="24" t="n">
         <v>5.52</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.0183883538928897</v>
+        <v>0.01983043645094449</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46171</v>
@@ -5801,11 +5854,11 @@
       <c r="F24" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="24" t="n">
         <v>1.172</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.04753002031413188</v>
+        <v>0.04857024619816713</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46125</v>
@@ -5854,11 +5907,11 @@
       <c r="F25" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <v>3.28</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.032106498457542</v>
+        <v>0.03371537109041089</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46113</v>
@@ -5907,11 +5960,11 @@
       <c r="F26" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="24" t="n">
         <v>2.44</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.01835552647588875</v>
+        <v>0.01969330080670224</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46174</v>
@@ -5960,11 +6013,11 @@
       <c r="F27" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <v>5.36</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.0226022049945517</v>
+        <v>0.02339538683117294</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46168</v>
@@ -6013,11 +6066,11 @@
       <c r="F28" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="24" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01860782416757036</v>
+        <v>0.0183281663555542</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46118</v>
@@ -6066,11 +6119,11 @@
       <c r="F29" s="7" t="n">
         <v>1.087</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="24" t="n">
         <v>2.174</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01997060433410721</v>
+        <v>0.0203615254130588</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46132</v>
@@ -6119,11 +6172,11 @@
       <c r="F30" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <v>3.16</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01185674287119766</v>
+        <v>0.01150366739745763</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46112</v>
@@ -6172,11 +6225,11 @@
       <c r="F31" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="24" t="n">
         <v>2.84</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.0353629695721003</v>
+        <v>0.03593581136590545</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46108</v>
@@ -6225,11 +6278,11 @@
       <c r="F32" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G32" s="23" t="n">
+      <c r="G32" s="24" t="n">
         <v>1.92</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.03946151573673406</v>
+        <v>0.04147764013882235</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46132</v>
@@ -6278,11 +6331,11 @@
       <c r="F33" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="24" t="n">
         <v>3.64</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.009130129594840641</v>
+        <v>0.009569377867591678</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46163</v>
@@ -6331,11 +6384,11 @@
       <c r="F34" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G34" s="23" t="n">
+      <c r="G34" s="24" t="n">
         <v>3.48</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.0297067745078635</v>
+        <v>0.02962206248349254</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46120</v>
@@ -6384,11 +6437,11 @@
       <c r="F35" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G35" s="23" t="n">
+      <c r="G35" s="24" t="n">
         <v>1.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.03599253921712346</v>
+        <v>0.03697024295390339</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46174</v>
@@ -6437,11 +6490,11 @@
       <c r="F36" s="7" t="n">
         <v>1.275</v>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G36" s="24" t="n">
         <v>2.55</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05762711864406779</v>
+        <v>0.05626667250263881</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46111</v>
@@ -6490,11 +6543,11 @@
       <c r="F37" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G37" s="23" t="n">
+      <c r="G37" s="24" t="n">
         <v>3.252</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.05178344011954825</v>
+        <v>0.0538588927206442</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46171</v>
@@ -6543,11 +6596,11 @@
       <c r="F38" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G38" s="23" t="n">
+      <c r="G38" s="24" t="n">
         <v>4.76</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.04691273022026855</v>
+        <v>0.04844290552121706</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46155</v>
@@ -6596,11 +6649,11 @@
       <c r="F39" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G39" s="23" t="n">
+      <c r="G39" s="24" t="n">
         <v>2.68</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.03341646012442573</v>
+        <v>0.03346026542424558</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46182</v>
@@ -6649,11 +6702,11 @@
       <c r="F40" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G40" s="23" t="n">
+      <c r="G40" s="24" t="n">
         <v>5.92</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.04087409621691405</v>
+        <v>0.0417518885698331</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46178</v>
@@ -6702,11 +6755,11 @@
       <c r="F41" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G41" s="23" t="n">
+      <c r="G41" s="24" t="n">
         <v>1.72</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.06536195953231798</v>
+        <v>0.06873126977897696</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46150</v>
@@ -6715,7 +6768,7 @@
         <v>0.02380952380952383</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>46370</v>
+        <v>46048</v>
       </c>
       <c r="L41" s="10" t="n">
         <v>46413</v>
@@ -6755,11 +6808,11 @@
       <c r="F42" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G42" s="23" t="n">
+      <c r="G42" s="24" t="n">
         <v>3.28</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.02934860359077146</v>
+        <v>0.02958686615498475</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46174</v>
@@ -6808,11 +6861,11 @@
       <c r="F43" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G43" s="23" t="n">
+      <c r="G43" s="24" t="n">
         <v>4.356</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02903903108701614</v>
+        <v>0.02920745620106488</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46136</v>
@@ -6861,11 +6914,11 @@
       <c r="F44" s="7" t="n">
         <v>0.525</v>
       </c>
-      <c r="G44" s="23" t="n">
+      <c r="G44" s="24" t="n">
         <v>2.1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.04173290963306585</v>
+        <v>0.04170390267283352</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46104</v>
@@ -6914,11 +6967,11 @@
       <c r="F45" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G45" s="23" t="n">
+      <c r="G45" s="24" t="n">
         <v>5.08</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.0296728977252015</v>
+        <v>0.03053068104233697</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46160</v>
@@ -6967,11 +7020,11 @@
       <c r="F46" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G46" s="23" t="n">
+      <c r="G46" s="24" t="n">
         <v>3.72</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.01740473010680046</v>
+        <v>0.01763534633993057</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46161</v>
@@ -7020,11 +7073,11 @@
       <c r="F47" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G47" s="23" t="n">
+      <c r="G47" s="24" t="n">
         <v>9.76</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.02487384647164909</v>
+        <v>0.02508836232408511</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46162</v>
@@ -7073,11 +7126,11 @@
       <c r="F48" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G48" s="23" t="n">
+      <c r="G48" s="24" t="n">
         <v>3.32</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.03826868889525783</v>
+        <v>0.03782398111404369</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46181</v>
@@ -7126,14 +7179,14 @@
       <c r="F49" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G49" s="23" t="n">
+      <c r="G49" s="24" t="n">
         <v>5.2</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04697804576120251</v>
+        <v>0.0476364952871926</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>46097</v>
+        <v>46188</v>
       </c>
       <c r="J49" s="8" t="n">
         <v>0.02362204724409451</v>
@@ -7179,11 +7232,11 @@
       <c r="F50" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G50" s="23" t="n">
+      <c r="G50" s="24" t="n">
         <v>3.896</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.04676509559683827</v>
+        <v>0.0483915028769668</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46112</v>
@@ -7232,11 +7285,11 @@
       <c r="F51" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G51" s="23" t="n">
+      <c r="G51" s="24" t="n">
         <v>5.68</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.01808629269472995</v>
+        <v>0.01719830968486408</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46147</v>
@@ -7285,11 +7338,11 @@
       <c r="F52" s="7" t="n">
         <v>0.545</v>
       </c>
-      <c r="G52" s="23" t="n">
+      <c r="G52" s="24" t="n">
         <v>2.18</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.03710322458292027</v>
+        <v>0.03775872481084097</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46157</v>
@@ -7338,11 +7391,11 @@
       <c r="F53" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G53" s="23" t="n">
+      <c r="G53" s="24" t="n">
         <v>5.52</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02047591733577578</v>
+        <v>0.02124752098652373</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46171</v>
@@ -7391,11 +7444,11 @@
       <c r="F54" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G54" s="23" t="n">
+      <c r="G54" s="24" t="n">
         <v>2.832</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.05953957913939176</v>
+        <v>0.06219391697573379</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46122</v>
@@ -7444,11 +7497,11 @@
       <c r="F55" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G55" s="23" t="n">
+      <c r="G55" s="24" t="n">
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02960833762641</v>
+        <v>0.02998108030051665</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/22/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/29/2026</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-147</v>
+        <v>-154</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06873126977897696</v>
+        <v>0.07063654920140841</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         <v>46218</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46248</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.01763534633993057</v>
+        <v>0.01731722625385386</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +758,7 @@
         <v>46220</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46264</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02124752098652373</v>
+        <v>0.02030046090334901</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +804,7 @@
         <v>46227</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46248</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="L9" s="18" t="n">
-        <v>0.02617162186093445</v>
+        <v>0.02451063829787234</v>
       </c>
     </row>
     <row r="10">
@@ -850,7 +850,7 @@
         <v>46227</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46267</v>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.03782398111404369</v>
+        <v>0.0366304399155838</v>
       </c>
     </row>
     <row r="11">
@@ -896,7 +896,7 @@
         <v>46232</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46264</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02793220338983051</v>
+        <v>0.02656522082200493</v>
       </c>
     </row>
     <row r="12">
@@ -942,7 +942,7 @@
         <v>46232</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46246</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05257857686051969</v>
+        <v>0.05151908513516609</v>
       </c>
     </row>
     <row r="13">
@@ -988,7 +988,7 @@
         <v>46263</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46297</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03371537109041089</v>
+        <v>0.03387554973798062</v>
       </c>
     </row>
     <row r="14">
@@ -1034,7 +1034,7 @@
         <v>46278</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46344</v>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.009569377867591678</v>
+        <v>0.009613226387814601</v>
       </c>
     </row>
     <row r="15">
@@ -1080,7 +1080,7 @@
         <v>46280</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46303</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.06219391697573379</v>
+        <v>0.06477481020832258</v>
       </c>
     </row>
     <row r="16">
@@ -1126,7 +1126,7 @@
         <v>46285</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46325</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01719830968486408</v>
+        <v>0.02014684548490726</v>
       </c>
     </row>
     <row r="17">
@@ -1172,7 +1172,7 @@
         <v>46305</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46339</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02962206248349254</v>
+        <v>0.02976903297327682</v>
       </c>
     </row>
     <row r="18">
@@ -1218,7 +1218,7 @@
         <v>46311</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46386</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01150366739745763</v>
+        <v>0.01183177102782167</v>
       </c>
     </row>
     <row r="19">
@@ -1264,7 +1264,7 @@
         <v>46317</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46351</v>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.01983043645094449</v>
+        <v>0.01960505770657732</v>
       </c>
     </row>
     <row r="20">
@@ -1310,7 +1310,7 @@
         <v>46322</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46338</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02287552422685487</v>
+        <v>0.02201724414764789</v>
       </c>
     </row>
     <row r="21">
@@ -1356,7 +1356,7 @@
         <v>46329</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46338</v>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.008822718698096135</v>
+        <v>0.008374625278987521</v>
       </c>
     </row>
     <row r="22">
@@ -1402,7 +1402,7 @@
         <v>46332</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46346</v>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02508836232408511</v>
+        <v>0.02468136743815182</v>
       </c>
     </row>
     <row r="23">
@@ -1448,7 +1448,7 @@
         <v>46341</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46339</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02998108030051665</v>
+        <v>0.03029189152561084</v>
       </c>
     </row>
     <row r="24">
@@ -1494,7 +1494,7 @@
         <v>46344</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46385</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.04147764013882235</v>
+        <v>0.03701918322307009</v>
       </c>
     </row>
     <row r="25">
@@ -1540,7 +1540,7 @@
         <v>46347</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46358</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03697024295390339</v>
+        <v>0.04014196593747481</v>
       </c>
     </row>
     <row r="26">
@@ -1586,7 +1586,7 @@
         <v>46352</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46400</v>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04857024619816713</v>
+        <v>0.04419306107730098</v>
       </c>
     </row>
     <row r="27">
@@ -1632,7 +1632,7 @@
         <v>46360</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46371</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.0464088388009079</v>
+        <v>0.04904393366268946</v>
       </c>
     </row>
     <row r="28">
@@ -1678,7 +1678,7 @@
         <v>46366</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46432</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02948144216909636</v>
+        <v>0.02792475819572862</v>
       </c>
     </row>
     <row r="29">
@@ -1724,7 +1724,7 @@
         <v>46371</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46344</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02141776186201622</v>
+        <v>0.02038103705005755</v>
       </c>
     </row>
     <row r="30">
@@ -1770,7 +1770,7 @@
         <v>46402</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>46483</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.01775667204802915</v>
+        <v>0.01647272886959504</v>
       </c>
     </row>
     <row r="31">
@@ -1816,7 +1816,7 @@
         <v>46411</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46435</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.03865823594422466</v>
+        <v>0.0373687707641196</v>
       </c>
     </row>
     <row r="32">
@@ -1862,7 +1862,7 @@
         <v>46417</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46433</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.04095955775758391</v>
+        <v>0.04189467565667787</v>
       </c>
     </row>
     <row r="33">
@@ -1908,7 +1908,7 @@
         <v>46422</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46472</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05626667250263881</v>
+        <v>0.05293751498715974</v>
       </c>
     </row>
     <row r="34">
@@ -1954,7 +1954,7 @@
         <v>46428</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46452</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01969330080670224</v>
+        <v>0.01789381042152013</v>
       </c>
     </row>
     <row r="35">
@@ -2000,7 +2000,7 @@
         <v>46428</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46460</v>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.0476364952871926</v>
+        <v>0.04650330901620179</v>
       </c>
     </row>
     <row r="36">
@@ -2046,7 +2046,7 @@
         <v>46431</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46480</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01383741001009712</v>
+        <v>0.01444043366754725</v>
       </c>
     </row>
     <row r="37">
@@ -2092,7 +2092,7 @@
         <v>46432</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46455</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.03346026542424558</v>
+        <v>0.03219606041300103</v>
       </c>
     </row>
     <row r="38">
@@ -2138,7 +2138,7 @@
         <v>46433</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46425</v>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.006605229735607282</v>
+        <v>0.007051303507108543</v>
       </c>
     </row>
     <row r="39">
@@ -2184,7 +2184,7 @@
         <v>46433</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46383</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.02108763565929368</v>
+        <v>0.02338576410879153</v>
       </c>
     </row>
     <row r="40">
@@ -2230,7 +2230,7 @@
         <v>46433</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46368</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.0301460204333374</v>
+        <v>0.0299976577203504</v>
       </c>
     </row>
     <row r="41">
@@ -2276,7 +2276,7 @@
         <v>46433</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46270</v>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02958686615498475</v>
+        <v>0.03064847788156331</v>
       </c>
     </row>
     <row r="42">
@@ -2322,7 +2322,7 @@
         <v>46433</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46243</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03775872481084097</v>
+        <v>0.03599735717577861</v>
       </c>
     </row>
     <row r="43">
@@ -2368,7 +2368,7 @@
         <v>46440</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46450</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.009718498609821541</v>
+        <v>0.009721756645716097</v>
       </c>
     </row>
     <row r="44">
@@ -2414,7 +2414,7 @@
         <v>46441</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46456</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02825055708305586</v>
+        <v>0.02690880658391252</v>
       </c>
     </row>
     <row r="45">
@@ -2460,7 +2460,7 @@
         <v>46452</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46487</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.0184674343897353</v>
+        <v>0.01815975412709446</v>
       </c>
     </row>
     <row r="46">
@@ -2506,7 +2506,7 @@
         <v>46461</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46300</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.0183281663555542</v>
+        <v>0.01821161948526943</v>
       </c>
     </row>
     <row r="47">
@@ -2552,7 +2552,7 @@
         <v>46461</v>
       </c>
       <c r="I47" s="13" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46386</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.0538588927206442</v>
+        <v>0.05195294805937987</v>
       </c>
     </row>
     <row r="48">
@@ -2598,7 +2598,7 @@
         <v>46488</v>
       </c>
       <c r="I48" s="13" t="n">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46498</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02920745620106488</v>
+        <v>0.02944038795851004</v>
       </c>
     </row>
     <row r="49">
@@ -2644,7 +2644,7 @@
         <v>46492</v>
       </c>
       <c r="I49" s="13" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46501</v>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.0203615254130588</v>
+        <v>0.02013615591849956</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2671,43 +2671,43 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.525</v>
+        <v>0.974</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.5</v>
+        <v>0.994</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46562</v>
+        <v>46376</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>Notion + yfinance</t>
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.04170390267283352</v>
+        <v>0.0498018641546523</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2717,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.994</v>
+        <v>1.3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="I51" s="13" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.0483915028769668</v>
+        <v>0.02100025461704885</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2767,25 +2767,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="I52" s="13" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02339538683117294</v>
+        <v>0.02889236506851984</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2809,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.2</v>
+        <v>0.525</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="I53" s="13" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.03053068104233697</v>
+        <v>0.04219797088486882</v>
       </c>
     </row>
     <row r="54">
@@ -2874,7 +2874,7 @@
         <v>46508</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46518</v>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04844290552121706</v>
+        <v>0.04748129675810474</v>
       </c>
     </row>
     <row r="55">
@@ -2920,7 +2920,7 @@
         <v>46515</v>
       </c>
       <c r="I55" s="13" t="n">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46542</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.0417518885698331</v>
+        <v>0.042147228513663</v>
       </c>
     </row>
     <row r="56">
@@ -2951,22 +2951,22 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E56" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="E56" s="7" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F56" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46527</v>
+        <v>46532</v>
       </c>
       <c r="I56" s="13" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46563</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.03593581136590545</v>
+        <v>0.03548983297408272</v>
       </c>
     </row>
   </sheetData>
@@ -3012,7 +3012,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 06/22/2026</t>
+          <t>Expected Increase Announcements by Month - 06/29/2026</t>
         </is>
       </c>
     </row>
@@ -4504,44 +4504,44 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46562</v>
+        <v>46376</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.525</v>
+        <v>0.974</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4552,20 +4552,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4576,20 +4576,20 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B83" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="C83" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
@@ -4691,16 +4691,16 @@
         </is>
       </c>
       <c r="B89" s="10" t="n">
-        <v>46527</v>
+        <v>46532</v>
       </c>
       <c r="C89" s="10" t="n">
         <v>46563</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 06/22/2026</t>
+          <t>Complete Holdings Dividend Summary - 06/29/2026</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009718498609821541</v>
+        <v>0.009721756645716097</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4904,7 +4904,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02948144216909636</v>
+        <v>0.02792475819572862</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -4957,7 +4957,7 @@
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.006605229735607282</v>
+        <v>0.007051303507108543</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -5010,7 +5010,7 @@
         <v>2.016</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.02617162186093445</v>
+        <v>0.02451063829787234</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>46160</v>
@@ -5063,7 +5063,7 @@
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03865823594422466</v>
+        <v>0.0373687707641196</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46157</v>
@@ -5116,7 +5116,7 @@
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02793220338983051</v>
+        <v>0.02656522082200493</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46171</v>
@@ -5169,7 +5169,7 @@
         <v>4.96</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05257857686051969</v>
+        <v>0.05151908513516609</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46134</v>
@@ -5222,7 +5222,7 @@
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02108763565929368</v>
+        <v>0.02338576410879153</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46182</v>
@@ -5275,7 +5275,7 @@
         <v>0.92</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02141776186201622</v>
+        <v>0.02038103705005755</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46163</v>
@@ -5328,7 +5328,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.008822718698096135</v>
+        <v>0.008374625278987521</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46157</v>
@@ -5381,7 +5381,7 @@
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01383741001009712</v>
+        <v>0.01444043366754725</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46114</v>
@@ -5434,7 +5434,7 @@
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.04095955775758391</v>
+        <v>0.04189467565667787</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46161</v>
@@ -5487,7 +5487,7 @@
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01775667204802915</v>
+        <v>0.01647272886959504</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46118</v>
@@ -5540,7 +5540,7 @@
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.0301460204333374</v>
+        <v>0.0299976577203504</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46188</v>
@@ -5593,7 +5593,7 @@
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.0464088388009079</v>
+        <v>0.04904393366268946</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46188</v>
@@ -5646,7 +5646,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02287552422685487</v>
+        <v>0.02201724414764789</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46143</v>
@@ -5699,7 +5699,7 @@
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.0184674343897353</v>
+        <v>0.01815975412709446</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46122</v>
@@ -5752,7 +5752,7 @@
         <v>9.32</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0.02825055708305586</v>
+        <v>0.02690880658391252</v>
       </c>
       <c r="I22" s="10" t="n">
         <v>46177</v>
@@ -5805,7 +5805,7 @@
         <v>5.52</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.01983043645094449</v>
+        <v>0.01960505770657732</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46171</v>
@@ -5858,7 +5858,7 @@
         <v>1.172</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.04857024619816713</v>
+        <v>0.04419306107730098</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46125</v>
@@ -5911,7 +5911,7 @@
         <v>3.28</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.03371537109041089</v>
+        <v>0.03387554973798062</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46113</v>
@@ -5964,7 +5964,7 @@
         <v>2.44</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.01969330080670224</v>
+        <v>0.01789381042152013</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46174</v>
@@ -6017,7 +6017,7 @@
         <v>5.36</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02339538683117294</v>
+        <v>0.02100025461704885</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46168</v>
@@ -6070,7 +6070,7 @@
         <v>6</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.0183281663555542</v>
+        <v>0.01821161948526943</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46118</v>
@@ -6123,7 +6123,7 @@
         <v>2.174</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.0203615254130588</v>
+        <v>0.02013615591849956</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46132</v>
@@ -6176,7 +6176,7 @@
         <v>3.16</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01150366739745763</v>
+        <v>0.01183177102782167</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46112</v>
@@ -6223,22 +6223,22 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.03593581136590545</v>
+        <v>0.03548983297408272</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>46108</v>
+        <v>46199</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.0142857142857143</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>46527</v>
+        <v>46532</v>
       </c>
       <c r="L31" s="10" t="n">
         <v>46563</v>
@@ -6282,7 +6282,7 @@
         <v>1.92</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.04147764013882235</v>
+        <v>0.03701918322307009</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46132</v>
@@ -6335,7 +6335,7 @@
         <v>3.64</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.009569377867591678</v>
+        <v>0.009613226387814601</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46163</v>
@@ -6388,7 +6388,7 @@
         <v>3.48</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02962206248349254</v>
+        <v>0.02976903297327682</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46120</v>
@@ -6441,7 +6441,7 @@
         <v>1.64</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.03697024295390339</v>
+        <v>0.04014196593747481</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46174</v>
@@ -6494,7 +6494,7 @@
         <v>2.55</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05626667250263881</v>
+        <v>0.05293751498715974</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46111</v>
@@ -6547,7 +6547,7 @@
         <v>3.252</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.0538588927206442</v>
+        <v>0.05195294805937987</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46171</v>
@@ -6600,7 +6600,7 @@
         <v>4.76</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.04844290552121706</v>
+        <v>0.04748129675810474</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46155</v>
@@ -6653,7 +6653,7 @@
         <v>2.68</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.03346026542424558</v>
+        <v>0.03219606041300103</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46182</v>
@@ -6706,7 +6706,7 @@
         <v>5.92</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.0417518885698331</v>
+        <v>0.042147228513663</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46178</v>
@@ -6759,7 +6759,7 @@
         <v>1.72</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.06873126977897696</v>
+        <v>0.07063654920140841</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46150</v>
@@ -6812,7 +6812,7 @@
         <v>3.28</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.02958686615498475</v>
+        <v>0.03064847788156331</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46174</v>
@@ -6865,7 +6865,7 @@
         <v>4.356</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02920745620106488</v>
+        <v>0.02944038795851004</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46136</v>
@@ -6912,29 +6912,29 @@
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.525</v>
+        <v>0.551</v>
       </c>
       <c r="G44" s="24" t="n">
-        <v>2.1</v>
+        <v>2.204</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.04170390267283352</v>
+        <v>0.04219797088486882</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>46104</v>
+        <v>46198</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>46492</v>
+        <v>46504</v>
       </c>
       <c r="L44" s="10" t="n">
         <v>46562</v>
       </c>
       <c r="M44" s="12" t="inlineStr">
         <is>
-          <t>yfinance</t>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>5.08</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.03053068104233697</v>
+        <v>0.02889236506851984</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46160</v>
@@ -7024,7 +7024,7 @@
         <v>3.72</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.01763534633993057</v>
+        <v>0.01731722625385386</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46161</v>
@@ -7077,7 +7077,7 @@
         <v>9.76</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.02508836232408511</v>
+        <v>0.02468136743815182</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46162</v>
@@ -7130,7 +7130,7 @@
         <v>3.32</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.03782398111404369</v>
+        <v>0.0366304399155838</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46181</v>
@@ -7183,7 +7183,7 @@
         <v>5.2</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.0476364952871926</v>
+        <v>0.04650330901620179</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46188</v>
@@ -7236,7 +7236,7 @@
         <v>3.896</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.0483915028769668</v>
+        <v>0.0498018641546523</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46112</v>
@@ -7289,7 +7289,7 @@
         <v>5.68</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.01719830968486408</v>
+        <v>0.02014684548490726</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46147</v>
@@ -7342,7 +7342,7 @@
         <v>2.18</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.03775872481084097</v>
+        <v>0.03599735717577861</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46157</v>
@@ -7395,7 +7395,7 @@
         <v>5.52</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02124752098652373</v>
+        <v>0.02030046090334901</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46171</v>
@@ -7448,7 +7448,7 @@
         <v>2.832</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.06219391697573379</v>
+        <v>0.06477481020832258</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46122</v>
@@ -7501,7 +7501,7 @@
         <v>4.12</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.02998108030051665</v>
+        <v>0.03029189152561084</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="168" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,6 +84,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00856404"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001a3a5c"/>
       <sz val="12"/>
     </font>
@@ -94,7 +100,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +122,11 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,7 +163,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,8 +176,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -534,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -561,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 06/29/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/06/2026</t>
         </is>
       </c>
     </row>
@@ -666,7 +680,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-154</v>
+        <v>-161</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -677,7 +691,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.07063654920140841</v>
+        <v>0.07243629981928987</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +726,7 @@
         <v>46218</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46248</v>
@@ -723,7 +737,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.01731722625385386</v>
+        <v>0.01674921160635266</v>
       </c>
     </row>
     <row r="8">
@@ -758,7 +772,7 @@
         <v>46220</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46264</v>
@@ -769,7 +783,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.02030046090334901</v>
+        <v>0.01950736818810225</v>
       </c>
     </row>
     <row r="9">
@@ -804,7 +818,7 @@
         <v>46227</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46248</v>
@@ -815,7 +829,7 @@
         </is>
       </c>
       <c r="L9" s="18" t="n">
-        <v>0.02451063829787234</v>
+        <v>0.02398429590958984</v>
       </c>
     </row>
     <row r="10">
@@ -849,8 +863,8 @@
       <c r="H10" s="10" t="n">
         <v>46227</v>
       </c>
-      <c r="I10" s="13" t="n">
-        <v>25</v>
+      <c r="I10" s="22" t="n">
+        <v>18</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46267</v>
@@ -861,7 +875,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.0366304399155838</v>
+        <v>0.03601062976288923</v>
       </c>
     </row>
     <row r="11">
@@ -895,8 +909,8 @@
       <c r="H11" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I11" s="13" t="n">
-        <v>30</v>
+      <c r="I11" s="22" t="n">
+        <v>23</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46264</v>
@@ -907,7 +921,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02656522082200493</v>
+        <v>0.02647389558232932</v>
       </c>
     </row>
     <row r="12">
@@ -941,8 +955,8 @@
       <c r="H12" s="10" t="n">
         <v>46232</v>
       </c>
-      <c r="I12" s="13" t="n">
-        <v>30</v>
+      <c r="I12" s="22" t="n">
+        <v>23</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46246</v>
@@ -953,7 +967,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05151908513516609</v>
+        <v>0.05178804407181118</v>
       </c>
     </row>
     <row r="13">
@@ -987,8 +1001,8 @@
       <c r="H13" s="10" t="n">
         <v>46263</v>
       </c>
-      <c r="I13" s="13" t="n">
-        <v>61</v>
+      <c r="I13" s="22" t="n">
+        <v>54</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46297</v>
@@ -999,7 +1013,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03387554973798062</v>
+        <v>0.03396144718830089</v>
       </c>
     </row>
     <row r="14">
@@ -1033,8 +1047,8 @@
       <c r="H14" s="10" t="n">
         <v>46278</v>
       </c>
-      <c r="I14" s="13" t="n">
-        <v>76</v>
+      <c r="I14" s="22" t="n">
+        <v>69</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46344</v>
@@ -1045,7 +1059,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.009613226387814601</v>
+        <v>0.009451599621287882</v>
       </c>
     </row>
     <row r="15">
@@ -1079,8 +1093,8 @@
       <c r="H15" s="10" t="n">
         <v>46280</v>
       </c>
-      <c r="I15" s="13" t="n">
-        <v>78</v>
+      <c r="I15" s="22" t="n">
+        <v>71</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46303</v>
@@ -1091,7 +1105,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.06477481020832258</v>
+        <v>0.06707721265084407</v>
       </c>
     </row>
     <row r="16">
@@ -1125,8 +1139,8 @@
       <c r="H16" s="10" t="n">
         <v>46285</v>
       </c>
-      <c r="I16" s="13" t="n">
-        <v>83</v>
+      <c r="I16" s="22" t="n">
+        <v>76</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46325</v>
@@ -1137,7 +1151,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02014684548490726</v>
+        <v>0.01867254003883344</v>
       </c>
     </row>
     <row r="17">
@@ -1171,8 +1185,8 @@
       <c r="H17" s="10" t="n">
         <v>46305</v>
       </c>
-      <c r="I17" s="13" t="n">
-        <v>103</v>
+      <c r="I17" s="22" t="n">
+        <v>96</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46339</v>
@@ -1183,7 +1197,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02976903297327682</v>
+        <v>0.02871523995292049</v>
       </c>
     </row>
     <row r="18">
@@ -1217,8 +1231,8 @@
       <c r="H18" s="10" t="n">
         <v>46311</v>
       </c>
-      <c r="I18" s="13" t="n">
-        <v>109</v>
+      <c r="I18" s="22" t="n">
+        <v>102</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46386</v>
@@ -1229,7 +1243,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01183177102782167</v>
+        <v>0.01222579016936565</v>
       </c>
     </row>
     <row r="19">
@@ -1263,8 +1277,8 @@
       <c r="H19" s="10" t="n">
         <v>46317</v>
       </c>
-      <c r="I19" s="13" t="n">
-        <v>115</v>
+      <c r="I19" s="22" t="n">
+        <v>108</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46351</v>
@@ -1275,7 +1289,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.01960505770657732</v>
+        <v>0.01891447392155589</v>
       </c>
     </row>
     <row r="20">
@@ -1309,8 +1323,8 @@
       <c r="H20" s="10" t="n">
         <v>46322</v>
       </c>
-      <c r="I20" s="13" t="n">
-        <v>120</v>
+      <c r="I20" s="22" t="n">
+        <v>113</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46338</v>
@@ -1321,7 +1335,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02201724414764789</v>
+        <v>0.0223122847115672</v>
       </c>
     </row>
     <row r="21">
@@ -1355,8 +1369,8 @@
       <c r="H21" s="10" t="n">
         <v>46329</v>
       </c>
-      <c r="I21" s="13" t="n">
-        <v>127</v>
+      <c r="I21" s="22" t="n">
+        <v>120</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46338</v>
@@ -1367,7 +1381,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.008374625278987521</v>
+        <v>0.008169517657604557</v>
       </c>
     </row>
     <row r="22">
@@ -1401,8 +1415,8 @@
       <c r="H22" s="10" t="n">
         <v>46332</v>
       </c>
-      <c r="I22" s="13" t="n">
-        <v>130</v>
+      <c r="I22" s="22" t="n">
+        <v>123</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46346</v>
@@ -1413,7 +1427,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02468136743815182</v>
+        <v>0.02366835262725075</v>
       </c>
     </row>
     <row r="23">
@@ -1447,8 +1461,8 @@
       <c r="H23" s="10" t="n">
         <v>46341</v>
       </c>
-      <c r="I23" s="13" t="n">
-        <v>139</v>
+      <c r="I23" s="22" t="n">
+        <v>132</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46339</v>
@@ -1459,7 +1473,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03029189152561084</v>
+        <v>0.03013899116296197</v>
       </c>
     </row>
     <row r="24">
@@ -1493,8 +1507,8 @@
       <c r="H24" s="10" t="n">
         <v>46344</v>
       </c>
-      <c r="I24" s="13" t="n">
-        <v>142</v>
+      <c r="I24" s="22" t="n">
+        <v>135</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46385</v>
@@ -1505,7 +1519,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03701918322307009</v>
+        <v>0.03727793340807439</v>
       </c>
     </row>
     <row r="25">
@@ -1539,8 +1553,8 @@
       <c r="H25" s="10" t="n">
         <v>46347</v>
       </c>
-      <c r="I25" s="13" t="n">
-        <v>145</v>
+      <c r="I25" s="22" t="n">
+        <v>138</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46358</v>
@@ -1551,7 +1565,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.04014196593747481</v>
+        <v>0.03838502185069386</v>
       </c>
     </row>
     <row r="26">
@@ -1585,8 +1599,8 @@
       <c r="H26" s="10" t="n">
         <v>46352</v>
       </c>
-      <c r="I26" s="13" t="n">
-        <v>150</v>
+      <c r="I26" s="22" t="n">
+        <v>143</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46400</v>
@@ -1597,7 +1611,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04419306107730098</v>
+        <v>0.04816108666911</v>
       </c>
     </row>
     <row r="27">
@@ -1631,8 +1645,8 @@
       <c r="H27" s="10" t="n">
         <v>46360</v>
       </c>
-      <c r="I27" s="13" t="n">
-        <v>158</v>
+      <c r="I27" s="22" t="n">
+        <v>151</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46371</v>
@@ -1643,7 +1657,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.04904393366268946</v>
+        <v>0.0491947269380616</v>
       </c>
     </row>
     <row r="28">
@@ -1677,8 +1691,8 @@
       <c r="H28" s="10" t="n">
         <v>46366</v>
       </c>
-      <c r="I28" s="13" t="n">
-        <v>164</v>
+      <c r="I28" s="22" t="n">
+        <v>157</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46432</v>
@@ -1689,7 +1703,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02792475819572862</v>
+        <v>0.02790465823278872</v>
       </c>
     </row>
     <row r="29">
@@ -1723,8 +1737,8 @@
       <c r="H29" s="10" t="n">
         <v>46371</v>
       </c>
-      <c r="I29" s="13" t="n">
-        <v>169</v>
+      <c r="I29" s="22" t="n">
+        <v>162</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46344</v>
@@ -1735,59 +1749,59 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02038103705005755</v>
+        <v>0.02077922006309264</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="G30" s="9" t="n">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G30" s="18" t="n">
         <v>0.06</v>
       </c>
-      <c r="H30" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="n">
-        <v>0.01647272886959504</v>
+      <c r="H30" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>174</v>
+      </c>
+      <c r="J30" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L30" s="18" t="n">
+        <v>0.01574908177427583</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1797,29 +1811,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.703</v>
+        <v>0.86</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.676</v>
+        <v>0.8</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46411</v>
-      </c>
-      <c r="I31" s="13" t="n">
-        <v>209</v>
+        <v>46402</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>193</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46435</v>
+        <v>46483</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1827,13 +1841,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0373687707641196</v>
+        <v>0.01611920688332178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1847,25 +1861,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1.78</v>
+        <v>0.703</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1.71</v>
+        <v>0.676</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>215</v>
+        <v>46411</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <v>202</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46433</v>
+        <v>46435</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1873,45 +1887,45 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.04189467565667787</v>
+        <v>0.03827152172028183</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1.275</v>
+        <v>1.78</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.584</v>
+        <v>1.71</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>220</v>
+        <v>46417</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <v>208</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46472</v>
+        <v>46433</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1919,18 +1933,18 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05293751498715974</v>
+        <v>0.04217010278625639</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1939,25 +1953,25 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.61</v>
+        <v>1.275</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.58</v>
+        <v>0.584</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46428</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>226</v>
+        <v>46422</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <v>213</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46452</v>
+        <v>46472</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1965,13 +1979,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01789381042152013</v>
+        <v>0.05230232682053303</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1985,13 +1999,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1.27</v>
+        <v>0.58</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0.08</v>
@@ -1999,11 +2013,11 @@
       <c r="H35" s="10" t="n">
         <v>46428</v>
       </c>
-      <c r="I35" s="13" t="n">
-        <v>226</v>
+      <c r="I35" s="22" t="n">
+        <v>219</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46460</v>
+        <v>46452</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2011,13 +2025,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04650330901620179</v>
+        <v>0.01677321770485241</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2027,29 +2041,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.41</v>
+        <v>1.27</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46431</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>229</v>
+        <v>46428</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>219</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46480</v>
+        <v>46460</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2057,13 +2071,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01444043366754725</v>
+        <v>0.04387260015233685</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2073,29 +2087,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.63</v>
+        <v>0.41</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46432</v>
-      </c>
-      <c r="I37" s="13" t="n">
-        <v>230</v>
+        <v>46431</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <v>222</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46455</v>
+        <v>46480</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2103,13 +2117,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.03219606041300103</v>
+        <v>0.01464499022474442</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2119,29 +2133,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.177</v>
+        <v>0.67</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1.883</v>
+        <v>0.63</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>231</v>
+        <v>46432</v>
+      </c>
+      <c r="I38" s="22" t="n">
+        <v>223</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46425</v>
+        <v>46455</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2149,13 +2163,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.007051303507108543</v>
+        <v>0.03305581376353177</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2165,29 +2179,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.3</v>
+        <v>3.177</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.25</v>
+        <v>1.883</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.96</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H39" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I39" s="13" t="n">
-        <v>231</v>
+      <c r="I39" s="22" t="n">
+        <v>224</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46383</v>
+        <v>46425</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2195,13 +2209,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.02338576410879153</v>
+        <v>0.006916520750870562</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2215,13 +2229,13 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.32</v>
+        <v>1.3</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.24</v>
+        <v>1.25</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>4.96</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0.06</v>
@@ -2229,11 +2243,11 @@
       <c r="H40" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I40" s="13" t="n">
-        <v>231</v>
+      <c r="I40" s="22" t="n">
+        <v>224</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46368</v>
+        <v>46383</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2241,13 +2255,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.0299976577203504</v>
+        <v>0.0222478932745187</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2257,29 +2271,29 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I41" s="13" t="n">
-        <v>231</v>
+      <c r="I41" s="22" t="n">
+        <v>224</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46270</v>
+        <v>46368</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2287,13 +2301,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03064847788156331</v>
+        <v>0.03159713781868049</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2303,29 +2317,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.545</v>
+        <v>0.8</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.79</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H42" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="I42" s="13" t="n">
-        <v>231</v>
+      <c r="I42" s="22" t="n">
+        <v>224</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46243</v>
+        <v>46270</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2333,13 +2347,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03599735717577861</v>
+        <v>0.02865842642888866</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2349,29 +2363,29 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.29</v>
+        <v>0.545</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.27</v>
+        <v>0.588964</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46440</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>238</v>
+        <v>46433</v>
+      </c>
+      <c r="I43" s="22" t="n">
+        <v>224</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46450</v>
+        <v>46243</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2379,13 +2393,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.009721756645716097</v>
+        <v>0.03565587212565616</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2399,25 +2413,25 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2.33</v>
+        <v>0.29</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2.3</v>
+        <v>0.27</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>239</v>
+        <v>46440</v>
+      </c>
+      <c r="I44" s="22" t="n">
+        <v>231</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46456</v>
+        <v>46450</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2425,13 +2439,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02690880658391252</v>
+        <v>0.01012128081164349</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2441,29 +2455,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.59</v>
+        <v>2.33</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>250</v>
+        <v>46441</v>
+      </c>
+      <c r="I45" s="22" t="n">
+        <v>232</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46487</v>
+        <v>46456</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2471,13 +2485,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.01815975412709446</v>
+        <v>0.02669798647274613</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2487,29 +2501,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="E46" s="7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="F46" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>259</v>
+        <v>46452</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>243</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46300</v>
+        <v>46487</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2517,45 +2531,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01821161948526943</v>
+        <v>0.01706993074294785</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.271</v>
+        <v>1.5</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.27</v>
+        <v>1.4</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H47" s="10" t="n">
         <v>46461</v>
       </c>
-      <c r="I47" s="13" t="n">
-        <v>259</v>
+      <c r="I47" s="22" t="n">
+        <v>252</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46386</v>
+        <v>46300</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2563,45 +2577,45 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.05195294805937987</v>
+        <v>0.01781049606101486</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.089</v>
+        <v>0.271</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.057</v>
+        <v>0.27</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>286</v>
+        <v>46461</v>
+      </c>
+      <c r="I48" s="22" t="n">
+        <v>252</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46498</v>
+        <v>46386</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2609,18 +2623,18 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02944038795851004</v>
+        <v>0.0514516241719684</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2629,25 +2643,25 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.087</v>
+        <v>1.089</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.976</v>
+        <v>1.057</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46492</v>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>290</v>
+        <v>46488</v>
+      </c>
+      <c r="I49" s="22" t="n">
+        <v>279</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46501</v>
+        <v>46498</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2655,33 +2669,33 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02013615591849956</v>
+        <v>0.02947325724122701</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.974</v>
+        <v>1.087</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.994</v>
+        <v>0.976</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0.06</v>
@@ -2689,11 +2703,11 @@
       <c r="H50" s="10" t="n">
         <v>46492</v>
       </c>
-      <c r="I50" s="13" t="n">
-        <v>290</v>
+      <c r="I50" s="22" t="n">
+        <v>283</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46376</v>
+        <v>46501</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2701,13 +2715,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.0498018641546523</v>
+        <v>0.02022325581395349</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2717,29 +2731,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.34</v>
+        <v>0.974</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1.3</v>
+        <v>0.994</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46493</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>291</v>
+        <v>46492</v>
+      </c>
+      <c r="I51" s="22" t="n">
+        <v>283</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46531</v>
+        <v>46376</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2747,13 +2761,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.02100025461704885</v>
+        <v>0.05102481603972341</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2767,25 +2781,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46499</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>297</v>
+        <v>46493</v>
+      </c>
+      <c r="I52" s="22" t="n">
+        <v>284</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46526</v>
+        <v>46531</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2793,13 +2807,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02889236506851984</v>
+        <v>0.02086008852056917</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2809,29 +2823,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.551</v>
+        <v>1.27</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.525</v>
+        <v>1.2</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.04952380952380957</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>302</v>
+        <v>46499</v>
+      </c>
+      <c r="I53" s="22" t="n">
+        <v>290</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46562</v>
+        <v>46526</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2839,13 +2853,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.04219797088486882</v>
+        <v>0.02839337221937417</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2855,29 +2869,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.19</v>
+        <v>0.551</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1.08</v>
+        <v>0.525</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>306</v>
+        <v>46504</v>
+      </c>
+      <c r="I54" s="22" t="n">
+        <v>295</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46518</v>
+        <v>46562</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2885,13 +2899,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04748129675810474</v>
+        <v>0.04190114189992526</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2901,29 +2915,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.423</v>
+        <v>1.08</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46515</v>
-      </c>
-      <c r="I55" s="13" t="n">
-        <v>313</v>
+        <v>46508</v>
+      </c>
+      <c r="I55" s="22" t="n">
+        <v>299</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46542</v>
+        <v>46518</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2931,53 +2945,99 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.042147228513663</v>
+        <v>0.04495018793044805</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>0.04005621925509482</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>46515</v>
+      </c>
+      <c r="I56" s="22" t="n">
+        <v>306</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>46542</v>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>0.04171070461141636</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>MDT</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n">
+      <c r="D57" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E57" s="7" t="n">
         <v>0.71</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F57" s="8" t="n">
         <v>0.01408450704225353</v>
       </c>
-      <c r="G56" s="9" t="n">
+      <c r="G57" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="H56" s="10" t="n">
+      <c r="H57" s="10" t="n">
         <v>46532</v>
       </c>
-      <c r="I56" s="13" t="n">
-        <v>330</v>
-      </c>
-      <c r="J56" s="10" t="n">
+      <c r="I57" s="22" t="n">
+        <v>323</v>
+      </c>
+      <c r="J57" s="10" t="n">
         <v>46563</v>
       </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="n">
-        <v>0.03548983297408272</v>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>0.03518201781732959</v>
       </c>
     </row>
   </sheetData>
@@ -2991,7 +3051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3012,44 +3072,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 06/29/2026</t>
+          <t>Expected Increase Announcements by Month - 07/06/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3080,39 +3140,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3263,39 +3323,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3326,39 +3386,39 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3437,39 +3497,39 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3572,39 +3632,39 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3755,39 +3815,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D44" s="23" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3865,86 +3925,86 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C51" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D51" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E51" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
+      <c r="F51" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>DGX</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>46402</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>46483</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.07499999999999993</v>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>46411</v>
+        <v>46402</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46435</v>
+        <v>46483</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.703</v>
+        <v>0.86</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.07499999999999993</v>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
@@ -3955,107 +4015,107 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
+          <t>BKH</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>46411</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>46435</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0.03994082840236673</v>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n">
+      <c r="B54" s="10" t="n">
         <v>46417</v>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C54" s="10" t="n">
         <v>46433</v>
       </c>
-      <c r="D53" s="7" t="n">
+      <c r="D54" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="E54" s="8" t="n">
         <v>0.04093567251461992</v>
       </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="inlineStr">
         <is>
+          <t>February 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr">
+      <c r="B57" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E56" s="23" t="inlineStr">
+      <c r="E57" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>46422</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>46472</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>1.275</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>1.183219178082192</v>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46428</v>
+        <v>46422</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46452</v>
+        <v>46472</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.61</v>
+        <v>1.275</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4066,20 +4126,20 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
         <v>46428</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46460</v>
+        <v>46452</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4090,20 +4150,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46431</v>
+        <v>46428</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46480</v>
+        <v>46460</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4114,20 +4174,20 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46432</v>
+        <v>46431</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46455</v>
+        <v>46480</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4138,20 +4198,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
-        <v>46433</v>
+        <v>46432</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46425</v>
+        <v>46455</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>3.177</v>
+        <v>0.67</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4162,20 +4222,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46383</v>
+        <v>46425</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.3</v>
+        <v>3.177</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>4.96</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4186,20 +4246,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46368</v>
+        <v>46383</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.32</v>
+        <v>1.3</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>4.96</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4210,20 +4270,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46270</v>
+        <v>46368</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4234,20 +4294,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46243</v>
+        <v>46270</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.545</v>
+        <v>0.8</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4258,20 +4318,20 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>46440</v>
+        <v>46433</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46450</v>
+        <v>46243</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.29</v>
+        <v>0.545</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
@@ -4282,107 +4342,107 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n">
+        <v>46440</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>46450</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.07407407407407393</v>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n">
+      <c r="B69" s="10" t="n">
         <v>46441</v>
       </c>
-      <c r="C68" s="10" t="n">
+      <c r="C69" s="10" t="n">
         <v>46456</v>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D69" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="E69" s="8" t="n">
         <v>0.01304347826086967</v>
       </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="22" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
+          <t>March 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B71" s="23" t="inlineStr">
+      <c r="B72" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C71" s="23" t="inlineStr">
+      <c r="C72" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D71" s="23" t="inlineStr">
+      <c r="D72" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E71" s="23" t="inlineStr">
+      <c r="E72" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F71" s="23" t="inlineStr">
+      <c r="F72" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>46452</v>
-      </c>
-      <c r="C72" s="10" t="n">
-        <v>46487</v>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
-        <v>46461</v>
+        <v>46452</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46300</v>
+        <v>46487</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4393,107 +4453,107 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B74" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C74" s="10" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.07142857142857149</v>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C75" s="10" t="n">
         <v>46386</v>
       </c>
-      <c r="D74" s="7" t="n">
+      <c r="D75" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="E74" s="8" t="n">
+      <c r="E75" s="8" t="n">
         <v>0.003703703703703707</v>
       </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="22" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="23" t="inlineStr">
         <is>
+          <t>April 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B77" s="23" t="inlineStr">
+      <c r="B78" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
+      <c r="C78" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D77" s="23" t="inlineStr">
+      <c r="D78" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E77" s="23" t="inlineStr">
+      <c r="E78" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F77" s="23" t="inlineStr">
+      <c r="F78" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="n">
-        <v>46488</v>
-      </c>
-      <c r="C78" s="10" t="n">
-        <v>46498</v>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0.03027436140018924</v>
-      </c>
-      <c r="F78" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46492</v>
+        <v>46488</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46501</v>
+        <v>46498</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.087</v>
+        <v>1.089</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4504,20 +4564,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46376</v>
+        <v>46501</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.974</v>
+        <v>1.087</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4528,20 +4588,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46493</v>
+        <v>46492</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46531</v>
+        <v>46376</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.34</v>
+        <v>0.974</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4552,20 +4612,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46499</v>
+        <v>46493</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46526</v>
+        <v>46531</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4576,107 +4636,107 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n">
+        <v>46499</v>
+      </c>
+      <c r="C83" s="10" t="n">
+        <v>46526</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.05833333333333339</v>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
           <t>POR</t>
         </is>
       </c>
-      <c r="B83" s="10" t="n">
+      <c r="B84" s="10" t="n">
         <v>46504</v>
       </c>
-      <c r="C83" s="10" t="n">
+      <c r="C84" s="10" t="n">
         <v>46562</v>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D84" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E84" s="8" t="n">
         <v>0.04952380952380957</v>
       </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="23" t="inlineStr">
         <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B86" s="23" t="inlineStr">
+      <c r="B87" s="24" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C86" s="23" t="inlineStr">
+      <c r="C87" s="24" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D86" s="23" t="inlineStr">
+      <c r="D87" s="24" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E86" s="23" t="inlineStr">
+      <c r="E87" s="24" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F86" s="23" t="inlineStr">
+      <c r="F87" s="24" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>46508</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>46518</v>
-      </c>
-      <c r="D87" s="7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0.1018518518518517</v>
-      </c>
-      <c r="F87" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
-        <v>46515</v>
+        <v>46508</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46542</v>
+        <v>46518</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4687,22 +4747,46 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
+        <v>46515</v>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>46542</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.04005621925509482</v>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>MDT</t>
         </is>
       </c>
-      <c r="B89" s="10" t="n">
+      <c r="B90" s="10" t="n">
         <v>46532</v>
       </c>
-      <c r="C89" s="10" t="n">
+      <c r="C90" s="10" t="n">
         <v>46563</v>
       </c>
-      <c r="D89" s="7" t="n">
+      <c r="D90" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="E89" s="8" t="n">
+      <c r="E90" s="8" t="n">
         <v>0.01408450704225353</v>
       </c>
-      <c r="F89" s="12" t="inlineStr">
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4719,7 +4803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4747,7 +4831,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 06/29/2026</t>
+          <t>Complete Holdings Dividend Summary - 07/06/2026</t>
         </is>
       </c>
     </row>
@@ -4847,11 +4931,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="25" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009721756645716097</v>
+        <v>0.01012128081164349</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4900,11 +4984,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="25" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02792475819572862</v>
+        <v>0.02790465823278872</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -4953,11 +5037,11 @@
       <c r="F7" s="7" t="n">
         <v>3.177</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="25" t="n">
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.007051303507108543</v>
+        <v>0.006916520750870562</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -5006,11 +5090,11 @@
       <c r="F8" s="16" t="n">
         <v>0.504</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="26" t="n">
         <v>2.016</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.02451063829787234</v>
+        <v>0.02398429590958984</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>46160</v>
@@ -5059,11 +5143,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="25" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.0373687707641196</v>
+        <v>0.03827152172028183</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46157</v>
@@ -5112,11 +5196,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="25" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02656522082200493</v>
+        <v>0.02647389558232932</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46171</v>
@@ -5165,11 +5249,11 @@
       <c r="F11" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="25" t="n">
         <v>4.96</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05151908513516609</v>
+        <v>0.05178804407181118</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46134</v>
@@ -5218,11 +5302,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02338576410879153</v>
+        <v>0.0222478932745187</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46182</v>
@@ -5271,11 +5355,11 @@
       <c r="F13" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="25" t="n">
         <v>0.92</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02038103705005755</v>
+        <v>0.02077922006309264</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46163</v>
@@ -5324,11 +5408,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="25" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.008374625278987521</v>
+        <v>0.008169517657604557</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46157</v>
@@ -5377,11 +5461,11 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="25" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01444043366754725</v>
+        <v>0.01464499022474442</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46114</v>
@@ -5430,11 +5514,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="25" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.04189467565667787</v>
+        <v>0.04217010278625639</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46161</v>
@@ -5483,11 +5567,11 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="25" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01647272886959504</v>
+        <v>0.01611920688332178</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46118</v>
@@ -5536,11 +5620,11 @@
       <c r="F18" s="7" t="n">
         <v>0.32</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="25" t="n">
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.0299976577203504</v>
+        <v>0.03159713781868049</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46188</v>
@@ -5589,11 +5673,11 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="25" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.04904393366268946</v>
+        <v>0.0491947269380616</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46188</v>
@@ -5642,11 +5726,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02201724414764789</v>
+        <v>0.0223122847115672</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46143</v>
@@ -5695,14 +5779,14 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="25" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01815975412709446</v>
+        <v>0.01706993074294785</v>
       </c>
       <c r="I21" s="10" t="n">
-        <v>46122</v>
+        <v>46205</v>
       </c>
       <c r="J21" s="8" t="n">
         <v>0.06000000000000005</v>
@@ -5720,67 +5804,67 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>QDVD/DAC</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Mar/Jun/Aug/Nov</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="G22" s="24" t="n">
-        <v>9.32</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>0.02690880658391252</v>
-      </c>
-      <c r="I22" s="10" t="n">
-        <v>46177</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>SMID/DAC</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Jan/Apr/Jul/Oct</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>0.01574908177427583</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <v>46125</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>46404</v>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5790,34 +5874,34 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Aug/Nov</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G23" s="24" t="n">
-        <v>5.52</v>
+        <v>2.33</v>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.01960505770657732</v>
+        <v>0.02669798647274613</v>
       </c>
       <c r="I23" s="10" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>46317</v>
+        <v>46441</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>46351</v>
+        <v>46456</v>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
@@ -5828,7 +5912,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -5843,34 +5927,34 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="G24" s="24" t="n">
-        <v>1.172</v>
+        <v>1.38</v>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.04419306107730098</v>
+        <v>0.01891447392155589</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>46125</v>
+        <v>46171</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>46352</v>
+        <v>46317</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>46400</v>
+        <v>46351</v>
       </c>
       <c r="M24" s="12" t="inlineStr">
         <is>
@@ -5881,7 +5965,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -5896,34 +5980,34 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Oct/Dec</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G25" s="24" t="n">
-        <v>3.28</v>
+        <v>0.293</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.03387554973798062</v>
+        <v>0.04816108666911</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>46263</v>
+        <v>46352</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>46297</v>
+        <v>46400</v>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
@@ -5934,12 +6018,12 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -5949,34 +6033,34 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Mar/May/Sep/Dec</t>
+          <t>Mar/Jul/Oct/Dec</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="G26" s="24" t="n">
-        <v>2.44</v>
+        <v>0.82</v>
+      </c>
+      <c r="G26" s="25" t="n">
+        <v>3.28</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.01789381042152013</v>
+        <v>0.03396144718830089</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>46428</v>
+        <v>46263</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>46452</v>
+        <v>46297</v>
       </c>
       <c r="M26" s="12" t="inlineStr">
         <is>
@@ -5987,12 +6071,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -6002,34 +6086,34 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/May/Sep/Dec</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G27" s="24" t="n">
-        <v>5.36</v>
+        <v>0.61</v>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>2.44</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.02100025461704885</v>
+        <v>0.01677321770485241</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>46168</v>
+        <v>46086</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>46493</v>
+        <v>46428</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>46531</v>
+        <v>46452</v>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
@@ -6040,7 +6124,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -6055,34 +6139,34 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G28" s="24" t="n">
-        <v>6</v>
+        <v>1.34</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>5.36</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.01821161948526943</v>
+        <v>0.02086008852056917</v>
       </c>
       <c r="I28" s="10" t="n">
-        <v>46118</v>
+        <v>46168</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>46461</v>
+        <v>46493</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>46300</v>
+        <v>46531</v>
       </c>
       <c r="M28" s="12" t="inlineStr">
         <is>
@@ -6093,49 +6177,49 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Apr/Oct</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1.087</v>
-      </c>
-      <c r="G29" s="24" t="n">
-        <v>2.174</v>
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.02013615591849956</v>
+        <v>0.01781049606101486</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>46492</v>
+        <v>46461</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>46501</v>
+        <v>46300</v>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
@@ -6146,49 +6230,49 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Apr/Oct</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G30" s="24" t="n">
-        <v>3.16</v>
+        <v>1.087</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>2.174</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.01183177102782167</v>
+        <v>0.02022325581395349</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>46112</v>
+        <v>46132</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.1137295081967213</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>46311</v>
+        <v>46492</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>46386</v>
+        <v>46501</v>
       </c>
       <c r="M30" s="12" t="inlineStr">
         <is>
@@ -6199,12 +6283,12 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -6219,29 +6303,29 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G31" s="24" t="n">
-        <v>2.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>3.16</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.03548983297408272</v>
+        <v>0.01222579016936565</v>
       </c>
       <c r="I31" s="10" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>46532</v>
+        <v>46311</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>46563</v>
+        <v>46386</v>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
@@ -6252,12 +6336,12 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -6267,34 +6351,34 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Apr/Jul/Oct/Dec</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G32" s="24" t="n">
-        <v>1.92</v>
+        <v>0.72</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>2.88</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.03701918322307009</v>
+        <v>0.03518201781732959</v>
       </c>
       <c r="I32" s="10" t="n">
-        <v>46132</v>
+        <v>46199</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>46344</v>
+        <v>46532</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>46385</v>
+        <v>46563</v>
       </c>
       <c r="M32" s="12" t="inlineStr">
         <is>
@@ -6305,12 +6389,12 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -6320,34 +6404,34 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Apr/Jul/Oct/Dec</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G33" s="24" t="n">
-        <v>3.64</v>
+        <v>0.48</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>1.92</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.009613226387814601</v>
+        <v>0.03727793340807439</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>46163</v>
+        <v>46132</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>46278</v>
+        <v>46344</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>46344</v>
+        <v>46385</v>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
@@ -6358,12 +6442,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -6373,7 +6457,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Nov</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -6382,25 +6466,25 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G34" s="24" t="n">
-        <v>3.48</v>
+        <v>0.91</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>3.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.02976903297327682</v>
+        <v>0.009451599621287882</v>
       </c>
       <c r="I34" s="10" t="n">
-        <v>46120</v>
+        <v>46163</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>46305</v>
+        <v>46278</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>46339</v>
+        <v>46344</v>
       </c>
       <c r="M34" s="12" t="inlineStr">
         <is>
@@ -6411,12 +6495,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -6426,34 +6510,34 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Jan/Apr/Jul/Nov</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G35" s="24" t="n">
-        <v>1.64</v>
+        <v>0.87</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>3.48</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.04014196593747481</v>
+        <v>0.02871523995292049</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>46174</v>
+        <v>46120</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>46347</v>
+        <v>46305</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>46358</v>
+        <v>46339</v>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
@@ -6464,49 +6548,49 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Mar/Aug</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>1.275</v>
-      </c>
-      <c r="G36" s="24" t="n">
-        <v>2.55</v>
+        <v>0.41</v>
+      </c>
+      <c r="G36" s="25" t="n">
+        <v>1.64</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.05293751498715974</v>
+        <v>0.03838502185069386</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>46111</v>
+        <v>46083</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>46422</v>
+        <v>46347</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>46472</v>
+        <v>46358</v>
       </c>
       <c r="M36" s="12" t="inlineStr">
         <is>
@@ -6517,49 +6601,49 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Jan/Feb/Mar/Apr/May/Jun/Jul/Aug/Sep/Oct/Nov/Dec</t>
+          <t>Mar/Aug</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="G37" s="24" t="n">
-        <v>3.252</v>
+        <v>1.275</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>2.55</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.05195294805937987</v>
+        <v>0.05230232682053303</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>46171</v>
+        <v>46111</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>46461</v>
+        <v>46422</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>46386</v>
+        <v>46472</v>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
@@ -6570,49 +6654,49 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Jan/Feb/Mar/Apr/May/Jun/Jul/Aug/Sep/Oct/Nov/Dec</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G38" s="24" t="n">
-        <v>4.76</v>
+        <v>0.271</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>3.252</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.04748129675810474</v>
+        <v>0.0514516241719684</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>46155</v>
+        <v>46203</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>46508</v>
+        <v>46461</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>46518</v>
+        <v>46386</v>
       </c>
       <c r="M38" s="12" t="inlineStr">
         <is>
@@ -6623,12 +6707,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -6638,34 +6722,34 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>2.68</v>
+        <v>1.19</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>4.76</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.03219606041300103</v>
+        <v>0.04495018793044805</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>46182</v>
+        <v>46155</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>46432</v>
+        <v>46508</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>46455</v>
+        <v>46518</v>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
@@ -6676,7 +6760,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -6696,29 +6780,29 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G40" s="24" t="n">
-        <v>5.92</v>
+        <v>0.67</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>2.68</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.042147228513663</v>
+        <v>0.03305581376353177</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>46515</v>
+        <v>46432</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>46542</v>
+        <v>46455</v>
       </c>
       <c r="M40" s="12" t="inlineStr">
         <is>
@@ -6729,7 +6813,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -6744,34 +6828,34 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G41" s="24" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>5.92</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.07063654920140841</v>
+        <v>0.04171070461141636</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>46150</v>
+        <v>46178</v>
       </c>
       <c r="J41" s="8" t="n">
-        <v>0.02380952380952383</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="K41" s="10" t="n">
-        <v>46048</v>
+        <v>46515</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>46413</v>
+        <v>46542</v>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
@@ -6782,12 +6866,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -6797,34 +6881,34 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Jan/May/Jul/Nov</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G42" s="24" t="n">
-        <v>3.28</v>
+        <v>0.43</v>
+      </c>
+      <c r="G42" s="25" t="n">
+        <v>1.72</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.03064847788156331</v>
+        <v>0.07243629981928987</v>
       </c>
       <c r="I42" s="10" t="n">
-        <v>46174</v>
+        <v>46150</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.02380952380952383</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>46433</v>
+        <v>46048</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>46270</v>
+        <v>46413</v>
       </c>
       <c r="M42" s="12" t="inlineStr">
         <is>
@@ -6835,12 +6919,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -6850,34 +6934,34 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>1.089</v>
-      </c>
-      <c r="G43" s="24" t="n">
-        <v>4.356</v>
+        <v>0.8</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>3.2</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02944038795851004</v>
+        <v>0.02865842642888866</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>46136</v>
+        <v>46092</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.01265822784810128</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>46488</v>
+        <v>46433</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>46498</v>
+        <v>46270</v>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
@@ -6888,12 +6972,12 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -6903,34 +6987,34 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="G44" s="24" t="n">
-        <v>2.204</v>
+        <v>1.089</v>
+      </c>
+      <c r="G44" s="25" t="n">
+        <v>4.356</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.04219797088486882</v>
+        <v>0.02947325724122701</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>46198</v>
+        <v>46136</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>0.04952380952380957</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>46504</v>
+        <v>46488</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>46562</v>
+        <v>46498</v>
       </c>
       <c r="M44" s="12" t="inlineStr">
         <is>
@@ -6941,12 +7025,12 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -6956,34 +7040,34 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="F45" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="G45" s="24" t="n">
-        <v>5.08</v>
+        <v>0.551</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>2.204</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.02889236506851984</v>
+        <v>0.04190114189992526</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>46160</v>
+        <v>46198</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="L45" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
@@ -6994,12 +7078,12 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -7014,29 +7098,29 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>May</t>
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G46" s="24" t="n">
-        <v>3.72</v>
+        <v>1.27</v>
+      </c>
+      <c r="G46" s="25" t="n">
+        <v>5.08</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.01731722625385386</v>
+        <v>0.02839337221937417</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>46218</v>
+        <v>46499</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>46248</v>
+        <v>46526</v>
       </c>
       <c r="M46" s="12" t="inlineStr">
         <is>
@@ -7047,12 +7131,12 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>SMID/DAC</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -7067,29 +7151,29 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="G47" s="24" t="n">
-        <v>9.76</v>
+        <v>0.93</v>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>3.72</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.02468136743815182</v>
+        <v>0.01674921160635266</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>46332</v>
+        <v>46218</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>46346</v>
+        <v>46248</v>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
@@ -7100,7 +7184,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -7115,34 +7199,34 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Nov</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G48" s="24" t="n">
-        <v>3.32</v>
+        <v>2.44</v>
+      </c>
+      <c r="G48" s="25" t="n">
+        <v>9.76</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.0366304399155838</v>
+        <v>0.02366835262725075</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>46181</v>
+        <v>46162</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>46227</v>
+        <v>46332</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>46267</v>
+        <v>46346</v>
       </c>
       <c r="M48" s="12" t="inlineStr">
         <is>
@@ -7153,12 +7237,12 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>QDVD/SMID/DAC</t>
+          <t>SMID/DAC</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -7168,34 +7252,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Mar/Jun/Sep/Dec</t>
+          <t>Mar/Jun/Sep/Nov</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F49" s="7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G49" s="24" t="n">
-        <v>5.2</v>
+        <v>0.83</v>
+      </c>
+      <c r="G49" s="25" t="n">
+        <v>3.32</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.04650330901620179</v>
+        <v>0.03601062976288923</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>46428</v>
+        <v>46227</v>
       </c>
       <c r="L49" s="10" t="n">
-        <v>46460</v>
+        <v>46267</v>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
@@ -7206,12 +7290,12 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/SMID/DAC</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -7226,29 +7310,29 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="G50" s="24" t="n">
-        <v>3.896</v>
+        <v>1.3</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>5.2</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.0498018641546523</v>
+        <v>0.04387260015233685</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>46112</v>
+        <v>46188</v>
       </c>
       <c r="J50" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>46492</v>
+        <v>46428</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>46376</v>
+        <v>46460</v>
       </c>
       <c r="M50" s="12" t="inlineStr">
         <is>
@@ -7259,12 +7343,12 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -7274,34 +7358,34 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Jan/May/Jul/Oct</t>
+          <t>Mar/Jun/Sep/Dec</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G51" s="24" t="n">
-        <v>5.68</v>
+        <v>0.974</v>
+      </c>
+      <c r="G51" s="25" t="n">
+        <v>3.896</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.02014684548490726</v>
+        <v>0.05102481603972341</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>46147</v>
+        <v>46112</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>46285</v>
+        <v>46492</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>46325</v>
+        <v>46376</v>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
@@ -7312,12 +7396,12 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>QDVD</t>
+          <t>QDVD/DAC</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -7327,34 +7411,34 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Nov</t>
+          <t>Jan/May/Jul/Oct</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="G52" s="24" t="n">
-        <v>2.18</v>
+        <v>1.42</v>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>5.68</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.03599735717577861</v>
+        <v>0.01867254003883344</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>46157</v>
+        <v>46147</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>46433</v>
+        <v>46285</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>46243</v>
+        <v>46325</v>
       </c>
       <c r="M52" s="12" t="inlineStr">
         <is>
@@ -7365,12 +7449,12 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>QDVD/DAC</t>
+          <t>QDVD</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -7380,7 +7464,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Feb/May/Aug/Dec</t>
+          <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -7389,25 +7473,25 @@
         </is>
       </c>
       <c r="F53" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G53" s="24" t="n">
-        <v>5.52</v>
+        <v>0.545</v>
+      </c>
+      <c r="G53" s="25" t="n">
+        <v>2.18</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.02030046090334901</v>
+        <v>0.03565587212565616</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>0.02985074626865658</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>46220</v>
+        <v>46433</v>
       </c>
       <c r="L53" s="10" t="n">
-        <v>46264</v>
+        <v>46243</v>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
@@ -7418,7 +7502,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -7433,34 +7517,34 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Jan/Apr/Jul/Oct</t>
+          <t>Feb/May/Aug/Dec</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="G54" s="24" t="n">
-        <v>2.832</v>
+        <v>1.38</v>
+      </c>
+      <c r="G54" s="25" t="n">
+        <v>5.52</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.06477481020832258</v>
+        <v>0.01950736818810225</v>
       </c>
       <c r="I54" s="10" t="n">
-        <v>46122</v>
+        <v>46171</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>46280</v>
+        <v>46220</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>46303</v>
+        <v>46264</v>
       </c>
       <c r="M54" s="12" t="inlineStr">
         <is>
@@ -7471,51 +7555,104 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>QDVD/DAC</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Jan/Apr/Jul/Oct</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="G55" s="25" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>0.06707721265084407</v>
+      </c>
+      <c r="I55" s="10" t="n">
+        <v>46122</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0.02608695652173916</v>
+      </c>
+      <c r="K55" s="10" t="n">
+        <v>46280</v>
+      </c>
+      <c r="L55" s="10" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M55" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
           <t>XOM</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>QDVD/DAC</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="F55" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G55" s="24" t="n">
+      <c r="G56" s="25" t="n">
         <v>4.12</v>
       </c>
-      <c r="H55" s="9" t="n">
-        <v>0.03029189152561084</v>
-      </c>
-      <c r="I55" s="10" t="n">
+      <c r="H56" s="9" t="n">
+        <v>0.03013899116296197</v>
+      </c>
+      <c r="I56" s="10" t="n">
         <v>46157</v>
       </c>
-      <c r="J55" s="8" t="n">
+      <c r="J56" s="8" t="n">
         <v>0.04040404040404044</v>
       </c>
-      <c r="K55" s="10" t="n">
+      <c r="K56" s="10" t="n">
         <v>46341</v>
       </c>
-      <c r="L55" s="10" t="n">
+      <c r="L56" s="10" t="n">
         <v>46339</v>
       </c>
-      <c r="M55" s="12" t="inlineStr">
+      <c r="M56" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,11 +172,14 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/06/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/13/2026</t>
         </is>
       </c>
     </row>
@@ -680,7 +683,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-161</v>
+        <v>-168</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -691,7 +694,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.07243629981928987</v>
+        <v>0.06981936204666597</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +729,7 @@
         <v>46218</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46248</v>
@@ -737,7 +740,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.01674921160635266</v>
+        <v>0.01586015754252245</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +775,7 @@
         <v>46220</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>46264</v>
@@ -783,7 +786,7 @@
         </is>
       </c>
       <c r="L8" s="9" t="n">
-        <v>0.01950736818810225</v>
+        <v>0.0191056338898471</v>
       </c>
     </row>
     <row r="9">
@@ -818,7 +821,7 @@
         <v>46227</v>
       </c>
       <c r="I9" s="20" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>46248</v>
@@ -829,7 +832,7 @@
         </is>
       </c>
       <c r="L9" s="18" t="n">
-        <v>0.02398429590958984</v>
+        <v>0.02358722325034518</v>
       </c>
     </row>
     <row r="10">
@@ -863,8 +866,8 @@
       <c r="H10" s="10" t="n">
         <v>46227</v>
       </c>
-      <c r="I10" s="22" t="n">
-        <v>18</v>
+      <c r="I10" s="13" t="n">
+        <v>11</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>46267</v>
@@ -875,7 +878,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.03601062976288923</v>
+        <v>0.03744008892858095</v>
       </c>
     </row>
     <row r="11">
@@ -910,7 +913,7 @@
         <v>46232</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46264</v>
@@ -921,7 +924,7 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02647389558232932</v>
+        <v>0.02615374869501659</v>
       </c>
     </row>
     <row r="12">
@@ -956,7 +959,7 @@
         <v>46232</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>46246</v>
@@ -967,7 +970,7 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05178804407181118</v>
+        <v>0.05128205063482052</v>
       </c>
     </row>
     <row r="13">
@@ -1002,7 +1005,7 @@
         <v>46263</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>46297</v>
@@ -1013,7 +1016,7 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03396144718830089</v>
+        <v>0.03269048716727996</v>
       </c>
     </row>
     <row r="14">
@@ -1048,7 +1051,7 @@
         <v>46278</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>46344</v>
@@ -1059,7 +1062,7 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.009451599621287882</v>
+        <v>0.009398884557615285</v>
       </c>
     </row>
     <row r="15">
@@ -1094,7 +1097,7 @@
         <v>46280</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>46303</v>
@@ -1105,7 +1108,7 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.06707721265084407</v>
+        <v>0.06631898910307311</v>
       </c>
     </row>
     <row r="16">
@@ -1140,7 +1143,7 @@
         <v>46285</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>46325</v>
@@ -1151,7 +1154,7 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01867254003883344</v>
+        <v>0.01881667089258208</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1189,7 @@
         <v>46305</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>46339</v>
@@ -1197,7 +1200,7 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02871523995292049</v>
+        <v>0.02772466613344378</v>
       </c>
     </row>
     <row r="18">
@@ -1232,7 +1235,7 @@
         <v>46311</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>46386</v>
@@ -1243,7 +1246,7 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01222579016936565</v>
+        <v>0.01243017852579043</v>
       </c>
     </row>
     <row r="19">
@@ -1278,7 +1281,7 @@
         <v>46317</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>46351</v>
@@ -1289,7 +1292,7 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.01891447392155589</v>
+        <v>0.01918932048156368</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1327,7 @@
         <v>46322</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>46338</v>
@@ -1335,7 +1338,7 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.0223122847115672</v>
+        <v>0.02204615862425437</v>
       </c>
     </row>
     <row r="21">
@@ -1370,7 +1373,7 @@
         <v>46329</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>46338</v>
@@ -1381,7 +1384,7 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.008169517657604557</v>
+        <v>0.007805259164950651</v>
       </c>
     </row>
     <row r="22">
@@ -1416,7 +1419,7 @@
         <v>46332</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>46346</v>
@@ -1427,7 +1430,7 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02366835262725075</v>
+        <v>0.02413332593824269</v>
       </c>
     </row>
     <row r="23">
@@ -1462,7 +1465,7 @@
         <v>46341</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>46339</v>
@@ -1473,7 +1476,7 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03013899116296197</v>
+        <v>0.02883740561914779</v>
       </c>
     </row>
     <row r="24">
@@ -1508,7 +1511,7 @@
         <v>46344</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>46385</v>
@@ -1519,7 +1522,7 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03727793340807439</v>
+        <v>0.03590798496665439</v>
       </c>
     </row>
     <row r="25">
@@ -1554,7 +1557,7 @@
         <v>46347</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>46358</v>
@@ -1565,7 +1568,7 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03838502185069386</v>
+        <v>0.03671778722453514</v>
       </c>
     </row>
     <row r="26">
@@ -1600,7 +1603,7 @@
         <v>46352</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>46400</v>
@@ -1611,7 +1614,7 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04816108666911</v>
+        <v>0.0475552841643708</v>
       </c>
     </row>
     <row r="27">
@@ -1646,7 +1649,7 @@
         <v>46360</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>46371</v>
@@ -1657,7 +1660,7 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.0491947269380616</v>
+        <v>0.04913358039101189</v>
       </c>
     </row>
     <row r="28">
@@ -1692,7 +1695,7 @@
         <v>46366</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>46432</v>
@@ -1703,7 +1706,7 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02790465823278872</v>
+        <v>0.02787263837801698</v>
       </c>
     </row>
     <row r="29">
@@ -1738,7 +1741,7 @@
         <v>46371</v>
       </c>
       <c r="I29" s="22" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>46344</v>
@@ -1749,7 +1752,7 @@
         </is>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.02077922006309264</v>
+        <v>0.02089959087762214</v>
       </c>
     </row>
     <row r="30">
@@ -1783,8 +1786,8 @@
       <c r="H30" s="19" t="n">
         <v>46383</v>
       </c>
-      <c r="I30" s="20" t="n">
-        <v>174</v>
+      <c r="I30" s="23" t="n">
+        <v>167</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>46404</v>
@@ -1795,7 +1798,7 @@
         </is>
       </c>
       <c r="L30" s="18" t="n">
-        <v>0.01574908177427583</v>
+        <v>0.01576907618770492</v>
       </c>
     </row>
     <row r="31">
@@ -1830,7 +1833,7 @@
         <v>46402</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>46483</v>
@@ -1841,7 +1844,7 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01611920688332178</v>
+        <v>0.01638173203491813</v>
       </c>
     </row>
     <row r="32">
@@ -1876,7 +1879,7 @@
         <v>46411</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>46435</v>
@@ -1887,7 +1890,7 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03827152172028183</v>
+        <v>0.03690046496205276</v>
       </c>
     </row>
     <row r="33">
@@ -1922,7 +1925,7 @@
         <v>46417</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>46433</v>
@@ -1933,7 +1936,7 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.04217010278625639</v>
+        <v>0.03954566954044979</v>
       </c>
     </row>
     <row r="34">
@@ -1968,7 +1971,7 @@
         <v>46422</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>46472</v>
@@ -1979,7 +1982,7 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.05230232682053303</v>
+        <v>0.05161421036343746</v>
       </c>
     </row>
     <row r="35">
@@ -2014,7 +2017,7 @@
         <v>46428</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>46452</v>
@@ -2025,7 +2028,7 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01677321770485241</v>
+        <v>0.01603364514018875</v>
       </c>
     </row>
     <row r="36">
@@ -2060,7 +2063,7 @@
         <v>46428</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>46460</v>
@@ -2071,7 +2074,7 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.04387260015233685</v>
+        <v>0.04476198744909742</v>
       </c>
     </row>
     <row r="37">
@@ -2106,7 +2109,7 @@
         <v>46431</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>46480</v>
@@ -2117,7 +2120,7 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01464499022474442</v>
+        <v>0.01424996859778785</v>
       </c>
     </row>
     <row r="38">
@@ -2152,7 +2155,7 @@
         <v>46432</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>46455</v>
@@ -2163,7 +2166,7 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.03305581376353177</v>
+        <v>0.0330425677095552</v>
       </c>
     </row>
     <row r="39">
@@ -2198,7 +2201,7 @@
         <v>46433</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>46425</v>
@@ -2209,7 +2212,7 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.006916520750870562</v>
+        <v>0.007227558827049737</v>
       </c>
     </row>
     <row r="40">
@@ -2244,7 +2247,7 @@
         <v>46433</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>46383</v>
@@ -2255,7 +2258,7 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.0222478932745187</v>
+        <v>0.02151071350144007</v>
       </c>
     </row>
     <row r="41">
@@ -2290,7 +2293,7 @@
         <v>46433</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>46368</v>
@@ -2301,7 +2304,7 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.03159713781868049</v>
+        <v>0.02956461610196163</v>
       </c>
     </row>
     <row r="42">
@@ -2321,13 +2324,13 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E42" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="E42" s="7" t="n">
-        <v>0.79</v>
-      </c>
       <c r="F42" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0.04</v>
@@ -2336,7 +2339,7 @@
         <v>46433</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>46270</v>
@@ -2347,7 +2350,7 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.02865842642888866</v>
+        <v>0.0289241618683001</v>
       </c>
     </row>
     <row r="43">
@@ -2382,7 +2385,7 @@
         <v>46433</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>46243</v>
@@ -2393,7 +2396,7 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.03565587212565616</v>
+        <v>0.03523517112712499</v>
       </c>
     </row>
     <row r="44">
@@ -2428,7 +2431,7 @@
         <v>46440</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J44" s="10" t="n">
         <v>46450</v>
@@ -2439,7 +2442,7 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.01012128081164349</v>
+        <v>0.009957936486157157</v>
       </c>
     </row>
     <row r="45">
@@ -2474,7 +2477,7 @@
         <v>46441</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>46456</v>
@@ -2485,7 +2488,7 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.02669798647274613</v>
+        <v>0.02709302325581395</v>
       </c>
     </row>
     <row r="46">
@@ -2520,7 +2523,7 @@
         <v>46452</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>46487</v>
@@ -2531,7 +2534,7 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01706993074294785</v>
+        <v>0.01690972219968362</v>
       </c>
     </row>
     <row r="47">
@@ -2566,7 +2569,7 @@
         <v>46461</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>46300</v>
@@ -2577,7 +2580,7 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.01781049606101486</v>
+        <v>0.01787310033310249</v>
       </c>
     </row>
     <row r="48">
@@ -2612,7 +2615,7 @@
         <v>46461</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>46386</v>
@@ -2623,7 +2626,7 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.0514516241719684</v>
+        <v>0.05076490983355867</v>
       </c>
     </row>
     <row r="49">
@@ -2658,7 +2661,7 @@
         <v>46488</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>46498</v>
@@ -2669,7 +2672,7 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02947325724122701</v>
+        <v>0.0291079196636194</v>
       </c>
     </row>
     <row r="50">
@@ -2704,7 +2707,7 @@
         <v>46492</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>46501</v>
@@ -2715,7 +2718,7 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.02022325581395349</v>
+        <v>0.02087073374830579</v>
       </c>
     </row>
     <row r="51">
@@ -2750,7 +2753,7 @@
         <v>46492</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>46376</v>
@@ -2761,7 +2764,7 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.05102481603972341</v>
+        <v>0.04866350385719938</v>
       </c>
     </row>
     <row r="52">
@@ -2796,7 +2799,7 @@
         <v>46493</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>46531</v>
@@ -2807,7 +2810,7 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02086008852056917</v>
+        <v>0.02073100078539538</v>
       </c>
     </row>
     <row r="53">
@@ -2842,7 +2845,7 @@
         <v>46499</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>46526</v>
@@ -2853,7 +2856,7 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02839337221937417</v>
+        <v>0.02606063813098966</v>
       </c>
     </row>
     <row r="54">
@@ -2888,7 +2891,7 @@
         <v>46504</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>46562</v>
@@ -2899,7 +2902,7 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04190114189992526</v>
+        <v>0.04122323003291564</v>
       </c>
     </row>
     <row r="55">
@@ -2934,7 +2937,7 @@
         <v>46508</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J55" s="10" t="n">
         <v>46518</v>
@@ -2945,7 +2948,7 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.04495018793044805</v>
+        <v>0.04346634925710766</v>
       </c>
     </row>
     <row r="56">
@@ -2980,7 +2983,7 @@
         <v>46515</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>46542</v>
@@ -2991,7 +2994,7 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.04171070461141636</v>
+        <v>0.04234620794541938</v>
       </c>
     </row>
     <row r="57">
@@ -3026,7 +3029,7 @@
         <v>46532</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="J57" s="10" t="n">
         <v>46563</v>
@@ -3037,7 +3040,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.03518201781732959</v>
+        <v>0.03406872745296734</v>
       </c>
     </row>
   </sheetData>
@@ -3072,44 +3075,44 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 07/06/2026</t>
+          <t>Expected Increase Announcements by Month - 07/13/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>January 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3140,39 +3143,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>July 2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3323,39 +3326,39 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3386,39 +3389,39 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>September 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F22" s="24" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3497,39 +3500,39 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F28" s="24" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3632,39 +3635,39 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>November 2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3815,39 +3818,39 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D44" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F44" s="24" t="inlineStr">
+      <c r="F44" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -3950,39 +3953,39 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>January 2027</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="inlineStr">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B51" s="24" t="inlineStr">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C51" s="24" t="inlineStr">
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D51" s="24" t="inlineStr">
+      <c r="D51" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F51" s="24" t="inlineStr">
+      <c r="F51" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4061,39 +4064,39 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B57" s="24" t="inlineStr">
+      <c r="B57" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C57" s="24" t="inlineStr">
+      <c r="C57" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D57" s="24" t="inlineStr">
+      <c r="D57" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F57" s="24" t="inlineStr">
+      <c r="F57" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4304,10 +4307,10 @@
         <v>46270</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4388,39 +4391,39 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="inlineStr">
+      <c r="A71" s="24" t="inlineStr">
         <is>
           <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B72" s="24" t="inlineStr">
+      <c r="B72" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="C72" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D72" s="24" t="inlineStr">
+      <c r="D72" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E72" s="24" t="inlineStr">
+      <c r="E72" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F72" s="24" t="inlineStr">
+      <c r="F72" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4499,39 +4502,39 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
+      <c r="A77" s="24" t="inlineStr">
         <is>
           <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24" t="inlineStr">
+      <c r="A78" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B78" s="24" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C78" s="24" t="inlineStr">
+      <c r="C78" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D78" s="24" t="inlineStr">
+      <c r="D78" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E78" s="24" t="inlineStr">
+      <c r="E78" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F78" s="24" t="inlineStr">
+      <c r="F78" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4682,39 +4685,39 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="23" t="inlineStr">
+      <c r="A86" s="24" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B87" s="24" t="inlineStr">
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C87" s="24" t="inlineStr">
+      <c r="C87" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D87" s="24" t="inlineStr">
+      <c r="D87" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E87" s="24" t="inlineStr">
+      <c r="E87" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F87" s="24" t="inlineStr">
+      <c r="F87" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -4831,7 +4834,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 07/06/2026</t>
+          <t>Complete Holdings Dividend Summary - 07/13/2026</t>
         </is>
       </c>
     </row>
@@ -4931,11 +4934,11 @@
       <c r="F5" s="7" t="n">
         <v>0.29</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.01012128081164349</v>
+        <v>0.009957936486157157</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4984,11 +4987,11 @@
       <c r="F6" s="7" t="n">
         <v>2.52</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02790465823278872</v>
+        <v>0.02787263837801698</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -5037,11 +5040,11 @@
       <c r="F7" s="7" t="n">
         <v>3.177</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.006916520750870562</v>
+        <v>0.007227558827049737</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -5090,11 +5093,11 @@
       <c r="F8" s="16" t="n">
         <v>0.504</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="27" t="n">
         <v>2.016</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.02398429590958984</v>
+        <v>0.02358722325034518</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>46160</v>
@@ -5143,11 +5146,11 @@
       <c r="F9" s="7" t="n">
         <v>0.703</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03827152172028183</v>
+        <v>0.03690046496205276</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46157</v>
@@ -5196,11 +5199,11 @@
       <c r="F10" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="26" t="n">
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02647389558232932</v>
+        <v>0.02615374869501659</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46171</v>
@@ -5249,11 +5252,11 @@
       <c r="F11" s="7" t="n">
         <v>1.24</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>4.96</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05178804407181118</v>
+        <v>0.05128205063482052</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46134</v>
@@ -5302,11 +5305,11 @@
       <c r="F12" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="26" t="n">
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.0222478932745187</v>
+        <v>0.02151071350144007</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46182</v>
@@ -5355,11 +5358,11 @@
       <c r="F13" s="7" t="n">
         <v>0.23</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <v>0.92</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02077922006309264</v>
+        <v>0.02089959087762214</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46163</v>
@@ -5408,11 +5411,11 @@
       <c r="F14" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="26" t="n">
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.008169517657604557</v>
+        <v>0.007805259164950651</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46157</v>
@@ -5461,14 +5464,14 @@
       <c r="F15" s="7" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01464499022474442</v>
+        <v>0.01424996859778785</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>46114</v>
+        <v>46209</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>0.02439024390243905</v>
@@ -5514,11 +5517,11 @@
       <c r="F16" s="7" t="n">
         <v>1.78</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="26" t="n">
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.04217010278625639</v>
+        <v>0.03954566954044979</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46161</v>
@@ -5567,14 +5570,14 @@
       <c r="F17" s="7" t="n">
         <v>0.86</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01611920688332178</v>
+        <v>0.01638173203491813</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>46118</v>
+        <v>46211</v>
       </c>
       <c r="J17" s="8" t="n">
         <v>0.07499999999999993</v>
@@ -5620,11 +5623,11 @@
       <c r="F18" s="7" t="n">
         <v>0.32</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.03159713781868049</v>
+        <v>0.02956461610196163</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46188</v>
@@ -5673,11 +5676,11 @@
       <c r="F19" s="7" t="n">
         <v>0.84</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.0491947269380616</v>
+        <v>0.04913358039101189</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46188</v>
@@ -5726,11 +5729,11 @@
       <c r="F20" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="26" t="n">
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.0223122847115672</v>
+        <v>0.02204615862425437</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46143</v>
@@ -5779,11 +5782,11 @@
       <c r="F21" s="7" t="n">
         <v>1.59</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01706993074294785</v>
+        <v>0.01690972219968362</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5832,11 +5835,11 @@
       <c r="F22" s="16" t="n">
         <v>0.295</v>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="27" t="n">
         <v>1.18</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>0.01574908177427583</v>
+        <v>0.01576907618770492</v>
       </c>
       <c r="I22" s="19" t="n">
         <v>46125</v>
@@ -5885,11 +5888,11 @@
       <c r="F23" s="7" t="n">
         <v>2.33</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.02669798647274613</v>
+        <v>0.02709302325581395</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46177</v>
@@ -5938,11 +5941,11 @@
       <c r="F24" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="26" t="n">
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.01891447392155589</v>
+        <v>0.01918932048156368</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46171</v>
@@ -5991,11 +5994,11 @@
       <c r="F25" s="7" t="n">
         <v>0.293</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.04816108666911</v>
+        <v>0.0475552841643708</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>46125</v>
@@ -6044,11 +6047,11 @@
       <c r="F26" s="7" t="n">
         <v>0.82</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="26" t="n">
         <v>3.28</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.03396144718830089</v>
+        <v>0.03269048716727996</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46204</v>
@@ -6097,14 +6100,14 @@
       <c r="F27" s="7" t="n">
         <v>0.61</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <v>2.44</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01677321770485241</v>
+        <v>0.01603364514018875</v>
       </c>
       <c r="I27" s="10" t="n">
-        <v>46086</v>
+        <v>46174</v>
       </c>
       <c r="J27" s="8" t="n">
         <v>0.05172413793103453</v>
@@ -6150,11 +6153,11 @@
       <c r="F28" s="7" t="n">
         <v>1.34</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="26" t="n">
         <v>5.36</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02086008852056917</v>
+        <v>0.02073100078539538</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46168</v>
@@ -6203,14 +6206,14 @@
       <c r="F29" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01781049606101486</v>
+        <v>0.01787310033310249</v>
       </c>
       <c r="I29" s="10" t="n">
-        <v>46118</v>
+        <v>46209</v>
       </c>
       <c r="J29" s="8" t="n">
         <v>0.07142857142857149</v>
@@ -6256,11 +6259,11 @@
       <c r="F30" s="7" t="n">
         <v>1.087</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="26" t="n">
         <v>2.174</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.02022325581395349</v>
+        <v>0.02087073374830579</v>
       </c>
       <c r="I30" s="10" t="n">
         <v>46132</v>
@@ -6309,11 +6312,11 @@
       <c r="F31" s="7" t="n">
         <v>0.79</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <v>3.16</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.01222579016936565</v>
+        <v>0.01243017852579043</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46203</v>
@@ -6362,11 +6365,11 @@
       <c r="F32" s="7" t="n">
         <v>0.72</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="26" t="n">
         <v>2.88</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.03518201781732959</v>
+        <v>0.03406872745296734</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46199</v>
@@ -6415,14 +6418,14 @@
       <c r="F33" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <v>1.92</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03727793340807439</v>
+        <v>0.03590798496665439</v>
       </c>
       <c r="I33" s="10" t="n">
-        <v>46132</v>
+        <v>46209</v>
       </c>
       <c r="J33" s="8" t="n">
         <v>0.0666666666666666</v>
@@ -6468,11 +6471,11 @@
       <c r="F34" s="7" t="n">
         <v>0.91</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="26" t="n">
         <v>3.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.009451599621287882</v>
+        <v>0.009398884557615285</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46163</v>
@@ -6521,14 +6524,14 @@
       <c r="F35" s="7" t="n">
         <v>0.87</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <v>3.48</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02871523995292049</v>
+        <v>0.02772466613344378</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>46120</v>
+        <v>46211</v>
       </c>
       <c r="J35" s="8" t="n">
         <v>0.0235294117647059</v>
@@ -6574,14 +6577,14 @@
       <c r="F36" s="7" t="n">
         <v>0.41</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="26" t="n">
         <v>1.64</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.03838502185069386</v>
+        <v>0.03671778722453514</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>46083</v>
+        <v>46174</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>0.02499999999999988</v>
@@ -6627,11 +6630,11 @@
       <c r="F37" s="7" t="n">
         <v>1.275</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="26" t="n">
         <v>2.55</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.05230232682053303</v>
+        <v>0.05161421036343746</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46111</v>
@@ -6680,11 +6683,11 @@
       <c r="F38" s="7" t="n">
         <v>0.271</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G38" s="26" t="n">
         <v>3.252</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.0514516241719684</v>
+        <v>0.05076490983355867</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46203</v>
@@ -6733,11 +6736,11 @@
       <c r="F39" s="7" t="n">
         <v>1.19</v>
       </c>
-      <c r="G39" s="25" t="n">
+      <c r="G39" s="26" t="n">
         <v>4.76</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.04495018793044805</v>
+        <v>0.04346634925710766</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46155</v>
@@ -6786,11 +6789,11 @@
       <c r="F40" s="7" t="n">
         <v>0.67</v>
       </c>
-      <c r="G40" s="25" t="n">
+      <c r="G40" s="26" t="n">
         <v>2.68</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.03305581376353177</v>
+        <v>0.0330425677095552</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46182</v>
@@ -6839,11 +6842,11 @@
       <c r="F41" s="7" t="n">
         <v>1.48</v>
       </c>
-      <c r="G41" s="25" t="n">
+      <c r="G41" s="26" t="n">
         <v>5.92</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.04171070461141636</v>
+        <v>0.04234620794541938</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46178</v>
@@ -6892,11 +6895,11 @@
       <c r="F42" s="7" t="n">
         <v>0.43</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G42" s="26" t="n">
         <v>1.72</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.07243629981928987</v>
+        <v>0.06981936204666597</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46150</v>
@@ -6943,19 +6946,19 @@
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G43" s="25" t="n">
-        <v>3.2</v>
+        <v>0.82</v>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>3.28</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.02865842642888866</v>
+        <v>0.0289241618683001</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="J43" s="8" t="n">
-        <v>0.01265822784810128</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="K43" s="10" t="n">
         <v>46433</v>
@@ -6998,11 +7001,11 @@
       <c r="F44" s="7" t="n">
         <v>1.089</v>
       </c>
-      <c r="G44" s="25" t="n">
+      <c r="G44" s="26" t="n">
         <v>4.356</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.02947325724122701</v>
+        <v>0.0291079196636194</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46136</v>
@@ -7051,11 +7054,11 @@
       <c r="F45" s="7" t="n">
         <v>0.551</v>
       </c>
-      <c r="G45" s="25" t="n">
+      <c r="G45" s="26" t="n">
         <v>2.204</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.04190114189992526</v>
+        <v>0.04122323003291564</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46198</v>
@@ -7104,11 +7107,11 @@
       <c r="F46" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="G46" s="25" t="n">
+      <c r="G46" s="26" t="n">
         <v>5.08</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02839337221937417</v>
+        <v>0.02606063813098966</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46160</v>
@@ -7157,11 +7160,11 @@
       <c r="F47" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="G47" s="25" t="n">
+      <c r="G47" s="26" t="n">
         <v>3.72</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.01674921160635266</v>
+        <v>0.01586015754252245</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46161</v>
@@ -7210,11 +7213,11 @@
       <c r="F48" s="7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G48" s="25" t="n">
+      <c r="G48" s="26" t="n">
         <v>9.76</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.02366835262725075</v>
+        <v>0.02413332593824269</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46162</v>
@@ -7263,11 +7266,11 @@
       <c r="F49" s="7" t="n">
         <v>0.83</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G49" s="26" t="n">
         <v>3.32</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.03601062976288923</v>
+        <v>0.03744008892858095</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46181</v>
@@ -7316,11 +7319,11 @@
       <c r="F50" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="G50" s="25" t="n">
+      <c r="G50" s="26" t="n">
         <v>5.2</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.04387260015233685</v>
+        <v>0.04476198744909742</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46188</v>
@@ -7369,11 +7372,11 @@
       <c r="F51" s="7" t="n">
         <v>0.974</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G51" s="26" t="n">
         <v>3.896</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.05102481603972341</v>
+        <v>0.04866350385719938</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46112</v>
@@ -7422,11 +7425,11 @@
       <c r="F52" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="G52" s="25" t="n">
+      <c r="G52" s="26" t="n">
         <v>5.68</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.01867254003883344</v>
+        <v>0.01881667089258208</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46147</v>
@@ -7475,11 +7478,11 @@
       <c r="F53" s="7" t="n">
         <v>0.545</v>
       </c>
-      <c r="G53" s="25" t="n">
+      <c r="G53" s="26" t="n">
         <v>2.18</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.03565587212565616</v>
+        <v>0.03523517112712499</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46157</v>
@@ -7528,11 +7531,11 @@
       <c r="F54" s="7" t="n">
         <v>1.38</v>
       </c>
-      <c r="G54" s="25" t="n">
+      <c r="G54" s="26" t="n">
         <v>5.52</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.01950736818810225</v>
+        <v>0.0191056338898471</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46171</v>
@@ -7581,14 +7584,14 @@
       <c r="F55" s="7" t="n">
         <v>0.708</v>
       </c>
-      <c r="G55" s="25" t="n">
+      <c r="G55" s="26" t="n">
         <v>2.832</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.06707721265084407</v>
+        <v>0.06631898910307311</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>46122</v>
+        <v>46213</v>
       </c>
       <c r="J55" s="8" t="n">
         <v>0.02608695652173916</v>
@@ -7634,11 +7637,11 @@
       <c r="F56" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="G56" s="25" t="n">
+      <c r="G56" s="26" t="n">
         <v>4.12</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.03013899116296197</v>
+        <v>0.02883740561914779</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -163,9 +163,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,6 +173,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/13/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/20/2026</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-168</v>
+        <v>-175</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06981936204666597</v>
+        <v>0.06888266108522105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -714,131 +714,131 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.93</v>
+        <v>1.38</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.89</v>
+        <v>1.34</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.02985074626865658</v>
       </c>
       <c r="G7" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>46220</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0.0183203071113388</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.08154506437768236</v>
+      </c>
+      <c r="G8" s="17" t="n">
         <v>0.06</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="10" t="n">
+      <c r="H8" s="18" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <v>46248</v>
       </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>0.01586015754252245</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I8" s="13" t="n">
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>0.02243365100899626</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J8" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="n">
-        <v>0.0191056338898471</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>0.08154506437768236</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>46248</v>
-      </c>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="n">
-        <v>0.02358722325034518</v>
+      <c r="J9" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0.03708668593049086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -848,29 +848,29 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46227</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>11</v>
+        <v>46232</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>9</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46267</v>
+        <v>46246</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.03744008892858095</v>
+        <v>0.05183946471759877</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +910,10 @@
         <v>0.06</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>16</v>
+        <v>46233</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>10</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>46264</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02615374869501659</v>
+        <v>0.02553692520871774</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1.22</v>
+        <v>0.8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46246</v>
+        <v>46297</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.05128205063482052</v>
+        <v>0.03226440961877044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -986,29 +986,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46263</v>
+        <v>46278</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46297</v>
+        <v>46344</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.03269048716727996</v>
+        <v>0.009322576222817316</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46344</v>
+        <v>46303</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.009398884557615285</v>
+        <v>0.06532118625075922</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1082,25 +1082,25 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.06631898910307311</v>
+        <v>0.01952225386386402</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1124,29 +1124,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46285</v>
+        <v>46305</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.01881667089258208</v>
+        <v>0.02769487910395309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1170,29 +1170,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.02772466613344378</v>
+        <v>0.01261955638028287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1216,29 +1216,29 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.01243017852579043</v>
+        <v>0.02040740951344267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1266,25 +1266,25 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.01918932048156368</v>
+        <v>0.0224207391238197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="I20" s="22" t="n">
         <v>106</v>
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.02204615862425437</v>
+        <v>0.007855716419377497</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1358,25 +1358,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1384,13 +1384,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.007805259164950651</v>
+        <v>0.0238887802484879</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1404,25 +1404,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.02413332593824269</v>
+        <v>0.0278425398213389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.02883740561914779</v>
+        <v>0.03724539337373385</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1496,25 +1496,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03590798496665439</v>
+        <v>0.03817504736848928</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1538,29 +1538,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.03671778722453514</v>
+        <v>0.04632411206887323</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1584,29 +1584,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.0475552841643708</v>
+        <v>0.04945904350849515</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.04913358039101189</v>
+        <v>0.02744051859446339</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2.38</v>
+        <v>0.22</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>46432</v>
+        <v>46344</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -1706,105 +1706,105 @@
         </is>
       </c>
       <c r="L28" s="9" t="n">
-        <v>0.02787263837801698</v>
+        <v>0.02117376257412431</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I29" s="22" t="n">
-        <v>155</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>0.02089959087762214</v>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I29" s="23" t="n">
+        <v>160</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>0.01603260902804103</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G30" s="18" t="n">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="G30" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H30" s="19" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I30" s="23" t="n">
-        <v>167</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K30" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L30" s="18" t="n">
-        <v>0.01576907618770492</v>
+      <c r="H30" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <v>179</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>0.01637549331204981</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1814,29 +1814,29 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.8</v>
+        <v>0.676</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46402</v>
+        <v>46411</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.01638173203491813</v>
+        <v>0.0373439559898445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0.676</v>
+        <v>1.71</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46411</v>
+        <v>46417</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1890,45 +1890,45 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03690046496205276</v>
+        <v>0.03774585069020881</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1.78</v>
+        <v>1.275</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46417</v>
+        <v>46422</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1936,18 +1936,18 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.03954566954044979</v>
+        <v>0.05120533388894676</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1956,25 +1956,25 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1.275</v>
+        <v>0.61</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>46422</v>
+        <v>46428</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46472</v>
+        <v>46452</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.05161421036343746</v>
+        <v>0.01638353669506887</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2002,13 +2002,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0.08</v>
@@ -2017,10 +2017,10 @@
         <v>46428</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.01603364514018875</v>
+        <v>0.04457779624500369</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2044,29 +2044,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.04476198744909742</v>
+        <v>0.01490550983627364</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2090,29 +2090,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.41</v>
+        <v>0.63</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.01424996859778785</v>
+        <v>0.03404904117866635</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.67</v>
+        <v>3.177</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0.63</v>
+        <v>1.883</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.0330425677095552</v>
+        <v>0.007234924474692065</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2182,29 +2182,29 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3.177</v>
+        <v>1.3</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H39" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.007227558827049737</v>
+        <v>0.0214716333192788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0.06</v>
@@ -2247,10 +2247,10 @@
         <v>46433</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46383</v>
+        <v>46368</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02151071350144007</v>
+        <v>0.02927052397436503</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2274,29 +2274,29 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46368</v>
+        <v>46270</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02956461610196163</v>
+        <v>0.02877445443871275</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2320,29 +2320,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.82</v>
+        <v>0.545</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.8</v>
+        <v>0.588964</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H42" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.0289241618683001</v>
+        <v>0.03509054325955735</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2366,29 +2366,29 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="I43" s="22" t="n">
         <v>217</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.03523517112712499</v>
+        <v>0.01028824833702882</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2416,25 +2416,25 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.009957936486157157</v>
+        <v>0.02785290639092999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2458,29 +2458,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46441</v>
+        <v>46452</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.02709302325581395</v>
+        <v>0.0170896535606438</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2504,29 +2504,29 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2534,45 +2534,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01690972219968362</v>
+        <v>0.01753668014004512</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H47" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46300</v>
+        <v>46386</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2580,45 +2580,45 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.01787310033310249</v>
+        <v>0.04935872952202137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.271</v>
+        <v>1.089</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0.27</v>
+        <v>1.057</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46461</v>
+        <v>46488</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46386</v>
+        <v>46498</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2626,18 +2626,18 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.05076490983355867</v>
+        <v>0.02920451902819247</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2646,25 +2646,25 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.089</v>
+        <v>1.125</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.057</v>
+        <v>1.087</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2672,33 +2672,33 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.0291079196636194</v>
+        <v>0.02164918688918688</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1.087</v>
+        <v>0.974</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.976</v>
+        <v>0.994</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0.06</v>
@@ -2707,10 +2707,10 @@
         <v>46492</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.02087073374830579</v>
+        <v>0.0482058898133045</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2734,29 +2734,29 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>0.994</v>
+        <v>1.3</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.04866350385719938</v>
+        <v>0.02120588746829965</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2784,25 +2784,25 @@
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2810,13 +2810,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02073100078539538</v>
+        <v>0.02428298314582114</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>1.2</v>
+        <v>0.525</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.02606063813098966</v>
+        <v>0.04171082501202561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2872,29 +2872,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.551</v>
+        <v>1.19</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0.525</v>
+        <v>1.08</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.04952380952380957</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46504</v>
+        <v>46508</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46562</v>
+        <v>46518</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04122323003291564</v>
+        <v>0.04221729490022173</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2918,29 +2918,29 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.08</v>
+        <v>1.423</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="I55" s="22" t="n">
         <v>292</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.04346634925710766</v>
+        <v>0.04330651157396478</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2968,25 +2968,25 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1.423</v>
+        <v>0.71</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46515</v>
+        <v>46532</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.04234620794541938</v>
+        <v>0.03458628697134464</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3010,29 +3010,29 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>46532</v>
+        <v>46583</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>46563</v>
+        <v>46248</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.03406872745296734</v>
+        <v>0.01529228021048674</v>
       </c>
     </row>
   </sheetData>
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3075,7 +3075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 07/13/2026</t>
+          <t>Expected Increase Announcements by Month - 07/20/2026</t>
         </is>
       </c>
     </row>
@@ -3184,92 +3184,92 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="C10" s="10" t="n">
+        <v>46629</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.02985074626865658</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>AWR</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C11" s="18" t="n">
         <v>46248</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.04494382022471914</v>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>46220</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.02985074626865658</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+      <c r="D11" s="15" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.08154506437768236</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>AWR</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SWK</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
         <v>46227</v>
       </c>
-      <c r="C12" s="19" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.08154506437768236</v>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>yfinance</t>
+      <c r="C12" s="10" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.01219512195121952</v>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46267</v>
+        <v>46246</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>46264</v>
@@ -3301,149 +3301,149 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>46232</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.01639344262295083</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>46297</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C22" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>46344</v>
+        <v>46303</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
@@ -3454,20 +3454,20 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
@@ -3475,86 +3475,86 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0235294117647059</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
@@ -3565,20 +3565,20 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
@@ -3589,20 +3589,20 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B31" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
@@ -3610,86 +3610,86 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C32" s="10" t="n">
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C35" s="10" t="n">
         <v>46338</v>
       </c>
-      <c r="D32" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F35" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="D35" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3700,20 +3700,20 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3724,20 +3724,20 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -3748,20 +3748,20 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -3772,20 +3772,20 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
@@ -3793,86 +3793,86 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>HRL</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>46400</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.01034482758620691</v>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
@@ -3883,20 +3883,20 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>46432</v>
+        <v>46344</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
@@ -3905,109 +3905,109 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n">
+      <c r="B47" s="18" t="n">
         <v>46383</v>
       </c>
-      <c r="C48" s="19" t="n">
+      <c r="C47" s="18" t="n">
         <v>46404</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D47" s="15" t="n">
         <v>0.295</v>
       </c>
-      <c r="E48" s="17" t="n">
+      <c r="E47" s="16" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="F48" s="21" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C51" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D51" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F51" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>46402</v>
+        <v>46411</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
@@ -4018,20 +4018,20 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>46411</v>
+        <v>46417</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
@@ -4039,86 +4039,86 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F56" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C57" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D57" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F57" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>46422</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>46472</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>1.183219178082192</v>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
-        <v>46422</v>
+        <v>46428</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46472</v>
+        <v>46452</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1.275</v>
+        <v>0.61</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4129,20 +4129,20 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
         <v>46428</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4153,20 +4153,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4177,20 +4177,20 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4201,20 +4201,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>0.67</v>
+        <v>3.177</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4225,20 +4225,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>3.177</v>
+        <v>1.3</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4249,20 +4249,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46383</v>
+        <v>46368</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4273,20 +4273,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46368</v>
+        <v>46270</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4297,20 +4297,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46270</v>
+        <v>46243</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.82</v>
+        <v>0.545</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4321,20 +4321,20 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
@@ -4345,20 +4345,20 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B68" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="C68" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F68" s="12" t="inlineStr">
         <is>
@@ -4366,86 +4366,86 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B72" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C72" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D72" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E72" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F72" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4456,20 +4456,20 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B74" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>46300</v>
+        <v>46386</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E74" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
@@ -4477,86 +4477,86 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D75" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F77" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B78" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C78" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D78" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E78" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F78" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.089</v>
+        <v>1.125</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4567,20 +4567,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>1.087</v>
+        <v>0.974</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4591,20 +4591,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4615,20 +4615,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4639,20 +4639,20 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B83" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="C83" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
@@ -4660,86 +4660,86 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D84" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F84" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>May 2027</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E86" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F86" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B87" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C87" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D87" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E87" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F87" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C87" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4750,20 +4750,20 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B89" s="10" t="n">
-        <v>46515</v>
+        <v>46532</v>
       </c>
       <c r="C89" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E89" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
@@ -4771,25 +4771,64 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C90" s="10" t="n">
-        <v>46563</v>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.01408450704225353</v>
-      </c>
-      <c r="F90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>July 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C92" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D92" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E92" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F92" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>46583</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.04494382022471914</v>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
         <is>
           <t>Notion + yfinance</t>
         </is>
@@ -4834,7 +4873,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Complete Holdings Dividend Summary - 07/13/2026</t>
+          <t>Complete Holdings Dividend Summary - 07/20/2026</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4977,7 @@
         <v>1.16</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.009957936486157157</v>
+        <v>0.01028824833702882</v>
       </c>
       <c r="I5" s="10" t="n">
         <v>46160</v>
@@ -4991,7 +5030,7 @@
         <v>10.08</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.02787263837801698</v>
+        <v>0.02744051859446339</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>46157</v>
@@ -5044,7 +5083,7 @@
         <v>12.708</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.007227558827049737</v>
+        <v>0.007234924474692065</v>
       </c>
       <c r="I7" s="10" t="n">
         <v>46139</v>
@@ -5065,53 +5104,53 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>AWR</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Feb/May/Aug/Nov</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="15" t="n">
         <v>0.504</v>
       </c>
       <c r="G8" s="27" t="n">
         <v>2.016</v>
       </c>
-      <c r="H8" s="18" t="n">
-        <v>0.02358722325034518</v>
-      </c>
-      <c r="I8" s="19" t="n">
+      <c r="H8" s="17" t="n">
+        <v>0.02243365100899626</v>
+      </c>
+      <c r="I8" s="18" t="n">
         <v>46160</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.08154506437768236</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="K8" s="18" t="n">
         <v>46227</v>
       </c>
-      <c r="L8" s="19" t="n">
+      <c r="L8" s="18" t="n">
         <v>46248</v>
       </c>
-      <c r="M8" s="21" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5150,7 +5189,7 @@
         <v>2.812</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03690046496205276</v>
+        <v>0.0373439559898445</v>
       </c>
       <c r="I9" s="10" t="n">
         <v>46157</v>
@@ -5203,7 +5242,7 @@
         <v>4.12</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.02615374869501659</v>
+        <v>0.02553692520871774</v>
       </c>
       <c r="I10" s="10" t="n">
         <v>46171</v>
@@ -5212,7 +5251,7 @@
         <v>0.03000000000000003</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="L10" s="10" t="n">
         <v>46264</v>
@@ -5256,7 +5295,7 @@
         <v>4.96</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.05128205063482052</v>
+        <v>0.05183946471759877</v>
       </c>
       <c r="I11" s="10" t="n">
         <v>46134</v>
@@ -5309,7 +5348,7 @@
         <v>5.2</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.02151071350144007</v>
+        <v>0.0214716333192788</v>
       </c>
       <c r="I12" s="10" t="n">
         <v>46182</v>
@@ -5362,7 +5401,7 @@
         <v>0.92</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.02089959087762214</v>
+        <v>0.02117376257412431</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>46163</v>
@@ -5415,7 +5454,7 @@
         <v>2.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.007805259164950651</v>
+        <v>0.007855716419377497</v>
       </c>
       <c r="I14" s="10" t="n">
         <v>46157</v>
@@ -5468,7 +5507,7 @@
         <v>1.68</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.01424996859778785</v>
+        <v>0.01490550983627364</v>
       </c>
       <c r="I15" s="10" t="n">
         <v>46209</v>
@@ -5521,7 +5560,7 @@
         <v>7.12</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.03954566954044979</v>
+        <v>0.03774585069020881</v>
       </c>
       <c r="I16" s="10" t="n">
         <v>46161</v>
@@ -5574,7 +5613,7 @@
         <v>3.44</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01638173203491813</v>
+        <v>0.01637549331204981</v>
       </c>
       <c r="I17" s="10" t="n">
         <v>46211</v>
@@ -5627,7 +5666,7 @@
         <v>1.28</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0.02956461610196163</v>
+        <v>0.02927052397436503</v>
       </c>
       <c r="I18" s="10" t="n">
         <v>46188</v>
@@ -5680,7 +5719,7 @@
         <v>3.36</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.04913358039101189</v>
+        <v>0.04945904350849515</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>46188</v>
@@ -5733,7 +5772,7 @@
         <v>2.56</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.02204615862425437</v>
+        <v>0.0224207391238197</v>
       </c>
       <c r="I20" s="10" t="n">
         <v>46143</v>
@@ -5786,7 +5825,7 @@
         <v>6.36</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.01690972219968362</v>
+        <v>0.0170896535606438</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>46205</v>
@@ -5807,53 +5846,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>SMID/DAC</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Jan/Apr/Jul/Oct</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="15" t="n">
         <v>0.295</v>
       </c>
       <c r="G22" s="27" t="n">
         <v>1.18</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <v>0.01576907618770492</v>
-      </c>
-      <c r="I22" s="19" t="n">
+      <c r="H22" s="17" t="n">
+        <v>0.01603260902804103</v>
+      </c>
+      <c r="I22" s="18" t="n">
         <v>46125</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="16" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="18" t="n">
         <v>46383</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="18" t="n">
         <v>46404</v>
       </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
@@ -5892,7 +5931,7 @@
         <v>9.32</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0.02709302325581395</v>
+        <v>0.02785290639092999</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>46177</v>
@@ -5945,7 +5984,7 @@
         <v>5.52</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0.01918932048156368</v>
+        <v>0.02040740951344267</v>
       </c>
       <c r="I24" s="10" t="n">
         <v>46171</v>
@@ -5998,10 +6037,10 @@
         <v>1.172</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0.0475552841643708</v>
+        <v>0.04632411206887323</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>46125</v>
+        <v>46216</v>
       </c>
       <c r="J25" s="8" t="n">
         <v>0.01034482758620691</v>
@@ -6051,7 +6090,7 @@
         <v>3.28</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.03269048716727996</v>
+        <v>0.03226440961877044</v>
       </c>
       <c r="I26" s="10" t="n">
         <v>46204</v>
@@ -6104,7 +6143,7 @@
         <v>2.44</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.01603364514018875</v>
+        <v>0.01638353669506887</v>
       </c>
       <c r="I27" s="10" t="n">
         <v>46174</v>
@@ -6157,7 +6196,7 @@
         <v>5.36</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.02073100078539538</v>
+        <v>0.02120588746829965</v>
       </c>
       <c r="I28" s="10" t="n">
         <v>46168</v>
@@ -6210,7 +6249,7 @@
         <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01787310033310249</v>
+        <v>0.01753668014004512</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>46209</v>
@@ -6257,19 +6296,19 @@
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.087</v>
+        <v>1.125</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>2.174</v>
+        <v>2.25</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.02087073374830579</v>
+        <v>0.02164918688918688</v>
       </c>
       <c r="I30" s="10" t="n">
-        <v>46132</v>
+        <v>46216</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>0.1137295081967213</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="K30" s="10" t="n">
         <v>46492</v>
@@ -6316,7 +6355,7 @@
         <v>3.16</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0.01243017852579043</v>
+        <v>0.01261955638028287</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>46203</v>
@@ -6369,7 +6408,7 @@
         <v>2.88</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.03406872745296734</v>
+        <v>0.03458628697134464</v>
       </c>
       <c r="I32" s="10" t="n">
         <v>46199</v>
@@ -6422,7 +6461,7 @@
         <v>1.92</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03590798496665439</v>
+        <v>0.03724539337373385</v>
       </c>
       <c r="I33" s="10" t="n">
         <v>46209</v>
@@ -6475,7 +6514,7 @@
         <v>3.64</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.009398884557615285</v>
+        <v>0.009322576222817316</v>
       </c>
       <c r="I34" s="10" t="n">
         <v>46163</v>
@@ -6528,7 +6567,7 @@
         <v>3.48</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.02772466613344378</v>
+        <v>0.02769487910395309</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>46211</v>
@@ -6581,7 +6620,7 @@
         <v>1.64</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.03671778722453514</v>
+        <v>0.03817504736848928</v>
       </c>
       <c r="I36" s="10" t="n">
         <v>46174</v>
@@ -6634,7 +6673,7 @@
         <v>2.55</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.05161421036343746</v>
+        <v>0.05120533388894676</v>
       </c>
       <c r="I37" s="10" t="n">
         <v>46111</v>
@@ -6687,7 +6726,7 @@
         <v>3.252</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.05076490983355867</v>
+        <v>0.04935872952202137</v>
       </c>
       <c r="I38" s="10" t="n">
         <v>46203</v>
@@ -6740,7 +6779,7 @@
         <v>4.76</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.04346634925710766</v>
+        <v>0.04221729490022173</v>
       </c>
       <c r="I39" s="10" t="n">
         <v>46155</v>
@@ -6793,7 +6832,7 @@
         <v>2.68</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.0330425677095552</v>
+        <v>0.03404904117866635</v>
       </c>
       <c r="I40" s="10" t="n">
         <v>46182</v>
@@ -6846,7 +6885,7 @@
         <v>5.92</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.04234620794541938</v>
+        <v>0.04330651157396478</v>
       </c>
       <c r="I41" s="10" t="n">
         <v>46178</v>
@@ -6899,7 +6938,7 @@
         <v>1.72</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0.06981936204666597</v>
+        <v>0.06888266108522105</v>
       </c>
       <c r="I42" s="10" t="n">
         <v>46150</v>
@@ -6952,7 +6991,7 @@
         <v>3.28</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0.0289241618683001</v>
+        <v>0.02877445443871275</v>
       </c>
       <c r="I43" s="10" t="n">
         <v>46174</v>
@@ -7005,7 +7044,7 @@
         <v>4.356</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0291079196636194</v>
+        <v>0.02920451902819247</v>
       </c>
       <c r="I44" s="10" t="n">
         <v>46136</v>
@@ -7058,7 +7097,7 @@
         <v>2.204</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0.04122323003291564</v>
+        <v>0.04171082501202561</v>
       </c>
       <c r="I45" s="10" t="n">
         <v>46198</v>
@@ -7111,7 +7150,7 @@
         <v>5.08</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>0.02606063813098966</v>
+        <v>0.02428298314582114</v>
       </c>
       <c r="I46" s="10" t="n">
         <v>46160</v>
@@ -7164,7 +7203,7 @@
         <v>3.72</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.01586015754252245</v>
+        <v>0.01529228021048674</v>
       </c>
       <c r="I47" s="10" t="n">
         <v>46161</v>
@@ -7173,7 +7212,7 @@
         <v>0.04494382022471914</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>46218</v>
+        <v>46583</v>
       </c>
       <c r="L47" s="10" t="n">
         <v>46248</v>
@@ -7217,7 +7256,7 @@
         <v>9.76</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.02413332593824269</v>
+        <v>0.0238887802484879</v>
       </c>
       <c r="I48" s="10" t="n">
         <v>46162</v>
@@ -7270,7 +7309,7 @@
         <v>3.32</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.03744008892858095</v>
+        <v>0.03708668593049086</v>
       </c>
       <c r="I49" s="10" t="n">
         <v>46181</v>
@@ -7323,7 +7362,7 @@
         <v>5.2</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.04476198744909742</v>
+        <v>0.04457779624500369</v>
       </c>
       <c r="I50" s="10" t="n">
         <v>46188</v>
@@ -7376,7 +7415,7 @@
         <v>3.896</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0.04866350385719938</v>
+        <v>0.0482058898133045</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>46112</v>
@@ -7429,7 +7468,7 @@
         <v>5.68</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.01881667089258208</v>
+        <v>0.01952225386386402</v>
       </c>
       <c r="I52" s="10" t="n">
         <v>46147</v>
@@ -7482,7 +7521,7 @@
         <v>2.18</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.03523517112712499</v>
+        <v>0.03509054325955735</v>
       </c>
       <c r="I53" s="10" t="n">
         <v>46157</v>
@@ -7535,7 +7574,7 @@
         <v>5.52</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.0191056338898471</v>
+        <v>0.0183203071113388</v>
       </c>
       <c r="I54" s="10" t="n">
         <v>46171</v>
@@ -7547,7 +7586,7 @@
         <v>46220</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>46264</v>
+        <v>46629</v>
       </c>
       <c r="M54" s="12" t="inlineStr">
         <is>
@@ -7588,7 +7627,7 @@
         <v>2.832</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.06631898910307311</v>
+        <v>0.06532118625075922</v>
       </c>
       <c r="I55" s="10" t="n">
         <v>46213</v>
@@ -7641,7 +7680,7 @@
         <v>4.12</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.02883740561914779</v>
+        <v>0.0278425398213389</v>
       </c>
       <c r="I56" s="10" t="n">
         <v>46157</v>

--- a/data/dividend_calendar.xlsx
+++ b/data/dividend_calendar.xlsx
@@ -169,7 +169,7 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/20/2026</t>
+          <t>Estimated Dividend Calendar: Anticipated Announcements - 07/27/2026</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         <v>46048</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>-175</v>
+        <v>-182</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>46413</v>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="L6" s="9" t="n">
-        <v>0.06888266108522105</v>
+        <v>0.06983353871728128</v>
       </c>
     </row>
     <row r="7">
@@ -729,7 +729,7 @@
         <v>46220</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>46629</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.0183203071113388</v>
+        <v>0.01816237631556698</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +775,10 @@
         <v>46227</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>46248</v>
+        <v>46613</v>
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="L8" s="17" t="n">
-        <v>0.02243365100899626</v>
+        <v>0.02343913440214634</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -802,29 +802,29 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="I9" s="21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>46267</v>
+        <v>46246</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="L9" s="9" t="n">
-        <v>0.03708668593049086</v>
+        <v>0.05152711292256609</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.05183946471759877</v>
+        <v>0.02503113684768318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -894,29 +894,29 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>46233</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>10</v>
+        <v>46263</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <v>33</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>46264</v>
+        <v>46297</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.02553692520871774</v>
+        <v>0.03241587269990922</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.09638554216867479</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>46263</v>
+        <v>46278</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>46297</v>
+        <v>46344</v>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="L12" s="9" t="n">
-        <v>0.03226440961877044</v>
+        <v>0.009300899775765661</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -986,29 +986,29 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>46344</v>
+        <v>46303</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0.009322576222817316</v>
+        <v>0.06014654465468421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1036,25 +1036,25 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="L14" s="9" t="n">
-        <v>0.06532118625075922</v>
+        <v>0.02014327178771334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1078,29 +1078,29 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.42</v>
+        <v>0.87</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.36</v>
+        <v>0.85</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.0441176470588234</v>
+        <v>0.0235294117647059</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>46285</v>
+        <v>46305</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="L15" s="9" t="n">
-        <v>0.01952225386386402</v>
+        <v>0.02761466507459607</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1124,29 +1124,29 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="L16" s="9" t="n">
-        <v>0.02769487910395309</v>
+        <v>0.01245590141220857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1170,29 +1170,29 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="L17" s="9" t="n">
-        <v>0.01261955638028287</v>
+        <v>0.01922407090059692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1220,25 +1220,25 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H18" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="L18" s="9" t="n">
-        <v>0.02040740951344267</v>
+        <v>0.02215107732767995</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.06666666666666674</v>
+        <v>0.09090909090909079</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="I19" s="22" t="n">
         <v>99</v>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="L19" s="9" t="n">
-        <v>0.0224207391238197</v>
+        <v>0.007755445182801244</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1312,25 +1312,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="L20" s="9" t="n">
-        <v>0.007855716419377497</v>
+        <v>0.02411782192508699</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1358,25 +1358,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>2.14</v>
+        <v>0.99</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
@@ -1384,13 +1384,13 @@
         </is>
       </c>
       <c r="L21" s="9" t="n">
-        <v>0.0238887802484879</v>
+        <v>0.02657978691149243</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1400,29 +1400,29 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.0278425398213389</v>
+        <v>0.037873557778047</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="L23" s="9" t="n">
-        <v>0.03724539337373385</v>
+        <v>0.03934740854107783</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1492,29 +1492,29 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.03817504736848928</v>
+        <v>0.04542635793246359</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1538,29 +1538,29 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.293</v>
+        <v>0.84</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.29</v>
+        <v>0.83</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.01034482758620691</v>
+        <v>0.01204819277108435</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>46352</v>
+        <v>46360</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>46400</v>
+        <v>46371</v>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.04632411206887323</v>
+        <v>0.04930423783974043</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1584,29 +1584,29 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0.83</v>
+        <v>2.38</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.04945904350849515</v>
+        <v>0.02653679041208973</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1630,29 +1630,29 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>2.38</v>
+        <v>0.22</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>46432</v>
+        <v>46344</v>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
@@ -1660,105 +1660,105 @@
         </is>
       </c>
       <c r="L27" s="9" t="n">
-        <v>0.02744051859446339</v>
+        <v>0.0207909604519774</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="I28" s="22" t="n">
-        <v>148</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="n">
-        <v>0.02117376257412431</v>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>GGG</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>0.07272727272727258</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <v>46383</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <v>153</v>
+      </c>
+      <c r="J28" s="18" t="n">
+        <v>46404</v>
+      </c>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>yfinance</t>
+        </is>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>0.01477585763813589</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>GGG</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>0.07272727272727258</v>
-      </c>
-      <c r="G29" s="17" t="n">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="G29" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="H29" s="18" t="n">
-        <v>46383</v>
-      </c>
-      <c r="I29" s="23" t="n">
-        <v>160</v>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>46404</v>
-      </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>yfinance</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>0.01603260902804103</v>
+      <c r="H29" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <v>172</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0.01508573441395958</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1768,29 +1768,29 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.8</v>
+        <v>0.676</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>46402</v>
+        <v>46411</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="L30" s="9" t="n">
-        <v>0.01637549331204981</v>
+        <v>0.03728206677128487</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1818,25 +1818,25 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0.676</v>
+        <v>1.71</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>46411</v>
+        <v>46417</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
@@ -1844,45 +1844,45 @@
         </is>
       </c>
       <c r="L31" s="9" t="n">
-        <v>0.0373439559898445</v>
+        <v>0.03716075038198736</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1.78</v>
+        <v>1.275</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1.71</v>
+        <v>0.584</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.04093567251461992</v>
+        <v>1.183219178082192</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>46417</v>
+        <v>46422</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>46433</v>
+        <v>46472</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
@@ -1890,18 +1890,18 @@
         </is>
       </c>
       <c r="L32" s="9" t="n">
-        <v>0.03774585069020881</v>
+        <v>0.051729386240376</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1910,25 +1910,25 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1.275</v>
+        <v>0.61</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>46422</v>
+        <v>46428</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>46472</v>
+        <v>46452</v>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="L33" s="9" t="n">
-        <v>0.05120533388894676</v>
+        <v>0.01600839804036381</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.58</v>
+        <v>1.27</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0.08</v>
@@ -1971,10 +1971,10 @@
         <v>46428</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="L34" s="9" t="n">
-        <v>0.01638353669506887</v>
+        <v>0.04366445679657416</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1998,29 +1998,29 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1.27</v>
+        <v>0.41</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.04457779624500369</v>
+        <v>0.01474460210639316</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2044,29 +2044,29 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0.41</v>
+        <v>0.63</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="L36" s="9" t="n">
-        <v>0.01490550983627364</v>
+        <v>0.03368738595587236</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2090,29 +2090,29 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.67</v>
+        <v>3.177</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>0.63</v>
+        <v>1.883</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="L37" s="9" t="n">
-        <v>0.03404904117866635</v>
+        <v>0.007553742081024425</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2136,29 +2136,29 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.177</v>
+        <v>1.3</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1.883</v>
+        <v>1.25</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="H38" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="L38" s="9" t="n">
-        <v>0.007234924474692065</v>
+        <v>0.02046639796303647</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0.06</v>
@@ -2201,10 +2201,10 @@
         <v>46433</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>46383</v>
+        <v>46368</v>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="L39" s="9" t="n">
-        <v>0.0214716333192788</v>
+        <v>0.02899864108970018</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2228,29 +2228,29 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0.24</v>
+        <v>0.8</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H40" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>46368</v>
+        <v>46270</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L40" s="9" t="n">
-        <v>0.02927052397436503</v>
+        <v>0.02959220595786624</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2274,29 +2274,29 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.82</v>
+        <v>0.545</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0.8</v>
+        <v>0.588964</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H41" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>46270</v>
+        <v>46608</v>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="L41" s="9" t="n">
-        <v>0.02877445443871275</v>
+        <v>0.03553961517080348</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2320,29 +2320,29 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0.588964</v>
+        <v>0.27</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="H42" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="I42" s="22" t="n">
         <v>210</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="L42" s="9" t="n">
-        <v>0.03509054325955735</v>
+        <v>0.009483709903498437</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2370,25 +2370,25 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0.27</v>
+        <v>2.3</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="L43" s="9" t="n">
-        <v>0.01028824833702882</v>
+        <v>0.02756703265616085</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2412,29 +2412,29 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2.33</v>
+        <v>1.59</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>0.01304347826086967</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.08</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>46441</v>
+        <v>46452</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="L44" s="9" t="n">
-        <v>0.02785290639092999</v>
+        <v>0.01626598465473146</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2458,29 +2458,29 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
@@ -2488,45 +2488,45 @@
         </is>
       </c>
       <c r="L45" s="9" t="n">
-        <v>0.0170896535606438</v>
+        <v>0.01677688099924021</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.4</v>
+        <v>0.27</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H46" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>46300</v>
+        <v>46386</v>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
@@ -2534,45 +2534,45 @@
         </is>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.01753668014004512</v>
+        <v>0.04950525010104389</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.271</v>
+        <v>1.089</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.27</v>
+        <v>1.057</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>0.003703703703703707</v>
+        <v>0.03027436140018924</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>46461</v>
+        <v>46488</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>46386</v>
+        <v>46498</v>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
@@ -2580,18 +2580,18 @@
         </is>
       </c>
       <c r="L47" s="9" t="n">
-        <v>0.04935872952202137</v>
+        <v>0.02936041874633219</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-Annual</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2600,25 +2600,25 @@
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1.089</v>
+        <v>1.125</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1.057</v>
+        <v>1.087</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H48" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
@@ -2626,33 +2626,33 @@
         </is>
       </c>
       <c r="L48" s="9" t="n">
-        <v>0.02920451902819247</v>
+        <v>0.02184147952561259</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Semi-Annual</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.125</v>
+        <v>0.974</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>1.087</v>
+        <v>0.994</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0.06</v>
@@ -2661,10 +2661,10 @@
         <v>46492</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         </is>
       </c>
       <c r="L49" s="9" t="n">
-        <v>0.02164918688918688</v>
+        <v>0.04591902815659731</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -2688,29 +2688,29 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0.994</v>
+        <v>1.3</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="L50" s="9" t="n">
-        <v>0.0482058898133045</v>
+        <v>0.0202298513771813</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2738,25 +2738,25 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
@@ -2764,13 +2764,13 @@
         </is>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.02120588746829965</v>
+        <v>0.02461478767230646</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2780,29 +2780,29 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.2</v>
+        <v>0.525</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0.04</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
@@ -2810,13 +2810,13 @@
         </is>
       </c>
       <c r="L52" s="9" t="n">
-        <v>0.02428298314582114</v>
+        <v>0.04246628006168784</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2826,29 +2826,29 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.551</v>
+        <v>1.19</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0.525</v>
+        <v>1.08</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>0.04952380952380957</v>
+        <v>0.1018518518518517</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>46504</v>
+        <v>46508</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>46562</v>
+        <v>46518</v>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="L53" s="9" t="n">
-        <v>0.04171082501202561</v>
+        <v>0.04121569043247219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -2872,29 +2872,29 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1.08</v>
+        <v>1.423</v>
       </c>
       <c r="F54" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="I54" s="22" t="n">
         <v>285</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.04221729490022173</v>
+        <v>0.04283182112545537</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -2922,25 +2922,25 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>1.423</v>
+        <v>0.71</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>46515</v>
+        <v>46532</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="L55" s="9" t="n">
-        <v>0.04330651157396478</v>
+        <v>0.0342042767741469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -2964,29 +2964,29 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Aug</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.01408450704225353</v>
+        <v>0.04494382022471914</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>46532</v>
+        <v>46583</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>46563</v>
+        <v>46248</v>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
@@ -2994,13 +2994,13 @@
         </is>
       </c>
       <c r="L56" s="9" t="n">
-        <v>0.03458628697134464</v>
+        <v>0.015482581819833</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3010,29 +3010,29 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.04494382022471914</v>
+        <v>0.01219512195121952</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0.06</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>46583</v>
+        <v>46592</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>46248</v>
+        <v>46632</v>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="L57" s="9" t="n">
-        <v>0.01529228021048674</v>
+        <v>0.03567207489939028</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Expected Increase Announcements by Month - 07/20/2026</t>
+          <t>Expected Increase Announcements by Month - 07/27/2026</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
         <v>46227</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>46248</v>
+        <v>46613</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>0.504</v>
@@ -3232,20 +3232,20 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>46267</v>
+        <v>46246</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.83</v>
+        <v>1.24</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.01639344262295083</v>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
@@ -3256,20 +3256,20 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46246</v>
+        <v>46264</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.01639344262295083</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
@@ -3277,149 +3277,149 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>CFR</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>46233</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>46264</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.03000000000000003</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>August 2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>August 2026</t>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>46263</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.02499999999999988</v>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Est. Announce</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Est. Ex-Date</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Last Amount</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Last Change</t>
         </is>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>46263</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>46297</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.02499999999999988</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>September 2026</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.09638554216867479</v>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>46344</v>
+        <v>46303</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.91</v>
+        <v>0.708</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.09638554216867479</v>
+        <v>0.02608695652173916</v>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
@@ -3430,20 +3430,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>46303</v>
+        <v>46325</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.708</v>
+        <v>1.42</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.02608695652173916</v>
+        <v>0.0441176470588234</v>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
@@ -3451,86 +3451,86 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>TXN</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>46285</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.0441176470588234</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>October 2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>October 2026</t>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>MSM</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>46339</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.0235294117647059</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>46339</v>
+        <v>46386</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0235294117647059</v>
+        <v>0.05333333333333338</v>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
@@ -3541,20 +3541,20 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>46311</v>
+        <v>46317</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>46386</v>
+        <v>46351</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0.05333333333333338</v>
+        <v>0.02222222222222208</v>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
@@ -3565,20 +3565,20 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>46317</v>
+        <v>46322</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>46351</v>
+        <v>46338</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.38</v>
+        <v>0.64</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>0.02222222222222208</v>
+        <v>0.06666666666666674</v>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
@@ -3586,86 +3586,86 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C31" s="10" t="n">
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>November 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>46329</v>
+      </c>
+      <c r="C34" s="10" t="n">
         <v>46338</v>
       </c>
-      <c r="D31" s="7" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.06666666666666674</v>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>November 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="D34" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.09090909090909079</v>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>46338</v>
+        <v>46346</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.6</v>
+        <v>2.44</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.09090909090909079</v>
+        <v>0.1401869158878504</v>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
@@ -3676,20 +3676,20 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>46332</v>
+        <v>46341</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>46346</v>
+        <v>46339</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.1401869158878504</v>
+        <v>0.04040404040404044</v>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
@@ -3700,20 +3700,20 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>46339</v>
+        <v>46385</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>0.04040404040404044</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
@@ -3724,20 +3724,20 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>46344</v>
+        <v>46347</v>
       </c>
       <c r="C38" s="10" t="n">
-        <v>46385</v>
+        <v>46358</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
@@ -3748,20 +3748,20 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>46358</v>
+        <v>46400</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.41</v>
+        <v>0.293</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.01034482758620691</v>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
@@ -3769,86 +3769,86 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>HRL</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="n">
-        <v>46352</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>46400</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.01034482758620691</v>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>December 2026</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>December 2026</t>
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F43" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>EMN</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>46360</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>46371</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.01204819277108435</v>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>46360</v>
+        <v>46366</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>46371</v>
+        <v>46432</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.84</v>
+        <v>2.52</v>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0.01204819277108435</v>
+        <v>0.05882352941176476</v>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
@@ -3859,20 +3859,20 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46432</v>
+        <v>46344</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2.52</v>
+        <v>0.23</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0.05882352941176476</v>
+        <v>0.0454545454545455</v>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
@@ -3881,109 +3881,109 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>CNP</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>46371</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0454545454545455</v>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>GGG</t>
         </is>
       </c>
-      <c r="B47" s="18" t="n">
+      <c r="B46" s="18" t="n">
         <v>46383</v>
       </c>
-      <c r="C47" s="18" t="n">
+      <c r="C46" s="18" t="n">
         <v>46404</v>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D46" s="15" t="n">
         <v>0.295</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E46" s="16" t="n">
         <v>0.07272727272727258</v>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>yfinance</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>January 2027</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>January 2027</t>
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F49" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C50" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>DGX</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>46402</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>46483</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.07499999999999993</v>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>46402</v>
+        <v>46411</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46483</v>
+        <v>46435</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.86</v>
+        <v>0.703</v>
       </c>
       <c r="E51" s="8" t="n">
-        <v>0.07499999999999993</v>
+        <v>0.03994082840236673</v>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
@@ -3994,20 +3994,20 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>46411</v>
+        <v>46417</v>
       </c>
       <c r="C52" s="10" t="n">
-        <v>46435</v>
+        <v>46433</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.703</v>
+        <v>1.78</v>
       </c>
       <c r="E52" s="8" t="n">
-        <v>0.03994082840236673</v>
+        <v>0.04093567251461992</v>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
@@ -4015,86 +4015,86 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
-        <v>46417</v>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>46433</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.04093567251461992</v>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>February 2027</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>February 2027</t>
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F55" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B56" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C56" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E56" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F56" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>46422</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>46472</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>1.183219178082192</v>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>46422</v>
+        <v>46428</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46472</v>
+        <v>46452</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1.275</v>
+        <v>0.61</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>1.183219178082192</v>
+        <v>0.05172413793103453</v>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
@@ -4105,20 +4105,20 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B58" s="10" t="n">
         <v>46428</v>
       </c>
       <c r="C58" s="10" t="n">
-        <v>46452</v>
+        <v>46460</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E58" s="8" t="n">
-        <v>0.05172413793103453</v>
+        <v>0.02362204724409451</v>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
@@ -4129,20 +4129,20 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B59" s="10" t="n">
-        <v>46428</v>
+        <v>46431</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46460</v>
+        <v>46480</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E59" s="8" t="n">
-        <v>0.02362204724409451</v>
+        <v>0.02439024390243905</v>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
@@ -4153,20 +4153,20 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B60" s="10" t="n">
-        <v>46431</v>
+        <v>46432</v>
       </c>
       <c r="C60" s="10" t="n">
-        <v>46480</v>
+        <v>46455</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.06349206349206354</v>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
@@ -4177,20 +4177,20 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B61" s="10" t="n">
-        <v>46432</v>
+        <v>46433</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46455</v>
+        <v>46425</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.67</v>
+        <v>3.177</v>
       </c>
       <c r="E61" s="8" t="n">
-        <v>0.06349206349206354</v>
+        <v>0.6872012745618694</v>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
@@ -4201,20 +4201,20 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B62" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C62" s="10" t="n">
-        <v>46425</v>
+        <v>46383</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>3.177</v>
+        <v>1.3</v>
       </c>
       <c r="E62" s="8" t="n">
-        <v>0.6872012745618694</v>
+        <v>4.96</v>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
@@ -4225,20 +4225,20 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B63" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46383</v>
+        <v>46368</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1.3</v>
+        <v>0.32</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>4.96</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
@@ -4249,20 +4249,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B64" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>46368</v>
+        <v>46270</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="E64" s="8" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.02499999999999988</v>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
@@ -4273,20 +4273,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="B65" s="10" t="n">
         <v>46433</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46270</v>
+        <v>46608</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.82</v>
+        <v>0.545</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>0.02499999999999988</v>
+        <v>0.005735494868956323</v>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
@@ -4297,20 +4297,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="B66" s="10" t="n">
-        <v>46433</v>
+        <v>46440</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>46243</v>
+        <v>46450</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.005735494868956323</v>
+        <v>0.07407407407407393</v>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
@@ -4321,20 +4321,20 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B67" s="10" t="n">
-        <v>46440</v>
+        <v>46441</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46450</v>
+        <v>46456</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.29</v>
+        <v>2.33</v>
       </c>
       <c r="E67" s="8" t="n">
-        <v>0.07407407407407393</v>
+        <v>0.01304347826086967</v>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
@@ -4342,86 +4342,86 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="n">
-        <v>46441</v>
-      </c>
-      <c r="C68" s="10" t="n">
-        <v>46456</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0.01304347826086967</v>
-      </c>
-      <c r="F68" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>March 2027</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="inlineStr">
-        <is>
-          <t>March 2027</t>
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C70" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D70" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E70" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F70" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B71" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C71" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D71" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F71" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>GD</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>46452</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>46487</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.06000000000000005</v>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B72" s="10" t="n">
-        <v>46452</v>
+        <v>46461</v>
       </c>
       <c r="C72" s="10" t="n">
-        <v>46487</v>
+        <v>46300</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07142857142857149</v>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
@@ -4432,20 +4432,20 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B73" s="10" t="n">
         <v>46461</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46300</v>
+        <v>46386</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>1.5</v>
+        <v>0.271</v>
       </c>
       <c r="E73" s="8" t="n">
-        <v>0.07142857142857149</v>
+        <v>0.003703703703703707</v>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
@@ -4453,86 +4453,86 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="n">
-        <v>46461</v>
-      </c>
-      <c r="C74" s="10" t="n">
-        <v>46386</v>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.003703703703703707</v>
-      </c>
-      <c r="F74" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>April 2027</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="inlineStr">
-        <is>
-          <t>April 2027</t>
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C76" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D76" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F76" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B77" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C77" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D77" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E77" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F77" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
+        <v>46488</v>
+      </c>
+      <c r="C77" s="10" t="n">
+        <v>46498</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.03027436140018924</v>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="B78" s="10" t="n">
-        <v>46488</v>
+        <v>46492</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>46498</v>
+        <v>46501</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>1.089</v>
+        <v>1.125</v>
       </c>
       <c r="E78" s="8" t="n">
-        <v>0.03027436140018924</v>
+        <v>0.03495860165593379</v>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
@@ -4543,20 +4543,20 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B79" s="10" t="n">
         <v>46492</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46501</v>
+        <v>46376</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>1.125</v>
+        <v>0.974</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.03495860165593379</v>
+        <v>0.001006036217303824</v>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
@@ -4567,20 +4567,20 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B80" s="10" t="n">
-        <v>46492</v>
+        <v>46493</v>
       </c>
       <c r="C80" s="10" t="n">
-        <v>46376</v>
+        <v>46531</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0.974</v>
+        <v>1.34</v>
       </c>
       <c r="E80" s="8" t="n">
-        <v>0.001006036217303824</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
@@ -4591,20 +4591,20 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B81" s="10" t="n">
-        <v>46493</v>
+        <v>46499</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46531</v>
+        <v>46526</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.05833333333333339</v>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
@@ -4615,20 +4615,20 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="B82" s="10" t="n">
-        <v>46499</v>
+        <v>46504</v>
       </c>
       <c r="C82" s="10" t="n">
-        <v>46526</v>
+        <v>46562</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1.27</v>
+        <v>0.551</v>
       </c>
       <c r="E82" s="8" t="n">
-        <v>0.05833333333333339</v>
+        <v>0.04952380952380957</v>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
@@ -4636,86 +4636,86 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>POR</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>46504</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>46562</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.04952380952380957</v>
-      </c>
-      <c r="F83" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="84">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>May 2027</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="inlineStr">
-        <is>
-          <t>May 2027</t>
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E85" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B86" s="25" t="inlineStr">
-        <is>
-          <t>Est. Announce</t>
-        </is>
-      </c>
-      <c r="C86" s="25" t="inlineStr">
-        <is>
-          <t>Est. Ex-Date</t>
-        </is>
-      </c>
-      <c r="D86" s="25" t="inlineStr">
-        <is>
-          <t>Last Amount</t>
-        </is>
-      </c>
-      <c r="E86" s="25" t="inlineStr">
-        <is>
-          <t>Last Change</t>
-        </is>
-      </c>
-      <c r="F86" s="25" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="n">
+        <v>46508</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>46518</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.1018518518518517</v>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Notion + yfinance</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B87" s="10" t="n">
-        <v>46508</v>
+        <v>46515</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46518</v>
+        <v>46542</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.1018518518518517</v>
+        <v>0.04005621925509482</v>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -4726,20 +4726,20 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B88" s="10" t="n">
-        <v>46515</v>
+        <v>46532</v>
       </c>
       <c r="C88" s="10" t="n">
-        <v>46542</v>
+        <v>46563</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1.48</v>
+        <v>0.72</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.04005621925509482</v>
+        <v>0.01408450704225353</v>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
@@ -4747,86 +4747,86 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>46532</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>46563</v>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0.01408450704225353</v>
-      </c>
-      <c r="F89" s="12" t="inlineStr">
-        <is>
-          <t>Notion + yfinance</t>
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>July 2027</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="inlineStr">
-        <is>
-          <t>July 2027</t>
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Est. Announce</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Est. Ex-Date</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>Last Amount</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="inlineStr">
+        <is>
+          <t>Last Change</t>
+        </is>
+      </c>
+      <c r="F91" s="25" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="9